--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -2304,13 +2304,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46168.51630959491</v>
+        <v>46168.682976261574</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.704996643515</v>
+        <v>46175.87166331019</v>
       </c>
       <c r="D4" s="5">
-        <v>46182.64303600695</v>
+        <v>46182.80970267361</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2353,13 +2353,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46168.51645768518</v>
+        <v>46168.68312435185</v>
       </c>
       <c r="C5" s="8">
-        <v>46175.70497127315</v>
+        <v>46175.87163793981</v>
       </c>
       <c r="D5" s="8">
-        <v>46175.70499721065</v>
+        <v>46175.87166387732</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2416,13 +2416,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46168.51646107639</v>
+        <v>46168.683127743054</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70497195602</v>
+        <v>46175.87163862269</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.704996932865</v>
+        <v>46175.87166359954</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2479,13 +2479,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46168.51646608797</v>
+        <v>46168.683132754624</v>
       </c>
       <c r="C7" s="8">
-        <v>46175.70497236111</v>
+        <v>46175.87163902778</v>
       </c>
       <c r="D7" s="8">
-        <v>46175.70499733796</v>
+        <v>46175.87166400463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2542,13 +2542,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46168.51646875</v>
+        <v>46168.683135416664</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.7049728125</v>
+        <v>46175.87163947917</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.704998229165</v>
+        <v>46175.871664895836</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2605,13 +2605,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46168.51647253473</v>
+        <v>46168.683139201385</v>
       </c>
       <c r="C9" s="8">
-        <v>46175.7049734375</v>
+        <v>46175.87164010417</v>
       </c>
       <c r="D9" s="8">
-        <v>46175.7049974074</v>
+        <v>46175.871664074075</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -2668,11 +2668,11 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46168.51631346065</v>
+        <v>46168.68298012731</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46168.69363231481</v>
+        <v>46168.86029898148</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2715,11 +2715,11 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46168.51647598379</v>
+        <v>46168.683142650465</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="8">
-        <v>46175.70499815972</v>
+        <v>46175.87166482639</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2778,11 +2778,11 @@
         <v>55</v>
       </c>
       <c r="B12" s="5">
-        <v>46168.51648164351</v>
+        <v>46168.683148310185</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46168.69621689815</v>
+        <v>46168.86288356481</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2841,11 +2841,11 @@
         <v>62</v>
       </c>
       <c r="B13" s="8">
-        <v>46168.51648685185</v>
+        <v>46168.68315351852</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46168.6961905787</v>
+        <v>46168.862857245374</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>63</v>
@@ -2894,11 +2894,11 @@
         <v>64</v>
       </c>
       <c r="B14" s="5">
-        <v>46168.51648958333</v>
+        <v>46168.68315625</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46168.6961875</v>
+        <v>46168.86285416667</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2947,11 +2947,11 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46168.51649224537</v>
+        <v>46168.68315891204</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46168.69618452546</v>
+        <v>46168.86285119213</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>63</v>
@@ -3000,11 +3000,11 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46168.516494826385</v>
+        <v>46168.683161493056</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46168.696181736115</v>
+        <v>46168.86284840278</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -3053,11 +3053,11 @@
         <v>68</v>
       </c>
       <c r="B17" s="8">
-        <v>46168.51649733796</v>
+        <v>46168.68316400463</v>
       </c>
       <c r="C17" s="9"/>
       <c r="D17" s="8">
-        <v>46168.69617850694</v>
+        <v>46168.862845173615</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>67</v>
@@ -3106,11 +3106,11 @@
         <v>69</v>
       </c>
       <c r="B18" s="5">
-        <v>46168.516500474536</v>
+        <v>46168.68316714121</v>
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="5">
-        <v>46168.696174236116</v>
+        <v>46168.86284090277</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>70</v>
@@ -3159,11 +3159,11 @@
         <v>71</v>
       </c>
       <c r="B19" s="8">
-        <v>46168.51631752314</v>
+        <v>46168.682984189814</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46183.70474760416</v>
+        <v>46183.871414270834</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>72</v>
@@ -3206,13 +3206,13 @@
         <v>74</v>
       </c>
       <c r="B20" s="5">
-        <v>46168.51650914352</v>
+        <v>46168.68317581018</v>
       </c>
       <c r="C20" s="5">
-        <v>46183.70471096065</v>
+        <v>46183.871377627314</v>
       </c>
       <c r="D20" s="5">
-        <v>46183.704728564815</v>
+        <v>46183.87139523149</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>75</v>
@@ -3271,13 +3271,13 @@
         <v>80</v>
       </c>
       <c r="B21" s="8">
-        <v>46168.51651422454</v>
+        <v>46168.6831808912</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.70471878472</v>
+        <v>46183.87138545139</v>
       </c>
       <c r="D21" s="8">
-        <v>46183.70473398148</v>
+        <v>46183.871400648146</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>81</v>
@@ -3336,13 +3336,13 @@
         <v>84</v>
       </c>
       <c r="B22" s="5">
-        <v>46168.516519247685</v>
+        <v>46168.68318591436</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.70472876157</v>
+        <v>46183.87139542824</v>
       </c>
       <c r="D22" s="5">
-        <v>46183.70474410879</v>
+        <v>46183.871410775464</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>85</v>
@@ -3401,11 +3401,11 @@
         <v>87</v>
       </c>
       <c r="B23" s="8">
-        <v>46168.516524502316</v>
+        <v>46168.68319116898</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="8">
-        <v>46183.704754375</v>
+        <v>46183.871421041666</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>88</v>
@@ -3464,11 +3464,11 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46168.5163216088</v>
+        <v>46168.68298827547</v>
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46183.73774506945</v>
+        <v>46183.90441173611</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3511,11 +3511,11 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46168.516532222224</v>
+        <v>46168.68319888889</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="8">
-        <v>46185.551156875</v>
+        <v>46185.717823541665</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3574,11 +3574,11 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46168.516537731484</v>
+        <v>46168.68320439815</v>
       </c>
       <c r="C26" s="6"/>
       <c r="D26" s="5">
-        <v>46183.7047431713</v>
+        <v>46183.871409837964</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3637,13 +3637,13 @@
         <v>100</v>
       </c>
       <c r="B27" s="8">
-        <v>46168.51654296296</v>
+        <v>46168.68320962963</v>
       </c>
       <c r="C27" s="8">
-        <v>46183.737739108794</v>
+        <v>46183.904405775465</v>
       </c>
       <c r="D27" s="8">
-        <v>46183.73775480324</v>
+        <v>46183.90442146991</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -3702,11 +3702,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46168.51654810185</v>
+        <v>46168.68321476852</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46184.74535251157</v>
+        <v>46184.91201917824</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3765,11 +3765,11 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46168.51655292824</v>
+        <v>46168.68321959491</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46184.740727662036</v>
+        <v>46184.90739432871</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3828,11 +3828,11 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46168.51655674769</v>
+        <v>46168.68322341435</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46183.00171152777</v>
+        <v>46183.168378194445</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3891,11 +3891,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46168.516560578704</v>
+        <v>46168.683227245376</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46183.001711261575</v>
+        <v>46183.16837792824</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3954,11 +3954,11 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46168.51656469908</v>
+        <v>46168.683231365736</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46169.71480667824</v>
+        <v>46169.88147334491</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -4017,11 +4017,11 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46168.5163258449</v>
+        <v>46168.682992511574</v>
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46184.536965625</v>
+        <v>46184.70363229167</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -4064,11 +4064,11 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46168.51660986111</v>
+        <v>46168.68327652778</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="5">
-        <v>46169.71389954861</v>
+        <v>46169.88056621527</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -4127,11 +4127,11 @@
         <v>131</v>
       </c>
       <c r="B35" s="8">
-        <v>46168.51661482639</v>
+        <v>46168.68328149305</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46169.71442496528</v>
+        <v>46169.88109163195</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -4186,11 +4186,11 @@
         <v>134</v>
       </c>
       <c r="B36" s="5">
-        <v>46168.51661987268</v>
+        <v>46168.68328653935</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="5">
-        <v>46169.71446459491</v>
+        <v>46169.88113126157</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -4245,13 +4245,13 @@
         <v>137</v>
       </c>
       <c r="B37" s="8">
-        <v>46168.51662473379</v>
+        <v>46168.68329140046</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.536961226855</v>
+        <v>46184.70362789352</v>
       </c>
       <c r="D37" s="8">
-        <v>46185.01610857639</v>
+        <v>46185.182775243054</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>138</v>
@@ -4310,13 +4310,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46168.51662917824</v>
+        <v>46168.68329584491</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.53683564815</v>
+        <v>46184.70350231482</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.53683701389</v>
+        <v>46184.70350368056</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -4371,13 +4371,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46168.51663403935</v>
+        <v>46168.68330070602</v>
       </c>
       <c r="C39" s="8">
-        <v>46184.53688990741</v>
+        <v>46184.70355657407</v>
       </c>
       <c r="D39" s="8">
-        <v>46184.53689112268</v>
+        <v>46184.703557789355</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -4432,11 +4432,11 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46168.516638761575</v>
+        <v>46168.68330542824</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.358137766205</v>
+        <v>46185.52480443287</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -4495,11 +4495,11 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46168.51664342593</v>
+        <v>46168.683310092594</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46169.714311435186</v>
+        <v>46169.88097810185</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4554,11 +4554,11 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46168.516648530094</v>
+        <v>46168.68331519676</v>
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.7143277662</v>
+        <v>46169.88099443287</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4613,13 +4613,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46168.51665361111</v>
+        <v>46168.68332027778</v>
       </c>
       <c r="C43" s="8">
-        <v>46184.53618304398</v>
+        <v>46184.70284971065</v>
       </c>
       <c r="D43" s="8">
-        <v>46184.536185069446</v>
+        <v>46184.70285173611</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4674,11 +4674,11 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46168.51665854167</v>
+        <v>46168.68332520833</v>
       </c>
       <c r="C44" s="6"/>
       <c r="D44" s="5">
-        <v>46169.71484755787</v>
+        <v>46169.88151422454</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4737,11 +4737,11 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46168.516662141206</v>
+        <v>46168.68332880787</v>
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46170.005846319444</v>
+        <v>46170.172512986115</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>122</v>
@@ -4790,11 +4790,11 @@
         <v>164</v>
       </c>
       <c r="B46" s="5">
-        <v>46168.516666446754</v>
+        <v>46168.683333113426</v>
       </c>
       <c r="C46" s="6"/>
       <c r="D46" s="5">
-        <v>46169.714902962965</v>
+        <v>46169.88156962963</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4843,11 +4843,11 @@
         <v>167</v>
       </c>
       <c r="B47" s="8">
-        <v>46168.516670625</v>
+        <v>46168.683337291666</v>
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.71402443287</v>
+        <v>46169.88069109953</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>168</v>
@@ -4906,11 +4906,11 @@
         <v>172</v>
       </c>
       <c r="B48" s="5">
-        <v>46168.516675127314</v>
+        <v>46168.68334179398</v>
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.71426368055</v>
+        <v>46169.88093034722</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>173</v>
@@ -4965,11 +4965,11 @@
         <v>175</v>
       </c>
       <c r="B49" s="8">
-        <v>46168.51668017361</v>
+        <v>46168.68334684028</v>
       </c>
       <c r="C49" s="9"/>
       <c r="D49" s="8">
-        <v>46169.714277997686</v>
+        <v>46169.88094466436</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>176</v>
@@ -5024,11 +5024,11 @@
         <v>178</v>
       </c>
       <c r="B50" s="5">
-        <v>46168.51668528935</v>
+        <v>46168.68335195602</v>
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46169.71403746528</v>
+        <v>46169.880704131945</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>179</v>
@@ -5087,11 +5087,11 @@
         <v>181</v>
       </c>
       <c r="B51" s="8">
-        <v>46168.51668915509</v>
+        <v>46168.68335582176</v>
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46169.71421828704</v>
+        <v>46169.8808849537</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>113</v>
@@ -5140,11 +5140,11 @@
         <v>183</v>
       </c>
       <c r="B52" s="5">
-        <v>46168.51669376157</v>
+        <v>46168.683360428244</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.71422820602</v>
+        <v>46169.88089487268</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>184</v>
@@ -5193,11 +5193,11 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46168.51669804398</v>
+        <v>46168.68336471065</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.71405113426</v>
+        <v>46169.88071780093</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>187</v>
@@ -5256,11 +5256,11 @@
         <v>191</v>
       </c>
       <c r="B54" s="5">
-        <v>46168.51670710648</v>
+        <v>46168.68337377315</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.71415071759</v>
+        <v>46169.880817384255</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>119</v>
@@ -5309,11 +5309,11 @@
         <v>193</v>
       </c>
       <c r="B55" s="8">
-        <v>46168.51671152777</v>
+        <v>46168.683378194444</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46169.71416412037</v>
+        <v>46169.880830787035</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>
@@ -5362,11 +5362,11 @@
         <v>196</v>
       </c>
       <c r="B56" s="5">
-        <v>46168.516716053244</v>
+        <v>46168.68338271991</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46169.714180462965</v>
+        <v>46169.88084712963</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -5415,11 +5415,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46168.51671920139</v>
+        <v>46168.683385868055</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46169.714061412036</v>
+        <v>46169.8807280787</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5478,11 +5478,11 @@
         <v>203</v>
       </c>
       <c r="B58" s="5">
-        <v>46168.51676398148</v>
+        <v>46168.68343064815</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46169.71410465278</v>
+        <v>46169.88077131944</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -5531,11 +5531,11 @@
         <v>205</v>
       </c>
       <c r="B59" s="8">
-        <v>46168.51677028935</v>
+        <v>46168.683436956024</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46169.71411534722</v>
+        <v>46169.88078201389</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>206</v>
@@ -5584,11 +5584,11 @@
         <v>208</v>
       </c>
       <c r="B60" s="5">
-        <v>46168.516775543976</v>
+        <v>46168.68344221065</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46184.35217084491</v>
+        <v>46184.518837511576</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>209</v>
@@ -5631,13 +5631,13 @@
         <v>211</v>
       </c>
       <c r="B61" s="8">
-        <v>46168.51677912037</v>
+        <v>46168.683445787035</v>
       </c>
       <c r="C61" s="8">
-        <v>46184.3521603125</v>
+        <v>46184.51882697917</v>
       </c>
       <c r="D61" s="8">
-        <v>46184.35217791666</v>
+        <v>46184.518844583334</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>212</v>
@@ -5696,13 +5696,13 @@
         <v>216</v>
       </c>
       <c r="B62" s="5">
-        <v>46168.519933020834</v>
+        <v>46168.6865996875</v>
       </c>
       <c r="C62" s="5">
-        <v>46184.35211828703</v>
+        <v>46184.5187849537</v>
       </c>
       <c r="D62" s="5">
-        <v>46184.35211998843</v>
+        <v>46184.51878665509</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>217</v>
@@ -5751,13 +5751,13 @@
         <v>219</v>
       </c>
       <c r="B63" s="8">
-        <v>46168.520167939816</v>
+        <v>46168.68683460648</v>
       </c>
       <c r="C63" s="8">
-        <v>46184.352123159726</v>
+        <v>46184.51878982639</v>
       </c>
       <c r="D63" s="8">
-        <v>46184.35212465278</v>
+        <v>46184.518791319446</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>217</v>
@@ -5806,13 +5806,13 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46168.52025177084</v>
+        <v>46168.686918437495</v>
       </c>
       <c r="C64" s="5">
-        <v>46184.352131203705</v>
+        <v>46184.51879787037</v>
       </c>
       <c r="D64" s="5">
-        <v>46184.35213263889</v>
+        <v>46184.51879930556</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5861,13 +5861,13 @@
         <v>223</v>
       </c>
       <c r="B65" s="8">
-        <v>46168.52058747685</v>
+        <v>46168.687254143515</v>
       </c>
       <c r="C65" s="8">
-        <v>46184.35213895833</v>
+        <v>46184.518805625004</v>
       </c>
       <c r="D65" s="8">
-        <v>46184.35214016204</v>
+        <v>46184.5188068287</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>221</v>
@@ -5916,13 +5916,13 @@
         <v>224</v>
       </c>
       <c r="B66" s="5">
-        <v>46168.5206496875</v>
+        <v>46168.68731635417</v>
       </c>
       <c r="C66" s="5">
-        <v>46184.35214644676</v>
+        <v>46184.51881311343</v>
       </c>
       <c r="D66" s="5">
-        <v>46184.352147881946</v>
+        <v>46184.51881454861</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>225</v>
@@ -5971,11 +5971,11 @@
         <v>227</v>
       </c>
       <c r="B67" s="8">
-        <v>46168.51678475694</v>
+        <v>46168.68345142361</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46185.0047087037</v>
+        <v>46185.171375370366</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -6034,11 +6034,11 @@
         <v>229</v>
       </c>
       <c r="B68" s="5">
-        <v>46168.521906793976</v>
+        <v>46168.68857346065</v>
       </c>
       <c r="C68" s="6"/>
       <c r="D68" s="5">
-        <v>46185.00468236111</v>
+        <v>46185.171349027776</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>217</v>
@@ -6087,11 +6087,11 @@
         <v>232</v>
       </c>
       <c r="B69" s="8">
-        <v>46168.52194160879</v>
+        <v>46168.688608275465</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="8">
-        <v>46185.00468380787</v>
+        <v>46185.17135047454</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>217</v>
@@ -6140,11 +6140,11 @@
         <v>233</v>
       </c>
       <c r="B70" s="5">
-        <v>46168.521979930556</v>
+        <v>46168.68864659722</v>
       </c>
       <c r="C70" s="6"/>
       <c r="D70" s="5">
-        <v>46185.00468503472</v>
+        <v>46185.171351701385</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>221</v>
@@ -6193,11 +6193,11 @@
         <v>236</v>
       </c>
       <c r="B71" s="8">
-        <v>46168.52201971065</v>
+        <v>46168.68868637731</v>
       </c>
       <c r="C71" s="9"/>
       <c r="D71" s="8">
-        <v>46185.004686319444</v>
+        <v>46185.171352986115</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>221</v>
@@ -6246,11 +6246,11 @@
         <v>238</v>
       </c>
       <c r="B72" s="5">
-        <v>46168.52205267361</v>
+        <v>46168.68871934028</v>
       </c>
       <c r="C72" s="6"/>
       <c r="D72" s="5">
-        <v>46185.0046875463</v>
+        <v>46185.17135421296</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>225</v>
@@ -6299,11 +6299,11 @@
         <v>241</v>
       </c>
       <c r="B73" s="8">
-        <v>46168.51679123843</v>
+        <v>46168.68345790509</v>
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46181.01753873842</v>
+        <v>46181.184205405094</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>108</v>
@@ -6362,11 +6362,11 @@
         <v>244</v>
       </c>
       <c r="B74" s="5">
-        <v>46168.52213511574</v>
+        <v>46168.68880178241</v>
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46168.698078506946</v>
+        <v>46168.86474517361</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>217</v>
@@ -6415,11 +6415,11 @@
         <v>245</v>
       </c>
       <c r="B75" s="8">
-        <v>46168.52217190972</v>
+        <v>46168.68883857639</v>
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46168.69807587963</v>
+        <v>46168.8647425463</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>217</v>
@@ -6468,11 +6468,11 @@
         <v>246</v>
       </c>
       <c r="B76" s="5">
-        <v>46168.52220910879</v>
+        <v>46168.688875775464</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46168.69807322917</v>
+        <v>46168.864739895835</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>221</v>
@@ -6521,11 +6521,11 @@
         <v>247</v>
       </c>
       <c r="B77" s="8">
-        <v>46168.522250567126</v>
+        <v>46168.6889172338</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46168.69807056713</v>
+        <v>46168.864737233795</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>248</v>
@@ -6574,11 +6574,11 @@
         <v>249</v>
       </c>
       <c r="B78" s="5">
-        <v>46168.522289953704</v>
+        <v>46168.688956620375</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46168.698066412035</v>
+        <v>46168.864733078706</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>225</v>
@@ -6627,11 +6627,11 @@
         <v>250</v>
       </c>
       <c r="B79" s="8">
-        <v>46168.51681395833</v>
+        <v>46168.683480625</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46168.69828388889</v>
+        <v>46168.86495055555</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>251</v>
@@ -6688,11 +6688,11 @@
         <v>255</v>
       </c>
       <c r="B80" s="5">
-        <v>46168.51681796296</v>
+        <v>46168.683484629626</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46168.698261875004</v>
+        <v>46168.86492854166</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>217</v>
@@ -6741,11 +6741,11 @@
         <v>257</v>
       </c>
       <c r="B81" s="8">
-        <v>46168.516822210644</v>
+        <v>46168.683488877316</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46168.69825894676</v>
+        <v>46168.86492561342</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>217</v>
@@ -6794,11 +6794,11 @@
         <v>258</v>
       </c>
       <c r="B82" s="5">
-        <v>46168.51682634259</v>
+        <v>46168.68349300926</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46168.69825621528</v>
+        <v>46168.86492288194</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>221</v>
@@ -6847,11 +6847,11 @@
         <v>259</v>
       </c>
       <c r="B83" s="8">
-        <v>46168.51682927083</v>
+        <v>46168.6834959375</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46168.69825349537</v>
+        <v>46168.864920162036</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>221</v>
@@ -6900,11 +6900,11 @@
         <v>260</v>
       </c>
       <c r="B84" s="5">
-        <v>46168.51683232639</v>
+        <v>46168.68349899305</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46168.69824898148</v>
+        <v>46168.86491564815</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>225</v>
@@ -6953,11 +6953,11 @@
         <v>261</v>
       </c>
       <c r="B85" s="8">
-        <v>46168.51684435185</v>
+        <v>46168.68351101852</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46168.68313081018</v>
+        <v>46168.849797476854</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>262</v>
@@ -7000,11 +7000,11 @@
         <v>264</v>
       </c>
       <c r="B86" s="5">
-        <v>46168.5168478125</v>
+        <v>46168.68351447917</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46168.69835572917</v>
+        <v>46168.86502239583</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>265</v>
@@ -7063,11 +7063,11 @@
         <v>269</v>
       </c>
       <c r="B87" s="8">
-        <v>46168.51685344907</v>
+        <v>46168.68352011574</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46168.69852951389</v>
+        <v>46168.86519618056</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -7126,11 +7126,11 @@
         <v>273</v>
       </c>
       <c r="B88" s="5">
-        <v>46168.51686069445</v>
+        <v>46168.68352736111</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46168.698405462965</v>
+        <v>46168.86507212963</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>274</v>
@@ -7189,11 +7189,11 @@
         <v>276</v>
       </c>
       <c r="B89" s="8">
-        <v>46168.516866261576</v>
+        <v>46168.68353292824</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46168.69860578704</v>
+        <v>46168.8652724537</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>277</v>
@@ -7252,11 +7252,11 @@
         <v>279</v>
       </c>
       <c r="B90" s="5">
-        <v>46168.516871203705</v>
+        <v>46168.68353787037</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46168.698439155094</v>
+        <v>46168.86510582176</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>280</v>
@@ -7315,11 +7315,11 @@
         <v>282</v>
       </c>
       <c r="B91" s="8">
-        <v>46168.516875810186</v>
+        <v>46168.68354247685</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46168.69864109954</v>
+        <v>46168.8653077662</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>281</v>
@@ -7378,11 +7378,11 @@
         <v>283</v>
       </c>
       <c r="B92" s="5">
-        <v>46168.516880752315</v>
+        <v>46168.68354741899</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46168.69901351852</v>
+        <v>46168.86568018519</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>284</v>
@@ -7425,11 +7425,11 @@
         <v>286</v>
       </c>
       <c r="B93" s="8">
-        <v>46168.516883854165</v>
+        <v>46168.68355052083</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46168.69885722222</v>
+        <v>46168.86552388889</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>287</v>
@@ -7488,11 +7488,11 @@
         <v>291</v>
       </c>
       <c r="B94" s="5">
-        <v>46168.516895416666</v>
+        <v>46168.68356208333</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46168.69883275463</v>
+        <v>46168.8654994213</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>217</v>
@@ -7541,11 +7541,11 @@
         <v>294</v>
       </c>
       <c r="B95" s="8">
-        <v>46168.516902557865</v>
+        <v>46168.68356922454</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46168.698829201385</v>
+        <v>46168.865495868056</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>217</v>
@@ -7594,11 +7594,11 @@
         <v>296</v>
       </c>
       <c r="B96" s="5">
-        <v>46168.51690811342</v>
+        <v>46168.683574780094</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46168.6988264699</v>
+        <v>46168.865493136575</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>221</v>
@@ -7647,11 +7647,11 @@
         <v>299</v>
       </c>
       <c r="B97" s="8">
-        <v>46168.516913576386</v>
+        <v>46168.68358024306</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46168.698823865736</v>
+        <v>46168.86549053241</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>221</v>
@@ -7700,11 +7700,11 @@
         <v>300</v>
       </c>
       <c r="B98" s="5">
-        <v>46168.516919120375</v>
+        <v>46168.68358578703</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46168.69881969907</v>
+        <v>46168.86548636574</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>225</v>
@@ -7753,11 +7753,11 @@
         <v>302</v>
       </c>
       <c r="B99" s="8">
-        <v>46168.5169880787</v>
+        <v>46168.68365474537</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46168.69902525463</v>
+        <v>46168.865691921295</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>303</v>
@@ -7816,11 +7816,11 @@
         <v>305</v>
       </c>
       <c r="B100" s="5">
-        <v>46168.51699329861</v>
+        <v>46168.683659965274</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46168.69898951389</v>
+        <v>46168.865656180555</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>217</v>
@@ -7869,11 +7869,11 @@
         <v>308</v>
       </c>
       <c r="B101" s="8">
-        <v>46168.516999467596</v>
+        <v>46168.68366613426</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46168.6989862037</v>
+        <v>46168.86565287037</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>217</v>
@@ -7922,11 +7922,11 @@
         <v>310</v>
       </c>
       <c r="B102" s="5">
-        <v>46168.51700525463</v>
+        <v>46168.683671921295</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46168.698983379625</v>
+        <v>46168.8656500463</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>221</v>
@@ -7975,11 +7975,11 @@
         <v>312</v>
       </c>
       <c r="B103" s="8">
-        <v>46168.517009560186</v>
+        <v>46168.68367622685</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46168.69898047454</v>
+        <v>46168.8656471412</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>221</v>
@@ -8028,11 +8028,11 @@
         <v>314</v>
       </c>
       <c r="B104" s="5">
-        <v>46168.51701340278</v>
+        <v>46168.683680069444</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46168.698976458334</v>
+        <v>46168.865643125</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>225</v>
@@ -8081,11 +8081,11 @@
         <v>316</v>
       </c>
       <c r="B105" s="8">
-        <v>46168.51702743056</v>
+        <v>46168.68369409722</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46168.69920524306</v>
+        <v>46168.86587190972</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>317</v>
@@ -8144,11 +8144,11 @@
         <v>319</v>
       </c>
       <c r="B106" s="5">
-        <v>46168.517031828706</v>
+        <v>46168.68369849537</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46168.69918402778</v>
+        <v>46168.86585069445</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>217</v>
@@ -8197,11 +8197,11 @@
         <v>321</v>
       </c>
       <c r="B107" s="8">
-        <v>46168.51703782407</v>
+        <v>46168.683704490744</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46168.69918113426</v>
+        <v>46168.86584780093</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>322</v>
@@ -8250,11 +8250,11 @@
         <v>324</v>
       </c>
       <c r="B108" s="5">
-        <v>46168.51704348379</v>
+        <v>46168.683710150464</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46168.69917775463</v>
+        <v>46168.86584442129</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>221</v>
@@ -8303,11 +8303,11 @@
         <v>325</v>
       </c>
       <c r="B109" s="8">
-        <v>46168.517046423614</v>
+        <v>46168.68371309028</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46168.69917491898</v>
+        <v>46168.86584158565</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>221</v>
@@ -8356,11 +8356,11 @@
         <v>327</v>
       </c>
       <c r="B110" s="5">
-        <v>46168.51704980324</v>
+        <v>46168.68371646991</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46168.69917121528</v>
+        <v>46168.865837881945</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>225</v>
@@ -8409,11 +8409,11 @@
         <v>329</v>
       </c>
       <c r="B111" s="8">
-        <v>46168.517063391206</v>
+        <v>46168.68373005787</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46168.68819925926</v>
+        <v>46168.854865925925</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>262</v>
@@ -8456,11 +8456,11 @@
         <v>331</v>
       </c>
       <c r="B112" s="5">
-        <v>46168.51706699074</v>
+        <v>46168.68373365741</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46185.00471069444</v>
+        <v>46185.17137736111</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>332</v>
@@ -8519,11 +8519,11 @@
         <v>334</v>
       </c>
       <c r="B113" s="8">
-        <v>46168.51707422454</v>
+        <v>46168.6837408912</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46169.00027203704</v>
+        <v>46169.1669387037</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>335</v>
@@ -8580,11 +8580,11 @@
         <v>337</v>
       </c>
       <c r="B114" s="5">
-        <v>46168.51708105324</v>
+        <v>46168.68374771991</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46168.69934946759</v>
+        <v>46168.866016134256</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>338</v>
@@ -8643,11 +8643,11 @@
         <v>340</v>
       </c>
       <c r="B115" s="8">
-        <v>46168.517088356486</v>
+        <v>46168.68375502314</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46168.699346759255</v>
+        <v>46168.866013425926</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>341</v>
@@ -8706,11 +8706,11 @@
         <v>343</v>
       </c>
       <c r="B116" s="5">
-        <v>46168.51713047454</v>
+        <v>46168.6837971412</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46168.69934222222</v>
+        <v>46168.86600888889</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>59</v>
@@ -8769,11 +8769,11 @@
         <v>345</v>
       </c>
       <c r="B117" s="8">
-        <v>46168.517146956015</v>
+        <v>46168.68381362269</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46168.691813819445</v>
+        <v>46168.85848048611</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>346</v>
@@ -8816,11 +8816,11 @@
         <v>348</v>
       </c>
       <c r="B118" s="5">
-        <v>46168.517151168984</v>
+        <v>46168.68381783565</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46168.699495381945</v>
+        <v>46168.86616204861</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>349</v>
@@ -8879,11 +8879,11 @@
         <v>351</v>
       </c>
       <c r="B119" s="8">
-        <v>46168.51715914352</v>
+        <v>46168.683825810185</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46168.69946376157</v>
+        <v>46168.86613042824</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>217</v>
@@ -8932,11 +8932,11 @@
         <v>353</v>
       </c>
       <c r="B120" s="5">
-        <v>46168.517169212966</v>
+        <v>46168.68383587963</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46168.69946101852</v>
+        <v>46168.866127685185</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>217</v>
@@ -8985,11 +8985,11 @@
         <v>355</v>
       </c>
       <c r="B121" s="8">
-        <v>46168.51717368056</v>
+        <v>46168.68384034722</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46168.699458449075</v>
+        <v>46168.86612511574</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>221</v>
@@ -9038,11 +9038,11 @@
         <v>357</v>
       </c>
       <c r="B122" s="5">
-        <v>46168.51717740741</v>
+        <v>46168.683844074076</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46168.699455567126</v>
+        <v>46168.8661222338</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>221</v>
@@ -9091,11 +9091,11 @@
         <v>358</v>
       </c>
       <c r="B123" s="8">
-        <v>46168.517181006944</v>
+        <v>46168.683847673616</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46168.69945141204</v>
+        <v>46168.8661180787</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>225</v>
@@ -9144,11 +9144,11 @@
         <v>360</v>
       </c>
       <c r="B124" s="5">
-        <v>46168.51719578703</v>
+        <v>46168.683862453705</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46168.70048575231</v>
+        <v>46168.867152418985</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>361</v>
@@ -9207,11 +9207,11 @@
         <v>362</v>
       </c>
       <c r="B125" s="8">
-        <v>46168.51720047454</v>
+        <v>46168.683867141204</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46168.70045335648</v>
+        <v>46168.86712002315</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>217</v>
@@ -9260,11 +9260,11 @@
         <v>365</v>
       </c>
       <c r="B126" s="5">
-        <v>46168.51720670139</v>
+        <v>46168.683873368056</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46168.70044994213</v>
+        <v>46168.867116608795</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>217</v>
@@ -9313,11 +9313,11 @@
         <v>367</v>
       </c>
       <c r="B127" s="8">
-        <v>46168.51721237268</v>
+        <v>46168.68387903935</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46168.700447407406</v>
+        <v>46168.86711407408</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>221</v>
@@ -9366,11 +9366,11 @@
         <v>370</v>
       </c>
       <c r="B128" s="5">
-        <v>46168.51721795139</v>
+        <v>46168.683884618054</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46168.700444699076</v>
+        <v>46168.86711136574</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>221</v>
@@ -9419,11 +9419,11 @@
         <v>372</v>
       </c>
       <c r="B129" s="8">
-        <v>46168.51722366898</v>
+        <v>46168.68389033565</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46168.70044112268</v>
+        <v>46168.86710778935</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>225</v>
@@ -9472,11 +9472,11 @@
         <v>375</v>
       </c>
       <c r="B130" s="5">
-        <v>46168.51724622685</v>
+        <v>46168.68391289352</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46168.70062618055</v>
+        <v>46168.86729284722</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>376</v>
@@ -9535,11 +9535,11 @@
         <v>377</v>
       </c>
       <c r="B131" s="8">
-        <v>46168.517251516205</v>
+        <v>46168.68391818287</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46168.7005942824</v>
+        <v>46168.867260949075</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>217</v>
@@ -9588,11 +9588,11 @@
         <v>380</v>
       </c>
       <c r="B132" s="5">
-        <v>46168.517264016205</v>
+        <v>46168.68393068287</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46168.70059115741</v>
+        <v>46168.86725782407</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>217</v>
@@ -9641,11 +9641,11 @@
         <v>383</v>
       </c>
       <c r="B133" s="8">
-        <v>46168.51727104167</v>
+        <v>46168.68393770834</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46168.70058820602</v>
+        <v>46168.86725487269</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>221</v>
@@ -9694,11 +9694,11 @@
         <v>386</v>
       </c>
       <c r="B134" s="5">
-        <v>46168.51727677083</v>
+        <v>46168.6839434375</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46168.700585555554</v>
+        <v>46168.86725222222</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>221</v>
@@ -9747,11 +9747,11 @@
         <v>387</v>
       </c>
       <c r="B135" s="8">
-        <v>46168.51731862269</v>
+        <v>46168.68398528935</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46168.70058133102</v>
+        <v>46168.86724799768</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>225</v>
@@ -9800,11 +9800,11 @@
         <v>390</v>
       </c>
       <c r="B136" s="5">
-        <v>46168.51734421296</v>
+        <v>46168.68401087963</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46168.70084508102</v>
+        <v>46168.86751174768</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>391</v>
@@ -9863,11 +9863,11 @@
         <v>392</v>
       </c>
       <c r="B137" s="8">
-        <v>46168.51734986111</v>
+        <v>46168.68401652778</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46168.70080704861</v>
+        <v>46168.867473715276</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>217</v>
@@ -9916,11 +9916,11 @@
         <v>395</v>
       </c>
       <c r="B138" s="5">
-        <v>46168.517357372686</v>
+        <v>46168.68402403935</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46168.700803831016</v>
+        <v>46168.86747049769</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>217</v>
@@ -9969,11 +9969,11 @@
         <v>396</v>
       </c>
       <c r="B139" s="8">
-        <v>46168.51736460648</v>
+        <v>46168.68403127315</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46168.700801122686</v>
+        <v>46168.86746778935</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>221</v>
@@ -10022,11 +10022,11 @@
         <v>399</v>
       </c>
       <c r="B140" s="5">
-        <v>46168.517370891204</v>
+        <v>46168.68403755787</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46168.700798171296</v>
+        <v>46168.86746483797</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>221</v>
@@ -10075,11 +10075,11 @@
         <v>401</v>
       </c>
       <c r="B141" s="8">
-        <v>46168.5173771875</v>
+        <v>46168.68404385417</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46168.700794247685</v>
+        <v>46168.86746091435</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>225</v>
@@ -10128,11 +10128,11 @@
         <v>404</v>
       </c>
       <c r="B142" s="5">
-        <v>46168.51739630787</v>
+        <v>46168.68406297454</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46168.70101440972</v>
+        <v>46168.867681076386</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>405</v>
@@ -10191,11 +10191,11 @@
         <v>406</v>
       </c>
       <c r="B143" s="8">
-        <v>46168.51740085648</v>
+        <v>46168.68406752315</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46168.700991192134</v>
+        <v>46168.86765785879</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>217</v>
@@ -10244,11 +10244,11 @@
         <v>408</v>
       </c>
       <c r="B144" s="5">
-        <v>46168.517412719906</v>
+        <v>46168.68407938657</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46168.70098826389</v>
+        <v>46168.86765493055</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>217</v>
@@ -10297,11 +10297,11 @@
         <v>410</v>
       </c>
       <c r="B145" s="8">
-        <v>46168.517418564814</v>
+        <v>46168.68408523148</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46168.70098283565</v>
+        <v>46168.86764950231</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>221</v>
@@ -10350,11 +10350,11 @@
         <v>412</v>
       </c>
       <c r="B146" s="5">
-        <v>46168.51742321759</v>
+        <v>46168.684089884264</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46168.7009787037</v>
+        <v>46168.86764537037</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>221</v>
@@ -10403,11 +10403,11 @@
         <v>413</v>
       </c>
       <c r="B147" s="8">
-        <v>46168.51742790509</v>
+        <v>46168.684094571756</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46168.70097791667</v>
+        <v>46168.86764458333</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>225</v>
@@ -10456,11 +10456,11 @@
         <v>415</v>
       </c>
       <c r="B148" s="5">
-        <v>46168.51747907407</v>
+        <v>46168.68414574074</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46168.70116519676</v>
+        <v>46168.86783186343</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>416</v>
@@ -10519,11 +10519,11 @@
         <v>418</v>
       </c>
       <c r="B149" s="8">
-        <v>46168.517484386575</v>
+        <v>46168.68415105324</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46168.70113376157</v>
+        <v>46168.86780042824</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>217</v>
@@ -10572,11 +10572,11 @@
         <v>420</v>
       </c>
       <c r="B150" s="5">
-        <v>46168.51748921296</v>
+        <v>46168.68415587963</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46168.70113033565</v>
+        <v>46168.86779700231</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>217</v>
@@ -10625,11 +10625,11 @@
         <v>422</v>
       </c>
       <c r="B151" s="8">
-        <v>46168.5174940162</v>
+        <v>46168.68416068287</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46168.70112755787</v>
+        <v>46168.86779422454</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>221</v>
@@ -10678,11 +10678,11 @@
         <v>424</v>
       </c>
       <c r="B152" s="5">
-        <v>46168.517497650464</v>
+        <v>46168.68416431713</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46168.70112471065</v>
+        <v>46168.86779137731</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>221</v>
@@ -10731,11 +10731,11 @@
         <v>425</v>
       </c>
       <c r="B153" s="8">
-        <v>46168.517501319446</v>
+        <v>46168.68416798611</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46168.70112032407</v>
+        <v>46168.86778699074</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>225</v>
@@ -10784,11 +10784,11 @@
         <v>427</v>
       </c>
       <c r="B154" s="5">
-        <v>46168.51751679398</v>
+        <v>46168.684183460646</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46168.69303797453</v>
+        <v>46168.8597046412</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>428</v>
@@ -10831,11 +10831,11 @@
         <v>430</v>
       </c>
       <c r="B155" s="8">
-        <v>46168.51752033565</v>
+        <v>46168.68418700232</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46168.70141100694</v>
+        <v>46168.868077673615</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>431</v>
@@ -10894,11 +10894,11 @@
         <v>435</v>
       </c>
       <c r="B156" s="5">
-        <v>46168.517526932876</v>
+        <v>46168.68419359953</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46168.70138209491</v>
+        <v>46168.86804876158</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>217</v>
@@ -10947,11 +10947,11 @@
         <v>437</v>
       </c>
       <c r="B157" s="8">
-        <v>46168.51753167824</v>
+        <v>46168.68419834491</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46168.70137912037</v>
+        <v>46168.868045787036</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>217</v>
@@ -11000,11 +11000,11 @@
         <v>438</v>
       </c>
       <c r="B158" s="5">
-        <v>46168.51753611111</v>
+        <v>46168.684202777775</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46168.70137597222</v>
+        <v>46168.86804263889</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>221</v>
@@ -11053,11 +11053,11 @@
         <v>440</v>
       </c>
       <c r="B159" s="8">
-        <v>46168.51754043982</v>
+        <v>46168.68420710648</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46168.70137328704</v>
+        <v>46168.868039953704</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>221</v>
@@ -11106,11 +11106,11 @@
         <v>441</v>
       </c>
       <c r="B160" s="5">
-        <v>46168.51754460648</v>
+        <v>46168.68421127315</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46168.70137042824</v>
+        <v>46168.86803709491</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>225</v>
@@ -11159,11 +11159,11 @@
         <v>443</v>
       </c>
       <c r="B161" s="8">
-        <v>46168.51756329861</v>
+        <v>46168.68422996528</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46168.701367118054</v>
+        <v>46168.86803378472</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>63</v>
@@ -11212,11 +11212,11 @@
         <v>445</v>
       </c>
       <c r="B162" s="5">
-        <v>46168.51756674769</v>
+        <v>46168.68423341435</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46168.70136349537</v>
+        <v>46168.86803016203</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>63</v>
@@ -11265,11 +11265,11 @@
         <v>446</v>
       </c>
       <c r="B163" s="8">
-        <v>46168.51757037037</v>
+        <v>46168.684237037036</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46168.70136064815</v>
+        <v>46168.86802731482</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>63</v>
@@ -11318,11 +11318,11 @@
         <v>447</v>
       </c>
       <c r="B164" s="5">
-        <v>46168.517573923615</v>
+        <v>46168.68424059028</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46168.70135783565</v>
+        <v>46168.86802450231</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>67</v>
@@ -11371,11 +11371,11 @@
         <v>449</v>
       </c>
       <c r="B165" s="8">
-        <v>46168.51757753472</v>
+        <v>46168.68424420139</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46168.70135107639</v>
+        <v>46168.86801774305</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>67</v>
@@ -11424,11 +11424,11 @@
         <v>450</v>
       </c>
       <c r="B166" s="5">
-        <v>46168.51758112268</v>
+        <v>46168.68424778935</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46168.70135047454</v>
+        <v>46168.868017141205</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>70</v>
@@ -11477,11 +11477,11 @@
         <v>452</v>
       </c>
       <c r="B167" s="8">
-        <v>46168.51759153935</v>
+        <v>46168.68425820602</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46168.70160638889</v>
+        <v>46168.86827305556</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>453</v>
@@ -11538,11 +11538,11 @@
         <v>455</v>
       </c>
       <c r="B168" s="5">
-        <v>46168.5175958912</v>
+        <v>46168.68426255787</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46168.70160164352</v>
+        <v>46168.86826831019</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>217</v>
@@ -11589,11 +11589,11 @@
         <v>457</v>
       </c>
       <c r="B169" s="8">
-        <v>46168.51760038194</v>
+        <v>46168.68426704861</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46168.70159834491</v>
+        <v>46168.86826501157</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>217</v>
@@ -11640,11 +11640,11 @@
         <v>458</v>
       </c>
       <c r="B170" s="5">
-        <v>46168.517604953704</v>
+        <v>46168.68427162037</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46168.70159511574</v>
+        <v>46168.86826178241</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>221</v>
@@ -11691,11 +11691,11 @@
         <v>460</v>
       </c>
       <c r="B171" s="8">
-        <v>46168.51760960648</v>
+        <v>46168.68427627315</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46168.70159207176</v>
+        <v>46168.868258738425</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>221</v>
@@ -11742,11 +11742,11 @@
         <v>461</v>
       </c>
       <c r="B172" s="5">
-        <v>46168.51761401621</v>
+        <v>46168.68428068287</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46168.70158836806</v>
+        <v>46168.86825503472</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>225</v>
@@ -11793,11 +11793,11 @@
         <v>463</v>
       </c>
       <c r="B173" s="8">
-        <v>46168.517669560184</v>
+        <v>46168.684336226856</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46168.701585092596</v>
+        <v>46168.86825175926</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>63</v>
@@ -11844,11 +11844,11 @@
         <v>465</v>
       </c>
       <c r="B174" s="5">
-        <v>46168.5176734375</v>
+        <v>46168.68434010417</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46168.701582002315</v>
+        <v>46168.86824866898</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>63</v>
@@ -11895,11 +11895,11 @@
         <v>467</v>
       </c>
       <c r="B175" s="8">
-        <v>46168.51767756944</v>
+        <v>46168.68434423611</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46168.701578796296</v>
+        <v>46168.86824546296</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>63</v>
@@ -11946,11 +11946,11 @@
         <v>468</v>
       </c>
       <c r="B176" s="5">
-        <v>46168.51768159722</v>
+        <v>46168.684348263894</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46168.70157584491</v>
+        <v>46168.86824251157</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>67</v>
@@ -11997,11 +11997,11 @@
         <v>470</v>
       </c>
       <c r="B177" s="8">
-        <v>46168.51768535879</v>
+        <v>46168.68435202546</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46168.701568425924</v>
+        <v>46168.868235092596</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>67</v>
@@ -12048,11 +12048,11 @@
         <v>471</v>
       </c>
       <c r="B178" s="5">
-        <v>46168.51768986111</v>
+        <v>46168.68435652778</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46168.7015677662</v>
+        <v>46168.86823443287</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>70</v>
@@ -12099,11 +12099,11 @@
         <v>473</v>
       </c>
       <c r="B179" s="8">
-        <v>46168.51770648148</v>
+        <v>46168.68437314815</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46168.70178509259</v>
+        <v>46168.86845175926</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>474</v>
@@ -12160,11 +12160,11 @@
         <v>476</v>
       </c>
       <c r="B180" s="5">
-        <v>46168.51771180556</v>
+        <v>46168.68437847222</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46168.701782476855</v>
+        <v>46168.86844914352</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>217</v>
@@ -12213,11 +12213,11 @@
         <v>478</v>
       </c>
       <c r="B181" s="8">
-        <v>46168.517721550925</v>
+        <v>46168.68438821759</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46168.701779201394</v>
+        <v>46168.86844586805</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>217</v>
@@ -12266,11 +12266,11 @@
         <v>480</v>
       </c>
       <c r="B182" s="5">
-        <v>46168.51772787037</v>
+        <v>46168.684394537035</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46168.70177555556</v>
+        <v>46168.86844222222</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>221</v>
@@ -12319,11 +12319,11 @@
         <v>482</v>
       </c>
       <c r="B183" s="8">
-        <v>46168.51773277778</v>
+        <v>46168.68439944445</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46168.70177208333</v>
+        <v>46168.868438749996</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>221</v>
@@ -12372,11 +12372,11 @@
         <v>484</v>
       </c>
       <c r="B184" s="5">
-        <v>46168.51773770833</v>
+        <v>46168.684404375</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46168.701768391205</v>
+        <v>46168.86843505787</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>225</v>
@@ -12425,11 +12425,11 @@
         <v>486</v>
       </c>
       <c r="B185" s="8">
-        <v>46168.517752395834</v>
+        <v>46168.6844190625</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46168.701765150465</v>
+        <v>46168.86843181713</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>63</v>
@@ -12478,11 +12478,11 @@
         <v>488</v>
       </c>
       <c r="B186" s="5">
-        <v>46168.51775611111</v>
+        <v>46168.68442277778</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46168.701757627314</v>
+        <v>46168.86842429398</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>489</v>
@@ -12531,11 +12531,11 @@
         <v>491</v>
       </c>
       <c r="B187" s="8">
-        <v>46168.51775987269</v>
+        <v>46168.68442653935</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46168.70175685185</v>
+        <v>46168.86842351852</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>63</v>
@@ -12584,11 +12584,11 @@
         <v>493</v>
       </c>
       <c r="B188" s="5">
-        <v>46168.51776332176</v>
+        <v>46168.684429988425</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46168.70175613426</v>
+        <v>46168.86842280092</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>67</v>
@@ -12637,11 +12637,11 @@
         <v>495</v>
       </c>
       <c r="B189" s="8">
-        <v>46168.51776693287</v>
+        <v>46168.68443359954</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46168.701755381946</v>
+        <v>46168.86842204861</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>67</v>
@@ -12690,11 +12690,11 @@
         <v>497</v>
       </c>
       <c r="B190" s="5">
-        <v>46168.517770624996</v>
+        <v>46168.68443729167</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46168.70175445602</v>
+        <v>46168.86842112269</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>70</v>
@@ -12743,11 +12743,11 @@
         <v>499</v>
       </c>
       <c r="B191" s="8">
-        <v>46168.517817395834</v>
+        <v>46168.6844840625</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46168.70196324074</v>
+        <v>46168.8686299074</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>500</v>
@@ -12806,11 +12806,11 @@
         <v>503</v>
       </c>
       <c r="B192" s="5">
-        <v>46168.5178246412</v>
+        <v>46168.68449130787</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46168.701955173616</v>
+        <v>46168.86862184027</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>504</v>
@@ -12857,11 +12857,11 @@
         <v>505</v>
       </c>
       <c r="B193" s="8">
-        <v>46168.51782923611</v>
+        <v>46168.68449590278</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46168.70195228009</v>
+        <v>46168.868618946755</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>506</v>
@@ -12908,11 +12908,11 @@
         <v>507</v>
       </c>
       <c r="B194" s="5">
-        <v>46168.51783361111</v>
+        <v>46168.68450027778</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46168.701949594906</v>
+        <v>46168.86861626158</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>508</v>
@@ -12959,11 +12959,11 @@
         <v>509</v>
       </c>
       <c r="B195" s="8">
-        <v>46168.51783813657</v>
+        <v>46168.68450480324</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46168.701946574074</v>
+        <v>46168.868613240746</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>510</v>
@@ -13010,11 +13010,11 @@
         <v>511</v>
       </c>
       <c r="B196" s="5">
-        <v>46168.51784267361</v>
+        <v>46168.68450934028</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46168.70194290509</v>
+        <v>46168.86860957176</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>512</v>
@@ -13061,11 +13061,11 @@
         <v>513</v>
       </c>
       <c r="B197" s="8">
-        <v>46168.51785674768</v>
+        <v>46168.684523414355</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46168.70193974537</v>
+        <v>46168.86860641204</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>514</v>
@@ -13112,11 +13112,11 @@
         <v>515</v>
       </c>
       <c r="B198" s="5">
-        <v>46168.51786047454</v>
+        <v>46168.6845271412</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46168.701936666665</v>
+        <v>46168.868603333336</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>516</v>
@@ -13163,11 +13163,11 @@
         <v>517</v>
       </c>
       <c r="B199" s="8">
-        <v>46168.517868449075</v>
+        <v>46168.68453511574</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46168.70193398148</v>
+        <v>46168.868600648144</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>518</v>
@@ -13214,11 +13214,11 @@
         <v>519</v>
       </c>
       <c r="B200" s="5">
-        <v>46168.51787196759</v>
+        <v>46168.68453863426</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46168.7019261574</v>
+        <v>46168.868592824074</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>520</v>
@@ -13265,11 +13265,11 @@
         <v>521</v>
       </c>
       <c r="B201" s="8">
-        <v>46168.517875439815</v>
+        <v>46168.68454210648</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46168.701925416666</v>
+        <v>46168.86859208334</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>522</v>
@@ -13316,11 +13316,11 @@
         <v>523</v>
       </c>
       <c r="B202" s="5">
-        <v>46168.51787891204</v>
+        <v>46168.684545578704</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46168.70192471065</v>
+        <v>46168.868591377315</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>524</v>
@@ -13367,11 +13367,11 @@
         <v>525</v>
       </c>
       <c r="B203" s="8">
-        <v>46168.5178891088</v>
+        <v>46168.684555775464</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46168.69520931713</v>
+        <v>46168.8618759838</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>526</v>
@@ -13414,11 +13414,11 @@
         <v>528</v>
       </c>
       <c r="B204" s="5">
-        <v>46168.517892800926</v>
+        <v>46168.6845594676</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46168.7020271875</v>
+        <v>46168.868693854165</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>529</v>
@@ -13477,11 +13477,11 @@
         <v>532</v>
       </c>
       <c r="B205" s="8">
-        <v>46168.517897592596</v>
+        <v>46168.68456425926</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46168.702061435186</v>
+        <v>46168.86872810185</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>533</v>
@@ -13540,11 +13540,11 @@
         <v>535</v>
       </c>
       <c r="B206" s="5">
-        <v>46168.517903831016</v>
+        <v>46168.68457049769</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46168.69567876158</v>
+        <v>46168.86234542824</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>536</v>
@@ -13593,11 +13593,11 @@
         <v>538</v>
       </c>
       <c r="B207" s="8">
-        <v>46168.51790748842</v>
+        <v>46168.68457415509</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46168.70213266204</v>
+        <v>46168.8687993287</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>539</v>
@@ -13656,11 +13656,11 @@
         <v>541</v>
       </c>
       <c r="B208" s="5">
-        <v>46168.51791253472</v>
+        <v>46168.68457920139</v>
       </c>
       <c r="C208" s="6"/>
       <c r="D208" s="5">
-        <v>46168.70212927084</v>
+        <v>46168.868795937495</v>
       </c>
       <c r="E208" s="6" t="s">
         <v>542</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -5975,7 +5975,7 @@
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46185.171375370366</v>
+        <v>46186.16818146991</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -6019,8 +6019,8 @@
       <c r="R67" s="8">
         <v>46185</v>
       </c>
-      <c r="S67" s="11" t="s">
-        <v>110</v>
+      <c r="S67" s="12" t="s">
+        <v>140</v>
       </c>
       <c r="T67" s="9">
         <v>0</v>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46185.17137736111</v>
+        <v>46186.16818170139</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>332</v>
@@ -8504,8 +8504,8 @@
       <c r="R112" s="5">
         <v>46185</v>
       </c>
-      <c r="S112" s="11" t="s">
-        <v>110</v>
+      <c r="S112" s="12" t="s">
+        <v>140</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46181.184205405094</v>
+        <v>46188.17147876158</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>108</v>
@@ -6366,7 +6366,7 @@
       </c>
       <c r="C74" s="6"/>
       <c r="D74" s="5">
-        <v>46168.86474517361</v>
+        <v>46188.1714565625</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>217</v>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="C75" s="9"/>
       <c r="D75" s="8">
-        <v>46168.8647425463</v>
+        <v>46188.17145818287</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>217</v>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46168.864739895835</v>
+        <v>46188.171459652775</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>221</v>
@@ -6525,7 +6525,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46168.864737233795</v>
+        <v>46188.171461412036</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>248</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46168.864733078706</v>
+        <v>46188.17146267361</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>225</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -6303,7 +6303,7 @@
       </c>
       <c r="C73" s="9"/>
       <c r="D73" s="8">
-        <v>46188.17147876158</v>
+        <v>46189.20161289352</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>108</v>
@@ -6347,8 +6347,8 @@
       <c r="R73" s="8">
         <v>46188</v>
       </c>
-      <c r="S73" s="11" t="s">
-        <v>110</v>
+      <c r="S73" s="12" t="s">
+        <v>140</v>
       </c>
       <c r="T73" s="9">
         <v>0</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46184.91201917824</v>
+        <v>46190.16996086805</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46184.90739432871</v>
+        <v>46190.16996216435</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46183.168378194445</v>
+        <v>46190.169963402775</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46183.16837792824</v>
+        <v>46190.169958831015</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2403" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="543">
   <si>
     <t>50001557 - ATACAMA KOZAN OT  4335 - 4337 -4339</t>
   </si>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46190.16996086805</v>
+        <v>46190.605452488424</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3756,8 +3756,8 @@
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="12" t="s">
-        <v>61</v>
+      <c r="U28" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46190.16996216435</v>
+        <v>46190.60545243055</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3819,8 +3819,8 @@
       <c r="T29" s="9">
         <v>0</v>
       </c>
-      <c r="U29" s="12" t="s">
-        <v>61</v>
+      <c r="U29" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46190.169963402775</v>
+        <v>46190.60545216435</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3882,8 +3882,8 @@
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="12" t="s">
-        <v>61</v>
+      <c r="U30" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46190.169958831015</v>
+        <v>46190.60545229167</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3945,8 +3945,8 @@
       <c r="T31" s="9">
         <v>0</v>
       </c>
-      <c r="U31" s="12" t="s">
-        <v>61</v>
+      <c r="U31" s="11" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46184.518837511576</v>
+        <v>46190.60524740741</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>209</v>
@@ -5624,7 +5624,9 @@
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
       <c r="T60" s="6"/>
-      <c r="U60" s="6"/>
+      <c r="U60" s="11" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
@@ -5973,9 +5975,11 @@
       <c r="B67" s="8">
         <v>46168.68345142361</v>
       </c>
-      <c r="C67" s="9"/>
+      <c r="C67" s="8">
+        <v>46190.60523084491</v>
+      </c>
       <c r="D67" s="8">
-        <v>46186.16818146991</v>
+        <v>46190.605242708334</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>228</v>
@@ -6023,10 +6027,10 @@
         <v>140</v>
       </c>
       <c r="T67" s="9">
-        <v>0</v>
-      </c>
-      <c r="U67" s="12" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U67" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
@@ -6036,9 +6040,11 @@
       <c r="B68" s="5">
         <v>46168.68857346065</v>
       </c>
-      <c r="C68" s="6"/>
+      <c r="C68" s="5">
+        <v>46190.60518377315</v>
+      </c>
       <c r="D68" s="5">
-        <v>46185.171349027776</v>
+        <v>46190.60518608797</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>217</v>
@@ -6089,9 +6095,11 @@
       <c r="B69" s="8">
         <v>46168.688608275465</v>
       </c>
-      <c r="C69" s="9"/>
+      <c r="C69" s="8">
+        <v>46190.60519341435</v>
+      </c>
       <c r="D69" s="8">
-        <v>46185.17135047454</v>
+        <v>46190.60519502315</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>217</v>
@@ -6142,9 +6150,11 @@
       <c r="B70" s="5">
         <v>46168.68864659722</v>
       </c>
-      <c r="C70" s="6"/>
+      <c r="C70" s="5">
+        <v>46190.60520133102</v>
+      </c>
       <c r="D70" s="5">
-        <v>46185.171351701385</v>
+        <v>46190.605203761574</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>221</v>
@@ -6195,9 +6205,11 @@
       <c r="B71" s="8">
         <v>46168.68868637731</v>
       </c>
-      <c r="C71" s="9"/>
+      <c r="C71" s="8">
+        <v>46190.60520737269</v>
+      </c>
       <c r="D71" s="8">
-        <v>46185.171352986115</v>
+        <v>46190.605208946756</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>221</v>
@@ -6248,9 +6260,11 @@
       <c r="B72" s="5">
         <v>46168.68871934028</v>
       </c>
-      <c r="C72" s="6"/>
+      <c r="C72" s="5">
+        <v>46190.60521491898</v>
+      </c>
       <c r="D72" s="5">
-        <v>46185.17135421296</v>
+        <v>46190.60521709491</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>225</v>
@@ -6301,9 +6315,11 @@
       <c r="B73" s="8">
         <v>46168.68345790509</v>
       </c>
-      <c r="C73" s="9"/>
+      <c r="C73" s="8">
+        <v>46190.60541208333</v>
+      </c>
       <c r="D73" s="8">
-        <v>46189.20161289352</v>
+        <v>46190.6054244213</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>108</v>
@@ -6351,10 +6367,10 @@
         <v>140</v>
       </c>
       <c r="T73" s="9">
-        <v>0</v>
-      </c>
-      <c r="U73" s="12" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U73" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
@@ -6364,9 +6380,11 @@
       <c r="B74" s="5">
         <v>46168.68880178241</v>
       </c>
-      <c r="C74" s="6"/>
+      <c r="C74" s="5">
+        <v>46190.605361643524</v>
+      </c>
       <c r="D74" s="5">
-        <v>46188.1714565625</v>
+        <v>46190.60536361111</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>217</v>
@@ -6417,9 +6435,11 @@
       <c r="B75" s="8">
         <v>46168.68883857639</v>
       </c>
-      <c r="C75" s="9"/>
+      <c r="C75" s="8">
+        <v>46190.60536678241</v>
+      </c>
       <c r="D75" s="8">
-        <v>46188.17145818287</v>
+        <v>46190.605368206016</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>217</v>
@@ -6470,9 +6490,11 @@
       <c r="B76" s="5">
         <v>46168.688875775464</v>
       </c>
-      <c r="C76" s="6"/>
+      <c r="C76" s="5">
+        <v>46190.605371956015</v>
+      </c>
       <c r="D76" s="5">
-        <v>46188.171459652775</v>
+        <v>46190.605373530096</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>221</v>
@@ -6523,9 +6545,11 @@
       <c r="B77" s="8">
         <v>46168.6889172338</v>
       </c>
-      <c r="C77" s="9"/>
+      <c r="C77" s="8">
+        <v>46190.60539791667</v>
+      </c>
       <c r="D77" s="8">
-        <v>46188.171461412036</v>
+        <v>46190.60539957176</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>248</v>
@@ -6576,9 +6600,11 @@
       <c r="B78" s="5">
         <v>46168.688956620375</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46190.60538663194</v>
+      </c>
       <c r="D78" s="5">
-        <v>46188.17146267361</v>
+        <v>46190.60538814815</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>225</v>
@@ -7820,7 +7846,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46168.865656180555</v>
+        <v>46190.60542900463</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>217</v>
@@ -7873,7 +7899,7 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46168.86565287037</v>
+        <v>46190.605429560186</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>217</v>
@@ -8148,7 +8174,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46168.86585069445</v>
+        <v>46190.60544303241</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>217</v>
@@ -8201,7 +8227,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46168.86584780093</v>
+        <v>46190.60543011574</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>322</v>
@@ -9211,7 +9237,7 @@
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46168.86712002315</v>
+        <v>46190.60544122686</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>217</v>
@@ -9264,7 +9290,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46168.867116608795</v>
+        <v>46190.60544332176</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>217</v>
@@ -9317,7 +9343,7 @@
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46168.86711407408</v>
+        <v>46190.60543283565</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>221</v>
@@ -9370,7 +9396,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46168.86711136574</v>
+        <v>46190.605433379635</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>221</v>
@@ -9423,7 +9449,7 @@
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46168.86710778935</v>
+        <v>46190.605440740736</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>225</v>
@@ -9539,7 +9565,7 @@
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46168.867260949075</v>
+        <v>46190.60543055556</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>217</v>
@@ -9592,7 +9618,7 @@
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46168.86725782407</v>
+        <v>46190.60543111111</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>217</v>
@@ -9645,7 +9671,7 @@
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46168.86725487269</v>
+        <v>46190.605433923614</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>221</v>
@@ -9698,7 +9724,7 @@
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46168.86725222222</v>
+        <v>46190.605443622684</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>221</v>
@@ -9751,7 +9777,7 @@
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46168.86724799768</v>
+        <v>46190.605442071756</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>225</v>
@@ -9867,7 +9893,7 @@
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46168.867473715276</v>
+        <v>46190.60543435185</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>217</v>
@@ -9920,7 +9946,7 @@
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46168.86747049769</v>
+        <v>46190.605431805554</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>217</v>
@@ -9973,7 +9999,7 @@
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46168.86746778935</v>
+        <v>46190.60543226852</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>221</v>
@@ -10026,7 +10052,7 @@
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46168.86746483797</v>
+        <v>46190.605434826386</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>221</v>
@@ -10079,7 +10105,7 @@
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46168.86746091435</v>
+        <v>46190.605442569446</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>225</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -381,124 +381,124 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser ot 4335 - 4337 -4339</t>
   </si>
   <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>1215141533737633</t>
+  </si>
+  <si>
+    <t>Propuesta Corte plasma  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141533737645</t>
+  </si>
+  <si>
+    <t>Propuesta Mecanizad ot 4335 - 4337 -4339o</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402280771</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Generacion OC Fabricación Externa ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402280783</t>
+  </si>
+  <si>
+    <t>Propuesta Tableros  ot 4336 - 4338 -4341</t>
+  </si>
+  <si>
+    <t>Generación OC   ot 4336 - 4338 -4341</t>
+  </si>
+  <si>
+    <t>1215139673478165</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>rodete ot 4335 - 4337 -4339,Alabe ot 4335 - 4337 -4339,Materiales corte Laser ot 4335 - 4337 -4339,Motor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402213042</t>
+  </si>
+  <si>
+    <t>Alabe ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe ot 4335 - 4337 -4339,Generación OC Alabe ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402333247</t>
+  </si>
+  <si>
+    <t>Generación OC Alabe ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe ot 4335 - 4337 -4339,Alabe ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402333267</t>
+  </si>
+  <si>
+    <t>Fabricación Alabe ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Alabe ot 4335 - 4337 -4339,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215141318211252</t>
+  </si>
+  <si>
+    <t>rodete ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4335 - 4337 -4339,Fabricación Rodete ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141318211269</t>
+  </si>
+  <si>
+    <t>Generación OC Rodete ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>rodete ot 4335 - 4337 -4339,Fabricación Rodete ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141533850688</t>
+  </si>
+  <si>
+    <t>Fabricación Rodete ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>rodete ot 4335 - 4337 -4339,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215141566531440</t>
+  </si>
+  <si>
+    <t>Motor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Generación OC motor ot 4335 - 4337 -4339,Fabricación motor ot 4335 - 4337 -4339,Planos motor proveedor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141533737633</t>
-  </si>
-  <si>
-    <t>Propuesta Corte plasma  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141533737645</t>
-  </si>
-  <si>
-    <t>Propuesta Mecanizad ot 4335 - 4337 -4339o</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402280771</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Generacion OC Fabricación Externa ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402280783</t>
-  </si>
-  <si>
-    <t>Propuesta Tableros  ot 4336 - 4338 -4341</t>
-  </si>
-  <si>
-    <t>Generación OC   ot 4336 - 4338 -4341</t>
-  </si>
-  <si>
-    <t>1215139673478165</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>rodete ot 4335 - 4337 -4339,Alabe ot 4335 - 4337 -4339,Materiales corte Laser ot 4335 - 4337 -4339,Motor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402213042</t>
-  </si>
-  <si>
-    <t>Alabe ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe ot 4335 - 4337 -4339,Generación OC Alabe ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402333247</t>
-  </si>
-  <si>
-    <t>Generación OC Alabe ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe ot 4335 - 4337 -4339,Alabe ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402333267</t>
-  </si>
-  <si>
-    <t>Fabricación Alabe ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Alabe ot 4335 - 4337 -4339,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215141318211252</t>
-  </si>
-  <si>
-    <t>rodete ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4335 - 4337 -4339,Fabricación Rodete ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>1215141318211269</t>
-  </si>
-  <si>
-    <t>Generación OC Rodete ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>rodete ot 4335 - 4337 -4339,Fabricación Rodete ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141533850688</t>
-  </si>
-  <si>
-    <t>Fabricación Rodete ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>rodete ot 4335 - 4337 -4339,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215141566531440</t>
-  </si>
-  <si>
-    <t>Motor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Generación OC motor ot 4335 - 4337 -4339,Fabricación motor ot 4335 - 4337 -4339,Planos motor proveedor ot 4335 - 4337 -4339</t>
   </si>
   <si>
     <t>1215141566531457</t>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46190.605452488424</v>
+        <v>46191.16899662037</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3750,7 +3750,7 @@
       <c r="R28" s="5">
         <v>46190</v>
       </c>
-      <c r="S28" s="11" t="s">
+      <c r="S28" s="12" t="s">
         <v>110</v>
       </c>
       <c r="T28" s="6">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46190.60545243055</v>
+        <v>46191.16899663194</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3813,7 +3813,7 @@
       <c r="R29" s="8">
         <v>46190</v>
       </c>
-      <c r="S29" s="11" t="s">
+      <c r="S29" s="12" t="s">
         <v>110</v>
       </c>
       <c r="T29" s="9">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46190.60545216435</v>
+        <v>46191.16899667824</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3876,7 +3876,7 @@
       <c r="R30" s="5">
         <v>46190</v>
       </c>
-      <c r="S30" s="11" t="s">
+      <c r="S30" s="12" t="s">
         <v>110</v>
       </c>
       <c r="T30" s="6">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46190.60545229167</v>
+        <v>46191.16899697916</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3939,7 +3939,7 @@
       <c r="R31" s="8">
         <v>46190</v>
       </c>
-      <c r="S31" s="11" t="s">
+      <c r="S31" s="12" t="s">
         <v>110</v>
       </c>
       <c r="T31" s="9">
@@ -4296,7 +4296,7 @@
         <v>46184</v>
       </c>
       <c r="S37" s="12" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="T37" s="9">
         <v>1</v>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46168.68329584491</v>
@@ -4319,7 +4319,7 @@
         <v>46184.70350368056</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -4352,7 +4352,7 @@
         <v>101</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4368,7 +4368,7 @@
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46168.68330070602</v>
@@ -4380,7 +4380,7 @@
         <v>46184.703557789355</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
@@ -4410,10 +4410,10 @@
         <v>138</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="Q39" s="9"/>
       <c r="R39" s="9"/>
@@ -4429,17 +4429,17 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46168.68330542824</v>
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46185.52480443287</v>
+        <v>46191.178832627316</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4469,7 +4469,7 @@
         <v>124</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>124</v>
@@ -4480,8 +4480,8 @@
       <c r="R40" s="5">
         <v>46198</v>
       </c>
-      <c r="S40" s="10" t="s">
-        <v>32</v>
+      <c r="S40" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
@@ -4529,7 +4529,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O41" s="9" t="s">
         <v>95</v>
@@ -4588,7 +4588,7 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>151</v>
@@ -4649,7 +4649,7 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>151</v>
@@ -5684,7 +5684,7 @@
         <v>46171</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="T61" s="9">
         <v>1</v>
@@ -6024,7 +6024,7 @@
         <v>46185</v>
       </c>
       <c r="S67" s="12" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="T67" s="9">
         <v>1</v>
@@ -6364,7 +6364,7 @@
         <v>46188</v>
       </c>
       <c r="S73" s="12" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="T73" s="9">
         <v>1</v>
@@ -8519,7 +8519,7 @@
         <v>262</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>333</v>
@@ -8531,7 +8531,7 @@
         <v>46185</v>
       </c>
       <c r="S112" s="12" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
@@ -8592,7 +8592,7 @@
         <v>46168</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="T113" s="9">
         <v>0</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -4910,7 +4910,7 @@
       </c>
       <c r="C48" s="6"/>
       <c r="D48" s="5">
-        <v>46169.88093034722</v>
+        <v>46192.17523146991</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>173</v>
@@ -5091,7 +5091,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46169.8808849537</v>
+        <v>46192.17524251157</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>113</v>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46169.88077131944</v>
+        <v>46192.17521509259</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>
@@ -8610,7 +8610,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46168.866016134256</v>
+        <v>46192.18714875</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>338</v>
@@ -8654,8 +8654,8 @@
       <c r="R114" s="5">
         <v>46199</v>
       </c>
-      <c r="S114" s="10" t="s">
-        <v>32</v>
+      <c r="S114" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -7408,7 +7408,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46168.86568018519</v>
+        <v>46192.63406376158</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>284</v>
@@ -7453,9 +7453,11 @@
       <c r="B93" s="8">
         <v>46168.68355052083</v>
       </c>
-      <c r="C93" s="9"/>
+      <c r="C93" s="8">
+        <v>46192.63405665509</v>
+      </c>
       <c r="D93" s="8">
-        <v>46168.86552388889</v>
+        <v>46192.63407395833</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>287</v>
@@ -7503,10 +7505,10 @@
         <v>32</v>
       </c>
       <c r="T93" s="9">
-        <v>0</v>
-      </c>
-      <c r="U93" s="12" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U93" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="50001557 - ATACAMA KOZAN OT  43" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="50001557 - ATACAMA KOZAN" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -13,7 +13,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2404" uniqueCount="543">
   <si>
-    <t>50001557 - ATACAMA KOZAN OT  4335 - 4337 -4339</t>
+    <t>50001557 - ATACAMA KOZAN</t>
   </si>
   <si>
     <t xml:space="preserve">Powered by </t>
@@ -207,9 +207,6 @@
     <t xml:space="preserve">Propuesta Tableros  ot 4336 - 4338 -4341,Ingenieria Servicios </t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1215141566425238</t>
   </si>
   <si>
@@ -322,6 +319,9 @@
   </si>
   <si>
     <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215139673478163</t>
@@ -1746,12 +1746,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46168.86029898148</v>
+        <v>46193.55318365741</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2717,9 +2717,11 @@
       <c r="B11" s="8">
         <v>46168.683142650465</v>
       </c>
-      <c r="C11" s="9"/>
+      <c r="C11" s="8">
+        <v>46193.553165543985</v>
+      </c>
       <c r="D11" s="8">
-        <v>46175.87166482639</v>
+        <v>46193.553190729166</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2767,34 +2769,34 @@
         <v>32</v>
       </c>
       <c r="T11" s="9">
-        <v>0</v>
-      </c>
-      <c r="U11" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U11" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="5">
         <v>46168.683148310185</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46168.86288356481</v>
+        <v>46193.55337256944</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I12" s="5">
         <v>46223</v>
@@ -2815,10 +2817,10 @@
         <v>47</v>
       </c>
       <c r="O12" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>60</v>
       </c>
       <c r="Q12" s="5">
         <v>46223</v>
@@ -2832,13 +2834,13 @@
       <c r="T12" s="6">
         <v>0</v>
       </c>
-      <c r="U12" s="12" t="s">
-        <v>61</v>
+      <c r="U12" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B13" s="8">
         <v>46168.68315351852</v>
@@ -2848,16 +2850,16 @@
         <v>46168.862857245374</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="I13" s="8">
         <v>46223</v>
@@ -2875,13 +2877,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2891,7 +2893,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" s="5">
         <v>46168.68315625</v>
@@ -2901,16 +2903,16 @@
         <v>46168.86285416667</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H14" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I14" s="5">
         <v>46223</v>
@@ -2928,13 +2930,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2944,7 +2946,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8">
         <v>46168.68315891204</v>
@@ -2954,16 +2956,16 @@
         <v>46168.86285119213</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="H15" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="I15" s="8">
         <v>46223</v>
@@ -2981,13 +2983,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -2997,7 +2999,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B16" s="5">
         <v>46168.683161493056</v>
@@ -3007,16 +3009,16 @@
         <v>46168.86284840278</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I16" s="5">
         <v>46223</v>
@@ -3034,13 +3036,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -3050,7 +3052,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B17" s="8">
         <v>46168.68316400463</v>
@@ -3060,16 +3062,16 @@
         <v>46168.862845173615</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="I17" s="8">
         <v>46223</v>
@@ -3087,13 +3089,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -3103,7 +3105,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B18" s="5">
         <v>46168.68316714121</v>
@@ -3113,16 +3115,16 @@
         <v>46168.86284090277</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="I18" s="5">
         <v>46223</v>
@@ -3140,13 +3142,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -3156,7 +3158,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B19" s="8">
         <v>46168.682984189814</v>
@@ -3166,7 +3168,7 @@
         <v>46183.871414270834</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>25</v>
@@ -3190,7 +3192,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P19" s="9" t="s">
         <v>26</v>
@@ -3203,7 +3205,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="5">
         <v>46168.68317581018</v>
@@ -3215,16 +3217,16 @@
         <v>46183.87139523149</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I20" s="5">
         <v>46155</v>
@@ -3236,19 +3238,19 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q20" s="5">
         <v>46155</v>
@@ -3268,7 +3270,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" s="8">
         <v>46168.6831808912</v>
@@ -3280,16 +3282,16 @@
         <v>46183.871400648146</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="I21" s="8">
         <v>46155</v>
@@ -3301,19 +3303,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="Q21" s="8">
         <v>46155</v>
@@ -3333,7 +3335,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B22" s="5">
         <v>46168.68318591436</v>
@@ -3345,16 +3347,16 @@
         <v>46183.871410775464</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I22" s="5">
         <v>46155</v>
@@ -3372,13 +3374,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="Q22" s="5">
         <v>46155</v>
@@ -3398,7 +3400,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="8">
         <v>46168.68319116898</v>
@@ -3408,16 +3410,16 @@
         <v>46183.871421041666</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G23" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="H23" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="I23" s="8">
         <v>46155</v>
@@ -3435,13 +3437,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O23" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="P23" s="9" t="s">
         <v>89</v>
-      </c>
-      <c r="P23" s="9" t="s">
-        <v>90</v>
       </c>
       <c r="Q23" s="8">
         <v>46155</v>
@@ -3455,8 +3457,8 @@
       <c r="T23" s="9">
         <v>0</v>
       </c>
-      <c r="U23" s="11" t="s">
-        <v>54</v>
+      <c r="U23" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
@@ -3468,7 +3470,7 @@
       </c>
       <c r="C24" s="6"/>
       <c r="D24" s="5">
-        <v>46183.90441173611</v>
+        <v>46193.55308</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3513,9 +3515,11 @@
       <c r="B25" s="8">
         <v>46168.68319888889</v>
       </c>
-      <c r="C25" s="9"/>
+      <c r="C25" s="8">
+        <v>46193.553062349536</v>
+      </c>
       <c r="D25" s="8">
-        <v>46185.717823541665</v>
+        <v>46193.5530831713</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3524,10 +3528,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="I25" s="8">
         <v>46157</v>
@@ -3548,7 +3552,7 @@
         <v>92</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P25" s="9" t="s">
         <v>96</v>
@@ -3563,10 +3567,10 @@
         <v>32</v>
       </c>
       <c r="T25" s="9">
-        <v>0</v>
-      </c>
-      <c r="U25" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U25" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
@@ -3576,9 +3580,11 @@
       <c r="B26" s="5">
         <v>46168.68320439815</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="5">
+        <v>46193.55307400463</v>
+      </c>
       <c r="D26" s="5">
-        <v>46183.871409837964</v>
+        <v>46193.55308946759</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3587,10 +3593,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H26" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3611,7 +3617,7 @@
         <v>92</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>99</v>
@@ -3626,10 +3632,10 @@
         <v>32</v>
       </c>
       <c r="T26" s="6">
-        <v>0</v>
-      </c>
-      <c r="U26" s="11" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="U26" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
@@ -3676,7 +3682,7 @@
         <v>92</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="P27" s="9" t="s">
         <v>103</v>
@@ -3750,14 +3756,14 @@
       <c r="R28" s="5">
         <v>46190</v>
       </c>
-      <c r="S28" s="12" t="s">
+      <c r="S28" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T28" s="6">
         <v>0</v>
       </c>
-      <c r="U28" s="11" t="s">
-        <v>54</v>
+      <c r="U28" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
@@ -3813,14 +3819,14 @@
       <c r="R29" s="8">
         <v>46190</v>
       </c>
-      <c r="S29" s="12" t="s">
+      <c r="S29" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T29" s="9">
         <v>0</v>
       </c>
-      <c r="U29" s="11" t="s">
-        <v>54</v>
+      <c r="U29" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3876,14 +3882,14 @@
       <c r="R30" s="5">
         <v>46190</v>
       </c>
-      <c r="S30" s="12" t="s">
+      <c r="S30" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T30" s="6">
         <v>0</v>
       </c>
-      <c r="U30" s="11" t="s">
-        <v>54</v>
+      <c r="U30" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3939,14 +3945,14 @@
       <c r="R31" s="8">
         <v>46190</v>
       </c>
-      <c r="S31" s="12" t="s">
+      <c r="S31" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T31" s="9">
         <v>0</v>
       </c>
-      <c r="U31" s="11" t="s">
-        <v>54</v>
+      <c r="U31" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -3956,9 +3962,11 @@
       <c r="B32" s="5">
         <v>46168.683231365736</v>
       </c>
-      <c r="C32" s="6"/>
+      <c r="C32" s="5">
+        <v>46193.55346230324</v>
+      </c>
       <c r="D32" s="5">
-        <v>46169.88147334491</v>
+        <v>46193.553499305555</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3967,10 +3975,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" s="6" t="s">
         <v>76</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>77</v>
       </c>
       <c r="I32" s="5">
         <v>46157</v>
@@ -4006,10 +4014,10 @@
         <v>32</v>
       </c>
       <c r="T32" s="6">
-        <v>0</v>
-      </c>
-      <c r="U32" s="12" t="s">
-        <v>61</v>
+        <v>1</v>
+      </c>
+      <c r="U32" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
@@ -4118,8 +4126,8 @@
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="12" t="s">
-        <v>61</v>
+      <c r="U34" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4131,7 +4139,7 @@
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="8">
-        <v>46169.88109163195</v>
+        <v>46193.55308153935</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -4177,8 +4185,8 @@
       <c r="T35" s="9">
         <v>0</v>
       </c>
-      <c r="U35" s="12" t="s">
-        <v>61</v>
+      <c r="U35" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
@@ -4236,8 +4244,8 @@
       <c r="T36" s="6">
         <v>0</v>
       </c>
-      <c r="U36" s="12" t="s">
-        <v>61</v>
+      <c r="U36" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
@@ -4295,7 +4303,7 @@
       <c r="R37" s="8">
         <v>46184</v>
       </c>
-      <c r="S37" s="12" t="s">
+      <c r="S37" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T37" s="9">
@@ -4362,8 +4370,8 @@
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="12" t="s">
-        <v>61</v>
+      <c r="U38" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
@@ -4423,8 +4431,8 @@
       <c r="T39" s="9">
         <v>0</v>
       </c>
-      <c r="U39" s="12" t="s">
-        <v>61</v>
+      <c r="U39" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4480,14 +4488,14 @@
       <c r="R40" s="5">
         <v>46198</v>
       </c>
-      <c r="S40" s="11" t="s">
+      <c r="S40" s="12" t="s">
         <v>149</v>
       </c>
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="12" t="s">
-        <v>61</v>
+      <c r="U40" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -4499,7 +4507,7 @@
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46169.88097810185</v>
+        <v>46193.55307162037</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4545,8 +4553,8 @@
       <c r="T41" s="9">
         <v>0</v>
       </c>
-      <c r="U41" s="12" t="s">
-        <v>61</v>
+      <c r="U41" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -4604,8 +4612,8 @@
       <c r="T42" s="6">
         <v>0</v>
       </c>
-      <c r="U42" s="12" t="s">
-        <v>61</v>
+      <c r="U42" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -4665,8 +4673,8 @@
       <c r="T43" s="9">
         <v>0</v>
       </c>
-      <c r="U43" s="12" t="s">
-        <v>61</v>
+      <c r="U43" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -4728,8 +4736,8 @@
       <c r="T44" s="6">
         <v>0</v>
       </c>
-      <c r="U44" s="12" t="s">
-        <v>61</v>
+      <c r="U44" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4741,7 +4749,7 @@
       </c>
       <c r="C45" s="9"/>
       <c r="D45" s="8">
-        <v>46170.172512986115</v>
+        <v>46193.55348179398</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>122</v>
@@ -4897,8 +4905,8 @@
       <c r="T47" s="9">
         <v>0</v>
       </c>
-      <c r="U47" s="12" t="s">
-        <v>61</v>
+      <c r="U47" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -4956,8 +4964,8 @@
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="12" t="s">
-        <v>61</v>
+      <c r="U48" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -5015,8 +5023,8 @@
       <c r="T49" s="9">
         <v>0</v>
       </c>
-      <c r="U49" s="12" t="s">
-        <v>61</v>
+      <c r="U49" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -5078,8 +5086,8 @@
       <c r="T50" s="6">
         <v>0</v>
       </c>
-      <c r="U50" s="12" t="s">
-        <v>61</v>
+      <c r="U50" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
@@ -5247,8 +5255,8 @@
       <c r="T53" s="9">
         <v>0</v>
       </c>
-      <c r="U53" s="12" t="s">
-        <v>61</v>
+      <c r="U53" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
@@ -5469,8 +5477,8 @@
       <c r="T57" s="9">
         <v>0</v>
       </c>
-      <c r="U57" s="12" t="s">
-        <v>61</v>
+      <c r="U57" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
@@ -5624,8 +5632,8 @@
       <c r="R60" s="6"/>
       <c r="S60" s="6"/>
       <c r="T60" s="6"/>
-      <c r="U60" s="11" t="s">
-        <v>54</v>
+      <c r="U60" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
@@ -5683,7 +5691,7 @@
       <c r="R61" s="8">
         <v>46171</v>
       </c>
-      <c r="S61" s="12" t="s">
+      <c r="S61" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T61" s="9">
@@ -5737,7 +5745,7 @@
         <v>212</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>218</v>
@@ -5792,7 +5800,7 @@
         <v>212</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>218</v>
@@ -5847,7 +5855,7 @@
         <v>212</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>222</v>
@@ -5902,7 +5910,7 @@
         <v>212</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>222</v>
@@ -5957,7 +5965,7 @@
         <v>212</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>226</v>
@@ -6023,7 +6031,7 @@
       <c r="R67" s="8">
         <v>46185</v>
       </c>
-      <c r="S67" s="12" t="s">
+      <c r="S67" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T67" s="9">
@@ -6363,7 +6371,7 @@
       <c r="R73" s="8">
         <v>46188</v>
       </c>
-      <c r="S73" s="12" t="s">
+      <c r="S73" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T73" s="9">
@@ -6705,8 +6713,8 @@
       <c r="T79" s="9">
         <v>0</v>
       </c>
-      <c r="U79" s="12" t="s">
-        <v>61</v>
+      <c r="U79" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
@@ -7080,8 +7088,8 @@
       <c r="T86" s="6">
         <v>0</v>
       </c>
-      <c r="U86" s="12" t="s">
-        <v>61</v>
+      <c r="U86" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -7143,8 +7151,8 @@
       <c r="T87" s="9">
         <v>0</v>
       </c>
-      <c r="U87" s="12" t="s">
-        <v>61</v>
+      <c r="U87" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -7206,8 +7214,8 @@
       <c r="T88" s="6">
         <v>0</v>
       </c>
-      <c r="U88" s="12" t="s">
-        <v>61</v>
+      <c r="U88" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7269,8 +7277,8 @@
       <c r="T89" s="9">
         <v>0</v>
       </c>
-      <c r="U89" s="12" t="s">
-        <v>61</v>
+      <c r="U89" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -7332,8 +7340,8 @@
       <c r="T90" s="6">
         <v>0</v>
       </c>
-      <c r="U90" s="12" t="s">
-        <v>61</v>
+      <c r="U90" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -7395,8 +7403,8 @@
       <c r="T91" s="9">
         <v>0</v>
       </c>
-      <c r="U91" s="12" t="s">
-        <v>61</v>
+      <c r="U91" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7835,8 +7843,8 @@
       <c r="T99" s="9">
         <v>0</v>
       </c>
-      <c r="U99" s="12" t="s">
-        <v>61</v>
+      <c r="U99" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
@@ -8163,8 +8171,8 @@
       <c r="T105" s="9">
         <v>0</v>
       </c>
-      <c r="U105" s="12" t="s">
-        <v>61</v>
+      <c r="U105" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
@@ -8532,14 +8540,14 @@
       <c r="R112" s="5">
         <v>46185</v>
       </c>
-      <c r="S112" s="12" t="s">
+      <c r="S112" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T112" s="6">
         <v>0</v>
       </c>
-      <c r="U112" s="11" t="s">
-        <v>54</v>
+      <c r="U112" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8593,14 +8601,14 @@
       <c r="R113" s="8">
         <v>46168</v>
       </c>
-      <c r="S113" s="12" t="s">
+      <c r="S113" s="11" t="s">
         <v>110</v>
       </c>
       <c r="T113" s="9">
         <v>0</v>
       </c>
-      <c r="U113" s="12" t="s">
-        <v>61</v>
+      <c r="U113" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
@@ -8656,14 +8664,14 @@
       <c r="R114" s="5">
         <v>46199</v>
       </c>
-      <c r="S114" s="11" t="s">
+      <c r="S114" s="12" t="s">
         <v>149</v>
       </c>
       <c r="T114" s="6">
         <v>0</v>
       </c>
-      <c r="U114" s="12" t="s">
-        <v>61</v>
+      <c r="U114" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8725,8 +8733,8 @@
       <c r="T115" s="9">
         <v>0</v>
       </c>
-      <c r="U115" s="12" t="s">
-        <v>61</v>
+      <c r="U115" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8741,7 +8749,7 @@
         <v>46168.86600888889</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8788,8 +8796,8 @@
       <c r="T116" s="6">
         <v>0</v>
       </c>
-      <c r="U116" s="12" t="s">
-        <v>61</v>
+      <c r="U116" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -8898,8 +8906,8 @@
       <c r="T118" s="6">
         <v>0</v>
       </c>
-      <c r="U118" s="12" t="s">
-        <v>61</v>
+      <c r="U118" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
@@ -9226,8 +9234,8 @@
       <c r="T124" s="6">
         <v>0</v>
       </c>
-      <c r="U124" s="12" t="s">
-        <v>61</v>
+      <c r="U124" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
@@ -9554,8 +9562,8 @@
       <c r="T130" s="6">
         <v>0</v>
       </c>
-      <c r="U130" s="12" t="s">
-        <v>61</v>
+      <c r="U130" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
@@ -9882,8 +9890,8 @@
       <c r="T136" s="6">
         <v>0</v>
       </c>
-      <c r="U136" s="12" t="s">
-        <v>61</v>
+      <c r="U136" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
@@ -10210,8 +10218,8 @@
       <c r="T142" s="6">
         <v>0</v>
       </c>
-      <c r="U142" s="12" t="s">
-        <v>61</v>
+      <c r="U142" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
@@ -10538,8 +10546,8 @@
       <c r="T148" s="6">
         <v>0</v>
       </c>
-      <c r="U148" s="12" t="s">
-        <v>61</v>
+      <c r="U148" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
@@ -10863,7 +10871,7 @@
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46168.868077673615</v>
+        <v>46193.55226163194</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>431</v>
@@ -10913,8 +10921,8 @@
       <c r="T155" s="9">
         <v>0</v>
       </c>
-      <c r="U155" s="12" t="s">
-        <v>61</v>
+      <c r="U155" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
@@ -11194,7 +11202,7 @@
         <v>46168.86803378472</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>26</v>
@@ -11224,7 +11232,7 @@
         <v>431</v>
       </c>
       <c r="O161" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P161" s="9" t="s">
         <v>444</v>
@@ -11247,7 +11255,7 @@
         <v>46168.86803016203</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11277,7 +11285,7 @@
         <v>431</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>444</v>
@@ -11300,7 +11308,7 @@
         <v>46168.86802731482</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
@@ -11330,7 +11338,7 @@
         <v>431</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P163" s="9" t="s">
         <v>444</v>
@@ -11353,7 +11361,7 @@
         <v>46168.86802450231</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11383,7 +11391,7 @@
         <v>431</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>448</v>
@@ -11406,7 +11414,7 @@
         <v>46168.86801774305</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
@@ -11436,7 +11444,7 @@
         <v>431</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P165" s="9" t="s">
         <v>448</v>
@@ -11459,7 +11467,7 @@
         <v>46168.868017141205</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11489,7 +11497,7 @@
         <v>431</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>451</v>
@@ -11509,7 +11517,7 @@
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46168.86827305556</v>
+        <v>46193.552515069445</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>453</v>
@@ -11557,8 +11565,8 @@
       <c r="T167" s="9">
         <v>0</v>
       </c>
-      <c r="U167" s="12" t="s">
-        <v>61</v>
+      <c r="U167" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
@@ -11828,7 +11836,7 @@
         <v>46168.86825175926</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
@@ -11856,7 +11864,7 @@
         <v>453</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P173" s="9" t="s">
         <v>464</v>
@@ -11879,7 +11887,7 @@
         <v>46168.86824866898</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -11907,7 +11915,7 @@
         <v>453</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>466</v>
@@ -11930,7 +11938,7 @@
         <v>46168.86824546296</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>26</v>
@@ -11958,7 +11966,7 @@
         <v>453</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P175" s="9" t="s">
         <v>464</v>
@@ -11981,7 +11989,7 @@
         <v>46168.86824251157</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -12009,7 +12017,7 @@
         <v>453</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>469</v>
@@ -12032,7 +12040,7 @@
         <v>46168.868235092596</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
@@ -12060,7 +12068,7 @@
         <v>453</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P177" s="9" t="s">
         <v>469</v>
@@ -12083,7 +12091,7 @@
         <v>46168.86823443287</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -12111,7 +12119,7 @@
         <v>453</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>472</v>
@@ -12179,8 +12187,8 @@
       <c r="T179" s="9">
         <v>0</v>
       </c>
-      <c r="U179" s="12" t="s">
-        <v>61</v>
+      <c r="U179" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
@@ -12460,7 +12468,7 @@
         <v>46168.86843181713</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
@@ -12490,7 +12498,7 @@
         <v>474</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P185" s="9" t="s">
         <v>487</v>
@@ -12543,7 +12551,7 @@
         <v>474</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>490</v>
@@ -12566,7 +12574,7 @@
         <v>46168.86842351852</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
@@ -12596,7 +12604,7 @@
         <v>474</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P187" s="9" t="s">
         <v>492</v>
@@ -12619,7 +12627,7 @@
         <v>46168.86842280092</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12649,7 +12657,7 @@
         <v>474</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>494</v>
@@ -12672,7 +12680,7 @@
         <v>46168.86842204861</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>26</v>
@@ -12702,7 +12710,7 @@
         <v>474</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P189" s="9" t="s">
         <v>496</v>
@@ -12725,7 +12733,7 @@
         <v>46168.86842112269</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -12755,7 +12763,7 @@
         <v>474</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P190" s="6" t="s">
         <v>498</v>
@@ -12825,8 +12833,8 @@
       <c r="T191" s="9">
         <v>0</v>
       </c>
-      <c r="U191" s="12" t="s">
-        <v>61</v>
+      <c r="U191" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
@@ -13124,7 +13132,7 @@
         <v>500</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P197" s="9" t="s">
         <v>500</v>
@@ -13226,7 +13234,7 @@
         <v>500</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P199" s="9" t="s">
         <v>500</v>
@@ -13277,7 +13285,7 @@
         <v>500</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>500</v>
@@ -13328,7 +13336,7 @@
         <v>500</v>
       </c>
       <c r="O201" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="P201" s="9" t="s">
         <v>500</v>
@@ -13379,7 +13387,7 @@
         <v>500</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>500</v>
@@ -13496,8 +13504,8 @@
       <c r="T204" s="6">
         <v>0</v>
       </c>
-      <c r="U204" s="12" t="s">
-        <v>61</v>
+      <c r="U204" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
@@ -13518,10 +13526,10 @@
         <v>26</v>
       </c>
       <c r="G205" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="H205" s="9" t="s">
         <v>76</v>
-      </c>
-      <c r="H205" s="9" t="s">
-        <v>77</v>
       </c>
       <c r="I205" s="8">
         <v>46246</v>
@@ -13559,8 +13567,8 @@
       <c r="T205" s="9">
         <v>0</v>
       </c>
-      <c r="U205" s="12" t="s">
-        <v>61</v>
+      <c r="U205" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
@@ -13612,8 +13620,8 @@
       <c r="T206" s="6">
         <v>0</v>
       </c>
-      <c r="U206" s="12" t="s">
-        <v>61</v>
+      <c r="U206" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
@@ -13675,8 +13683,8 @@
       <c r="T207" s="9">
         <v>0</v>
       </c>
-      <c r="U207" s="12" t="s">
-        <v>61</v>
+      <c r="U207" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="208" spans="1:21" x14ac:dyDescent="0.25">
@@ -13738,8 +13746,8 @@
       <c r="T208" s="6">
         <v>0</v>
       </c>
-      <c r="U208" s="12" t="s">
-        <v>61</v>
+      <c r="U208" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -2784,7 +2784,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46193.55337256944</v>
+        <v>46195.55805550926</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -10871,7 +10871,7 @@
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46193.55226163194</v>
+        <v>46195.56582541666</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>431</v>
@@ -11517,7 +11517,7 @@
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46193.552515069445</v>
+        <v>46195.55227060185</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>453</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -4029,7 +4029,7 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="8">
-        <v>46184.70363229167</v>
+        <v>46195.928393263894</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -4074,9 +4074,11 @@
       <c r="B34" s="5">
         <v>46168.68327652778</v>
       </c>
-      <c r="C34" s="6"/>
+      <c r="C34" s="5">
+        <v>46195.928382708335</v>
+      </c>
       <c r="D34" s="5">
-        <v>46169.88056621527</v>
+        <v>46195.928396574076</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -4124,10 +4126,10 @@
         <v>32</v>
       </c>
       <c r="T34" s="6">
-        <v>0</v>
-      </c>
-      <c r="U34" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U34" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
@@ -4137,9 +4139,11 @@
       <c r="B35" s="8">
         <v>46168.68328149305</v>
       </c>
-      <c r="C35" s="9"/>
+      <c r="C35" s="8">
+        <v>46195.92582877315</v>
+      </c>
       <c r="D35" s="8">
-        <v>46193.55308153935</v>
+        <v>46195.9258303588</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>132</v>
@@ -4196,9 +4200,11 @@
       <c r="B36" s="5">
         <v>46168.68328653935</v>
       </c>
-      <c r="C36" s="6"/>
+      <c r="C36" s="5">
+        <v>46195.92836857639</v>
+      </c>
       <c r="D36" s="5">
-        <v>46169.88113126157</v>
+        <v>46195.928370243055</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>135</v>
@@ -4444,7 +4450,7 @@
       </c>
       <c r="C40" s="6"/>
       <c r="D40" s="5">
-        <v>46191.178832627316</v>
+        <v>46195.925876678244</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>147</v>
@@ -4505,9 +4511,11 @@
       <c r="B41" s="8">
         <v>46168.683310092594</v>
       </c>
-      <c r="C41" s="9"/>
+      <c r="C41" s="8">
+        <v>46195.92586883102</v>
+      </c>
       <c r="D41" s="8">
-        <v>46193.55307162037</v>
+        <v>46195.92587128472</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4566,7 +4574,7 @@
       </c>
       <c r="C42" s="6"/>
       <c r="D42" s="5">
-        <v>46169.88099443287</v>
+        <v>46195.925877835645</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4627,7 +4635,7 @@
         <v>46184.70284971065</v>
       </c>
       <c r="D43" s="8">
-        <v>46184.70285173611</v>
+        <v>46195.92587850694</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4684,9 +4692,11 @@
       <c r="B44" s="5">
         <v>46168.68332520833</v>
       </c>
-      <c r="C44" s="6"/>
+      <c r="C44" s="5">
+        <v>46195.92858413194</v>
+      </c>
       <c r="D44" s="5">
-        <v>46169.88151422454</v>
+        <v>46195.92859513889</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4734,10 +4744,10 @@
         <v>32</v>
       </c>
       <c r="T44" s="6">
-        <v>0</v>
-      </c>
-      <c r="U44" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U44" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -4747,9 +4757,11 @@
       <c r="B45" s="8">
         <v>46168.68332880787</v>
       </c>
-      <c r="C45" s="9"/>
+      <c r="C45" s="8">
+        <v>46195.92577711806</v>
+      </c>
       <c r="D45" s="8">
-        <v>46193.55348179398</v>
+        <v>46195.92577891204</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>122</v>
@@ -4800,9 +4812,11 @@
       <c r="B46" s="5">
         <v>46168.683333113426</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46195.92856840278</v>
+      </c>
       <c r="D46" s="5">
-        <v>46169.88156962963</v>
+        <v>46195.92857017361</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>165</v>
@@ -4855,7 +4869,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46169.88069109953</v>
+        <v>46196.18789538194</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>168</v>
@@ -4899,8 +4913,8 @@
       <c r="R47" s="8">
         <v>46203</v>
       </c>
-      <c r="S47" s="10" t="s">
-        <v>32</v>
+      <c r="S47" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -5036,7 +5050,7 @@
       </c>
       <c r="C50" s="6"/>
       <c r="D50" s="5">
-        <v>46169.880704131945</v>
+        <v>46196.18789538194</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>179</v>
@@ -5080,8 +5094,8 @@
       <c r="R50" s="5">
         <v>46203</v>
       </c>
-      <c r="S50" s="10" t="s">
-        <v>32</v>
+      <c r="S50" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -5427,7 +5441,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46169.8807280787</v>
+        <v>46196.187896284726</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5471,8 +5485,8 @@
       <c r="R57" s="8">
         <v>46203</v>
       </c>
-      <c r="S57" s="10" t="s">
-        <v>32</v>
+      <c r="S57" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="T57" s="9">
         <v>0</v>
@@ -8559,7 +8573,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46169.1669387037</v>
+        <v>46195.928386898144</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>335</v>
@@ -8607,8 +8621,8 @@
       <c r="T113" s="9">
         <v>0</v>
       </c>
-      <c r="U113" s="11" t="s">
-        <v>60</v>
+      <c r="U113" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
@@ -8746,7 +8760,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46168.86600888889</v>
+        <v>46195.92858807871</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>58</v>
@@ -8796,8 +8810,8 @@
       <c r="T116" s="6">
         <v>0</v>
       </c>
-      <c r="U116" s="11" t="s">
-        <v>60</v>
+      <c r="U116" s="12" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -3773,9 +3773,11 @@
       <c r="B29" s="8">
         <v>46168.68321959491</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="8">
+        <v>46196.646673379626</v>
+      </c>
       <c r="D29" s="8">
-        <v>46191.16899663194</v>
+        <v>46196.64668813658</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3823,10 +3825,10 @@
         <v>110</v>
       </c>
       <c r="T29" s="9">
-        <v>0</v>
-      </c>
-      <c r="U29" s="12" t="s">
-        <v>90</v>
+        <v>1</v>
+      </c>
+      <c r="U29" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
@@ -3836,9 +3838,11 @@
       <c r="B30" s="5">
         <v>46168.68322341435</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46196.6474043287</v>
+      </c>
       <c r="D30" s="5">
-        <v>46191.16899667824</v>
+        <v>46196.647418912034</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3886,10 +3890,10 @@
         <v>110</v>
       </c>
       <c r="T30" s="6">
-        <v>0</v>
-      </c>
-      <c r="U30" s="12" t="s">
-        <v>90</v>
+        <v>1</v>
+      </c>
+      <c r="U30" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
@@ -3899,9 +3903,11 @@
       <c r="B31" s="8">
         <v>46168.683227245376</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="8">
+        <v>46196.64760480324</v>
+      </c>
       <c r="D31" s="8">
-        <v>46191.16899697916</v>
+        <v>46196.64801533565</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3949,10 +3955,10 @@
         <v>110</v>
       </c>
       <c r="T31" s="9">
-        <v>0</v>
-      </c>
-      <c r="U31" s="12" t="s">
-        <v>90</v>
+        <v>1</v>
+      </c>
+      <c r="U31" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -5113,7 +5119,7 @@
       </c>
       <c r="C51" s="9"/>
       <c r="D51" s="8">
-        <v>46192.17524251157</v>
+        <v>46196.64667890046</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>113</v>
@@ -5282,7 +5288,7 @@
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.880817384255</v>
+        <v>46196.64761290509</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>119</v>
@@ -5504,7 +5510,7 @@
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46192.17521509259</v>
+        <v>46196.64740983796</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>116</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -219,7 +219,7 @@
     <t>sergio.saavedra@zitron.com</t>
   </si>
   <si>
-    <t>Recepcion Tableros</t>
+    <t xml:space="preserve">Recepcion Tableros ot 4336 - 4338 -4341 </t>
   </si>
   <si>
     <t>Ingenieria Servicios ,Coordinacion Entrega con Cliente</t>
@@ -549,7 +549,7 @@
     <t>fabricación tableros   ot 4336 - 4338 -4341</t>
   </si>
   <si>
-    <t>Tableros  ot 4336 - 4338 -4341 ,Recepcion Tableros</t>
+    <t xml:space="preserve">Tableros  ot 4336 - 4338 -4341 ,Recepcion Tableros ot 4336 - 4338 -4341 </t>
   </si>
   <si>
     <t>1215141533879267</t>
@@ -8766,7 +8766,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46195.92858807871</v>
+        <v>46196.80794189815</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>58</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -909,7 +909,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4232 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215141566712673</t>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -8820,7 +8820,7 @@
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46168.86616204861</v>
+        <v>46197.49658452546</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>345</v>
@@ -8868,7 +8868,7 @@
         <v>32</v>
       </c>
       <c r="T117" s="9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U117" s="12" t="s">
         <v>129</v>
@@ -9093,9 +9093,11 @@
       <c r="B122" s="5">
         <v>46168.683847673616</v>
       </c>
-      <c r="C122" s="6"/>
+      <c r="C122" s="5">
+        <v>46197.49592710648</v>
+      </c>
       <c r="D122" s="5">
-        <v>46168.8661180787</v>
+        <v>46197.49592886574</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>221</v>
@@ -9148,7 +9150,7 @@
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46168.867152418985</v>
+        <v>46197.49666800926</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>357</v>
@@ -9196,7 +9198,7 @@
         <v>32</v>
       </c>
       <c r="T123" s="9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U123" s="12" t="s">
         <v>129</v>
@@ -9421,9 +9423,11 @@
       <c r="B128" s="5">
         <v>46168.68389033565</v>
       </c>
-      <c r="C128" s="6"/>
+      <c r="C128" s="5">
+        <v>46197.49605328703</v>
+      </c>
       <c r="D128" s="5">
-        <v>46190.605440740736</v>
+        <v>46197.49605478009</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>221</v>
@@ -9476,7 +9480,7 @@
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46168.86729284722</v>
+        <v>46197.49669130787</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>372</v>
@@ -9524,7 +9528,7 @@
         <v>32</v>
       </c>
       <c r="T129" s="9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U129" s="12" t="s">
         <v>129</v>
@@ -9749,9 +9753,11 @@
       <c r="B134" s="5">
         <v>46168.68398528935</v>
       </c>
-      <c r="C134" s="6"/>
+      <c r="C134" s="5">
+        <v>46197.49614903935</v>
+      </c>
       <c r="D134" s="5">
-        <v>46190.605442071756</v>
+        <v>46197.49615070602</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>221</v>
@@ -9804,7 +9810,7 @@
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46168.86751174768</v>
+        <v>46197.496712824075</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>387</v>
@@ -9852,7 +9858,7 @@
         <v>32</v>
       </c>
       <c r="T135" s="9">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="U135" s="12" t="s">
         <v>129</v>
@@ -10077,9 +10083,11 @@
       <c r="B140" s="5">
         <v>46168.68404385417</v>
       </c>
-      <c r="C140" s="6"/>
+      <c r="C140" s="5">
+        <v>46197.49627</v>
+      </c>
       <c r="D140" s="5">
-        <v>46190.605442569446</v>
+        <v>46197.49635938657</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>221</v>
@@ -10407,7 +10415,7 @@
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46168.86764458333</v>
+        <v>46197.49627510417</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>221</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="538">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -3412,9 +3412,11 @@
       <c r="B23" s="8">
         <v>46168.68298827547</v>
       </c>
-      <c r="C23" s="9"/>
+      <c r="C23" s="8">
+        <v>46197.85300722222</v>
+      </c>
       <c r="D23" s="8">
-        <v>46193.55308</v>
+        <v>46197.85302019676</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3449,8 +3451,12 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
+      <c r="T23" s="9">
+        <v>1</v>
+      </c>
+      <c r="U23" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -3654,9 +3660,11 @@
       <c r="B27" s="8">
         <v>46168.68321476852</v>
       </c>
-      <c r="C27" s="9"/>
+      <c r="C27" s="8">
+        <v>46197.852991875</v>
+      </c>
       <c r="D27" s="8">
-        <v>46191.16899662037</v>
+        <v>46197.8530077662</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>100</v>
@@ -3704,10 +3712,10 @@
         <v>105</v>
       </c>
       <c r="T27" s="9">
-        <v>0</v>
-      </c>
-      <c r="U27" s="11" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="U27" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
@@ -4882,7 +4890,7 @@
       </c>
       <c r="C47" s="9"/>
       <c r="D47" s="8">
-        <v>46192.17523146991</v>
+        <v>46197.85300241898</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>169</v>
@@ -6955,7 +6963,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46168.849797476854</v>
+        <v>46197.851189953704</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>258</v>
@@ -7063,9 +7071,11 @@
       <c r="B86" s="5">
         <v>46168.68352011574</v>
       </c>
-      <c r="C86" s="6"/>
+      <c r="C86" s="5">
+        <v>46197.85117512732</v>
+      </c>
       <c r="D86" s="5">
-        <v>46168.86519618056</v>
+        <v>46197.851191678245</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>266</v>
@@ -7113,10 +7123,10 @@
         <v>32</v>
       </c>
       <c r="T86" s="6">
-        <v>0</v>
-      </c>
-      <c r="U86" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U86" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -7189,9 +7199,11 @@
       <c r="B88" s="5">
         <v>46168.68353292824</v>
       </c>
-      <c r="C88" s="6"/>
+      <c r="C88" s="5">
+        <v>46197.851300173614</v>
+      </c>
       <c r="D88" s="5">
-        <v>46168.8652724537</v>
+        <v>46197.851317175926</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>273</v>
@@ -7239,10 +7251,10 @@
         <v>32</v>
       </c>
       <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U88" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7315,9 +7327,11 @@
       <c r="B90" s="5">
         <v>46168.68354247685</v>
       </c>
-      <c r="C90" s="6"/>
+      <c r="C90" s="5">
+        <v>46197.85161460648</v>
+      </c>
       <c r="D90" s="5">
-        <v>46168.8653077662</v>
+        <v>46197.85163635417</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>277</v>
@@ -7365,10 +7379,10 @@
         <v>32</v>
       </c>
       <c r="T90" s="6">
-        <v>0</v>
-      </c>
-      <c r="U90" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U90" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -7380,7 +7394,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46192.63406376158</v>
+        <v>46197.85008266204</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -7429,7 +7443,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46192.63407395833</v>
+        <v>46197.85264056713</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>
@@ -7490,9 +7504,11 @@
       <c r="B93" s="8">
         <v>46168.68356208333</v>
       </c>
-      <c r="C93" s="9"/>
+      <c r="C93" s="8">
+        <v>46197.85262831018</v>
+      </c>
       <c r="D93" s="8">
-        <v>46168.8654994213</v>
+        <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>213</v>
@@ -7543,9 +7559,11 @@
       <c r="B94" s="5">
         <v>46168.68356922454</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46197.85262942129</v>
+      </c>
       <c r="D94" s="5">
-        <v>46168.865495868056</v>
+        <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>213</v>
@@ -7596,9 +7614,11 @@
       <c r="B95" s="8">
         <v>46168.683574780094</v>
       </c>
-      <c r="C95" s="9"/>
+      <c r="C95" s="8">
+        <v>46197.85263005787</v>
+      </c>
       <c r="D95" s="8">
-        <v>46168.865493136575</v>
+        <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>217</v>
@@ -7649,9 +7669,11 @@
       <c r="B96" s="5">
         <v>46168.68358024306</v>
       </c>
-      <c r="C96" s="6"/>
+      <c r="C96" s="5">
+        <v>46197.85263069444</v>
+      </c>
       <c r="D96" s="5">
-        <v>46168.86549053241</v>
+        <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>217</v>
@@ -7702,9 +7724,11 @@
       <c r="B97" s="8">
         <v>46168.68358578703</v>
       </c>
-      <c r="C97" s="9"/>
+      <c r="C97" s="8">
+        <v>46197.85263130787</v>
+      </c>
       <c r="D97" s="8">
-        <v>46168.86548636574</v>
+        <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>221</v>
@@ -7755,9 +7779,11 @@
       <c r="B98" s="5">
         <v>46168.68365474537</v>
       </c>
-      <c r="C98" s="6"/>
+      <c r="C98" s="5">
+        <v>46197.85007665509</v>
+      </c>
       <c r="D98" s="5">
-        <v>46168.865691921295</v>
+        <v>46197.85243150463</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>299</v>
@@ -7805,10 +7831,10 @@
         <v>32</v>
       </c>
       <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U98" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7818,9 +7844,11 @@
       <c r="B99" s="8">
         <v>46168.683659965274</v>
       </c>
-      <c r="C99" s="9"/>
+      <c r="C99" s="8">
+        <v>46197.85183020833</v>
+      </c>
       <c r="D99" s="8">
-        <v>46190.60542900463</v>
+        <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>213</v>
@@ -7871,9 +7899,11 @@
       <c r="B100" s="5">
         <v>46168.68366613426</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46197.85205292824</v>
+      </c>
       <c r="D100" s="5">
-        <v>46190.605429560186</v>
+        <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>213</v>
@@ -7924,9 +7954,11 @@
       <c r="B101" s="8">
         <v>46168.683671921295</v>
       </c>
-      <c r="C101" s="9"/>
+      <c r="C101" s="8">
+        <v>46197.852225717594</v>
+      </c>
       <c r="D101" s="8">
-        <v>46168.8656500463</v>
+        <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>217</v>
@@ -7977,9 +8009,11 @@
       <c r="B102" s="5">
         <v>46168.68367622685</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46197.8523160301</v>
+      </c>
       <c r="D102" s="5">
-        <v>46168.8656471412</v>
+        <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>217</v>
@@ -8030,9 +8064,11 @@
       <c r="B103" s="8">
         <v>46168.683680069444</v>
       </c>
-      <c r="C103" s="9"/>
+      <c r="C103" s="8">
+        <v>46197.852413217595</v>
+      </c>
       <c r="D103" s="8">
-        <v>46168.865643125</v>
+        <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>221</v>
@@ -8148,7 +8184,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46190.60544303241</v>
+        <v>46197.85183748843</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>213</v>
@@ -8201,7 +8237,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46190.60543011574</v>
+        <v>46197.852060370366</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>318</v>
@@ -8254,7 +8290,7 @@
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46168.86584442129</v>
+        <v>46197.85223857639</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>217</v>
@@ -8307,7 +8343,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46168.86584158565</v>
+        <v>46197.85232365741</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>217</v>
@@ -8360,7 +8396,7 @@
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46168.865837881945</v>
+        <v>46197.85242358796</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>221</v>
@@ -8989,7 +9025,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46168.86612511574</v>
+        <v>46197.85223737269</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>217</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46195.925876678244</v>
+        <v>46198.169370069445</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46195.925877835645</v>
+        <v>46198.16936840278</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>150</v>
@@ -7010,7 +7010,7 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46168.86502239583</v>
+        <v>46198.17006754629</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>261</v>
@@ -7054,8 +7054,8 @@
       <c r="R85" s="8">
         <v>46205</v>
       </c>
-      <c r="S85" s="10" t="s">
-        <v>32</v>
+      <c r="S85" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="T85" s="9">
         <v>0</v>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46168.86507212963</v>
+        <v>46198.170066886574</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -7182,8 +7182,8 @@
       <c r="R87" s="8">
         <v>46205</v>
       </c>
-      <c r="S87" s="10" t="s">
-        <v>32</v>
+      <c r="S87" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46168.86510582176</v>
+        <v>46198.170067037034</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>276</v>
@@ -7310,8 +7310,8 @@
       <c r="R89" s="8">
         <v>46205</v>
       </c>
-      <c r="S89" s="10" t="s">
-        <v>32</v>
+      <c r="S89" s="11" t="s">
+        <v>145</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -486,73 +486,73 @@
     <t>Generación OC motor ot 4335 - 4337 -4339,Fabricación motor ot 4335 - 4337 -4339,Planos motor proveedor ot 4335 - 4337 -4339</t>
   </si>
   <si>
+    <t>1215141566531457</t>
+  </si>
+  <si>
+    <t>Generación OC motor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Motor ot 4335 - 4337 -4339,Fabricación motor ot 4335 - 4337 -4339,Planos motor proveedor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402379997</t>
+  </si>
+  <si>
+    <t>Fabricación motor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Motor ot 4335 - 4337 -4339,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215141451287971</t>
+  </si>
+  <si>
+    <t>Planos motor proveedor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Motor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141451287991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros  ot 4336 - 4338 -4341 </t>
+  </si>
+  <si>
+    <t>Generación OC   ot 4336 - 4338 -4341,fabricación tableros   ot 4336 - 4338 -4341</t>
+  </si>
+  <si>
+    <t>1215141318244929</t>
+  </si>
+  <si>
+    <t>Tableros  ot 4336 - 4338 -4341 ,fabricación tableros   ot 4336 - 4338 -4341</t>
+  </si>
+  <si>
+    <t>1215141318244946</t>
+  </si>
+  <si>
+    <t>fabricación tableros   ot 4336 - 4338 -4341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tableros  ot 4336 - 4338 -4341 ,Recepcion Tableros ot 4336 - 4338 -4341 </t>
+  </si>
+  <si>
+    <t>1215141533879267</t>
+  </si>
+  <si>
+    <t>Materiales corte Laser ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Yerlia Ayleen Castillo Diaz</t>
+  </si>
+  <si>
+    <t>yerlia.castillo@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación OC materiales corte Laser ot 4335 - 4337 -4339,Fabricacion Corte Laser ot 4335 - 4337 -4339 </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141566531457</t>
-  </si>
-  <si>
-    <t>Generación OC motor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Motor ot 4335 - 4337 -4339,Fabricación motor ot 4335 - 4337 -4339,Planos motor proveedor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402379997</t>
-  </si>
-  <si>
-    <t>Fabricación motor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Motor ot 4335 - 4337 -4339,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215141451287971</t>
-  </si>
-  <si>
-    <t>Planos motor proveedor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Motor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141451287991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros  ot 4336 - 4338 -4341 </t>
-  </si>
-  <si>
-    <t>Generación OC   ot 4336 - 4338 -4341,fabricación tableros   ot 4336 - 4338 -4341</t>
-  </si>
-  <si>
-    <t>1215141318244929</t>
-  </si>
-  <si>
-    <t>Tableros  ot 4336 - 4338 -4341 ,fabricación tableros   ot 4336 - 4338 -4341</t>
-  </si>
-  <si>
-    <t>1215141318244946</t>
-  </si>
-  <si>
-    <t>fabricación tableros   ot 4336 - 4338 -4341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tableros  ot 4336 - 4338 -4341 ,Recepcion Tableros ot 4336 - 4338 -4341 </t>
-  </si>
-  <si>
-    <t>1215141533879267</t>
-  </si>
-  <si>
-    <t>Materiales corte Laser ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Yerlia Ayleen Castillo Diaz</t>
-  </si>
-  <si>
-    <t>yerlia.castillo@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación OC materiales corte Laser ot 4335 - 4337 -4339,Fabricacion Corte Laser ot 4335 - 4337 -4339 </t>
   </si>
   <si>
     <t>1215141533879284</t>
@@ -4408,7 +4408,7 @@
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46198.169370069445</v>
+        <v>46199.18005736111</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4452,8 +4452,8 @@
       <c r="R39" s="8">
         <v>46198</v>
       </c>
-      <c r="S39" s="11" t="s">
-        <v>145</v>
+      <c r="S39" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
@@ -4464,7 +4464,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46168.683310092594</v>
@@ -4476,7 +4476,7 @@
         <v>46195.92587128472</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
@@ -4509,7 +4509,7 @@
         <v>90</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4525,7 +4525,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46168.68331519676</v>
@@ -4535,7 +4535,7 @@
         <v>46198.16936840278</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
@@ -4565,10 +4565,10 @@
         <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4584,7 +4584,7 @@
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46168.68332027778</v>
@@ -4596,7 +4596,7 @@
         <v>46195.92587850694</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
@@ -4626,10 +4626,10 @@
         <v>143</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4645,7 +4645,7 @@
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B43" s="8">
         <v>46168.68332520833</v>
@@ -4657,7 +4657,7 @@
         <v>46195.92859513889</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
@@ -4687,7 +4687,7 @@
         <v>119</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4710,7 +4710,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46168.68332880787</v>
@@ -4749,13 +4749,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>116</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4765,7 +4765,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B45" s="8">
         <v>46168.683333113426</v>
@@ -4777,7 +4777,7 @@
         <v>46195.92857017361</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4804,13 +4804,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O45" s="9" t="s">
         <v>117</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4820,7 +4820,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46168.683337291666</v>
@@ -4830,16 +4830,16 @@
         <v>46196.18789538194</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46191</v>
@@ -4860,7 +4860,7 @@
         <v>119</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>119</v>
@@ -4872,7 +4872,7 @@
         <v>46203</v>
       </c>
       <c r="S46" s="11" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="T46" s="6">
         <v>0</v>
@@ -4899,10 +4899,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I47" s="8">
         <v>46191</v>
@@ -4920,7 +4920,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>100</v>
@@ -4958,10 +4958,10 @@
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I48" s="5">
         <v>46195</v>
@@ -4979,7 +4979,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>169</v>
@@ -5017,10 +5017,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I49" s="8">
         <v>46191</v>
@@ -5053,7 +5053,7 @@
         <v>46203</v>
       </c>
       <c r="S49" s="11" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="T49" s="9">
         <v>0</v>
@@ -5080,10 +5080,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I50" s="5">
         <v>46191</v>
@@ -5133,10 +5133,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I51" s="8">
         <v>46195</v>
@@ -5240,7 +5240,7 @@
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46196.64761290509</v>
+        <v>46199.1706862963</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>114</v>
@@ -5408,10 +5408,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I56" s="5">
         <v>46191</v>
@@ -5444,7 +5444,7 @@
         <v>46203</v>
       </c>
       <c r="S56" s="11" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="T56" s="6">
         <v>0</v>
@@ -5471,10 +5471,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>165</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>166</v>
       </c>
       <c r="I57" s="8">
         <v>46191</v>
@@ -5524,10 +5524,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>165</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>166</v>
       </c>
       <c r="I58" s="5">
         <v>46195</v>
@@ -7055,7 +7055,7 @@
         <v>46205</v>
       </c>
       <c r="S85" s="11" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="T85" s="9">
         <v>0</v>
@@ -7183,7 +7183,7 @@
         <v>46205</v>
       </c>
       <c r="S87" s="11" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>46205</v>
       </c>
       <c r="S89" s="11" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46192.18714875</v>
+        <v>46199.17068362268</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>334</v>
@@ -8653,7 +8653,7 @@
         <v>258</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>335</v>
@@ -8665,7 +8665,7 @@
         <v>46199</v>
       </c>
       <c r="S113" s="11" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
       <c r="T113" s="9">
         <v>0</v>
@@ -8779,7 +8779,7 @@
         <v>258</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>340</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46195.928393263894</v>
+        <v>46199.56506112269</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -4825,9 +4825,11 @@
       <c r="B46" s="5">
         <v>46168.683337291666</v>
       </c>
-      <c r="C46" s="6"/>
+      <c r="C46" s="5">
+        <v>46199.5650503588</v>
+      </c>
       <c r="D46" s="5">
-        <v>46196.18789538194</v>
+        <v>46199.56506390046</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4875,10 +4877,10 @@
         <v>167</v>
       </c>
       <c r="T46" s="6">
-        <v>0</v>
-      </c>
-      <c r="U46" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U46" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -4888,9 +4890,11 @@
       <c r="B47" s="8">
         <v>46168.68334179398</v>
       </c>
-      <c r="C47" s="9"/>
+      <c r="C47" s="8">
+        <v>46199.56498643519</v>
+      </c>
       <c r="D47" s="8">
-        <v>46197.85300241898</v>
+        <v>46199.564988564816</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>169</v>
@@ -4947,9 +4951,11 @@
       <c r="B48" s="5">
         <v>46168.68334684028</v>
       </c>
-      <c r="C48" s="6"/>
+      <c r="C48" s="5">
+        <v>46199.56503596065</v>
+      </c>
       <c r="D48" s="5">
-        <v>46169.88094466436</v>
+        <v>46199.5650378125</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>172</v>
@@ -5006,9 +5012,11 @@
       <c r="B49" s="8">
         <v>46168.68335195602</v>
       </c>
-      <c r="C49" s="9"/>
+      <c r="C49" s="8">
+        <v>46199.565312569444</v>
+      </c>
       <c r="D49" s="8">
-        <v>46196.18789538194</v>
+        <v>46199.56531440972</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>175</v>
@@ -5056,10 +5064,10 @@
         <v>167</v>
       </c>
       <c r="T49" s="9">
-        <v>0</v>
-      </c>
-      <c r="U49" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U49" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
@@ -5069,9 +5077,11 @@
       <c r="B50" s="5">
         <v>46168.68335582176</v>
       </c>
-      <c r="C50" s="6"/>
+      <c r="C50" s="5">
+        <v>46199.56512105324</v>
+      </c>
       <c r="D50" s="5">
-        <v>46196.64667890046</v>
+        <v>46199.56512275463</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>108</v>
@@ -5122,9 +5132,11 @@
       <c r="B51" s="8">
         <v>46168.683360428244</v>
       </c>
-      <c r="C51" s="9"/>
+      <c r="C51" s="8">
+        <v>46199.565198819444</v>
+      </c>
       <c r="D51" s="8">
-        <v>46169.88089487268</v>
+        <v>46199.56520053241</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>180</v>
@@ -5397,9 +5409,11 @@
       <c r="B56" s="5">
         <v>46168.683385868055</v>
       </c>
-      <c r="C56" s="6"/>
+      <c r="C56" s="5">
+        <v>46199.56545385417</v>
+      </c>
       <c r="D56" s="5">
-        <v>46196.187896284726</v>
+        <v>46199.56546679398</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>197</v>
@@ -5447,10 +5461,10 @@
         <v>167</v>
       </c>
       <c r="T56" s="6">
-        <v>0</v>
-      </c>
-      <c r="U56" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U56" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
@@ -5460,9 +5474,11 @@
       <c r="B57" s="8">
         <v>46168.68343064815</v>
       </c>
-      <c r="C57" s="9"/>
+      <c r="C57" s="8">
+        <v>46199.565352418984</v>
+      </c>
       <c r="D57" s="8">
-        <v>46196.64740983796</v>
+        <v>46199.56535409723</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>111</v>
@@ -5513,9 +5529,11 @@
       <c r="B58" s="5">
         <v>46168.683436956024</v>
       </c>
-      <c r="C58" s="6"/>
+      <c r="C58" s="5">
+        <v>46199.56543844908</v>
+      </c>
       <c r="D58" s="5">
-        <v>46169.88078201389</v>
+        <v>46199.56544034722</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>202</v>
@@ -7010,7 +7028,7 @@
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46198.17006754629</v>
+        <v>46199.56505399305</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>261</v>
@@ -7060,8 +7078,8 @@
       <c r="T85" s="9">
         <v>0</v>
       </c>
-      <c r="U85" s="12" t="s">
-        <v>129</v>
+      <c r="U85" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -7138,7 +7156,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46198.170066886574</v>
+        <v>46199.56521630787</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -7188,8 +7206,8 @@
       <c r="T87" s="9">
         <v>0</v>
       </c>
-      <c r="U87" s="12" t="s">
-        <v>129</v>
+      <c r="U87" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -7266,7 +7284,7 @@
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46198.170067037034</v>
+        <v>46199.56545707176</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>276</v>
@@ -7316,8 +7334,8 @@
       <c r="T89" s="9">
         <v>0</v>
       </c>
-      <c r="U89" s="12" t="s">
-        <v>129</v>
+      <c r="U89" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -8638,7 +8638,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46199.17068362268</v>
+        <v>46200.16903983796</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>334</v>
@@ -8682,8 +8682,8 @@
       <c r="R113" s="8">
         <v>46199</v>
       </c>
-      <c r="S113" s="11" t="s">
-        <v>167</v>
+      <c r="S113" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T113" s="9">
         <v>0</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -7093,7 +7093,7 @@
         <v>46197.85117512732</v>
       </c>
       <c r="D86" s="5">
-        <v>46197.851191678245</v>
+        <v>46202.16723841435</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>266</v>
@@ -7137,8 +7137,8 @@
       <c r="R86" s="5">
         <v>46209</v>
       </c>
-      <c r="S86" s="10" t="s">
-        <v>32</v>
+      <c r="S86" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -7221,7 +7221,7 @@
         <v>46197.851300173614</v>
       </c>
       <c r="D88" s="5">
-        <v>46197.851317175926</v>
+        <v>46202.167238229165</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>273</v>
@@ -7265,8 +7265,8 @@
       <c r="R88" s="5">
         <v>46209</v>
       </c>
-      <c r="S88" s="10" t="s">
-        <v>32</v>
+      <c r="S88" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -7349,7 +7349,7 @@
         <v>46197.85161460648</v>
       </c>
       <c r="D90" s="5">
-        <v>46197.85163635417</v>
+        <v>46202.16723857639</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>277</v>
@@ -7393,8 +7393,8 @@
       <c r="R90" s="5">
         <v>46209</v>
       </c>
-      <c r="S90" s="10" t="s">
-        <v>32</v>
+      <c r="S90" s="11" t="s">
+        <v>167</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -552,298 +552,298 @@
     <t xml:space="preserve">Generación OC materiales corte Laser ot 4335 - 4337 -4339,Fabricacion Corte Laser ot 4335 - 4337 -4339 </t>
   </si>
   <si>
+    <t>1215141533879284</t>
+  </si>
+  <si>
+    <t>Generación OC materiales corte Laser ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Materiales corte Laser ot 4335 - 4337 -4339,Fabricacion Corte Laser ot 4335 - 4337 -4339 </t>
+  </si>
+  <si>
+    <t>1215141533887787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricacion Corte Laser ot 4335 - 4337 -4339 </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Materiales corte Laser ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141533887807</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Generación OC Corte Plasma  ot 4335 - 4337 -4339,Fabricación Corte Plasma  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141566544666</t>
+  </si>
+  <si>
+    <t>Materiales Corte Plasma  ot 4335 - 4337 -4339,Fabricación Corte Plasma  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141566544683</t>
+  </si>
+  <si>
+    <t>Fabricación Corte Plasma  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141566544924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa ot 4335 - 4337 -4339 </t>
+  </si>
+  <si>
+    <t>Rosemary Singh</t>
+  </si>
+  <si>
+    <t>rosemary.singh@zitron.com</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4335 - 4337 -4339,Generacion OC Fabricación Externa ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141566544936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación estructura proveedor externo ot 4335 - 4337 -4339,Fabricación Externa ot 4335 - 4337 -4339 </t>
+  </si>
+  <si>
+    <t>1215141318257122</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa ot 4335 - 4337 -4339 ,Control de calidad fabricación externa  ot 4335 - 4337 -4339,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215141318257139</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215141451318143</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4335 - 4337 -4339,Fabricación Mecanizado ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402333046</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4335 - 4337 -4339,Fabricación Mecanizado ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402333063</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4335 - 4337 -4339,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215141533944733</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>1215141533944745</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215139673478167</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215137857526183</t>
+  </si>
+  <si>
+    <t>1215137857526184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos preliminar,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526185</t>
+  </si>
+  <si>
+    <t>1215137857526186</t>
+  </si>
+  <si>
+    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141566627433</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215137857526187</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Planos motor proveedor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215137857526188</t>
+  </si>
+  <si>
+    <t>1215137857526189</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Planos motor proveedor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos definitivos,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos definitivos,OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526191</t>
+  </si>
+  <si>
+    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Planos motor proveedor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141318332820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Mecanizad ot 4335 - 4337 -4339o,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT  4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Propuesta Fabricación externa  ot 4335 - 4337 -4339,propuesta Corte Laser ot 4335 - 4337 -4339,Propuesta Corte plasma  ot 4335 - 4337 -4339,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526192</t>
+  </si>
+  <si>
+    <t>1215137857526193</t>
+  </si>
+  <si>
+    <t>1215137857526194</t>
+  </si>
+  <si>
+    <t>1215137857526195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526196</t>
+  </si>
+  <si>
+    <t>1215141533950987</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141533950999</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141533961665</t>
+  </si>
+  <si>
+    <t>1215141533961677</t>
+  </si>
+  <si>
+    <t>1215141533961684</t>
+  </si>
+  <si>
+    <t>1215141566669401</t>
+  </si>
+  <si>
+    <t>1215141402523613</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215141402523625</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141533879284</t>
-  </si>
-  <si>
-    <t>Generación OC materiales corte Laser ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Materiales corte Laser ot 4335 - 4337 -4339,Fabricacion Corte Laser ot 4335 - 4337 -4339 </t>
-  </si>
-  <si>
-    <t>1215141533887787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricacion Corte Laser ot 4335 - 4337 -4339 </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Materiales corte Laser ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141533887807</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Generación OC Corte Plasma  ot 4335 - 4337 -4339,Fabricación Corte Plasma  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141566544666</t>
-  </si>
-  <si>
-    <t>Materiales Corte Plasma  ot 4335 - 4337 -4339,Fabricación Corte Plasma  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141566544683</t>
-  </si>
-  <si>
-    <t>Fabricación Corte Plasma  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma,Materiales Corte Plasma  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141566544924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa ot 4335 - 4337 -4339 </t>
-  </si>
-  <si>
-    <t>Rosemary Singh</t>
-  </si>
-  <si>
-    <t>rosemary.singh@zitron.com</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4335 - 4337 -4339,Generacion OC Fabricación Externa ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141566544936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación estructura proveedor externo ot 4335 - 4337 -4339,Fabricación Externa ot 4335 - 4337 -4339 </t>
-  </si>
-  <si>
-    <t>1215141318257122</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa ot 4335 - 4337 -4339 ,Control de calidad fabricación externa  ot 4335 - 4337 -4339,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215141318257139</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215141451318143</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4335 - 4337 -4339,Fabricación Mecanizado ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402333046</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4335 - 4337 -4339,Fabricación Mecanizado ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402333063</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4335 - 4337 -4339,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215141533944733</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>1215141533944745</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215139673478167</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215137857526183</t>
-  </si>
-  <si>
-    <t>1215137857526184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planos preliminar,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526185</t>
-  </si>
-  <si>
-    <t>1215137857526186</t>
-  </si>
-  <si>
-    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141566627433</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215137857526187</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Planos motor proveedor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215137857526188</t>
-  </si>
-  <si>
-    <t>1215137857526189</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Planos motor proveedor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planos definitivos,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planos definitivos,OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526191</t>
-  </si>
-  <si>
-    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Planos motor proveedor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141318332820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Mecanizad ot 4335 - 4337 -4339o,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT  4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Propuesta Fabricación externa  ot 4335 - 4337 -4339,propuesta Corte Laser ot 4335 - 4337 -4339,Propuesta Corte plasma  ot 4335 - 4337 -4339,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526192</t>
-  </si>
-  <si>
-    <t>1215137857526193</t>
-  </si>
-  <si>
-    <t>1215137857526194</t>
-  </si>
-  <si>
-    <t>1215137857526195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526196</t>
-  </si>
-  <si>
-    <t>1215141533950987</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141533950999</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141533961665</t>
-  </si>
-  <si>
-    <t>1215141533961677</t>
-  </si>
-  <si>
-    <t>1215141533961684</t>
-  </si>
-  <si>
-    <t>1215141566669401</t>
-  </si>
-  <si>
-    <t>1215141402523613</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215141402523625</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
     <t>1215141533986830</t>
@@ -4829,7 +4829,7 @@
         <v>46199.5650503588</v>
       </c>
       <c r="D46" s="5">
-        <v>46199.56506390046</v>
+        <v>46204.1978837037</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4873,8 +4873,8 @@
       <c r="R46" s="5">
         <v>46203</v>
       </c>
-      <c r="S46" s="11" t="s">
-        <v>167</v>
+      <c r="S46" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4885,7 +4885,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46168.68334179398</v>
@@ -4897,7 +4897,7 @@
         <v>46199.564988564816</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
@@ -4930,7 +4930,7 @@
         <v>100</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4946,7 +4946,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46168.68334684028</v>
@@ -4958,7 +4958,7 @@
         <v>46199.5650378125</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
@@ -4988,10 +4988,10 @@
         <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -5007,7 +5007,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46168.68335195602</v>
@@ -5016,10 +5016,10 @@
         <v>46199.565312569444</v>
       </c>
       <c r="D49" s="8">
-        <v>46199.56531440972</v>
+        <v>46204.19788363426</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
@@ -5049,7 +5049,7 @@
         <v>119</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -5060,8 +5060,8 @@
       <c r="R49" s="8">
         <v>46203</v>
       </c>
-      <c r="S49" s="11" t="s">
-        <v>167</v>
+      <c r="S49" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -5072,7 +5072,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46168.68335582176</v>
@@ -5111,13 +5111,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -5127,7 +5127,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46168.683360428244</v>
@@ -5139,7 +5139,7 @@
         <v>46199.56520053241</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
@@ -5166,13 +5166,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>108</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46168.68336471065</v>
@@ -5192,16 +5192,16 @@
         <v>46169.88071780093</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -5222,7 +5222,7 @@
         <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -5245,7 +5245,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46168.68337377315</v>
@@ -5261,10 +5261,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>184</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="I53" s="8">
         <v>46191</v>
@@ -5282,13 +5282,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>113</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5298,7 +5298,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46168.683378194444</v>
@@ -5308,16 +5308,16 @@
         <v>46169.880830787035</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>184</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46202</v>
@@ -5335,13 +5335,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>114</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5351,7 +5351,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46168.68338271991</v>
@@ -5361,16 +5361,16 @@
         <v>46169.88084712963</v>
       </c>
       <c r="E55" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
+      <c r="H55" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>195</v>
       </c>
       <c r="I55" s="8">
         <v>46231</v>
@@ -5388,10 +5388,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5404,7 +5404,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46168.683385868055</v>
@@ -5413,10 +5413,10 @@
         <v>46199.56545385417</v>
       </c>
       <c r="D56" s="5">
-        <v>46199.56546679398</v>
+        <v>46204.19788391204</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5446,7 +5446,7 @@
         <v>119</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5457,8 +5457,8 @@
       <c r="R56" s="5">
         <v>46203</v>
       </c>
-      <c r="S56" s="11" t="s">
-        <v>167</v>
+      <c r="S56" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5469,7 +5469,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46168.68343064815</v>
@@ -5508,13 +5508,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>110</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5524,7 +5524,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46168.683436956024</v>
@@ -5536,7 +5536,7 @@
         <v>46199.56544034722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5563,13 +5563,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5579,7 +5579,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46168.68344221065</v>
@@ -5589,7 +5589,7 @@
         <v>46190.60524740741</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5613,7 +5613,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B60" s="5">
         <v>46168.683445787035</v>
@@ -5640,16 +5640,16 @@
         <v>46184.518844583334</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I60" s="5">
         <v>46167</v>
@@ -5667,13 +5667,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46167</v>
@@ -5693,7 +5693,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B61" s="8">
         <v>46168.6865996875</v>
@@ -5705,16 +5705,16 @@
         <v>46184.51878665509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I61" s="8">
         <v>46167</v>
@@ -5732,13 +5732,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5748,7 +5748,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46168.68683460648</v>
@@ -5760,16 +5760,16 @@
         <v>46184.518791319446</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46167</v>
@@ -5787,13 +5787,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5803,7 +5803,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B63" s="8">
         <v>46168.686918437495</v>
@@ -5815,16 +5815,16 @@
         <v>46184.51879930556</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I63" s="8">
         <v>46167</v>
@@ -5842,13 +5842,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5858,7 +5858,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B64" s="5">
         <v>46168.687254143515</v>
@@ -5870,16 +5870,16 @@
         <v>46184.5188068287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46167</v>
@@ -5897,13 +5897,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B65" s="8">
         <v>46168.68731635417</v>
@@ -5925,16 +5925,16 @@
         <v>46184.51881454861</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I65" s="8">
         <v>46167</v>
@@ -5952,13 +5952,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5968,7 +5968,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B66" s="5">
         <v>46168.68345142361</v>
@@ -5980,16 +5980,16 @@
         <v>46190.605242708334</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46181</v>
@@ -6007,13 +6007,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Q66" s="5">
         <v>46181</v>
@@ -6033,7 +6033,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B67" s="8">
         <v>46168.68857346065</v>
@@ -6045,16 +6045,16 @@
         <v>46190.60518608797</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I67" s="8">
         <v>46181</v>
@@ -6072,13 +6072,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O67" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="P67" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -6088,7 +6088,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B68" s="5">
         <v>46168.688608275465</v>
@@ -6100,16 +6100,16 @@
         <v>46190.60519502315</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46181</v>
@@ -6127,13 +6127,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6143,7 +6143,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B69" s="8">
         <v>46168.68864659722</v>
@@ -6155,16 +6155,16 @@
         <v>46190.605203761574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I69" s="8">
         <v>46181</v>
@@ -6182,13 +6182,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B70" s="5">
         <v>46168.68868637731</v>
@@ -6210,16 +6210,16 @@
         <v>46190.605208946756</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I70" s="5">
         <v>46181</v>
@@ -6237,13 +6237,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6253,7 +6253,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B71" s="8">
         <v>46168.68871934028</v>
@@ -6265,16 +6265,16 @@
         <v>46190.60521709491</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I71" s="8">
         <v>46181</v>
@@ -6292,13 +6292,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -6308,7 +6308,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B72" s="5">
         <v>46168.68345790509</v>
@@ -6326,10 +6326,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I72" s="5">
         <v>46188</v>
@@ -6347,13 +6347,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="Q72" s="5">
         <v>46188</v>
@@ -6373,7 +6373,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B73" s="8">
         <v>46168.68880178241</v>
@@ -6385,16 +6385,16 @@
         <v>46190.60536361111</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -6415,7 +6415,7 @@
         <v>103</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>103</v>
@@ -6428,7 +6428,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B74" s="5">
         <v>46168.68883857639</v>
@@ -6440,16 +6440,16 @@
         <v>46190.605368206016</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I74" s="5">
         <v>46188</v>
@@ -6470,7 +6470,7 @@
         <v>103</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>103</v>
@@ -6483,7 +6483,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B75" s="8">
         <v>46168.688875775464</v>
@@ -6495,16 +6495,16 @@
         <v>46190.605373530096</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I75" s="8">
         <v>46188</v>
@@ -6525,7 +6525,7 @@
         <v>103</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>103</v>
@@ -6538,7 +6538,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B76" s="5">
         <v>46168.6889172338</v>
@@ -6550,16 +6550,16 @@
         <v>46190.60539957176</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I76" s="5">
         <v>46188</v>
@@ -6580,7 +6580,7 @@
         <v>103</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>103</v>
@@ -6593,7 +6593,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B77" s="8">
         <v>46168.688956620375</v>
@@ -6605,16 +6605,16 @@
         <v>46190.60538814815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I77" s="8">
         <v>46188</v>
@@ -6635,7 +6635,7 @@
         <v>103</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B78" s="5">
         <v>46168.683480625</v>
@@ -6658,16 +6658,16 @@
         <v>46168.86495055555</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6683,10 +6683,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6709,7 +6709,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B79" s="8">
         <v>46168.683484629626</v>
@@ -6719,16 +6719,16 @@
         <v>46168.86492854166</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I79" s="8">
         <v>46238</v>
@@ -6746,13 +6746,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6762,7 +6762,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B80" s="5">
         <v>46168.683488877316</v>
@@ -6772,16 +6772,16 @@
         <v>46168.86492561342</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I80" s="5">
         <v>46238</v>
@@ -6799,13 +6799,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6815,7 +6815,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B81" s="8">
         <v>46168.68349300926</v>
@@ -6825,16 +6825,16 @@
         <v>46168.86492288194</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46238</v>
@@ -6852,13 +6852,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6868,7 +6868,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46168.6834959375</v>
@@ -6878,16 +6878,16 @@
         <v>46168.864920162036</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46238</v>
@@ -6905,13 +6905,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6921,7 +6921,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B83" s="8">
         <v>46168.68349899305</v>
@@ -6931,16 +6931,16 @@
         <v>46168.86491564815</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46238</v>
@@ -6958,13 +6958,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -6974,7 +6974,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B84" s="5">
         <v>46168.68351101852</v>
@@ -6984,7 +6984,7 @@
         <v>46197.851189953704</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -7008,7 +7008,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B85" s="8">
         <v>46168.68351447917</v>
@@ -7031,16 +7031,16 @@
         <v>46199.56505399305</v>
       </c>
       <c r="E85" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="F85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="9" t="s">
+      <c r="H85" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I85" s="8">
         <v>46204</v>
@@ -7058,13 +7058,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q85" s="8">
         <v>46204</v>
@@ -7073,7 +7073,7 @@
         <v>46205</v>
       </c>
       <c r="S85" s="11" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="T85" s="9">
         <v>0</v>
@@ -7102,10 +7102,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I86" s="5">
         <v>46206</v>
@@ -7123,7 +7123,7 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>267</v>
@@ -7138,7 +7138,7 @@
         <v>46209</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -7165,10 +7165,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -7186,10 +7186,10 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>271</v>
@@ -7201,7 +7201,7 @@
         <v>46205</v>
       </c>
       <c r="S87" s="11" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="T87" s="9">
         <v>0</v>
@@ -7230,10 +7230,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I88" s="5">
         <v>46206</v>
@@ -7251,7 +7251,7 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>270</v>
@@ -7266,7 +7266,7 @@
         <v>46209</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -7293,10 +7293,10 @@
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7314,10 +7314,10 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>277</v>
@@ -7329,7 +7329,7 @@
         <v>46205</v>
       </c>
       <c r="S89" s="11" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="T89" s="9">
         <v>0</v>
@@ -7358,10 +7358,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I90" s="5">
         <v>46206</v>
@@ -7379,7 +7379,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>276</v>
@@ -7394,7 +7394,7 @@
         <v>46209</v>
       </c>
       <c r="S90" s="11" t="s">
-        <v>167</v>
+        <v>264</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
@@ -7529,7 +7529,7 @@
         <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7584,7 +7584,7 @@
         <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7617,7 +7617,7 @@
         <v>291</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7639,7 +7639,7 @@
         <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7694,7 +7694,7 @@
         <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7749,7 +7749,7 @@
         <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7869,7 +7869,7 @@
         <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -7924,7 +7924,7 @@
         <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -7979,7 +7979,7 @@
         <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -8009,7 +8009,7 @@
         <v>299</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P101" s="9" t="s">
         <v>307</v>
@@ -8034,7 +8034,7 @@
         <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -8064,7 +8064,7 @@
         <v>299</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>309</v>
@@ -8089,7 +8089,7 @@
         <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -8119,7 +8119,7 @@
         <v>299</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>311</v>
@@ -8148,10 +8148,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I104" s="5">
         <v>46224</v>
@@ -8205,16 +8205,16 @@
         <v>46197.85183748843</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="H105" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>195</v>
       </c>
       <c r="I105" s="8">
         <v>46224</v>
@@ -8264,10 +8264,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I106" s="5">
         <v>46224</v>
@@ -8311,16 +8311,16 @@
         <v>46197.85223857639</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="H107" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>195</v>
       </c>
       <c r="I107" s="8">
         <v>46224</v>
@@ -8341,7 +8341,7 @@
         <v>313</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>313</v>
@@ -8364,16 +8364,16 @@
         <v>46197.85232365741</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>194</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>195</v>
       </c>
       <c r="I108" s="5">
         <v>46224</v>
@@ -8394,7 +8394,7 @@
         <v>313</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>322</v>
@@ -8417,16 +8417,16 @@
         <v>46197.85242358796</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
+        <v>193</v>
+      </c>
+      <c r="H109" s="9" t="s">
         <v>194</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>195</v>
       </c>
       <c r="I109" s="8">
         <v>46224</v>
@@ -8447,7 +8447,7 @@
         <v>313</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>324</v>
@@ -8470,7 +8470,7 @@
         <v>46168.854865925925</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8523,10 +8523,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H111" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I111" s="8">
         <v>46185</v>
@@ -8544,7 +8544,7 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>140</v>
@@ -8586,10 +8586,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8605,7 +8605,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>131</v>
@@ -8647,10 +8647,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H113" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I113" s="8">
         <v>46199</v>
@@ -8668,7 +8668,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>149</v>
@@ -8710,10 +8710,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8731,10 +8731,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>338</v>
@@ -8773,10 +8773,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H115" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I115" s="8">
         <v>46220</v>
@@ -8794,7 +8794,7 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>160</v>
@@ -8940,7 +8940,7 @@
         <v>46168.86613042824</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8993,7 +8993,7 @@
         <v>46168.866127685185</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -9046,7 +9046,7 @@
         <v>46197.85223737269</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -9076,7 +9076,7 @@
         <v>345</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>352</v>
@@ -9099,7 +9099,7 @@
         <v>46168.8661222338</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -9129,7 +9129,7 @@
         <v>345</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>352</v>
@@ -9154,7 +9154,7 @@
         <v>46197.49592886574</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9184,7 +9184,7 @@
         <v>345</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>355</v>
@@ -9270,7 +9270,7 @@
         <v>46190.60544122686</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9323,7 +9323,7 @@
         <v>46190.60544332176</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9376,7 +9376,7 @@
         <v>46190.60543283565</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9429,7 +9429,7 @@
         <v>46190.605433379635</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9484,7 +9484,7 @@
         <v>46197.49605478009</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9600,7 +9600,7 @@
         <v>46190.60543055556</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9653,7 +9653,7 @@
         <v>46190.60543111111</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9706,7 +9706,7 @@
         <v>46190.605433923614</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9759,7 +9759,7 @@
         <v>46190.605443622684</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9814,7 +9814,7 @@
         <v>46197.49615070602</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9930,7 +9930,7 @@
         <v>46190.60543435185</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9983,7 +9983,7 @@
         <v>46190.605431805554</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -10036,7 +10036,7 @@
         <v>46190.60543226852</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -10089,7 +10089,7 @@
         <v>46190.605434826386</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -10144,7 +10144,7 @@
         <v>46197.49635938657</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10260,7 +10260,7 @@
         <v>46168.86765785879</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10290,7 +10290,7 @@
         <v>401</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>403</v>
@@ -10313,7 +10313,7 @@
         <v>46168.86765493055</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -10343,7 +10343,7 @@
         <v>401</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>405</v>
@@ -10366,7 +10366,7 @@
         <v>46168.86764950231</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10396,7 +10396,7 @@
         <v>401</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>407</v>
@@ -10419,7 +10419,7 @@
         <v>46168.86764537037</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10449,7 +10449,7 @@
         <v>401</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>407</v>
@@ -10472,7 +10472,7 @@
         <v>46197.49627510417</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10502,7 +10502,7 @@
         <v>401</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>410</v>
@@ -10588,7 +10588,7 @@
         <v>46168.86780042824</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10618,7 +10618,7 @@
         <v>412</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>415</v>
@@ -10641,7 +10641,7 @@
         <v>46168.86779700231</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10671,7 +10671,7 @@
         <v>412</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>417</v>
@@ -10694,7 +10694,7 @@
         <v>46168.86779422454</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10724,7 +10724,7 @@
         <v>412</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>419</v>
@@ -10747,7 +10747,7 @@
         <v>46168.86779137731</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10777,7 +10777,7 @@
         <v>412</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>419</v>
@@ -10800,7 +10800,7 @@
         <v>46168.86778699074</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10830,7 +10830,7 @@
         <v>412</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>422</v>
@@ -10963,7 +10963,7 @@
         <v>46168.86804876158</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -10993,7 +10993,7 @@
         <v>427</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>432</v>
@@ -11016,7 +11016,7 @@
         <v>46168.868045787036</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -11046,7 +11046,7 @@
         <v>427</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>432</v>
@@ -11069,7 +11069,7 @@
         <v>46168.86804263889</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
@@ -11099,7 +11099,7 @@
         <v>427</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>435</v>
@@ -11122,7 +11122,7 @@
         <v>46168.868039953704</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11152,7 +11152,7 @@
         <v>427</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>435</v>
@@ -11175,7 +11175,7 @@
         <v>46168.86803709491</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -11205,7 +11205,7 @@
         <v>427</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>438</v>
@@ -11607,7 +11607,7 @@
         <v>46168.86826831019</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
@@ -11635,7 +11635,7 @@
         <v>449</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>452</v>
@@ -11658,7 +11658,7 @@
         <v>46168.86826501157</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11686,7 +11686,7 @@
         <v>449</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>452</v>
@@ -11709,7 +11709,7 @@
         <v>46168.86826178241</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
@@ -11737,7 +11737,7 @@
         <v>449</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P169" s="9" t="s">
         <v>455</v>
@@ -11760,7 +11760,7 @@
         <v>46168.868258738425</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11788,7 +11788,7 @@
         <v>449</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>455</v>
@@ -11811,7 +11811,7 @@
         <v>46168.86825503472</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
@@ -11839,7 +11839,7 @@
         <v>449</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P171" s="9" t="s">
         <v>458</v>
@@ -12229,7 +12229,7 @@
         <v>46168.86844914352</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
@@ -12259,7 +12259,7 @@
         <v>470</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P179" s="9" t="s">
         <v>473</v>
@@ -12282,7 +12282,7 @@
         <v>46168.86844586805</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12312,7 +12312,7 @@
         <v>470</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>475</v>
@@ -12335,7 +12335,7 @@
         <v>46168.86844222222</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
@@ -12365,7 +12365,7 @@
         <v>470</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P181" s="9" t="s">
         <v>477</v>
@@ -12388,7 +12388,7 @@
         <v>46168.868438749996</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12418,7 +12418,7 @@
         <v>470</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>479</v>
@@ -12441,7 +12441,7 @@
         <v>46168.86843505787</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
@@ -12471,7 +12471,7 @@
         <v>470</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P183" s="9" t="s">
         <v>481</v>
@@ -12903,7 +12903,7 @@
         <v>496</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P191" s="9" t="s">
         <v>496</v>
@@ -12954,7 +12954,7 @@
         <v>496</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P192" s="6" t="s">
         <v>496</v>
@@ -13005,7 +13005,7 @@
         <v>496</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P193" s="9" t="s">
         <v>496</v>
@@ -13056,7 +13056,7 @@
         <v>496</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P194" s="6" t="s">
         <v>496</v>
@@ -13107,7 +13107,7 @@
         <v>496</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P195" s="9" t="s">
         <v>496</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -5189,7 +5189,7 @@
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.88071780093</v>
+        <v>46204.601559456016</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -5239,8 +5239,8 @@
       <c r="T52" s="6">
         <v>0</v>
       </c>
-      <c r="U52" s="12" t="s">
-        <v>129</v>
+      <c r="U52" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
@@ -5250,9 +5250,11 @@
       <c r="B53" s="8">
         <v>46168.68337377315</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46204.601483715276</v>
+      </c>
       <c r="D53" s="8">
-        <v>46199.1706862963</v>
+        <v>46204.601485555555</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>114</v>
@@ -5303,9 +5305,11 @@
       <c r="B54" s="5">
         <v>46168.683378194444</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46204.60153940972</v>
+      </c>
       <c r="D54" s="5">
-        <v>46169.880830787035</v>
+        <v>46204.601540787036</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5358,7 +5362,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46169.88084712963</v>
+        <v>46204.60155028936</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>192</v>
@@ -8701,7 +8705,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46168.866013425926</v>
+        <v>46204.60155983796</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>337</v>
@@ -8751,8 +8755,8 @@
       <c r="T114" s="6">
         <v>0</v>
       </c>
-      <c r="U114" s="12" t="s">
-        <v>129</v>
+      <c r="U114" s="11" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -5187,9 +5187,11 @@
       <c r="B52" s="5">
         <v>46168.68336471065</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46204.86077883102</v>
+      </c>
       <c r="D52" s="5">
-        <v>46204.601559456016</v>
+        <v>46204.860797534726</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -5237,10 +5239,10 @@
         <v>32</v>
       </c>
       <c r="T52" s="6">
-        <v>0</v>
-      </c>
-      <c r="U52" s="11" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="U52" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="538">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46168.86491564815</v>
+        <v>46204.89334085648</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>220</v>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46197.85008266204</v>
+        <v>46204.89010925926</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -7454,7 +7454,9 @@
       <c r="R91" s="9"/>
       <c r="S91" s="9"/>
       <c r="T91" s="9"/>
-      <c r="U91" s="9"/>
+      <c r="U91" s="11" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
@@ -8143,9 +8145,11 @@
       <c r="B104" s="5">
         <v>46168.68369409722</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46204.89009226851</v>
+      </c>
       <c r="D104" s="5">
-        <v>46168.86587190972</v>
+        <v>46204.8901028588</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>313</v>
@@ -8193,10 +8197,10 @@
         <v>32</v>
       </c>
       <c r="T104" s="6">
-        <v>0</v>
-      </c>
-      <c r="U104" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U104" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
@@ -8206,9 +8210,11 @@
       <c r="B105" s="8">
         <v>46168.68369849537</v>
       </c>
-      <c r="C105" s="9"/>
+      <c r="C105" s="8">
+        <v>46204.890049884256</v>
+      </c>
       <c r="D105" s="8">
-        <v>46197.85183748843</v>
+        <v>46204.890051967595</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>212</v>
@@ -8259,9 +8265,11 @@
       <c r="B106" s="5">
         <v>46168.683704490744</v>
       </c>
-      <c r="C106" s="6"/>
+      <c r="C106" s="5">
+        <v>46204.89005663195</v>
+      </c>
       <c r="D106" s="5">
-        <v>46197.852060370366</v>
+        <v>46204.890058125005</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>318</v>
@@ -8312,9 +8320,11 @@
       <c r="B107" s="8">
         <v>46168.683710150464</v>
       </c>
-      <c r="C107" s="9"/>
+      <c r="C107" s="8">
+        <v>46204.89006237268</v>
+      </c>
       <c r="D107" s="8">
-        <v>46197.85223857639</v>
+        <v>46204.89006394676</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>216</v>
@@ -8365,9 +8375,11 @@
       <c r="B108" s="5">
         <v>46168.68371309028</v>
       </c>
-      <c r="C108" s="6"/>
+      <c r="C108" s="5">
+        <v>46204.89006787037</v>
+      </c>
       <c r="D108" s="5">
-        <v>46197.85232365741</v>
+        <v>46204.89006936342</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>216</v>
@@ -8418,9 +8430,11 @@
       <c r="B109" s="8">
         <v>46168.68371646991</v>
       </c>
-      <c r="C109" s="9"/>
+      <c r="C109" s="8">
+        <v>46204.89007861111</v>
+      </c>
       <c r="D109" s="8">
-        <v>46197.85242358796</v>
+        <v>46204.890080185185</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>220</v>
@@ -8833,7 +8847,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46168.85848048611</v>
+        <v>46204.893428194446</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>342</v>
@@ -8878,9 +8892,11 @@
       <c r="B117" s="8">
         <v>46168.68381783565</v>
       </c>
-      <c r="C117" s="9"/>
+      <c r="C117" s="8">
+        <v>46204.89075866898</v>
+      </c>
       <c r="D117" s="8">
-        <v>46197.49658452546</v>
+        <v>46204.890769143516</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>345</v>
@@ -8928,10 +8944,10 @@
         <v>32</v>
       </c>
       <c r="T117" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="U117" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U117" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8941,9 +8957,11 @@
       <c r="B118" s="5">
         <v>46168.683825810185</v>
       </c>
-      <c r="C118" s="6"/>
+      <c r="C118" s="5">
+        <v>46204.89074575232</v>
+      </c>
       <c r="D118" s="5">
-        <v>46168.86613042824</v>
+        <v>46204.89074728009</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>212</v>
@@ -8994,9 +9012,11 @@
       <c r="B119" s="8">
         <v>46168.68383587963</v>
       </c>
-      <c r="C119" s="9"/>
+      <c r="C119" s="8">
+        <v>46204.890660798614</v>
+      </c>
       <c r="D119" s="8">
-        <v>46168.866127685185</v>
+        <v>46204.8906627199</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>212</v>
@@ -9047,9 +9067,11 @@
       <c r="B120" s="5">
         <v>46168.68384034722</v>
       </c>
-      <c r="C120" s="6"/>
+      <c r="C120" s="5">
+        <v>46204.890518506945</v>
+      </c>
       <c r="D120" s="5">
-        <v>46197.85223737269</v>
+        <v>46204.89052016204</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>216</v>
@@ -9100,9 +9122,11 @@
       <c r="B121" s="8">
         <v>46168.683844074076</v>
       </c>
-      <c r="C121" s="9"/>
+      <c r="C121" s="8">
+        <v>46204.890504930554</v>
+      </c>
       <c r="D121" s="8">
-        <v>46168.8661222338</v>
+        <v>46204.89050689815</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>216</v>
@@ -9157,7 +9181,7 @@
         <v>46197.49592710648</v>
       </c>
       <c r="D122" s="5">
-        <v>46197.49592886574</v>
+        <v>46204.890087210646</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>220</v>
@@ -9208,9 +9232,11 @@
       <c r="B123" s="8">
         <v>46168.683862453705</v>
       </c>
-      <c r="C123" s="9"/>
+      <c r="C123" s="8">
+        <v>46204.89175555555</v>
+      </c>
       <c r="D123" s="8">
-        <v>46197.49666800926</v>
+        <v>46204.891766898145</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>357</v>
@@ -9258,10 +9284,10 @@
         <v>32</v>
       </c>
       <c r="T123" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="U123" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U123" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
@@ -9271,9 +9297,11 @@
       <c r="B124" s="5">
         <v>46168.683867141204</v>
       </c>
-      <c r="C124" s="6"/>
+      <c r="C124" s="5">
+        <v>46204.89097627315</v>
+      </c>
       <c r="D124" s="5">
-        <v>46190.60544122686</v>
+        <v>46204.89097825231</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>212</v>
@@ -9324,9 +9352,11 @@
       <c r="B125" s="8">
         <v>46168.683873368056</v>
       </c>
-      <c r="C125" s="9"/>
+      <c r="C125" s="8">
+        <v>46204.891655810185</v>
+      </c>
       <c r="D125" s="8">
-        <v>46190.60544332176</v>
+        <v>46204.89165733797</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>212</v>
@@ -9377,9 +9407,11 @@
       <c r="B126" s="5">
         <v>46168.68387903935</v>
       </c>
-      <c r="C126" s="6"/>
+      <c r="C126" s="5">
+        <v>46204.891740266205</v>
+      </c>
       <c r="D126" s="5">
-        <v>46190.60543283565</v>
+        <v>46204.89174199074</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>216</v>
@@ -9430,9 +9462,11 @@
       <c r="B127" s="8">
         <v>46168.683884618054</v>
       </c>
-      <c r="C127" s="9"/>
+      <c r="C127" s="8">
+        <v>46204.891592291664</v>
+      </c>
       <c r="D127" s="8">
-        <v>46190.605433379635</v>
+        <v>46204.89159396991</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>216</v>
@@ -9538,9 +9572,11 @@
       <c r="B129" s="8">
         <v>46168.68391289352</v>
       </c>
-      <c r="C129" s="9"/>
+      <c r="C129" s="8">
+        <v>46204.89298883102</v>
+      </c>
       <c r="D129" s="8">
-        <v>46197.49669130787</v>
+        <v>46204.89299085648</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>372</v>
@@ -9588,10 +9624,10 @@
         <v>32</v>
       </c>
       <c r="T129" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="U129" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U129" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
@@ -9601,9 +9637,11 @@
       <c r="B130" s="5">
         <v>46168.68391818287</v>
       </c>
-      <c r="C130" s="6"/>
+      <c r="C130" s="5">
+        <v>46204.89260358796</v>
+      </c>
       <c r="D130" s="5">
-        <v>46190.60543055556</v>
+        <v>46204.89260508102</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>212</v>
@@ -9654,9 +9692,11 @@
       <c r="B131" s="8">
         <v>46168.68393068287</v>
       </c>
-      <c r="C131" s="9"/>
+      <c r="C131" s="8">
+        <v>46204.89265783565</v>
+      </c>
       <c r="D131" s="8">
-        <v>46190.60543111111</v>
+        <v>46204.89265981481</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>212</v>
@@ -9707,9 +9747,11 @@
       <c r="B132" s="5">
         <v>46168.68393770834</v>
       </c>
-      <c r="C132" s="6"/>
+      <c r="C132" s="5">
+        <v>46204.89272398148</v>
+      </c>
       <c r="D132" s="5">
-        <v>46190.605433923614</v>
+        <v>46204.89272546297</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>216</v>
@@ -9760,9 +9802,11 @@
       <c r="B133" s="8">
         <v>46168.6839434375</v>
       </c>
-      <c r="C133" s="9"/>
+      <c r="C133" s="8">
+        <v>46204.89279275463</v>
+      </c>
       <c r="D133" s="8">
-        <v>46190.605443622684</v>
+        <v>46204.892794189815</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>216</v>
@@ -9868,9 +9912,11 @@
       <c r="B135" s="8">
         <v>46168.68401087963</v>
       </c>
-      <c r="C135" s="9"/>
+      <c r="C135" s="8">
+        <v>46204.893422152774</v>
+      </c>
       <c r="D135" s="8">
-        <v>46197.496712824075</v>
+        <v>46204.893423761576</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>387</v>
@@ -9918,10 +9964,10 @@
         <v>32</v>
       </c>
       <c r="T135" s="9">
-        <v>0.2</v>
-      </c>
-      <c r="U135" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U135" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
@@ -9931,9 +9977,11 @@
       <c r="B136" s="5">
         <v>46168.68401652778</v>
       </c>
-      <c r="C136" s="6"/>
+      <c r="C136" s="5">
+        <v>46204.89318240741</v>
+      </c>
       <c r="D136" s="5">
-        <v>46190.60543435185</v>
+        <v>46204.89318377315</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>212</v>
@@ -9984,9 +10032,11 @@
       <c r="B137" s="8">
         <v>46168.68402403935</v>
       </c>
-      <c r="C137" s="9"/>
+      <c r="C137" s="8">
+        <v>46204.89310061342</v>
+      </c>
       <c r="D137" s="8">
-        <v>46190.605431805554</v>
+        <v>46204.893101863425</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>212</v>
@@ -10037,9 +10087,11 @@
       <c r="B138" s="5">
         <v>46168.68403127315</v>
       </c>
-      <c r="C138" s="6"/>
+      <c r="C138" s="5">
+        <v>46204.89303716435</v>
+      </c>
       <c r="D138" s="5">
-        <v>46190.60543226852</v>
+        <v>46204.89303854167</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>216</v>
@@ -10090,9 +10142,11 @@
       <c r="B139" s="8">
         <v>46168.68403755787</v>
       </c>
-      <c r="C139" s="9"/>
+      <c r="C139" s="8">
+        <v>46204.892907511574</v>
+      </c>
       <c r="D139" s="8">
-        <v>46190.605434826386</v>
+        <v>46204.8929090625</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>216</v>
@@ -10200,7 +10254,7 @@
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46168.867681076386</v>
+        <v>46204.89333960648</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>401</v>
@@ -10263,7 +10317,7 @@
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46168.86765785879</v>
+        <v>46204.8931924537</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>212</v>
@@ -10316,7 +10370,7 @@
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46168.86765493055</v>
+        <v>46204.89310667824</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>212</v>
@@ -10369,7 +10423,7 @@
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46168.86764950231</v>
+        <v>46204.893044756944</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>216</v>
@@ -10422,7 +10476,7 @@
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46168.86764537037</v>
+        <v>46204.89291351852</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>216</v>
@@ -10473,9 +10527,11 @@
       <c r="B146" s="5">
         <v>46168.684094571756</v>
       </c>
-      <c r="C146" s="6"/>
+      <c r="C146" s="5">
+        <v>46204.8933341088</v>
+      </c>
       <c r="D146" s="5">
-        <v>46197.49627510417</v>
+        <v>46204.893335671295</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>220</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -2289,13 +2289,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46168.682976261574</v>
+        <v>46168.51630959491</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.87166331019</v>
+        <v>46175.704996643515</v>
       </c>
       <c r="D4" s="5">
-        <v>46182.80970267361</v>
+        <v>46182.64303600695</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2338,13 +2338,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46168.68312435185</v>
+        <v>46168.51645768518</v>
       </c>
       <c r="C5" s="8">
-        <v>46175.87163793981</v>
+        <v>46175.70497127315</v>
       </c>
       <c r="D5" s="8">
-        <v>46175.87166387732</v>
+        <v>46175.70499721065</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2401,13 +2401,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46168.683127743054</v>
+        <v>46168.51646107639</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.87163862269</v>
+        <v>46175.70497195602</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87166359954</v>
+        <v>46175.704996932865</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2464,13 +2464,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46168.683132754624</v>
+        <v>46168.51646608797</v>
       </c>
       <c r="C7" s="8">
-        <v>46175.87163902778</v>
+        <v>46175.70497236111</v>
       </c>
       <c r="D7" s="8">
-        <v>46175.87166400463</v>
+        <v>46175.70499733796</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2527,13 +2527,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46168.683135416664</v>
+        <v>46168.51646875</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.87163947917</v>
+        <v>46175.7049728125</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.871664895836</v>
+        <v>46175.704998229165</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2590,13 +2590,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46168.683139201385</v>
+        <v>46168.51647253473</v>
       </c>
       <c r="C9" s="8">
-        <v>46175.87164010417</v>
+        <v>46175.7049734375</v>
       </c>
       <c r="D9" s="8">
-        <v>46175.871664074075</v>
+        <v>46175.7049974074</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -2653,13 +2653,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46168.68298012731</v>
+        <v>46168.51631346065</v>
       </c>
       <c r="C10" s="5">
-        <v>46196.894165844904</v>
+        <v>46196.72749917824</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.89418670139</v>
+        <v>46196.72752003472</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2706,13 +2706,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46168.683142650465</v>
+        <v>46168.51647598379</v>
       </c>
       <c r="C11" s="8">
-        <v>46193.553165543985</v>
+        <v>46193.38649887731</v>
       </c>
       <c r="D11" s="8">
-        <v>46193.553190729166</v>
+        <v>46193.3865240625</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2771,13 +2771,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46168.683148310185</v>
+        <v>46168.51648164351</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.89414587963</v>
+        <v>46196.72747921296</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.894165879625</v>
+        <v>46196.72749921297</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2836,13 +2836,13 @@
         <v>60</v>
       </c>
       <c r="B13" s="8">
-        <v>46168.68315351852</v>
+        <v>46168.51648685185</v>
       </c>
       <c r="C13" s="8">
-        <v>46196.89430840278</v>
+        <v>46196.72764173611</v>
       </c>
       <c r="D13" s="8">
-        <v>46196.89431</v>
+        <v>46196.72764333333</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>61</v>
@@ -2891,13 +2891,13 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46168.68315625</v>
+        <v>46168.51648958333</v>
       </c>
       <c r="C14" s="5">
-        <v>46196.89435806713</v>
+        <v>46196.72769140046</v>
       </c>
       <c r="D14" s="5">
-        <v>46196.89435957176</v>
+        <v>46196.72769290509</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2946,13 +2946,13 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46168.68315891204</v>
+        <v>46168.51649224537</v>
       </c>
       <c r="C15" s="8">
-        <v>46196.894404120365</v>
+        <v>46196.72773745371</v>
       </c>
       <c r="D15" s="8">
-        <v>46196.89440576389</v>
+        <v>46196.72773909722</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>61</v>
@@ -3001,13 +3001,13 @@
         <v>64</v>
       </c>
       <c r="B16" s="5">
-        <v>46168.683161493056</v>
+        <v>46168.516494826385</v>
       </c>
       <c r="C16" s="5">
-        <v>46196.89445103009</v>
+        <v>46196.72778436342</v>
       </c>
       <c r="D16" s="5">
-        <v>46196.894452395834</v>
+        <v>46196.72778572916</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>65</v>
@@ -3056,13 +3056,13 @@
         <v>66</v>
       </c>
       <c r="B17" s="8">
-        <v>46168.68316400463</v>
+        <v>46168.51649733796</v>
       </c>
       <c r="C17" s="8">
-        <v>46196.894503090276</v>
+        <v>46196.72783642361</v>
       </c>
       <c r="D17" s="8">
-        <v>46196.89450475694</v>
+        <v>46196.72783809028</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>65</v>
@@ -3111,13 +3111,13 @@
         <v>67</v>
       </c>
       <c r="B18" s="5">
-        <v>46168.68316714121</v>
+        <v>46168.516500474536</v>
       </c>
       <c r="C18" s="5">
-        <v>46196.894556087966</v>
+        <v>46196.727889421294</v>
       </c>
       <c r="D18" s="5">
-        <v>46196.894558009255</v>
+        <v>46196.7278913426</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>68</v>
@@ -3166,11 +3166,11 @@
         <v>69</v>
       </c>
       <c r="B19" s="8">
-        <v>46168.682984189814</v>
+        <v>46168.51631752314</v>
       </c>
       <c r="C19" s="9"/>
       <c r="D19" s="8">
-        <v>46196.87778789352</v>
+        <v>46196.71112122685</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>70</v>
@@ -3215,13 +3215,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46168.68317581018</v>
+        <v>46168.51650914352</v>
       </c>
       <c r="C20" s="5">
-        <v>46183.871377627314</v>
+        <v>46183.70471096065</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.87777847222</v>
+        <v>46196.711111805555</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -3280,13 +3280,13 @@
         <v>79</v>
       </c>
       <c r="B21" s="8">
-        <v>46168.6831808912</v>
+        <v>46168.51651422454</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.87138545139</v>
+        <v>46183.70471878472</v>
       </c>
       <c r="D21" s="8">
-        <v>46196.877778333335</v>
+        <v>46196.711111666664</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>80</v>
@@ -3345,13 +3345,13 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46168.68318591436</v>
+        <v>46168.516519247685</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.87139542824</v>
+        <v>46183.70472876157</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.87777902778</v>
+        <v>46196.71111236111</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -3410,13 +3410,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46168.68298827547</v>
+        <v>46168.5163216088</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.85300722222</v>
+        <v>46197.686340555556</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.85302019676</v>
+        <v>46197.686353530094</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3463,13 +3463,13 @@
         <v>89</v>
       </c>
       <c r="B24" s="5">
-        <v>46168.68319888889</v>
+        <v>46168.516532222224</v>
       </c>
       <c r="C24" s="5">
-        <v>46193.553062349536</v>
+        <v>46193.38639568287</v>
       </c>
       <c r="D24" s="5">
-        <v>46193.5530831713</v>
+        <v>46193.386416504625</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>90</v>
@@ -3528,13 +3528,13 @@
         <v>92</v>
       </c>
       <c r="B25" s="8">
-        <v>46168.68320439815</v>
+        <v>46168.516537731484</v>
       </c>
       <c r="C25" s="8">
-        <v>46193.55307400463</v>
+        <v>46193.38640733797</v>
       </c>
       <c r="D25" s="8">
-        <v>46193.55308946759</v>
+        <v>46193.386422800926</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>93</v>
@@ -3593,13 +3593,13 @@
         <v>95</v>
       </c>
       <c r="B26" s="5">
-        <v>46168.68320962963</v>
+        <v>46168.51654296296</v>
       </c>
       <c r="C26" s="5">
-        <v>46183.904405775465</v>
+        <v>46183.737739108794</v>
       </c>
       <c r="D26" s="5">
-        <v>46183.90442146991</v>
+        <v>46183.73775480324</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>96</v>
@@ -3658,13 +3658,13 @@
         <v>99</v>
       </c>
       <c r="B27" s="8">
-        <v>46168.68321476852</v>
+        <v>46168.51654810185</v>
       </c>
       <c r="C27" s="8">
-        <v>46197.852991875</v>
+        <v>46197.686325208335</v>
       </c>
       <c r="D27" s="8">
-        <v>46197.8530077662</v>
+        <v>46197.686341099536</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>100</v>
@@ -3723,13 +3723,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="5">
-        <v>46168.68321959491</v>
+        <v>46168.51655292824</v>
       </c>
       <c r="C28" s="5">
-        <v>46196.646673379626</v>
+        <v>46196.48000671296</v>
       </c>
       <c r="D28" s="5">
-        <v>46196.64668813658</v>
+        <v>46196.480021469906</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -3788,13 +3788,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46168.68322341435</v>
+        <v>46168.51655674769</v>
       </c>
       <c r="C29" s="8">
-        <v>46196.6474043287</v>
+        <v>46196.48073766204</v>
       </c>
       <c r="D29" s="8">
-        <v>46196.647418912034</v>
+        <v>46196.48075224537</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>110</v>
@@ -3853,13 +3853,13 @@
         <v>112</v>
       </c>
       <c r="B30" s="5">
-        <v>46168.683227245376</v>
+        <v>46168.516560578704</v>
       </c>
       <c r="C30" s="5">
-        <v>46196.64760480324</v>
+        <v>46196.48093813658</v>
       </c>
       <c r="D30" s="5">
-        <v>46196.64801533565</v>
+        <v>46196.48134866898</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -3918,13 +3918,13 @@
         <v>115</v>
       </c>
       <c r="B31" s="8">
-        <v>46168.683231365736</v>
+        <v>46168.51656469908</v>
       </c>
       <c r="C31" s="8">
-        <v>46193.55346230324</v>
+        <v>46193.38679563657</v>
       </c>
       <c r="D31" s="8">
-        <v>46193.553499305555</v>
+        <v>46193.38683263889</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>116</v>
@@ -3983,11 +3983,11 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46168.682992511574</v>
+        <v>46168.5163258449</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46199.56506112269</v>
+        <v>46199.39839445602</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -4030,13 +4030,13 @@
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46168.68327652778</v>
+        <v>46168.51660986111</v>
       </c>
       <c r="C33" s="8">
-        <v>46195.928382708335</v>
+        <v>46195.76171604167</v>
       </c>
       <c r="D33" s="8">
-        <v>46195.928396574076</v>
+        <v>46195.761729907405</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -4095,13 +4095,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46168.68328149305</v>
+        <v>46168.51661482639</v>
       </c>
       <c r="C34" s="5">
-        <v>46195.92582877315</v>
+        <v>46195.75916210648</v>
       </c>
       <c r="D34" s="5">
-        <v>46195.9258303588</v>
+        <v>46195.75916369213</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -4156,13 +4156,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46168.68328653935</v>
+        <v>46168.51661987268</v>
       </c>
       <c r="C35" s="8">
-        <v>46195.92836857639</v>
+        <v>46195.76170190972</v>
       </c>
       <c r="D35" s="8">
-        <v>46195.928370243055</v>
+        <v>46195.76170357639</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -4217,13 +4217,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46168.68329140046</v>
+        <v>46168.51662473379</v>
       </c>
       <c r="C36" s="5">
-        <v>46184.70362789352</v>
+        <v>46184.536961226855</v>
       </c>
       <c r="D36" s="5">
-        <v>46185.182775243054</v>
+        <v>46185.01610857639</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4282,13 +4282,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46168.68329584491</v>
+        <v>46168.51662917824</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.70350231482</v>
+        <v>46184.53683564815</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.70350368056</v>
+        <v>46184.53683701389</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -4343,13 +4343,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46168.68330070602</v>
+        <v>46168.51663403935</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.70355657407</v>
+        <v>46184.53688990741</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.703557789355</v>
+        <v>46184.53689112268</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -4404,11 +4404,11 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46168.68330542824</v>
+        <v>46168.516638761575</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="8">
-        <v>46199.18005736111</v>
+        <v>46199.01339069444</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4467,13 +4467,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46168.683310092594</v>
+        <v>46168.51664342593</v>
       </c>
       <c r="C40" s="5">
-        <v>46195.92586883102</v>
+        <v>46195.75920216435</v>
       </c>
       <c r="D40" s="5">
-        <v>46195.92587128472</v>
+        <v>46195.75920461805</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4528,11 +4528,11 @@
         <v>148</v>
       </c>
       <c r="B41" s="8">
-        <v>46168.68331519676</v>
+        <v>46168.516648530094</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="8">
-        <v>46198.16936840278</v>
+        <v>46198.00270173611</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -4587,13 +4587,13 @@
         <v>151</v>
       </c>
       <c r="B42" s="5">
-        <v>46168.68332027778</v>
+        <v>46168.51665361111</v>
       </c>
       <c r="C42" s="5">
-        <v>46184.70284971065</v>
+        <v>46184.53618304398</v>
       </c>
       <c r="D42" s="5">
-        <v>46195.92587850694</v>
+        <v>46195.75921184028</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>152</v>
@@ -4648,13 +4648,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="8">
-        <v>46168.68332520833</v>
+        <v>46168.51665854167</v>
       </c>
       <c r="C43" s="8">
-        <v>46195.92858413194</v>
+        <v>46195.76191746528</v>
       </c>
       <c r="D43" s="8">
-        <v>46195.92859513889</v>
+        <v>46195.76192847222</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>155</v>
@@ -4713,13 +4713,13 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46168.68332880787</v>
+        <v>46168.516662141206</v>
       </c>
       <c r="C44" s="5">
-        <v>46195.92577711806</v>
+        <v>46195.759110451385</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.92577891204</v>
+        <v>46195.759112245374</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>117</v>
@@ -4768,13 +4768,13 @@
         <v>159</v>
       </c>
       <c r="B45" s="8">
-        <v>46168.683333113426</v>
+        <v>46168.516666446754</v>
       </c>
       <c r="C45" s="8">
-        <v>46195.92856840278</v>
+        <v>46195.761901736114</v>
       </c>
       <c r="D45" s="8">
-        <v>46195.92857017361</v>
+        <v>46195.761903506944</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -4823,13 +4823,13 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46168.683337291666</v>
+        <v>46168.516670625</v>
       </c>
       <c r="C46" s="5">
-        <v>46199.5650503588</v>
+        <v>46199.398383692125</v>
       </c>
       <c r="D46" s="5">
-        <v>46204.1978837037</v>
+        <v>46204.03121703704</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4888,13 +4888,13 @@
         <v>167</v>
       </c>
       <c r="B47" s="8">
-        <v>46168.68334179398</v>
+        <v>46168.516675127314</v>
       </c>
       <c r="C47" s="8">
-        <v>46199.56498643519</v>
+        <v>46199.398319768516</v>
       </c>
       <c r="D47" s="8">
-        <v>46199.564988564816</v>
+        <v>46199.398321898145</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>168</v>
@@ -4949,13 +4949,13 @@
         <v>170</v>
       </c>
       <c r="B48" s="5">
-        <v>46168.68334684028</v>
+        <v>46168.51668017361</v>
       </c>
       <c r="C48" s="5">
-        <v>46199.56503596065</v>
+        <v>46199.39836929398</v>
       </c>
       <c r="D48" s="5">
-        <v>46199.5650378125</v>
+        <v>46199.398371145835</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -5010,13 +5010,13 @@
         <v>173</v>
       </c>
       <c r="B49" s="8">
-        <v>46168.68335195602</v>
+        <v>46168.51668528935</v>
       </c>
       <c r="C49" s="8">
-        <v>46199.565312569444</v>
+        <v>46199.39864590278</v>
       </c>
       <c r="D49" s="8">
-        <v>46204.19788363426</v>
+        <v>46204.03121696759</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>174</v>
@@ -5075,13 +5075,13 @@
         <v>176</v>
       </c>
       <c r="B50" s="5">
-        <v>46168.68335582176</v>
+        <v>46168.51668915509</v>
       </c>
       <c r="C50" s="5">
-        <v>46199.56512105324</v>
+        <v>46199.39845438657</v>
       </c>
       <c r="D50" s="5">
-        <v>46199.56512275463</v>
+        <v>46199.39845608796</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>108</v>
@@ -5130,13 +5130,13 @@
         <v>178</v>
       </c>
       <c r="B51" s="8">
-        <v>46168.683360428244</v>
+        <v>46168.51669376157</v>
       </c>
       <c r="C51" s="8">
-        <v>46199.565198819444</v>
+        <v>46199.39853215277</v>
       </c>
       <c r="D51" s="8">
-        <v>46199.56520053241</v>
+        <v>46199.39853386574</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>179</v>
@@ -5185,13 +5185,13 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46168.68336471065</v>
+        <v>46168.51669804398</v>
       </c>
       <c r="C52" s="5">
-        <v>46204.86077883102</v>
+        <v>46204.69411216435</v>
       </c>
       <c r="D52" s="5">
-        <v>46204.860797534726</v>
+        <v>46204.694130868054</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -5250,13 +5250,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46168.68337377315</v>
+        <v>46168.51670710648</v>
       </c>
       <c r="C53" s="8">
-        <v>46204.601483715276</v>
+        <v>46204.43481704861</v>
       </c>
       <c r="D53" s="8">
-        <v>46204.601485555555</v>
+        <v>46204.43481888888</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>114</v>
@@ -5305,13 +5305,13 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46168.683378194444</v>
+        <v>46168.51671152777</v>
       </c>
       <c r="C54" s="5">
-        <v>46204.60153940972</v>
+        <v>46204.434872743055</v>
       </c>
       <c r="D54" s="5">
-        <v>46204.601540787036</v>
+        <v>46204.43487412037</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5360,11 +5360,11 @@
         <v>191</v>
       </c>
       <c r="B55" s="8">
-        <v>46168.68338271991</v>
+        <v>46168.516716053244</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46204.60155028936</v>
+        <v>46204.434883622685</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>192</v>
@@ -5413,13 +5413,13 @@
         <v>195</v>
       </c>
       <c r="B56" s="5">
-        <v>46168.683385868055</v>
+        <v>46168.51671920139</v>
       </c>
       <c r="C56" s="5">
-        <v>46199.56545385417</v>
+        <v>46199.3987871875</v>
       </c>
       <c r="D56" s="5">
-        <v>46204.19788391204</v>
+        <v>46204.03121724537</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5478,13 +5478,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46168.68343064815</v>
+        <v>46168.51676398148</v>
       </c>
       <c r="C57" s="8">
-        <v>46199.565352418984</v>
+        <v>46199.39868575231</v>
       </c>
       <c r="D57" s="8">
-        <v>46199.56535409723</v>
+        <v>46199.398687430556</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>111</v>
@@ -5533,13 +5533,13 @@
         <v>200</v>
       </c>
       <c r="B58" s="5">
-        <v>46168.683436956024</v>
+        <v>46168.51677028935</v>
       </c>
       <c r="C58" s="5">
-        <v>46199.56543844908</v>
+        <v>46199.398771782406</v>
       </c>
       <c r="D58" s="5">
-        <v>46199.56544034722</v>
+        <v>46199.39877368056</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>201</v>
@@ -5588,11 +5588,11 @@
         <v>203</v>
       </c>
       <c r="B59" s="8">
-        <v>46168.68344221065</v>
+        <v>46168.516775543976</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46190.60524740741</v>
+        <v>46190.43858074074</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>204</v>
@@ -5637,13 +5637,13 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46168.683445787035</v>
+        <v>46168.51677912037</v>
       </c>
       <c r="C60" s="5">
-        <v>46184.51882697917</v>
+        <v>46184.3521603125</v>
       </c>
       <c r="D60" s="5">
-        <v>46184.518844583334</v>
+        <v>46184.35217791666</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5702,13 +5702,13 @@
         <v>211</v>
       </c>
       <c r="B61" s="8">
-        <v>46168.6865996875</v>
+        <v>46168.519933020834</v>
       </c>
       <c r="C61" s="8">
-        <v>46184.5187849537</v>
+        <v>46184.35211828703</v>
       </c>
       <c r="D61" s="8">
-        <v>46184.51878665509</v>
+        <v>46184.35211998843</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>212</v>
@@ -5757,13 +5757,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46168.68683460648</v>
+        <v>46168.520167939816</v>
       </c>
       <c r="C62" s="5">
-        <v>46184.51878982639</v>
+        <v>46184.352123159726</v>
       </c>
       <c r="D62" s="5">
-        <v>46184.518791319446</v>
+        <v>46184.35212465278</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>212</v>
@@ -5812,13 +5812,13 @@
         <v>215</v>
       </c>
       <c r="B63" s="8">
-        <v>46168.686918437495</v>
+        <v>46168.52025177084</v>
       </c>
       <c r="C63" s="8">
-        <v>46184.51879787037</v>
+        <v>46184.352131203705</v>
       </c>
       <c r="D63" s="8">
-        <v>46184.51879930556</v>
+        <v>46184.35213263889</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>216</v>
@@ -5867,13 +5867,13 @@
         <v>218</v>
       </c>
       <c r="B64" s="5">
-        <v>46168.687254143515</v>
+        <v>46168.52058747685</v>
       </c>
       <c r="C64" s="5">
-        <v>46184.518805625004</v>
+        <v>46184.35213895833</v>
       </c>
       <c r="D64" s="5">
-        <v>46184.5188068287</v>
+        <v>46184.35214016204</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5922,13 +5922,13 @@
         <v>219</v>
       </c>
       <c r="B65" s="8">
-        <v>46168.68731635417</v>
+        <v>46168.5206496875</v>
       </c>
       <c r="C65" s="8">
-        <v>46184.51881311343</v>
+        <v>46184.35214644676</v>
       </c>
       <c r="D65" s="8">
-        <v>46184.51881454861</v>
+        <v>46184.352147881946</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>220</v>
@@ -5977,13 +5977,13 @@
         <v>222</v>
       </c>
       <c r="B66" s="5">
-        <v>46168.68345142361</v>
+        <v>46168.51678475694</v>
       </c>
       <c r="C66" s="5">
-        <v>46190.60523084491</v>
+        <v>46190.43856417824</v>
       </c>
       <c r="D66" s="5">
-        <v>46190.605242708334</v>
+        <v>46190.43857604166</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>223</v>
@@ -6042,13 +6042,13 @@
         <v>224</v>
       </c>
       <c r="B67" s="8">
-        <v>46168.68857346065</v>
+        <v>46168.521906793976</v>
       </c>
       <c r="C67" s="8">
-        <v>46190.60518377315</v>
+        <v>46190.43851710648</v>
       </c>
       <c r="D67" s="8">
-        <v>46190.60518608797</v>
+        <v>46190.438519421295</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>212</v>
@@ -6097,13 +6097,13 @@
         <v>227</v>
       </c>
       <c r="B68" s="5">
-        <v>46168.688608275465</v>
+        <v>46168.52194160879</v>
       </c>
       <c r="C68" s="5">
-        <v>46190.60519341435</v>
+        <v>46190.43852674769</v>
       </c>
       <c r="D68" s="5">
-        <v>46190.60519502315</v>
+        <v>46190.43852835648</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>212</v>
@@ -6152,13 +6152,13 @@
         <v>228</v>
       </c>
       <c r="B69" s="8">
-        <v>46168.68864659722</v>
+        <v>46168.521979930556</v>
       </c>
       <c r="C69" s="8">
-        <v>46190.60520133102</v>
+        <v>46190.438534664354</v>
       </c>
       <c r="D69" s="8">
-        <v>46190.605203761574</v>
+        <v>46190.4385370949</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>216</v>
@@ -6207,13 +6207,13 @@
         <v>231</v>
       </c>
       <c r="B70" s="5">
-        <v>46168.68868637731</v>
+        <v>46168.52201971065</v>
       </c>
       <c r="C70" s="5">
-        <v>46190.60520737269</v>
+        <v>46190.43854070602</v>
       </c>
       <c r="D70" s="5">
-        <v>46190.605208946756</v>
+        <v>46190.43854228009</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>216</v>
@@ -6262,13 +6262,13 @@
         <v>233</v>
       </c>
       <c r="B71" s="8">
-        <v>46168.68871934028</v>
+        <v>46168.52205267361</v>
       </c>
       <c r="C71" s="8">
-        <v>46190.60521491898</v>
+        <v>46190.438548252314</v>
       </c>
       <c r="D71" s="8">
-        <v>46190.60521709491</v>
+        <v>46190.43855042824</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>220</v>
@@ -6317,13 +6317,13 @@
         <v>236</v>
       </c>
       <c r="B72" s="5">
-        <v>46168.68345790509</v>
+        <v>46168.51679123843</v>
       </c>
       <c r="C72" s="5">
-        <v>46190.60541208333</v>
+        <v>46190.43874541667</v>
       </c>
       <c r="D72" s="5">
-        <v>46190.6054244213</v>
+        <v>46190.43875775463</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>103</v>
@@ -6382,13 +6382,13 @@
         <v>239</v>
       </c>
       <c r="B73" s="8">
-        <v>46168.68880178241</v>
+        <v>46168.52213511574</v>
       </c>
       <c r="C73" s="8">
-        <v>46190.605361643524</v>
+        <v>46190.43869497685</v>
       </c>
       <c r="D73" s="8">
-        <v>46190.60536361111</v>
+        <v>46190.438696944446</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>212</v>
@@ -6437,13 +6437,13 @@
         <v>240</v>
       </c>
       <c r="B74" s="5">
-        <v>46168.68883857639</v>
+        <v>46168.52217190972</v>
       </c>
       <c r="C74" s="5">
-        <v>46190.60536678241</v>
+        <v>46190.438700115745</v>
       </c>
       <c r="D74" s="5">
-        <v>46190.605368206016</v>
+        <v>46190.43870153935</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>212</v>
@@ -6492,13 +6492,13 @@
         <v>241</v>
       </c>
       <c r="B75" s="8">
-        <v>46168.688875775464</v>
+        <v>46168.52220910879</v>
       </c>
       <c r="C75" s="8">
-        <v>46190.605371956015</v>
+        <v>46190.43870528935</v>
       </c>
       <c r="D75" s="8">
-        <v>46190.605373530096</v>
+        <v>46190.438706863424</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>216</v>
@@ -6547,13 +6547,13 @@
         <v>242</v>
       </c>
       <c r="B76" s="5">
-        <v>46168.6889172338</v>
+        <v>46168.522250567126</v>
       </c>
       <c r="C76" s="5">
-        <v>46190.60539791667</v>
+        <v>46190.438731250004</v>
       </c>
       <c r="D76" s="5">
-        <v>46190.60539957176</v>
+        <v>46190.438732905095</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>243</v>
@@ -6602,13 +6602,13 @@
         <v>244</v>
       </c>
       <c r="B77" s="8">
-        <v>46168.688956620375</v>
+        <v>46168.522289953704</v>
       </c>
       <c r="C77" s="8">
-        <v>46190.60538663194</v>
+        <v>46190.43871996528</v>
       </c>
       <c r="D77" s="8">
-        <v>46190.60538814815</v>
+        <v>46190.43872148148</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>220</v>
@@ -6657,11 +6657,11 @@
         <v>245</v>
       </c>
       <c r="B78" s="5">
-        <v>46168.683480625</v>
+        <v>46168.51681395833</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46168.86495055555</v>
+        <v>46168.69828388889</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>246</v>
@@ -6718,11 +6718,11 @@
         <v>250</v>
       </c>
       <c r="B79" s="8">
-        <v>46168.683484629626</v>
+        <v>46168.51681796296</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46168.86492854166</v>
+        <v>46168.698261875004</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>212</v>
@@ -6771,11 +6771,11 @@
         <v>252</v>
       </c>
       <c r="B80" s="5">
-        <v>46168.683488877316</v>
+        <v>46168.516822210644</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46168.86492561342</v>
+        <v>46168.69825894676</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>212</v>
@@ -6824,11 +6824,11 @@
         <v>253</v>
       </c>
       <c r="B81" s="8">
-        <v>46168.68349300926</v>
+        <v>46168.51682634259</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46168.86492288194</v>
+        <v>46168.69825621528</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>216</v>
@@ -6877,11 +6877,11 @@
         <v>254</v>
       </c>
       <c r="B82" s="5">
-        <v>46168.6834959375</v>
+        <v>46168.51682927083</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46168.864920162036</v>
+        <v>46168.69825349537</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>216</v>
@@ -6930,11 +6930,11 @@
         <v>255</v>
       </c>
       <c r="B83" s="8">
-        <v>46168.68349899305</v>
+        <v>46168.51683232639</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46204.89334085648</v>
+        <v>46204.72667418982</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>220</v>
@@ -6983,11 +6983,11 @@
         <v>256</v>
       </c>
       <c r="B84" s="5">
-        <v>46168.68351101852</v>
+        <v>46168.51684435185</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46197.851189953704</v>
+        <v>46197.68452328704</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>257</v>
@@ -7030,11 +7030,11 @@
         <v>259</v>
       </c>
       <c r="B85" s="8">
-        <v>46168.68351447917</v>
+        <v>46168.5168478125</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46199.56505399305</v>
+        <v>46205.00218876157</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>260</v>
@@ -7093,13 +7093,13 @@
         <v>265</v>
       </c>
       <c r="B86" s="5">
-        <v>46168.68352011574</v>
+        <v>46168.51685344907</v>
       </c>
       <c r="C86" s="5">
-        <v>46197.85117512732</v>
+        <v>46197.68450846065</v>
       </c>
       <c r="D86" s="5">
-        <v>46202.16723841435</v>
+        <v>46202.00057174769</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>266</v>
@@ -7158,11 +7158,11 @@
         <v>269</v>
       </c>
       <c r="B87" s="8">
-        <v>46168.68352736111</v>
+        <v>46168.51686069445</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46199.56521630787</v>
+        <v>46205.00219209491</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -7221,13 +7221,13 @@
         <v>272</v>
       </c>
       <c r="B88" s="5">
-        <v>46168.68353292824</v>
+        <v>46168.516866261576</v>
       </c>
       <c r="C88" s="5">
-        <v>46197.851300173614</v>
+        <v>46197.68463350694</v>
       </c>
       <c r="D88" s="5">
-        <v>46202.167238229165</v>
+        <v>46202.0005715625</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>273</v>
@@ -7286,11 +7286,11 @@
         <v>275</v>
       </c>
       <c r="B89" s="8">
-        <v>46168.68353787037</v>
+        <v>46168.516871203705</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46199.56545707176</v>
+        <v>46205.00219377315</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>276</v>
@@ -7349,13 +7349,13 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46168.68354247685</v>
+        <v>46168.516875810186</v>
       </c>
       <c r="C90" s="5">
-        <v>46197.85161460648</v>
+        <v>46197.684947939815</v>
       </c>
       <c r="D90" s="5">
-        <v>46202.16723857639</v>
+        <v>46202.000571909724</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>277</v>
@@ -7414,11 +7414,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46168.68354741899</v>
+        <v>46168.516880752315</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46204.89010925926</v>
+        <v>46204.72344259259</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -7463,13 +7463,13 @@
         <v>282</v>
       </c>
       <c r="B92" s="5">
-        <v>46168.68355052083</v>
+        <v>46168.516883854165</v>
       </c>
       <c r="C92" s="5">
-        <v>46192.63405665509</v>
+        <v>46192.46738998842</v>
       </c>
       <c r="D92" s="5">
-        <v>46197.85264056713</v>
+        <v>46205.01169530093</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>
@@ -7513,8 +7513,8 @@
       <c r="R92" s="5">
         <v>46212</v>
       </c>
-      <c r="S92" s="10" t="s">
-        <v>32</v>
+      <c r="S92" s="11" t="s">
+        <v>264</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -7528,13 +7528,13 @@
         <v>287</v>
       </c>
       <c r="B93" s="8">
-        <v>46168.68356208333</v>
+        <v>46168.516895416666</v>
       </c>
       <c r="C93" s="8">
-        <v>46197.85262831018</v>
+        <v>46197.68596164352</v>
       </c>
       <c r="D93" s="8">
-        <v>46197.85263298611</v>
+        <v>46197.68596631945</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>212</v>
@@ -7583,13 +7583,13 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46168.68356922454</v>
+        <v>46168.516902557865</v>
       </c>
       <c r="C94" s="5">
-        <v>46197.85262942129</v>
+        <v>46197.68596275463</v>
       </c>
       <c r="D94" s="5">
-        <v>46197.85263334491</v>
+        <v>46197.68596667824</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>212</v>
@@ -7638,13 +7638,13 @@
         <v>292</v>
       </c>
       <c r="B95" s="8">
-        <v>46168.683574780094</v>
+        <v>46168.51690811342</v>
       </c>
       <c r="C95" s="8">
-        <v>46197.85263005787</v>
+        <v>46197.6859633912</v>
       </c>
       <c r="D95" s="8">
-        <v>46197.85263368055</v>
+        <v>46197.68596701389</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>216</v>
@@ -7693,13 +7693,13 @@
         <v>295</v>
       </c>
       <c r="B96" s="5">
-        <v>46168.68358024306</v>
+        <v>46168.516913576386</v>
       </c>
       <c r="C96" s="5">
-        <v>46197.85263069444</v>
+        <v>46197.685964027776</v>
       </c>
       <c r="D96" s="5">
-        <v>46197.852634062496</v>
+        <v>46197.68596739583</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>216</v>
@@ -7748,13 +7748,13 @@
         <v>296</v>
       </c>
       <c r="B97" s="8">
-        <v>46168.68358578703</v>
+        <v>46168.516919120375</v>
       </c>
       <c r="C97" s="8">
-        <v>46197.85263130787</v>
+        <v>46197.685964641205</v>
       </c>
       <c r="D97" s="8">
-        <v>46197.852634490744</v>
+        <v>46197.68596782407</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>220</v>
@@ -7803,13 +7803,13 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46168.68365474537</v>
+        <v>46168.5169880787</v>
       </c>
       <c r="C98" s="5">
-        <v>46197.85007665509</v>
+        <v>46197.68340998843</v>
       </c>
       <c r="D98" s="5">
-        <v>46197.85243150463</v>
+        <v>46197.68576483797</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>299</v>
@@ -7868,13 +7868,13 @@
         <v>301</v>
       </c>
       <c r="B99" s="8">
-        <v>46168.683659965274</v>
+        <v>46168.51699329861</v>
       </c>
       <c r="C99" s="8">
-        <v>46197.85183020833</v>
+        <v>46197.68516354167</v>
       </c>
       <c r="D99" s="8">
-        <v>46197.852639861114</v>
+        <v>46197.68597319444</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>212</v>
@@ -7923,13 +7923,13 @@
         <v>304</v>
       </c>
       <c r="B100" s="5">
-        <v>46168.68366613426</v>
+        <v>46168.516999467596</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.85205292824</v>
+        <v>46197.685386261575</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.85263996528</v>
+        <v>46197.68597329861</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>212</v>
@@ -7978,13 +7978,13 @@
         <v>306</v>
       </c>
       <c r="B101" s="8">
-        <v>46168.683671921295</v>
+        <v>46168.51700525463</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.852225717594</v>
+        <v>46197.68555905092</v>
       </c>
       <c r="D101" s="8">
-        <v>46197.852640173616</v>
+        <v>46197.685973506945</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>216</v>
@@ -8033,13 +8033,13 @@
         <v>308</v>
       </c>
       <c r="B102" s="5">
-        <v>46168.68367622685</v>
+        <v>46168.517009560186</v>
       </c>
       <c r="C102" s="5">
-        <v>46197.8523160301</v>
+        <v>46197.685649363426</v>
       </c>
       <c r="D102" s="5">
-        <v>46197.85264196759</v>
+        <v>46197.68597530093</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>216</v>
@@ -8088,13 +8088,13 @@
         <v>310</v>
       </c>
       <c r="B103" s="8">
-        <v>46168.683680069444</v>
+        <v>46168.51701340278</v>
       </c>
       <c r="C103" s="8">
-        <v>46197.852413217595</v>
+        <v>46197.685746550924</v>
       </c>
       <c r="D103" s="8">
-        <v>46197.85264373843</v>
+        <v>46197.68597707176</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>220</v>
@@ -8143,13 +8143,13 @@
         <v>312</v>
       </c>
       <c r="B104" s="5">
-        <v>46168.68369409722</v>
+        <v>46168.51702743056</v>
       </c>
       <c r="C104" s="5">
-        <v>46204.89009226851</v>
+        <v>46204.72342560186</v>
       </c>
       <c r="D104" s="5">
-        <v>46204.8901028588</v>
+        <v>46204.72343619213</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>313</v>
@@ -8208,13 +8208,13 @@
         <v>315</v>
       </c>
       <c r="B105" s="8">
-        <v>46168.68369849537</v>
+        <v>46168.517031828706</v>
       </c>
       <c r="C105" s="8">
-        <v>46204.890049884256</v>
+        <v>46204.72338321759</v>
       </c>
       <c r="D105" s="8">
-        <v>46204.890051967595</v>
+        <v>46204.723385300924</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>212</v>
@@ -8263,13 +8263,13 @@
         <v>317</v>
       </c>
       <c r="B106" s="5">
-        <v>46168.683704490744</v>
+        <v>46168.51703782407</v>
       </c>
       <c r="C106" s="5">
-        <v>46204.89005663195</v>
+        <v>46204.72338996528</v>
       </c>
       <c r="D106" s="5">
-        <v>46204.890058125005</v>
+        <v>46204.723391458334</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>318</v>
@@ -8318,13 +8318,13 @@
         <v>320</v>
       </c>
       <c r="B107" s="8">
-        <v>46168.683710150464</v>
+        <v>46168.51704348379</v>
       </c>
       <c r="C107" s="8">
-        <v>46204.89006237268</v>
+        <v>46204.72339570602</v>
       </c>
       <c r="D107" s="8">
-        <v>46204.89006394676</v>
+        <v>46204.72339728009</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>216</v>
@@ -8373,13 +8373,13 @@
         <v>321</v>
       </c>
       <c r="B108" s="5">
-        <v>46168.68371309028</v>
+        <v>46168.517046423614</v>
       </c>
       <c r="C108" s="5">
-        <v>46204.89006787037</v>
+        <v>46204.72340120371</v>
       </c>
       <c r="D108" s="5">
-        <v>46204.89006936342</v>
+        <v>46204.72340269676</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>216</v>
@@ -8428,13 +8428,13 @@
         <v>323</v>
       </c>
       <c r="B109" s="8">
-        <v>46168.68371646991</v>
+        <v>46168.51704980324</v>
       </c>
       <c r="C109" s="8">
-        <v>46204.89007861111</v>
+        <v>46204.72341194445</v>
       </c>
       <c r="D109" s="8">
-        <v>46204.890080185185</v>
+        <v>46204.72341351851</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>220</v>
@@ -8483,11 +8483,11 @@
         <v>325</v>
       </c>
       <c r="B110" s="5">
-        <v>46168.68373005787</v>
+        <v>46168.517063391206</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46168.854865925925</v>
+        <v>46168.68819925926</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>257</v>
@@ -8530,11 +8530,11 @@
         <v>327</v>
       </c>
       <c r="B111" s="8">
-        <v>46168.68373365741</v>
+        <v>46168.51706699074</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46186.16818170139</v>
+        <v>46186.00151503472</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>328</v>
@@ -8593,11 +8593,11 @@
         <v>330</v>
       </c>
       <c r="B112" s="5">
-        <v>46168.6837408912</v>
+        <v>46168.51707422454</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46195.928386898144</v>
+        <v>46195.76172023149</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>331</v>
@@ -8654,11 +8654,11 @@
         <v>333</v>
       </c>
       <c r="B113" s="8">
-        <v>46168.68374771991</v>
+        <v>46168.51708105324</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46200.16903983796</v>
+        <v>46200.0023731713</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>334</v>
@@ -8717,11 +8717,11 @@
         <v>336</v>
       </c>
       <c r="B114" s="5">
-        <v>46168.68375502314</v>
+        <v>46168.517088356486</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46204.60155983796</v>
+        <v>46204.434893171296</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>337</v>
@@ -8780,11 +8780,11 @@
         <v>339</v>
       </c>
       <c r="B115" s="8">
-        <v>46168.6837971412</v>
+        <v>46168.51713047454</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46196.80794189815</v>
+        <v>46196.64127523148</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>58</v>
@@ -8843,11 +8843,11 @@
         <v>341</v>
       </c>
       <c r="B116" s="5">
-        <v>46168.68381362269</v>
+        <v>46168.517146956015</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46204.893428194446</v>
+        <v>46204.72676152778</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>342</v>
@@ -8890,13 +8890,13 @@
         <v>344</v>
       </c>
       <c r="B117" s="8">
-        <v>46168.68381783565</v>
+        <v>46168.517151168984</v>
       </c>
       <c r="C117" s="8">
-        <v>46204.89075866898</v>
+        <v>46204.72409200232</v>
       </c>
       <c r="D117" s="8">
-        <v>46204.890769143516</v>
+        <v>46204.72410247685</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>345</v>
@@ -8955,13 +8955,13 @@
         <v>347</v>
       </c>
       <c r="B118" s="5">
-        <v>46168.683825810185</v>
+        <v>46168.51715914352</v>
       </c>
       <c r="C118" s="5">
-        <v>46204.89074575232</v>
+        <v>46204.724079085645</v>
       </c>
       <c r="D118" s="5">
-        <v>46204.89074728009</v>
+        <v>46204.72408061342</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>212</v>
@@ -9010,13 +9010,13 @@
         <v>349</v>
       </c>
       <c r="B119" s="8">
-        <v>46168.68383587963</v>
+        <v>46168.517169212966</v>
       </c>
       <c r="C119" s="8">
-        <v>46204.890660798614</v>
+        <v>46204.72399413194</v>
       </c>
       <c r="D119" s="8">
-        <v>46204.8906627199</v>
+        <v>46204.723996053246</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>212</v>
@@ -9065,13 +9065,13 @@
         <v>351</v>
       </c>
       <c r="B120" s="5">
-        <v>46168.68384034722</v>
+        <v>46168.51717368056</v>
       </c>
       <c r="C120" s="5">
-        <v>46204.890518506945</v>
+        <v>46204.723851840274</v>
       </c>
       <c r="D120" s="5">
-        <v>46204.89052016204</v>
+        <v>46204.72385349537</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>216</v>
@@ -9120,13 +9120,13 @@
         <v>353</v>
       </c>
       <c r="B121" s="8">
-        <v>46168.683844074076</v>
+        <v>46168.51717740741</v>
       </c>
       <c r="C121" s="8">
-        <v>46204.890504930554</v>
+        <v>46204.72383826389</v>
       </c>
       <c r="D121" s="8">
-        <v>46204.89050689815</v>
+        <v>46204.72384023148</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>216</v>
@@ -9175,13 +9175,13 @@
         <v>354</v>
       </c>
       <c r="B122" s="5">
-        <v>46168.683847673616</v>
+        <v>46168.517181006944</v>
       </c>
       <c r="C122" s="5">
-        <v>46197.49592710648</v>
+        <v>46197.329260439816</v>
       </c>
       <c r="D122" s="5">
-        <v>46204.890087210646</v>
+        <v>46204.72342054398</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>220</v>
@@ -9230,13 +9230,13 @@
         <v>356</v>
       </c>
       <c r="B123" s="8">
-        <v>46168.683862453705</v>
+        <v>46168.51719578703</v>
       </c>
       <c r="C123" s="8">
-        <v>46204.89175555555</v>
+        <v>46204.72508888889</v>
       </c>
       <c r="D123" s="8">
-        <v>46204.891766898145</v>
+        <v>46204.72510023148</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>357</v>
@@ -9295,13 +9295,13 @@
         <v>358</v>
       </c>
       <c r="B124" s="5">
-        <v>46168.683867141204</v>
+        <v>46168.51720047454</v>
       </c>
       <c r="C124" s="5">
-        <v>46204.89097627315</v>
+        <v>46204.72430960648</v>
       </c>
       <c r="D124" s="5">
-        <v>46204.89097825231</v>
+        <v>46204.72431158565</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>212</v>
@@ -9350,13 +9350,13 @@
         <v>361</v>
       </c>
       <c r="B125" s="8">
-        <v>46168.683873368056</v>
+        <v>46168.51720670139</v>
       </c>
       <c r="C125" s="8">
-        <v>46204.891655810185</v>
+        <v>46204.72498914352</v>
       </c>
       <c r="D125" s="8">
-        <v>46204.89165733797</v>
+        <v>46204.7249906713</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>212</v>
@@ -9405,13 +9405,13 @@
         <v>363</v>
       </c>
       <c r="B126" s="5">
-        <v>46168.68387903935</v>
+        <v>46168.51721237268</v>
       </c>
       <c r="C126" s="5">
-        <v>46204.891740266205</v>
+        <v>46204.72507359953</v>
       </c>
       <c r="D126" s="5">
-        <v>46204.89174199074</v>
+        <v>46204.72507532407</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>216</v>
@@ -9460,13 +9460,13 @@
         <v>366</v>
       </c>
       <c r="B127" s="8">
-        <v>46168.683884618054</v>
+        <v>46168.51721795139</v>
       </c>
       <c r="C127" s="8">
-        <v>46204.891592291664</v>
+        <v>46204.724925625</v>
       </c>
       <c r="D127" s="8">
-        <v>46204.89159396991</v>
+        <v>46204.724927303236</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>216</v>
@@ -9515,13 +9515,13 @@
         <v>368</v>
       </c>
       <c r="B128" s="5">
-        <v>46168.68389033565</v>
+        <v>46168.51722366898</v>
       </c>
       <c r="C128" s="5">
-        <v>46197.49605328703</v>
+        <v>46197.329386620375</v>
       </c>
       <c r="D128" s="5">
-        <v>46197.49605478009</v>
+        <v>46197.32938811343</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>220</v>
@@ -9570,13 +9570,13 @@
         <v>371</v>
       </c>
       <c r="B129" s="8">
-        <v>46168.68391289352</v>
+        <v>46168.51724622685</v>
       </c>
       <c r="C129" s="8">
-        <v>46204.89298883102</v>
+        <v>46204.72632216435</v>
       </c>
       <c r="D129" s="8">
-        <v>46204.89299085648</v>
+        <v>46204.72632418982</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>372</v>
@@ -9635,13 +9635,13 @@
         <v>373</v>
       </c>
       <c r="B130" s="5">
-        <v>46168.68391818287</v>
+        <v>46168.517251516205</v>
       </c>
       <c r="C130" s="5">
-        <v>46204.89260358796</v>
+        <v>46204.7259369213</v>
       </c>
       <c r="D130" s="5">
-        <v>46204.89260508102</v>
+        <v>46204.725938414354</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>212</v>
@@ -9690,13 +9690,13 @@
         <v>376</v>
       </c>
       <c r="B131" s="8">
-        <v>46168.68393068287</v>
+        <v>46168.517264016205</v>
       </c>
       <c r="C131" s="8">
-        <v>46204.89265783565</v>
+        <v>46204.725991168976</v>
       </c>
       <c r="D131" s="8">
-        <v>46204.89265981481</v>
+        <v>46204.72599314815</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>212</v>
@@ -9745,13 +9745,13 @@
         <v>379</v>
       </c>
       <c r="B132" s="5">
-        <v>46168.68393770834</v>
+        <v>46168.51727104167</v>
       </c>
       <c r="C132" s="5">
-        <v>46204.89272398148</v>
+        <v>46204.726057314816</v>
       </c>
       <c r="D132" s="5">
-        <v>46204.89272546297</v>
+        <v>46204.726058796296</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>216</v>
@@ -9800,13 +9800,13 @@
         <v>382</v>
       </c>
       <c r="B133" s="8">
-        <v>46168.6839434375</v>
+        <v>46168.51727677083</v>
       </c>
       <c r="C133" s="8">
-        <v>46204.89279275463</v>
+        <v>46204.72612608796</v>
       </c>
       <c r="D133" s="8">
-        <v>46204.892794189815</v>
+        <v>46204.72612752314</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>216</v>
@@ -9855,13 +9855,13 @@
         <v>383</v>
       </c>
       <c r="B134" s="5">
-        <v>46168.68398528935</v>
+        <v>46168.51731862269</v>
       </c>
       <c r="C134" s="5">
-        <v>46197.49614903935</v>
+        <v>46197.32948237269</v>
       </c>
       <c r="D134" s="5">
-        <v>46197.49615070602</v>
+        <v>46197.32948403935</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>220</v>
@@ -9910,13 +9910,13 @@
         <v>386</v>
       </c>
       <c r="B135" s="8">
-        <v>46168.68401087963</v>
+        <v>46168.51734421296</v>
       </c>
       <c r="C135" s="8">
-        <v>46204.893422152774</v>
+        <v>46204.72675548611</v>
       </c>
       <c r="D135" s="8">
-        <v>46204.893423761576</v>
+        <v>46204.726757094904</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>387</v>
@@ -9975,13 +9975,13 @@
         <v>388</v>
       </c>
       <c r="B136" s="5">
-        <v>46168.68401652778</v>
+        <v>46168.51734986111</v>
       </c>
       <c r="C136" s="5">
-        <v>46204.89318240741</v>
+        <v>46204.72651574074</v>
       </c>
       <c r="D136" s="5">
-        <v>46204.89318377315</v>
+        <v>46204.72651710648</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>212</v>
@@ -10030,13 +10030,13 @@
         <v>391</v>
       </c>
       <c r="B137" s="8">
-        <v>46168.68402403935</v>
+        <v>46168.517357372686</v>
       </c>
       <c r="C137" s="8">
-        <v>46204.89310061342</v>
+        <v>46204.72643394676</v>
       </c>
       <c r="D137" s="8">
-        <v>46204.893101863425</v>
+        <v>46204.72643519676</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>212</v>
@@ -10085,13 +10085,13 @@
         <v>392</v>
       </c>
       <c r="B138" s="5">
-        <v>46168.68403127315</v>
+        <v>46168.51736460648</v>
       </c>
       <c r="C138" s="5">
-        <v>46204.89303716435</v>
+        <v>46204.72637049769</v>
       </c>
       <c r="D138" s="5">
-        <v>46204.89303854167</v>
+        <v>46204.726371875004</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>216</v>
@@ -10140,13 +10140,13 @@
         <v>395</v>
       </c>
       <c r="B139" s="8">
-        <v>46168.68403755787</v>
+        <v>46168.517370891204</v>
       </c>
       <c r="C139" s="8">
-        <v>46204.892907511574</v>
+        <v>46204.7262408449</v>
       </c>
       <c r="D139" s="8">
-        <v>46204.8929090625</v>
+        <v>46204.72624239583</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>216</v>
@@ -10195,13 +10195,13 @@
         <v>397</v>
       </c>
       <c r="B140" s="5">
-        <v>46168.68404385417</v>
+        <v>46168.5173771875</v>
       </c>
       <c r="C140" s="5">
-        <v>46197.49627</v>
+        <v>46197.32960333333</v>
       </c>
       <c r="D140" s="5">
-        <v>46197.49635938657</v>
+        <v>46197.32969271991</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>220</v>
@@ -10250,11 +10250,11 @@
         <v>400</v>
       </c>
       <c r="B141" s="8">
-        <v>46168.68406297454</v>
+        <v>46168.51739630787</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46204.89333960648</v>
+        <v>46204.72667293981</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>401</v>
@@ -10313,11 +10313,11 @@
         <v>402</v>
       </c>
       <c r="B142" s="5">
-        <v>46168.68406752315</v>
+        <v>46168.51740085648</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46204.8931924537</v>
+        <v>46204.72652578704</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>212</v>
@@ -10366,11 +10366,11 @@
         <v>404</v>
       </c>
       <c r="B143" s="8">
-        <v>46168.68407938657</v>
+        <v>46168.517412719906</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46204.89310667824</v>
+        <v>46204.726440011575</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>212</v>
@@ -10419,11 +10419,11 @@
         <v>406</v>
       </c>
       <c r="B144" s="5">
-        <v>46168.68408523148</v>
+        <v>46168.517418564814</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46204.893044756944</v>
+        <v>46204.72637809028</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>216</v>
@@ -10472,11 +10472,11 @@
         <v>408</v>
       </c>
       <c r="B145" s="8">
-        <v>46168.684089884264</v>
+        <v>46168.51742321759</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46204.89291351852</v>
+        <v>46204.72624685185</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>216</v>
@@ -10525,13 +10525,13 @@
         <v>409</v>
       </c>
       <c r="B146" s="5">
-        <v>46168.684094571756</v>
+        <v>46168.51742790509</v>
       </c>
       <c r="C146" s="5">
-        <v>46204.8933341088</v>
+        <v>46204.726667442126</v>
       </c>
       <c r="D146" s="5">
-        <v>46204.893335671295</v>
+        <v>46204.72666900463</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>220</v>
@@ -10580,11 +10580,11 @@
         <v>411</v>
       </c>
       <c r="B147" s="8">
-        <v>46168.68414574074</v>
+        <v>46168.51747907407</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46168.86783186343</v>
+        <v>46168.70116519676</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>412</v>
@@ -10643,11 +10643,11 @@
         <v>414</v>
       </c>
       <c r="B148" s="5">
-        <v>46168.68415105324</v>
+        <v>46168.517484386575</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46168.86780042824</v>
+        <v>46168.70113376157</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>212</v>
@@ -10696,11 +10696,11 @@
         <v>416</v>
       </c>
       <c r="B149" s="8">
-        <v>46168.68415587963</v>
+        <v>46168.51748921296</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46168.86779700231</v>
+        <v>46168.70113033565</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>212</v>
@@ -10749,11 +10749,11 @@
         <v>418</v>
       </c>
       <c r="B150" s="5">
-        <v>46168.68416068287</v>
+        <v>46168.5174940162</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46168.86779422454</v>
+        <v>46168.70112755787</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>216</v>
@@ -10802,11 +10802,11 @@
         <v>420</v>
       </c>
       <c r="B151" s="8">
-        <v>46168.68416431713</v>
+        <v>46168.517497650464</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46168.86779137731</v>
+        <v>46168.70112471065</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>216</v>
@@ -10855,11 +10855,11 @@
         <v>421</v>
       </c>
       <c r="B152" s="5">
-        <v>46168.68416798611</v>
+        <v>46168.517501319446</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46168.86778699074</v>
+        <v>46168.70112032407</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>220</v>
@@ -10908,11 +10908,11 @@
         <v>423</v>
       </c>
       <c r="B153" s="8">
-        <v>46168.684183460646</v>
+        <v>46168.51751679398</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46168.8597046412</v>
+        <v>46168.69303797453</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>424</v>
@@ -10955,11 +10955,11 @@
         <v>426</v>
       </c>
       <c r="B154" s="5">
-        <v>46168.68418700232</v>
+        <v>46168.51752033565</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46196.89415666666</v>
+        <v>46196.727490000005</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>427</v>
@@ -11018,11 +11018,11 @@
         <v>431</v>
       </c>
       <c r="B155" s="8">
-        <v>46168.68419359953</v>
+        <v>46168.517526932876</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46168.86804876158</v>
+        <v>46168.70138209491</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>212</v>
@@ -11071,11 +11071,11 @@
         <v>433</v>
       </c>
       <c r="B156" s="5">
-        <v>46168.68419834491</v>
+        <v>46168.51753167824</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46168.868045787036</v>
+        <v>46168.70137912037</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>212</v>
@@ -11124,11 +11124,11 @@
         <v>434</v>
       </c>
       <c r="B157" s="8">
-        <v>46168.684202777775</v>
+        <v>46168.51753611111</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46168.86804263889</v>
+        <v>46168.70137597222</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>216</v>
@@ -11177,11 +11177,11 @@
         <v>436</v>
       </c>
       <c r="B158" s="5">
-        <v>46168.68420710648</v>
+        <v>46168.51754043982</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46168.868039953704</v>
+        <v>46168.70137328704</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>216</v>
@@ -11230,11 +11230,11 @@
         <v>437</v>
       </c>
       <c r="B159" s="8">
-        <v>46168.68421127315</v>
+        <v>46168.51754460648</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46168.86803709491</v>
+        <v>46168.70137042824</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>220</v>
@@ -11283,11 +11283,11 @@
         <v>439</v>
       </c>
       <c r="B160" s="5">
-        <v>46168.68422996528</v>
+        <v>46168.51756329861</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46196.89431579861</v>
+        <v>46196.72764913195</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>61</v>
@@ -11336,11 +11336,11 @@
         <v>441</v>
       </c>
       <c r="B161" s="8">
-        <v>46168.68423341435</v>
+        <v>46168.51756674769</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46196.89436430555</v>
+        <v>46196.72769763889</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>61</v>
@@ -11389,11 +11389,11 @@
         <v>442</v>
       </c>
       <c r="B162" s="5">
-        <v>46168.684237037036</v>
+        <v>46168.51757037037</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46196.894410243054</v>
+        <v>46196.72774357639</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>61</v>
@@ -11442,11 +11442,11 @@
         <v>443</v>
       </c>
       <c r="B163" s="8">
-        <v>46168.68424059028</v>
+        <v>46168.517573923615</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46196.89445856481</v>
+        <v>46196.72779189815</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>65</v>
@@ -11495,11 +11495,11 @@
         <v>445</v>
       </c>
       <c r="B164" s="5">
-        <v>46168.68424420139</v>
+        <v>46168.51757753472</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46196.89450880787</v>
+        <v>46196.727842141205</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>65</v>
@@ -11548,11 +11548,11 @@
         <v>446</v>
       </c>
       <c r="B165" s="8">
-        <v>46168.68424778935</v>
+        <v>46168.51758112268</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46196.89456226851</v>
+        <v>46196.727895601856</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>68</v>
@@ -11601,11 +11601,11 @@
         <v>448</v>
       </c>
       <c r="B166" s="5">
-        <v>46168.68425820602</v>
+        <v>46168.51759153935</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46195.55227060185</v>
+        <v>46195.38560393518</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>449</v>
@@ -11662,11 +11662,11 @@
         <v>451</v>
       </c>
       <c r="B167" s="8">
-        <v>46168.68426255787</v>
+        <v>46168.5175958912</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46168.86826831019</v>
+        <v>46168.70160164352</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>212</v>
@@ -11713,11 +11713,11 @@
         <v>453</v>
       </c>
       <c r="B168" s="5">
-        <v>46168.68426704861</v>
+        <v>46168.51760038194</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46168.86826501157</v>
+        <v>46168.70159834491</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>212</v>
@@ -11764,11 +11764,11 @@
         <v>454</v>
       </c>
       <c r="B169" s="8">
-        <v>46168.68427162037</v>
+        <v>46168.517604953704</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46168.86826178241</v>
+        <v>46168.70159511574</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>216</v>
@@ -11815,11 +11815,11 @@
         <v>456</v>
       </c>
       <c r="B170" s="5">
-        <v>46168.68427627315</v>
+        <v>46168.51760960648</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46168.868258738425</v>
+        <v>46168.70159207176</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>216</v>
@@ -11866,11 +11866,11 @@
         <v>457</v>
       </c>
       <c r="B171" s="8">
-        <v>46168.68428068287</v>
+        <v>46168.51761401621</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46168.86825503472</v>
+        <v>46168.70158836806</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>220</v>
@@ -11917,11 +11917,11 @@
         <v>459</v>
       </c>
       <c r="B172" s="5">
-        <v>46168.684336226856</v>
+        <v>46168.517669560184</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46168.86825175926</v>
+        <v>46168.701585092596</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>61</v>
@@ -11968,11 +11968,11 @@
         <v>461</v>
       </c>
       <c r="B173" s="8">
-        <v>46168.68434010417</v>
+        <v>46168.5176734375</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46168.86824866898</v>
+        <v>46168.701582002315</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>61</v>
@@ -12019,11 +12019,11 @@
         <v>463</v>
       </c>
       <c r="B174" s="5">
-        <v>46168.68434423611</v>
+        <v>46168.51767756944</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46168.86824546296</v>
+        <v>46168.701578796296</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>61</v>
@@ -12070,11 +12070,11 @@
         <v>464</v>
       </c>
       <c r="B175" s="8">
-        <v>46168.684348263894</v>
+        <v>46168.51768159722</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46168.86824251157</v>
+        <v>46168.70157584491</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>65</v>
@@ -12121,11 +12121,11 @@
         <v>466</v>
       </c>
       <c r="B176" s="5">
-        <v>46168.68435202546</v>
+        <v>46168.51768535879</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46168.868235092596</v>
+        <v>46168.701568425924</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>65</v>
@@ -12172,11 +12172,11 @@
         <v>467</v>
       </c>
       <c r="B177" s="8">
-        <v>46168.68435652778</v>
+        <v>46168.51768986111</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46168.86823443287</v>
+        <v>46168.7015677662</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>68</v>
@@ -12223,11 +12223,11 @@
         <v>469</v>
       </c>
       <c r="B178" s="5">
-        <v>46168.68437314815</v>
+        <v>46168.51770648148</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46168.86845175926</v>
+        <v>46168.70178509259</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>470</v>
@@ -12284,11 +12284,11 @@
         <v>472</v>
       </c>
       <c r="B179" s="8">
-        <v>46168.68437847222</v>
+        <v>46168.51771180556</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46168.86844914352</v>
+        <v>46168.701782476855</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>212</v>
@@ -12337,11 +12337,11 @@
         <v>474</v>
       </c>
       <c r="B180" s="5">
-        <v>46168.68438821759</v>
+        <v>46168.517721550925</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46168.86844586805</v>
+        <v>46168.701779201394</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>212</v>
@@ -12390,11 +12390,11 @@
         <v>476</v>
       </c>
       <c r="B181" s="8">
-        <v>46168.684394537035</v>
+        <v>46168.51772787037</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46168.86844222222</v>
+        <v>46168.70177555556</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>216</v>
@@ -12443,11 +12443,11 @@
         <v>478</v>
       </c>
       <c r="B182" s="5">
-        <v>46168.68439944445</v>
+        <v>46168.51773277778</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46168.868438749996</v>
+        <v>46168.70177208333</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>216</v>
@@ -12496,11 +12496,11 @@
         <v>480</v>
       </c>
       <c r="B183" s="8">
-        <v>46168.684404375</v>
+        <v>46168.51773770833</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46168.86843505787</v>
+        <v>46168.701768391205</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>220</v>
@@ -12549,11 +12549,11 @@
         <v>482</v>
       </c>
       <c r="B184" s="5">
-        <v>46168.6844190625</v>
+        <v>46168.517752395834</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46168.86843181713</v>
+        <v>46168.701765150465</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>61</v>
@@ -12602,11 +12602,11 @@
         <v>484</v>
       </c>
       <c r="B185" s="8">
-        <v>46168.68442277778</v>
+        <v>46168.51775611111</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46168.86842429398</v>
+        <v>46168.701757627314</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>485</v>
@@ -12655,11 +12655,11 @@
         <v>487</v>
       </c>
       <c r="B186" s="5">
-        <v>46168.68442653935</v>
+        <v>46168.51775987269</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46168.86842351852</v>
+        <v>46168.70175685185</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>61</v>
@@ -12708,11 +12708,11 @@
         <v>489</v>
       </c>
       <c r="B187" s="8">
-        <v>46168.684429988425</v>
+        <v>46168.51776332176</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46168.86842280092</v>
+        <v>46168.70175613426</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>65</v>
@@ -12761,11 +12761,11 @@
         <v>491</v>
       </c>
       <c r="B188" s="5">
-        <v>46168.68443359954</v>
+        <v>46168.51776693287</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46168.86842204861</v>
+        <v>46168.701755381946</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>65</v>
@@ -12814,11 +12814,11 @@
         <v>493</v>
       </c>
       <c r="B189" s="8">
-        <v>46168.68443729167</v>
+        <v>46168.517770624996</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46168.86842112269</v>
+        <v>46168.70175445602</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>68</v>
@@ -12867,11 +12867,11 @@
         <v>495</v>
       </c>
       <c r="B190" s="5">
-        <v>46168.6844840625</v>
+        <v>46168.517817395834</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46168.8686299074</v>
+        <v>46168.70196324074</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>496</v>
@@ -12930,11 +12930,11 @@
         <v>499</v>
       </c>
       <c r="B191" s="8">
-        <v>46168.68449130787</v>
+        <v>46168.5178246412</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46168.86862184027</v>
+        <v>46168.701955173616</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>500</v>
@@ -12981,11 +12981,11 @@
         <v>501</v>
       </c>
       <c r="B192" s="5">
-        <v>46168.68449590278</v>
+        <v>46168.51782923611</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46168.868618946755</v>
+        <v>46168.70195228009</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>502</v>
@@ -13032,11 +13032,11 @@
         <v>503</v>
       </c>
       <c r="B193" s="8">
-        <v>46168.68450027778</v>
+        <v>46168.51783361111</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46168.86861626158</v>
+        <v>46168.701949594906</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>504</v>
@@ -13083,11 +13083,11 @@
         <v>505</v>
       </c>
       <c r="B194" s="5">
-        <v>46168.68450480324</v>
+        <v>46168.51783813657</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46168.868613240746</v>
+        <v>46168.701946574074</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>506</v>
@@ -13134,11 +13134,11 @@
         <v>507</v>
       </c>
       <c r="B195" s="8">
-        <v>46168.68450934028</v>
+        <v>46168.51784267361</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46168.86860957176</v>
+        <v>46168.70194290509</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>508</v>
@@ -13185,11 +13185,11 @@
         <v>509</v>
       </c>
       <c r="B196" s="5">
-        <v>46168.684523414355</v>
+        <v>46168.51785674768</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46168.86860641204</v>
+        <v>46168.70193974537</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>510</v>
@@ -13236,11 +13236,11 @@
         <v>511</v>
       </c>
       <c r="B197" s="8">
-        <v>46168.6845271412</v>
+        <v>46168.51786047454</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46168.868603333336</v>
+        <v>46168.701936666665</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>512</v>
@@ -13287,11 +13287,11 @@
         <v>513</v>
       </c>
       <c r="B198" s="5">
-        <v>46168.68453511574</v>
+        <v>46168.517868449075</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46168.868600648144</v>
+        <v>46168.70193398148</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>514</v>
@@ -13338,11 +13338,11 @@
         <v>515</v>
       </c>
       <c r="B199" s="8">
-        <v>46168.68453863426</v>
+        <v>46168.51787196759</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46168.868592824074</v>
+        <v>46168.7019261574</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>516</v>
@@ -13389,11 +13389,11 @@
         <v>517</v>
       </c>
       <c r="B200" s="5">
-        <v>46168.68454210648</v>
+        <v>46168.517875439815</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46168.86859208334</v>
+        <v>46168.701925416666</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>518</v>
@@ -13440,11 +13440,11 @@
         <v>519</v>
       </c>
       <c r="B201" s="8">
-        <v>46168.684545578704</v>
+        <v>46168.51787891204</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46168.868591377315</v>
+        <v>46168.70192471065</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>520</v>
@@ -13491,11 +13491,11 @@
         <v>521</v>
       </c>
       <c r="B202" s="5">
-        <v>46168.684555775464</v>
+        <v>46168.5178891088</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46168.8618759838</v>
+        <v>46168.69520931713</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>522</v>
@@ -13538,11 +13538,11 @@
         <v>524</v>
       </c>
       <c r="B203" s="8">
-        <v>46168.6845594676</v>
+        <v>46168.517892800926</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46168.868693854165</v>
+        <v>46168.7020271875</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>525</v>
@@ -13601,11 +13601,11 @@
         <v>528</v>
       </c>
       <c r="B204" s="5">
-        <v>46168.68456425926</v>
+        <v>46168.517897592596</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46196.87777929398</v>
+        <v>46196.711112627316</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>529</v>
@@ -13664,11 +13664,11 @@
         <v>530</v>
       </c>
       <c r="B205" s="8">
-        <v>46168.68457049769</v>
+        <v>46168.517903831016</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46168.86234542824</v>
+        <v>46168.69567876158</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>531</v>
@@ -13717,11 +13717,11 @@
         <v>533</v>
       </c>
       <c r="B206" s="5">
-        <v>46168.68457415509</v>
+        <v>46168.51790748842</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46168.8687993287</v>
+        <v>46168.70213266204</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>534</v>
@@ -13780,11 +13780,11 @@
         <v>536</v>
       </c>
       <c r="B207" s="8">
-        <v>46168.68457920139</v>
+        <v>46168.51791253472</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46168.868795937495</v>
+        <v>46168.70212927084</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>537</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2395" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="538">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -225,6 +225,9 @@
     <t>Ingenieria Servicios ,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
     <t>1215141566425255</t>
   </si>
   <si>
@@ -259,9 +262,6 @@
   </si>
   <si>
     <t>Ingenieria Basica Motor,Ingenieria basica Rodete,Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215141533686344</t>
@@ -2289,13 +2289,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46168.51630959491</v>
+        <v>46168.682976261574</v>
       </c>
       <c r="C4" s="5">
-        <v>46175.704996643515</v>
+        <v>46175.87166331019</v>
       </c>
       <c r="D4" s="5">
-        <v>46182.64303600695</v>
+        <v>46182.80970267361</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2338,13 +2338,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46168.51645768518</v>
+        <v>46168.68312435185</v>
       </c>
       <c r="C5" s="8">
-        <v>46175.70497127315</v>
+        <v>46175.87163793981</v>
       </c>
       <c r="D5" s="8">
-        <v>46175.70499721065</v>
+        <v>46175.87166387732</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2401,13 +2401,13 @@
         <v>34</v>
       </c>
       <c r="B6" s="5">
-        <v>46168.51646107639</v>
+        <v>46168.683127743054</v>
       </c>
       <c r="C6" s="5">
-        <v>46175.70497195602</v>
+        <v>46175.87163862269</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.704996932865</v>
+        <v>46175.87166359954</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2464,13 +2464,13 @@
         <v>36</v>
       </c>
       <c r="B7" s="8">
-        <v>46168.51646608797</v>
+        <v>46168.683132754624</v>
       </c>
       <c r="C7" s="8">
-        <v>46175.70497236111</v>
+        <v>46175.87163902778</v>
       </c>
       <c r="D7" s="8">
-        <v>46175.70499733796</v>
+        <v>46175.87166400463</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>37</v>
@@ -2527,13 +2527,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46168.51646875</v>
+        <v>46168.683135416664</v>
       </c>
       <c r="C8" s="5">
-        <v>46175.7049728125</v>
+        <v>46175.87163947917</v>
       </c>
       <c r="D8" s="5">
-        <v>46175.704998229165</v>
+        <v>46175.871664895836</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2590,13 +2590,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="8">
-        <v>46168.51647253473</v>
+        <v>46168.683139201385</v>
       </c>
       <c r="C9" s="8">
-        <v>46175.7049734375</v>
+        <v>46175.87164010417</v>
       </c>
       <c r="D9" s="8">
-        <v>46175.7049974074</v>
+        <v>46175.871664074075</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>44</v>
@@ -2653,13 +2653,13 @@
         <v>46</v>
       </c>
       <c r="B10" s="5">
-        <v>46168.51631346065</v>
+        <v>46168.68298012731</v>
       </c>
       <c r="C10" s="5">
-        <v>46196.72749917824</v>
+        <v>46196.894165844904</v>
       </c>
       <c r="D10" s="5">
-        <v>46196.72752003472</v>
+        <v>46196.89418670139</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>47</v>
@@ -2706,13 +2706,13 @@
         <v>49</v>
       </c>
       <c r="B11" s="8">
-        <v>46168.51647598379</v>
+        <v>46168.683142650465</v>
       </c>
       <c r="C11" s="8">
-        <v>46193.38649887731</v>
+        <v>46193.553165543985</v>
       </c>
       <c r="D11" s="8">
-        <v>46193.3865240625</v>
+        <v>46193.553190729166</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>50</v>
@@ -2771,13 +2771,13 @@
         <v>54</v>
       </c>
       <c r="B12" s="5">
-        <v>46168.51648164351</v>
+        <v>46168.683148310185</v>
       </c>
       <c r="C12" s="5">
-        <v>46196.72747921296</v>
+        <v>46196.89414587963</v>
       </c>
       <c r="D12" s="5">
-        <v>46196.72749921297</v>
+        <v>46205.61958375</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>55</v>
@@ -2827,25 +2827,25 @@
       <c r="T12" s="6">
         <v>1</v>
       </c>
-      <c r="U12" s="10" t="s">
-        <v>33</v>
+      <c r="U12" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B13" s="8">
-        <v>46168.51648685185</v>
+        <v>46168.68315351852</v>
       </c>
       <c r="C13" s="8">
-        <v>46196.72764173611</v>
+        <v>46196.89430840278</v>
       </c>
       <c r="D13" s="8">
-        <v>46196.72764333333</v>
+        <v>46205.61659230324</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -2878,7 +2878,7 @@
         <v>58</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2888,19 +2888,19 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="5">
+        <v>46168.68315625</v>
+      </c>
+      <c r="C14" s="5">
+        <v>46196.89435806713</v>
+      </c>
+      <c r="D14" s="5">
+        <v>46205.616595300926</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="B14" s="5">
-        <v>46168.51648958333</v>
-      </c>
-      <c r="C14" s="5">
-        <v>46196.72769140046</v>
-      </c>
-      <c r="D14" s="5">
-        <v>46196.72769290509</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2933,7 +2933,7 @@
         <v>58</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2943,19 +2943,19 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8">
-        <v>46168.51649224537</v>
+        <v>46168.68315891204</v>
       </c>
       <c r="C15" s="8">
-        <v>46196.72773745371</v>
+        <v>46196.894404120365</v>
       </c>
       <c r="D15" s="8">
-        <v>46196.72773909722</v>
+        <v>46205.61659625</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -2988,7 +2988,7 @@
         <v>58</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -2998,19 +2998,19 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B16" s="5">
-        <v>46168.516494826385</v>
+        <v>46168.683161493056</v>
       </c>
       <c r="C16" s="5">
-        <v>46196.72778436342</v>
+        <v>46196.89445103009</v>
       </c>
       <c r="D16" s="5">
-        <v>46196.72778572916</v>
+        <v>46205.616596921296</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -3043,7 +3043,7 @@
         <v>58</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -3053,19 +3053,19 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B17" s="8">
+        <v>46168.68316400463</v>
+      </c>
+      <c r="C17" s="8">
+        <v>46196.894503090276</v>
+      </c>
+      <c r="D17" s="8">
+        <v>46205.61659773148</v>
+      </c>
+      <c r="E17" s="9" t="s">
         <v>66</v>
-      </c>
-      <c r="B17" s="8">
-        <v>46168.51649733796</v>
-      </c>
-      <c r="C17" s="8">
-        <v>46196.72783642361</v>
-      </c>
-      <c r="D17" s="8">
-        <v>46196.72783809028</v>
-      </c>
-      <c r="E17" s="9" t="s">
-        <v>65</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -3098,7 +3098,7 @@
         <v>58</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -3108,19 +3108,19 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B18" s="5">
-        <v>46168.516500474536</v>
+        <v>46168.68316714121</v>
       </c>
       <c r="C18" s="5">
-        <v>46196.727889421294</v>
+        <v>46196.894556087966</v>
       </c>
       <c r="D18" s="5">
-        <v>46196.7278913426</v>
+        <v>46205.61659839121</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -3153,7 +3153,7 @@
         <v>58</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -3163,17 +3163,19 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" s="8">
-        <v>46168.51631752314</v>
-      </c>
-      <c r="C19" s="9"/>
+        <v>46168.682984189814</v>
+      </c>
+      <c r="C19" s="8">
+        <v>46205.604937083335</v>
+      </c>
       <c r="D19" s="8">
-        <v>46196.71112122685</v>
+        <v>46205.60495420139</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>25</v>
@@ -3197,7 +3199,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P19" s="9" t="s">
         <v>26</v>
@@ -3205,9 +3207,11 @@
       <c r="Q19" s="9"/>
       <c r="R19" s="9"/>
       <c r="S19" s="9"/>
-      <c r="T19" s="9"/>
-      <c r="U19" s="11" t="s">
-        <v>72</v>
+      <c r="T19" s="9">
+        <v>1</v>
+      </c>
+      <c r="U19" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
@@ -3215,13 +3219,13 @@
         <v>73</v>
       </c>
       <c r="B20" s="5">
-        <v>46168.51650914352</v>
+        <v>46168.68317581018</v>
       </c>
       <c r="C20" s="5">
-        <v>46183.70471096065</v>
+        <v>46183.871377627314</v>
       </c>
       <c r="D20" s="5">
-        <v>46196.711111805555</v>
+        <v>46196.87777847222</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>74</v>
@@ -3251,7 +3255,7 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>40</v>
@@ -3280,13 +3284,13 @@
         <v>79</v>
       </c>
       <c r="B21" s="8">
-        <v>46168.51651422454</v>
+        <v>46168.6831808912</v>
       </c>
       <c r="C21" s="8">
-        <v>46183.70471878472</v>
+        <v>46183.87138545139</v>
       </c>
       <c r="D21" s="8">
-        <v>46196.711111666664</v>
+        <v>46196.877778333335</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>80</v>
@@ -3316,7 +3320,7 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>40</v>
@@ -3345,13 +3349,13 @@
         <v>83</v>
       </c>
       <c r="B22" s="5">
-        <v>46168.516519247685</v>
+        <v>46168.68318591436</v>
       </c>
       <c r="C22" s="5">
-        <v>46183.70472876157</v>
+        <v>46183.87139542824</v>
       </c>
       <c r="D22" s="5">
-        <v>46196.71111236111</v>
+        <v>46196.87777902778</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>84</v>
@@ -3381,7 +3385,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>40</v>
@@ -3410,13 +3414,13 @@
         <v>86</v>
       </c>
       <c r="B23" s="8">
-        <v>46168.5163216088</v>
+        <v>46168.68298827547</v>
       </c>
       <c r="C23" s="8">
-        <v>46197.686340555556</v>
+        <v>46197.85300722222</v>
       </c>
       <c r="D23" s="8">
-        <v>46197.686353530094</v>
+        <v>46205.605017905094</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>87</v>
@@ -3451,9 +3455,7 @@
       <c r="Q23" s="9"/>
       <c r="R23" s="9"/>
       <c r="S23" s="9"/>
-      <c r="T23" s="9">
-        <v>1</v>
-      </c>
+      <c r="T23" s="9"/>
       <c r="U23" s="10" t="s">
         <v>33</v>
       </c>
@@ -3463,13 +3465,13 @@
         <v>89</v>
       </c>
       <c r="B24" s="5">
-        <v>46168.516532222224</v>
+        <v>46168.68319888889</v>
       </c>
       <c r="C24" s="5">
-        <v>46193.38639568287</v>
+        <v>46193.553062349536</v>
       </c>
       <c r="D24" s="5">
-        <v>46193.386416504625</v>
+        <v>46193.5530831713</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>90</v>
@@ -3528,13 +3530,13 @@
         <v>92</v>
       </c>
       <c r="B25" s="8">
-        <v>46168.516537731484</v>
+        <v>46168.68320439815</v>
       </c>
       <c r="C25" s="8">
-        <v>46193.38640733797</v>
+        <v>46193.55307400463</v>
       </c>
       <c r="D25" s="8">
-        <v>46193.386422800926</v>
+        <v>46193.55308946759</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>93</v>
@@ -3593,13 +3595,13 @@
         <v>95</v>
       </c>
       <c r="B26" s="5">
-        <v>46168.51654296296</v>
+        <v>46168.68320962963</v>
       </c>
       <c r="C26" s="5">
-        <v>46183.737739108794</v>
+        <v>46183.904405775465</v>
       </c>
       <c r="D26" s="5">
-        <v>46183.73775480324</v>
+        <v>46183.90442146991</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>96</v>
@@ -3658,13 +3660,13 @@
         <v>99</v>
       </c>
       <c r="B27" s="8">
-        <v>46168.51654810185</v>
+        <v>46168.68321476852</v>
       </c>
       <c r="C27" s="8">
-        <v>46197.686325208335</v>
+        <v>46197.852991875</v>
       </c>
       <c r="D27" s="8">
-        <v>46197.686341099536</v>
+        <v>46197.8530077662</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>100</v>
@@ -3723,13 +3725,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="5">
-        <v>46168.51655292824</v>
+        <v>46168.68321959491</v>
       </c>
       <c r="C28" s="5">
-        <v>46196.48000671296</v>
+        <v>46196.646673379626</v>
       </c>
       <c r="D28" s="5">
-        <v>46196.480021469906</v>
+        <v>46196.64668813658</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -3788,13 +3790,13 @@
         <v>109</v>
       </c>
       <c r="B29" s="8">
-        <v>46168.51655674769</v>
+        <v>46168.68322341435</v>
       </c>
       <c r="C29" s="8">
-        <v>46196.48073766204</v>
+        <v>46196.6474043287</v>
       </c>
       <c r="D29" s="8">
-        <v>46196.48075224537</v>
+        <v>46196.647418912034</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>110</v>
@@ -3853,13 +3855,13 @@
         <v>112</v>
       </c>
       <c r="B30" s="5">
-        <v>46168.516560578704</v>
+        <v>46168.683227245376</v>
       </c>
       <c r="C30" s="5">
-        <v>46196.48093813658</v>
+        <v>46196.64760480324</v>
       </c>
       <c r="D30" s="5">
-        <v>46196.48134866898</v>
+        <v>46196.64801533565</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>113</v>
@@ -3918,13 +3920,13 @@
         <v>115</v>
       </c>
       <c r="B31" s="8">
-        <v>46168.51656469908</v>
+        <v>46168.683231365736</v>
       </c>
       <c r="C31" s="8">
-        <v>46193.38679563657</v>
+        <v>46193.55346230324</v>
       </c>
       <c r="D31" s="8">
-        <v>46193.38683263889</v>
+        <v>46193.553499305555</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>116</v>
@@ -3983,11 +3985,13 @@
         <v>118</v>
       </c>
       <c r="B32" s="5">
-        <v>46168.5163258449</v>
-      </c>
-      <c r="C32" s="6"/>
+        <v>46168.682992511574</v>
+      </c>
+      <c r="C32" s="5">
+        <v>46205.61593267361</v>
+      </c>
       <c r="D32" s="5">
-        <v>46199.39839445602</v>
+        <v>46205.61594793982</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>119</v>
@@ -4022,21 +4026,25 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="6"/>
-      <c r="T32" s="6"/>
-      <c r="U32" s="6"/>
+      <c r="T32" s="6">
+        <v>1</v>
+      </c>
+      <c r="U32" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>121</v>
       </c>
       <c r="B33" s="8">
-        <v>46168.51660986111</v>
+        <v>46168.68327652778</v>
       </c>
       <c r="C33" s="8">
-        <v>46195.76171604167</v>
+        <v>46195.928382708335</v>
       </c>
       <c r="D33" s="8">
-        <v>46195.761729907405</v>
+        <v>46195.928396574076</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>122</v>
@@ -4095,13 +4103,13 @@
         <v>126</v>
       </c>
       <c r="B34" s="5">
-        <v>46168.51661482639</v>
+        <v>46168.68328149305</v>
       </c>
       <c r="C34" s="5">
-        <v>46195.75916210648</v>
+        <v>46195.92582877315</v>
       </c>
       <c r="D34" s="5">
-        <v>46195.75916369213</v>
+        <v>46195.9258303588</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>127</v>
@@ -4156,13 +4164,13 @@
         <v>130</v>
       </c>
       <c r="B35" s="8">
-        <v>46168.51661987268</v>
+        <v>46168.68328653935</v>
       </c>
       <c r="C35" s="8">
-        <v>46195.76170190972</v>
+        <v>46195.92836857639</v>
       </c>
       <c r="D35" s="8">
-        <v>46195.76170357639</v>
+        <v>46195.928370243055</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>131</v>
@@ -4217,13 +4225,13 @@
         <v>133</v>
       </c>
       <c r="B36" s="5">
-        <v>46168.51662473379</v>
+        <v>46168.68329140046</v>
       </c>
       <c r="C36" s="5">
-        <v>46184.536961226855</v>
+        <v>46184.70362789352</v>
       </c>
       <c r="D36" s="5">
-        <v>46185.01610857639</v>
+        <v>46185.182775243054</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>134</v>
@@ -4282,13 +4290,13 @@
         <v>136</v>
       </c>
       <c r="B37" s="8">
-        <v>46168.51662917824</v>
+        <v>46168.68329584491</v>
       </c>
       <c r="C37" s="8">
-        <v>46184.53683564815</v>
+        <v>46184.70350231482</v>
       </c>
       <c r="D37" s="8">
-        <v>46184.53683701389</v>
+        <v>46184.70350368056</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>137</v>
@@ -4343,13 +4351,13 @@
         <v>139</v>
       </c>
       <c r="B38" s="5">
-        <v>46168.51663403935</v>
+        <v>46168.68330070602</v>
       </c>
       <c r="C38" s="5">
-        <v>46184.53688990741</v>
+        <v>46184.70355657407</v>
       </c>
       <c r="D38" s="5">
-        <v>46184.53689112268</v>
+        <v>46184.703557789355</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>140</v>
@@ -4404,11 +4412,13 @@
         <v>142</v>
       </c>
       <c r="B39" s="8">
-        <v>46168.516638761575</v>
-      </c>
-      <c r="C39" s="9"/>
+        <v>46168.68330542824</v>
+      </c>
+      <c r="C39" s="8">
+        <v>46205.60795291667</v>
+      </c>
       <c r="D39" s="8">
-        <v>46199.01339069444</v>
+        <v>46205.60819122686</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>143</v>
@@ -4456,10 +4466,10 @@
         <v>105</v>
       </c>
       <c r="T39" s="9">
-        <v>0</v>
-      </c>
-      <c r="U39" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U39" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -4467,13 +4477,13 @@
         <v>145</v>
       </c>
       <c r="B40" s="5">
-        <v>46168.51664342593</v>
+        <v>46168.683310092594</v>
       </c>
       <c r="C40" s="5">
-        <v>46195.75920216435</v>
+        <v>46195.92586883102</v>
       </c>
       <c r="D40" s="5">
-        <v>46195.75920461805</v>
+        <v>46195.92587128472</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>146</v>
@@ -4528,11 +4538,13 @@
         <v>148</v>
       </c>
       <c r="B41" s="8">
-        <v>46168.516648530094</v>
-      </c>
-      <c r="C41" s="9"/>
+        <v>46168.68331519676</v>
+      </c>
+      <c r="C41" s="8">
+        <v>46205.6079295949</v>
+      </c>
       <c r="D41" s="8">
-        <v>46198.00270173611</v>
+        <v>46205.60793128472</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>149</v>
@@ -4587,13 +4599,13 @@
         <v>151</v>
       </c>
       <c r="B42" s="5">
-        <v>46168.51665361111</v>
+        <v>46168.68332027778</v>
       </c>
       <c r="C42" s="5">
-        <v>46184.53618304398</v>
+        <v>46184.70284971065</v>
       </c>
       <c r="D42" s="5">
-        <v>46195.75921184028</v>
+        <v>46195.92587850694</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>152</v>
@@ -4648,13 +4660,13 @@
         <v>154</v>
       </c>
       <c r="B43" s="8">
-        <v>46168.51665854167</v>
+        <v>46168.68332520833</v>
       </c>
       <c r="C43" s="8">
-        <v>46195.76191746528</v>
+        <v>46195.92858413194</v>
       </c>
       <c r="D43" s="8">
-        <v>46195.76192847222</v>
+        <v>46195.92859513889</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>155</v>
@@ -4713,13 +4725,13 @@
         <v>157</v>
       </c>
       <c r="B44" s="5">
-        <v>46168.516662141206</v>
+        <v>46168.68332880787</v>
       </c>
       <c r="C44" s="5">
-        <v>46195.759110451385</v>
+        <v>46195.92577711806</v>
       </c>
       <c r="D44" s="5">
-        <v>46195.759112245374</v>
+        <v>46195.92577891204</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>117</v>
@@ -4768,13 +4780,13 @@
         <v>159</v>
       </c>
       <c r="B45" s="8">
-        <v>46168.516666446754</v>
+        <v>46168.683333113426</v>
       </c>
       <c r="C45" s="8">
-        <v>46195.761901736114</v>
+        <v>46195.92856840278</v>
       </c>
       <c r="D45" s="8">
-        <v>46195.761903506944</v>
+        <v>46195.92857017361</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>160</v>
@@ -4823,13 +4835,13 @@
         <v>162</v>
       </c>
       <c r="B46" s="5">
-        <v>46168.516670625</v>
+        <v>46168.683337291666</v>
       </c>
       <c r="C46" s="5">
-        <v>46199.398383692125</v>
+        <v>46199.5650503588</v>
       </c>
       <c r="D46" s="5">
-        <v>46204.03121703704</v>
+        <v>46204.1978837037</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>163</v>
@@ -4888,13 +4900,13 @@
         <v>167</v>
       </c>
       <c r="B47" s="8">
-        <v>46168.516675127314</v>
+        <v>46168.68334179398</v>
       </c>
       <c r="C47" s="8">
-        <v>46199.398319768516</v>
+        <v>46199.56498643519</v>
       </c>
       <c r="D47" s="8">
-        <v>46199.398321898145</v>
+        <v>46199.564988564816</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>168</v>
@@ -4949,13 +4961,13 @@
         <v>170</v>
       </c>
       <c r="B48" s="5">
-        <v>46168.51668017361</v>
+        <v>46168.68334684028</v>
       </c>
       <c r="C48" s="5">
-        <v>46199.39836929398</v>
+        <v>46199.56503596065</v>
       </c>
       <c r="D48" s="5">
-        <v>46199.398371145835</v>
+        <v>46199.5650378125</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>171</v>
@@ -5010,13 +5022,13 @@
         <v>173</v>
       </c>
       <c r="B49" s="8">
-        <v>46168.51668528935</v>
+        <v>46168.68335195602</v>
       </c>
       <c r="C49" s="8">
-        <v>46199.39864590278</v>
+        <v>46199.565312569444</v>
       </c>
       <c r="D49" s="8">
-        <v>46204.03121696759</v>
+        <v>46204.19788363426</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>174</v>
@@ -5075,13 +5087,13 @@
         <v>176</v>
       </c>
       <c r="B50" s="5">
-        <v>46168.51668915509</v>
+        <v>46168.68335582176</v>
       </c>
       <c r="C50" s="5">
-        <v>46199.39845438657</v>
+        <v>46199.56512105324</v>
       </c>
       <c r="D50" s="5">
-        <v>46199.39845608796</v>
+        <v>46199.56512275463</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>108</v>
@@ -5130,13 +5142,13 @@
         <v>178</v>
       </c>
       <c r="B51" s="8">
-        <v>46168.51669376157</v>
+        <v>46168.683360428244</v>
       </c>
       <c r="C51" s="8">
-        <v>46199.39853215277</v>
+        <v>46199.565198819444</v>
       </c>
       <c r="D51" s="8">
-        <v>46199.39853386574</v>
+        <v>46199.56520053241</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>179</v>
@@ -5185,13 +5197,13 @@
         <v>181</v>
       </c>
       <c r="B52" s="5">
-        <v>46168.51669804398</v>
+        <v>46168.68336471065</v>
       </c>
       <c r="C52" s="5">
-        <v>46204.69411216435</v>
+        <v>46204.86077883102</v>
       </c>
       <c r="D52" s="5">
-        <v>46204.694130868054</v>
+        <v>46205.61765122685</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>182</v>
@@ -5250,13 +5262,13 @@
         <v>186</v>
       </c>
       <c r="B53" s="8">
-        <v>46168.51670710648</v>
+        <v>46168.68337377315</v>
       </c>
       <c r="C53" s="8">
-        <v>46204.43481704861</v>
+        <v>46204.601483715276</v>
       </c>
       <c r="D53" s="8">
-        <v>46204.43481888888</v>
+        <v>46204.601485555555</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>114</v>
@@ -5305,13 +5317,13 @@
         <v>188</v>
       </c>
       <c r="B54" s="5">
-        <v>46168.51671152777</v>
+        <v>46168.683378194444</v>
       </c>
       <c r="C54" s="5">
-        <v>46204.434872743055</v>
+        <v>46204.60153940972</v>
       </c>
       <c r="D54" s="5">
-        <v>46204.43487412037</v>
+        <v>46204.601540787036</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>189</v>
@@ -5360,11 +5372,11 @@
         <v>191</v>
       </c>
       <c r="B55" s="8">
-        <v>46168.516716053244</v>
+        <v>46168.68338271991</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46204.434883622685</v>
+        <v>46204.60155028936</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>192</v>
@@ -5413,13 +5425,13 @@
         <v>195</v>
       </c>
       <c r="B56" s="5">
-        <v>46168.51671920139</v>
+        <v>46168.683385868055</v>
       </c>
       <c r="C56" s="5">
-        <v>46199.3987871875</v>
+        <v>46199.56545385417</v>
       </c>
       <c r="D56" s="5">
-        <v>46204.03121724537</v>
+        <v>46204.19788391204</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>196</v>
@@ -5478,13 +5490,13 @@
         <v>198</v>
       </c>
       <c r="B57" s="8">
-        <v>46168.51676398148</v>
+        <v>46168.68343064815</v>
       </c>
       <c r="C57" s="8">
-        <v>46199.39868575231</v>
+        <v>46199.565352418984</v>
       </c>
       <c r="D57" s="8">
-        <v>46199.398687430556</v>
+        <v>46199.56535409723</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>111</v>
@@ -5533,13 +5545,13 @@
         <v>200</v>
       </c>
       <c r="B58" s="5">
-        <v>46168.51677028935</v>
+        <v>46168.683436956024</v>
       </c>
       <c r="C58" s="5">
-        <v>46199.398771782406</v>
+        <v>46199.56543844908</v>
       </c>
       <c r="D58" s="5">
-        <v>46199.39877368056</v>
+        <v>46199.56544034722</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>201</v>
@@ -5588,11 +5600,11 @@
         <v>203</v>
       </c>
       <c r="B59" s="8">
-        <v>46168.516775543976</v>
+        <v>46168.68344221065</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46190.43858074074</v>
+        <v>46190.60524740741</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>204</v>
@@ -5629,7 +5641,7 @@
       <c r="S59" s="9"/>
       <c r="T59" s="9"/>
       <c r="U59" s="11" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5637,13 +5649,13 @@
         <v>206</v>
       </c>
       <c r="B60" s="5">
-        <v>46168.51677912037</v>
+        <v>46168.683445787035</v>
       </c>
       <c r="C60" s="5">
-        <v>46184.3521603125</v>
+        <v>46184.51882697917</v>
       </c>
       <c r="D60" s="5">
-        <v>46184.35217791666</v>
+        <v>46184.518844583334</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>207</v>
@@ -5702,13 +5714,13 @@
         <v>211</v>
       </c>
       <c r="B61" s="8">
-        <v>46168.519933020834</v>
+        <v>46168.6865996875</v>
       </c>
       <c r="C61" s="8">
-        <v>46184.35211828703</v>
+        <v>46184.5187849537</v>
       </c>
       <c r="D61" s="8">
-        <v>46184.35211998843</v>
+        <v>46184.51878665509</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>212</v>
@@ -5757,13 +5769,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46168.520167939816</v>
+        <v>46168.68683460648</v>
       </c>
       <c r="C62" s="5">
-        <v>46184.352123159726</v>
+        <v>46184.51878982639</v>
       </c>
       <c r="D62" s="5">
-        <v>46184.35212465278</v>
+        <v>46184.518791319446</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>212</v>
@@ -5812,13 +5824,13 @@
         <v>215</v>
       </c>
       <c r="B63" s="8">
-        <v>46168.52025177084</v>
+        <v>46168.686918437495</v>
       </c>
       <c r="C63" s="8">
-        <v>46184.352131203705</v>
+        <v>46184.51879787037</v>
       </c>
       <c r="D63" s="8">
-        <v>46184.35213263889</v>
+        <v>46184.51879930556</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>216</v>
@@ -5867,13 +5879,13 @@
         <v>218</v>
       </c>
       <c r="B64" s="5">
-        <v>46168.52058747685</v>
+        <v>46168.687254143515</v>
       </c>
       <c r="C64" s="5">
-        <v>46184.35213895833</v>
+        <v>46184.518805625004</v>
       </c>
       <c r="D64" s="5">
-        <v>46184.35214016204</v>
+        <v>46184.5188068287</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>216</v>
@@ -5922,13 +5934,13 @@
         <v>219</v>
       </c>
       <c r="B65" s="8">
-        <v>46168.5206496875</v>
+        <v>46168.68731635417</v>
       </c>
       <c r="C65" s="8">
-        <v>46184.35214644676</v>
+        <v>46184.51881311343</v>
       </c>
       <c r="D65" s="8">
-        <v>46184.352147881946</v>
+        <v>46184.51881454861</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>220</v>
@@ -5977,13 +5989,13 @@
         <v>222</v>
       </c>
       <c r="B66" s="5">
-        <v>46168.51678475694</v>
+        <v>46168.68345142361</v>
       </c>
       <c r="C66" s="5">
-        <v>46190.43856417824</v>
+        <v>46190.60523084491</v>
       </c>
       <c r="D66" s="5">
-        <v>46190.43857604166</v>
+        <v>46190.605242708334</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>223</v>
@@ -6042,13 +6054,13 @@
         <v>224</v>
       </c>
       <c r="B67" s="8">
-        <v>46168.521906793976</v>
+        <v>46168.68857346065</v>
       </c>
       <c r="C67" s="8">
-        <v>46190.43851710648</v>
+        <v>46190.60518377315</v>
       </c>
       <c r="D67" s="8">
-        <v>46190.438519421295</v>
+        <v>46190.60518608797</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>212</v>
@@ -6097,13 +6109,13 @@
         <v>227</v>
       </c>
       <c r="B68" s="5">
-        <v>46168.52194160879</v>
+        <v>46168.688608275465</v>
       </c>
       <c r="C68" s="5">
-        <v>46190.43852674769</v>
+        <v>46190.60519341435</v>
       </c>
       <c r="D68" s="5">
-        <v>46190.43852835648</v>
+        <v>46190.60519502315</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>212</v>
@@ -6152,13 +6164,13 @@
         <v>228</v>
       </c>
       <c r="B69" s="8">
-        <v>46168.521979930556</v>
+        <v>46168.68864659722</v>
       </c>
       <c r="C69" s="8">
-        <v>46190.438534664354</v>
+        <v>46190.60520133102</v>
       </c>
       <c r="D69" s="8">
-        <v>46190.4385370949</v>
+        <v>46190.605203761574</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>216</v>
@@ -6207,13 +6219,13 @@
         <v>231</v>
       </c>
       <c r="B70" s="5">
-        <v>46168.52201971065</v>
+        <v>46168.68868637731</v>
       </c>
       <c r="C70" s="5">
-        <v>46190.43854070602</v>
+        <v>46190.60520737269</v>
       </c>
       <c r="D70" s="5">
-        <v>46190.43854228009</v>
+        <v>46190.605208946756</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>216</v>
@@ -6262,13 +6274,13 @@
         <v>233</v>
       </c>
       <c r="B71" s="8">
-        <v>46168.52205267361</v>
+        <v>46168.68871934028</v>
       </c>
       <c r="C71" s="8">
-        <v>46190.438548252314</v>
+        <v>46190.60521491898</v>
       </c>
       <c r="D71" s="8">
-        <v>46190.43855042824</v>
+        <v>46190.60521709491</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>220</v>
@@ -6317,13 +6329,13 @@
         <v>236</v>
       </c>
       <c r="B72" s="5">
-        <v>46168.51679123843</v>
+        <v>46168.68345790509</v>
       </c>
       <c r="C72" s="5">
-        <v>46190.43874541667</v>
+        <v>46190.60541208333</v>
       </c>
       <c r="D72" s="5">
-        <v>46190.43875775463</v>
+        <v>46190.6054244213</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>103</v>
@@ -6382,13 +6394,13 @@
         <v>239</v>
       </c>
       <c r="B73" s="8">
-        <v>46168.52213511574</v>
+        <v>46168.68880178241</v>
       </c>
       <c r="C73" s="8">
-        <v>46190.43869497685</v>
+        <v>46190.605361643524</v>
       </c>
       <c r="D73" s="8">
-        <v>46190.438696944446</v>
+        <v>46190.60536361111</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>212</v>
@@ -6437,13 +6449,13 @@
         <v>240</v>
       </c>
       <c r="B74" s="5">
-        <v>46168.52217190972</v>
+        <v>46168.68883857639</v>
       </c>
       <c r="C74" s="5">
-        <v>46190.438700115745</v>
+        <v>46190.60536678241</v>
       </c>
       <c r="D74" s="5">
-        <v>46190.43870153935</v>
+        <v>46190.605368206016</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>212</v>
@@ -6492,13 +6504,13 @@
         <v>241</v>
       </c>
       <c r="B75" s="8">
-        <v>46168.52220910879</v>
+        <v>46168.688875775464</v>
       </c>
       <c r="C75" s="8">
-        <v>46190.43870528935</v>
+        <v>46190.605371956015</v>
       </c>
       <c r="D75" s="8">
-        <v>46190.438706863424</v>
+        <v>46190.605373530096</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>216</v>
@@ -6547,13 +6559,13 @@
         <v>242</v>
       </c>
       <c r="B76" s="5">
-        <v>46168.522250567126</v>
+        <v>46168.6889172338</v>
       </c>
       <c r="C76" s="5">
-        <v>46190.438731250004</v>
+        <v>46190.60539791667</v>
       </c>
       <c r="D76" s="5">
-        <v>46190.438732905095</v>
+        <v>46190.60539957176</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>243</v>
@@ -6602,13 +6614,13 @@
         <v>244</v>
       </c>
       <c r="B77" s="8">
-        <v>46168.522289953704</v>
+        <v>46168.688956620375</v>
       </c>
       <c r="C77" s="8">
-        <v>46190.43871996528</v>
+        <v>46190.60538663194</v>
       </c>
       <c r="D77" s="8">
-        <v>46190.43872148148</v>
+        <v>46190.60538814815</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>220</v>
@@ -6657,11 +6669,11 @@
         <v>245</v>
       </c>
       <c r="B78" s="5">
-        <v>46168.51681395833</v>
+        <v>46168.683480625</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46168.69828388889</v>
+        <v>46168.86495055555</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>246</v>
@@ -6718,11 +6730,11 @@
         <v>250</v>
       </c>
       <c r="B79" s="8">
-        <v>46168.51681796296</v>
+        <v>46168.683484629626</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46168.698261875004</v>
+        <v>46168.86492854166</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>212</v>
@@ -6771,11 +6783,11 @@
         <v>252</v>
       </c>
       <c r="B80" s="5">
-        <v>46168.516822210644</v>
+        <v>46168.683488877316</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46168.69825894676</v>
+        <v>46168.86492561342</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>212</v>
@@ -6824,11 +6836,11 @@
         <v>253</v>
       </c>
       <c r="B81" s="8">
-        <v>46168.51682634259</v>
+        <v>46168.68349300926</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46168.69825621528</v>
+        <v>46168.86492288194</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>216</v>
@@ -6877,11 +6889,11 @@
         <v>254</v>
       </c>
       <c r="B82" s="5">
-        <v>46168.51682927083</v>
+        <v>46168.6834959375</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46168.69825349537</v>
+        <v>46168.864920162036</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>216</v>
@@ -6930,11 +6942,11 @@
         <v>255</v>
       </c>
       <c r="B83" s="8">
-        <v>46168.51683232639</v>
+        <v>46168.68349899305</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46204.72667418982</v>
+        <v>46204.89334085648</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>220</v>
@@ -6983,11 +6995,13 @@
         <v>256</v>
       </c>
       <c r="B84" s="5">
-        <v>46168.51684435185</v>
-      </c>
-      <c r="C84" s="6"/>
+        <v>46168.68351101852</v>
+      </c>
+      <c r="C84" s="5">
+        <v>46205.61806340278</v>
+      </c>
       <c r="D84" s="5">
-        <v>46197.68452328704</v>
+        <v>46205.618076087965</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>257</v>
@@ -7022,19 +7036,25 @@
       <c r="Q84" s="6"/>
       <c r="R84" s="6"/>
       <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+      <c r="T84" s="6">
+        <v>1</v>
+      </c>
+      <c r="U84" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
         <v>259</v>
       </c>
       <c r="B85" s="8">
-        <v>46168.5168478125</v>
-      </c>
-      <c r="C85" s="9"/>
+        <v>46168.68351447917</v>
+      </c>
+      <c r="C85" s="8">
+        <v>46205.61802771991</v>
+      </c>
       <c r="D85" s="8">
-        <v>46205.00218876157</v>
+        <v>46205.618041678244</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>260</v>
@@ -7082,10 +7102,10 @@
         <v>264</v>
       </c>
       <c r="T85" s="9">
-        <v>0</v>
-      </c>
-      <c r="U85" s="11" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="U85" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
@@ -7093,13 +7113,13 @@
         <v>265</v>
       </c>
       <c r="B86" s="5">
-        <v>46168.51685344907</v>
+        <v>46168.68352011574</v>
       </c>
       <c r="C86" s="5">
-        <v>46197.68450846065</v>
+        <v>46197.85117512732</v>
       </c>
       <c r="D86" s="5">
-        <v>46202.00057174769</v>
+        <v>46205.618054756946</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>266</v>
@@ -7149,8 +7169,8 @@
       <c r="T86" s="6">
         <v>1</v>
       </c>
-      <c r="U86" s="10" t="s">
-        <v>33</v>
+      <c r="U86" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -7158,11 +7178,13 @@
         <v>269</v>
       </c>
       <c r="B87" s="8">
-        <v>46168.51686069445</v>
-      </c>
-      <c r="C87" s="9"/>
+        <v>46168.68352736111</v>
+      </c>
+      <c r="C87" s="8">
+        <v>46205.61804003472</v>
+      </c>
       <c r="D87" s="8">
-        <v>46205.00219209491</v>
+        <v>46205.618055127314</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -7210,10 +7232,10 @@
         <v>264</v>
       </c>
       <c r="T87" s="9">
-        <v>0</v>
-      </c>
-      <c r="U87" s="11" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="U87" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
@@ -7221,13 +7243,13 @@
         <v>272</v>
       </c>
       <c r="B88" s="5">
-        <v>46168.516866261576</v>
+        <v>46168.68353292824</v>
       </c>
       <c r="C88" s="5">
-        <v>46197.68463350694</v>
+        <v>46197.851300173614</v>
       </c>
       <c r="D88" s="5">
-        <v>46202.0005715625</v>
+        <v>46205.618055</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>273</v>
@@ -7277,8 +7299,8 @@
       <c r="T88" s="6">
         <v>1</v>
       </c>
-      <c r="U88" s="10" t="s">
-        <v>33</v>
+      <c r="U88" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7286,11 +7308,13 @@
         <v>275</v>
       </c>
       <c r="B89" s="8">
-        <v>46168.516871203705</v>
-      </c>
-      <c r="C89" s="9"/>
+        <v>46168.68353787037</v>
+      </c>
+      <c r="C89" s="8">
+        <v>46205.61804746528</v>
+      </c>
       <c r="D89" s="8">
-        <v>46205.00219377315</v>
+        <v>46205.618063437505</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>276</v>
@@ -7338,10 +7362,10 @@
         <v>264</v>
       </c>
       <c r="T89" s="9">
-        <v>0</v>
-      </c>
-      <c r="U89" s="11" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="U89" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
@@ -7349,13 +7373,13 @@
         <v>278</v>
       </c>
       <c r="B90" s="5">
-        <v>46168.516875810186</v>
+        <v>46168.68354247685</v>
       </c>
       <c r="C90" s="5">
-        <v>46197.684947939815</v>
+        <v>46197.85161460648</v>
       </c>
       <c r="D90" s="5">
-        <v>46202.000571909724</v>
+        <v>46205.61806439815</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>277</v>
@@ -7405,8 +7429,8 @@
       <c r="T90" s="6">
         <v>1</v>
       </c>
-      <c r="U90" s="10" t="s">
-        <v>33</v>
+      <c r="U90" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -7414,11 +7438,11 @@
         <v>279</v>
       </c>
       <c r="B91" s="8">
-        <v>46168.516880752315</v>
+        <v>46168.68354741899</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46204.72344259259</v>
+        <v>46204.89010925926</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>280</v>
@@ -7455,7 +7479,7 @@
       <c r="S91" s="9"/>
       <c r="T91" s="9"/>
       <c r="U91" s="11" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -7463,13 +7487,13 @@
         <v>282</v>
       </c>
       <c r="B92" s="5">
-        <v>46168.516883854165</v>
+        <v>46168.68355052083</v>
       </c>
       <c r="C92" s="5">
-        <v>46192.46738998842</v>
+        <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46205.01169530093</v>
+        <v>46205.17836196759</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>
@@ -7528,13 +7552,13 @@
         <v>287</v>
       </c>
       <c r="B93" s="8">
-        <v>46168.516895416666</v>
+        <v>46168.68356208333</v>
       </c>
       <c r="C93" s="8">
-        <v>46197.68596164352</v>
+        <v>46197.85262831018</v>
       </c>
       <c r="D93" s="8">
-        <v>46197.68596631945</v>
+        <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>212</v>
@@ -7583,13 +7607,13 @@
         <v>290</v>
       </c>
       <c r="B94" s="5">
-        <v>46168.516902557865</v>
+        <v>46168.68356922454</v>
       </c>
       <c r="C94" s="5">
-        <v>46197.68596275463</v>
+        <v>46197.85262942129</v>
       </c>
       <c r="D94" s="5">
-        <v>46197.68596667824</v>
+        <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>212</v>
@@ -7638,13 +7662,13 @@
         <v>292</v>
       </c>
       <c r="B95" s="8">
-        <v>46168.51690811342</v>
+        <v>46168.683574780094</v>
       </c>
       <c r="C95" s="8">
-        <v>46197.6859633912</v>
+        <v>46197.85263005787</v>
       </c>
       <c r="D95" s="8">
-        <v>46197.68596701389</v>
+        <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>216</v>
@@ -7693,13 +7717,13 @@
         <v>295</v>
       </c>
       <c r="B96" s="5">
-        <v>46168.516913576386</v>
+        <v>46168.68358024306</v>
       </c>
       <c r="C96" s="5">
-        <v>46197.685964027776</v>
+        <v>46197.85263069444</v>
       </c>
       <c r="D96" s="5">
-        <v>46197.68596739583</v>
+        <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>216</v>
@@ -7748,13 +7772,13 @@
         <v>296</v>
       </c>
       <c r="B97" s="8">
-        <v>46168.516919120375</v>
+        <v>46168.68358578703</v>
       </c>
       <c r="C97" s="8">
-        <v>46197.685964641205</v>
+        <v>46197.85263130787</v>
       </c>
       <c r="D97" s="8">
-        <v>46197.68596782407</v>
+        <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>220</v>
@@ -7803,13 +7827,13 @@
         <v>298</v>
       </c>
       <c r="B98" s="5">
-        <v>46168.5169880787</v>
+        <v>46168.68365474537</v>
       </c>
       <c r="C98" s="5">
-        <v>46197.68340998843</v>
+        <v>46197.85007665509</v>
       </c>
       <c r="D98" s="5">
-        <v>46197.68576483797</v>
+        <v>46197.85243150463</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>299</v>
@@ -7860,7 +7884,7 @@
         <v>1</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -7868,13 +7892,13 @@
         <v>301</v>
       </c>
       <c r="B99" s="8">
-        <v>46168.51699329861</v>
+        <v>46168.683659965274</v>
       </c>
       <c r="C99" s="8">
-        <v>46197.68516354167</v>
+        <v>46197.85183020833</v>
       </c>
       <c r="D99" s="8">
-        <v>46197.68597319444</v>
+        <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>212</v>
@@ -7923,13 +7947,13 @@
         <v>304</v>
       </c>
       <c r="B100" s="5">
-        <v>46168.516999467596</v>
+        <v>46168.68366613426</v>
       </c>
       <c r="C100" s="5">
-        <v>46197.685386261575</v>
+        <v>46197.85205292824</v>
       </c>
       <c r="D100" s="5">
-        <v>46197.68597329861</v>
+        <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>212</v>
@@ -7978,13 +8002,13 @@
         <v>306</v>
       </c>
       <c r="B101" s="8">
-        <v>46168.51700525463</v>
+        <v>46168.683671921295</v>
       </c>
       <c r="C101" s="8">
-        <v>46197.68555905092</v>
+        <v>46197.852225717594</v>
       </c>
       <c r="D101" s="8">
-        <v>46197.685973506945</v>
+        <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>216</v>
@@ -8033,13 +8057,13 @@
         <v>308</v>
       </c>
       <c r="B102" s="5">
-        <v>46168.517009560186</v>
+        <v>46168.68367622685</v>
       </c>
       <c r="C102" s="5">
-        <v>46197.685649363426</v>
+        <v>46197.8523160301</v>
       </c>
       <c r="D102" s="5">
-        <v>46197.68597530093</v>
+        <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>216</v>
@@ -8088,13 +8112,13 @@
         <v>310</v>
       </c>
       <c r="B103" s="8">
-        <v>46168.51701340278</v>
+        <v>46168.683680069444</v>
       </c>
       <c r="C103" s="8">
-        <v>46197.685746550924</v>
+        <v>46197.852413217595</v>
       </c>
       <c r="D103" s="8">
-        <v>46197.68597707176</v>
+        <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>220</v>
@@ -8143,13 +8167,13 @@
         <v>312</v>
       </c>
       <c r="B104" s="5">
-        <v>46168.51702743056</v>
+        <v>46168.68369409722</v>
       </c>
       <c r="C104" s="5">
-        <v>46204.72342560186</v>
+        <v>46204.89009226851</v>
       </c>
       <c r="D104" s="5">
-        <v>46204.72343619213</v>
+        <v>46204.8901028588</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>313</v>
@@ -8208,13 +8232,13 @@
         <v>315</v>
       </c>
       <c r="B105" s="8">
-        <v>46168.517031828706</v>
+        <v>46168.68369849537</v>
       </c>
       <c r="C105" s="8">
-        <v>46204.72338321759</v>
+        <v>46204.890049884256</v>
       </c>
       <c r="D105" s="8">
-        <v>46204.723385300924</v>
+        <v>46204.890051967595</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>212</v>
@@ -8263,13 +8287,13 @@
         <v>317</v>
       </c>
       <c r="B106" s="5">
-        <v>46168.51703782407</v>
+        <v>46168.683704490744</v>
       </c>
       <c r="C106" s="5">
-        <v>46204.72338996528</v>
+        <v>46204.89005663195</v>
       </c>
       <c r="D106" s="5">
-        <v>46204.723391458334</v>
+        <v>46204.890058125005</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>318</v>
@@ -8318,13 +8342,13 @@
         <v>320</v>
       </c>
       <c r="B107" s="8">
-        <v>46168.51704348379</v>
+        <v>46168.683710150464</v>
       </c>
       <c r="C107" s="8">
-        <v>46204.72339570602</v>
+        <v>46204.89006237268</v>
       </c>
       <c r="D107" s="8">
-        <v>46204.72339728009</v>
+        <v>46204.89006394676</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>216</v>
@@ -8373,13 +8397,13 @@
         <v>321</v>
       </c>
       <c r="B108" s="5">
-        <v>46168.517046423614</v>
+        <v>46168.68371309028</v>
       </c>
       <c r="C108" s="5">
-        <v>46204.72340120371</v>
+        <v>46204.89006787037</v>
       </c>
       <c r="D108" s="5">
-        <v>46204.72340269676</v>
+        <v>46204.89006936342</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>216</v>
@@ -8428,13 +8452,13 @@
         <v>323</v>
       </c>
       <c r="B109" s="8">
-        <v>46168.51704980324</v>
+        <v>46168.68371646991</v>
       </c>
       <c r="C109" s="8">
-        <v>46204.72341194445</v>
+        <v>46204.89007861111</v>
       </c>
       <c r="D109" s="8">
-        <v>46204.72341351851</v>
+        <v>46204.890080185185</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>220</v>
@@ -8483,11 +8507,11 @@
         <v>325</v>
       </c>
       <c r="B110" s="5">
-        <v>46168.517063391206</v>
+        <v>46168.68373005787</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46168.68819925926</v>
+        <v>46205.614553402775</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>257</v>
@@ -8523,18 +8547,22 @@
       <c r="R110" s="6"/>
       <c r="S110" s="6"/>
       <c r="T110" s="6"/>
-      <c r="U110" s="6"/>
+      <c r="U110" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
         <v>327</v>
       </c>
       <c r="B111" s="8">
-        <v>46168.51706699074</v>
-      </c>
-      <c r="C111" s="9"/>
+        <v>46168.68373365741</v>
+      </c>
+      <c r="C111" s="8">
+        <v>46205.60850809028</v>
+      </c>
       <c r="D111" s="8">
-        <v>46186.00151503472</v>
+        <v>46205.61049446759</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>328</v>
@@ -8582,10 +8610,10 @@
         <v>105</v>
       </c>
       <c r="T111" s="9">
-        <v>0</v>
-      </c>
-      <c r="U111" s="11" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="U111" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
@@ -8593,11 +8621,13 @@
         <v>330</v>
       </c>
       <c r="B112" s="5">
-        <v>46168.51707422454</v>
-      </c>
-      <c r="C112" s="6"/>
+        <v>46168.6837408912</v>
+      </c>
+      <c r="C112" s="5">
+        <v>46205.614536215275</v>
+      </c>
       <c r="D112" s="5">
-        <v>46195.76172023149</v>
+        <v>46205.61455358796</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>331</v>
@@ -8643,10 +8673,10 @@
         <v>105</v>
       </c>
       <c r="T112" s="6">
-        <v>0</v>
-      </c>
-      <c r="U112" s="11" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="U112" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
@@ -8654,11 +8684,13 @@
         <v>333</v>
       </c>
       <c r="B113" s="8">
-        <v>46168.51708105324</v>
-      </c>
-      <c r="C113" s="9"/>
+        <v>46168.68374771991</v>
+      </c>
+      <c r="C113" s="8">
+        <v>46205.608276342595</v>
+      </c>
       <c r="D113" s="8">
-        <v>46200.0023731713</v>
+        <v>46205.6084347338</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>334</v>
@@ -8706,10 +8738,10 @@
         <v>105</v>
       </c>
       <c r="T113" s="9">
-        <v>0</v>
-      </c>
-      <c r="U113" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U113" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
@@ -8717,11 +8749,11 @@
         <v>336</v>
       </c>
       <c r="B114" s="5">
-        <v>46168.517088356486</v>
+        <v>46168.68375502314</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46204.434893171296</v>
+        <v>46204.60155983796</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>337</v>
@@ -8772,7 +8804,7 @@
         <v>0</v>
       </c>
       <c r="U114" s="11" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8780,11 +8812,13 @@
         <v>339</v>
       </c>
       <c r="B115" s="8">
-        <v>46168.51713047454</v>
-      </c>
-      <c r="C115" s="9"/>
+        <v>46168.6837971412</v>
+      </c>
+      <c r="C115" s="8">
+        <v>46205.61658686343</v>
+      </c>
       <c r="D115" s="8">
-        <v>46196.64127523148</v>
+        <v>46205.61660277778</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>58</v>
@@ -8832,10 +8866,10 @@
         <v>32</v>
       </c>
       <c r="T115" s="9">
-        <v>0</v>
-      </c>
-      <c r="U115" s="11" t="s">
-        <v>72</v>
+        <v>1</v>
+      </c>
+      <c r="U115" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
@@ -8843,11 +8877,11 @@
         <v>341</v>
       </c>
       <c r="B116" s="5">
-        <v>46168.517146956015</v>
+        <v>46168.68381362269</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46204.72676152778</v>
+        <v>46204.893428194446</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>342</v>
@@ -8890,13 +8924,13 @@
         <v>344</v>
       </c>
       <c r="B117" s="8">
-        <v>46168.517151168984</v>
+        <v>46168.68381783565</v>
       </c>
       <c r="C117" s="8">
-        <v>46204.72409200232</v>
+        <v>46204.89075866898</v>
       </c>
       <c r="D117" s="8">
-        <v>46204.72410247685</v>
+        <v>46204.890769143516</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>345</v>
@@ -8955,13 +8989,13 @@
         <v>347</v>
       </c>
       <c r="B118" s="5">
-        <v>46168.51715914352</v>
+        <v>46168.683825810185</v>
       </c>
       <c r="C118" s="5">
-        <v>46204.724079085645</v>
+        <v>46204.89074575232</v>
       </c>
       <c r="D118" s="5">
-        <v>46204.72408061342</v>
+        <v>46204.89074728009</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>212</v>
@@ -9010,13 +9044,13 @@
         <v>349</v>
       </c>
       <c r="B119" s="8">
-        <v>46168.517169212966</v>
+        <v>46168.68383587963</v>
       </c>
       <c r="C119" s="8">
-        <v>46204.72399413194</v>
+        <v>46204.890660798614</v>
       </c>
       <c r="D119" s="8">
-        <v>46204.723996053246</v>
+        <v>46204.8906627199</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>212</v>
@@ -9065,13 +9099,13 @@
         <v>351</v>
       </c>
       <c r="B120" s="5">
-        <v>46168.51717368056</v>
+        <v>46168.68384034722</v>
       </c>
       <c r="C120" s="5">
-        <v>46204.723851840274</v>
+        <v>46204.890518506945</v>
       </c>
       <c r="D120" s="5">
-        <v>46204.72385349537</v>
+        <v>46204.89052016204</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>216</v>
@@ -9120,13 +9154,13 @@
         <v>353</v>
       </c>
       <c r="B121" s="8">
-        <v>46168.51717740741</v>
+        <v>46168.683844074076</v>
       </c>
       <c r="C121" s="8">
-        <v>46204.72383826389</v>
+        <v>46204.890504930554</v>
       </c>
       <c r="D121" s="8">
-        <v>46204.72384023148</v>
+        <v>46204.89050689815</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>216</v>
@@ -9175,13 +9209,13 @@
         <v>354</v>
       </c>
       <c r="B122" s="5">
-        <v>46168.517181006944</v>
+        <v>46168.683847673616</v>
       </c>
       <c r="C122" s="5">
-        <v>46197.329260439816</v>
+        <v>46197.49592710648</v>
       </c>
       <c r="D122" s="5">
-        <v>46204.72342054398</v>
+        <v>46204.890087210646</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>220</v>
@@ -9230,13 +9264,13 @@
         <v>356</v>
       </c>
       <c r="B123" s="8">
-        <v>46168.51719578703</v>
+        <v>46168.683862453705</v>
       </c>
       <c r="C123" s="8">
-        <v>46204.72508888889</v>
+        <v>46204.89175555555</v>
       </c>
       <c r="D123" s="8">
-        <v>46204.72510023148</v>
+        <v>46204.891766898145</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>357</v>
@@ -9295,13 +9329,13 @@
         <v>358</v>
       </c>
       <c r="B124" s="5">
-        <v>46168.51720047454</v>
+        <v>46168.683867141204</v>
       </c>
       <c r="C124" s="5">
-        <v>46204.72430960648</v>
+        <v>46204.89097627315</v>
       </c>
       <c r="D124" s="5">
-        <v>46204.72431158565</v>
+        <v>46205.61454657407</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>212</v>
@@ -9350,13 +9384,13 @@
         <v>361</v>
       </c>
       <c r="B125" s="8">
-        <v>46168.51720670139</v>
+        <v>46168.683873368056</v>
       </c>
       <c r="C125" s="8">
-        <v>46204.72498914352</v>
+        <v>46204.891655810185</v>
       </c>
       <c r="D125" s="8">
-        <v>46204.7249906713</v>
+        <v>46205.61454702546</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>212</v>
@@ -9405,13 +9439,13 @@
         <v>363</v>
       </c>
       <c r="B126" s="5">
-        <v>46168.51721237268</v>
+        <v>46168.68387903935</v>
       </c>
       <c r="C126" s="5">
-        <v>46204.72507359953</v>
+        <v>46204.891740266205</v>
       </c>
       <c r="D126" s="5">
-        <v>46204.72507532407</v>
+        <v>46205.614544861106</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>216</v>
@@ -9460,13 +9494,13 @@
         <v>366</v>
       </c>
       <c r="B127" s="8">
-        <v>46168.51721795139</v>
+        <v>46168.683884618054</v>
       </c>
       <c r="C127" s="8">
-        <v>46204.724925625</v>
+        <v>46204.891592291664</v>
       </c>
       <c r="D127" s="8">
-        <v>46204.724927303236</v>
+        <v>46205.61454555555</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>216</v>
@@ -9515,13 +9549,13 @@
         <v>368</v>
       </c>
       <c r="B128" s="5">
-        <v>46168.51722366898</v>
+        <v>46168.68389033565</v>
       </c>
       <c r="C128" s="5">
-        <v>46197.329386620375</v>
+        <v>46197.49605328703</v>
       </c>
       <c r="D128" s="5">
-        <v>46197.32938811343</v>
+        <v>46205.614546122684</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>220</v>
@@ -9570,13 +9604,13 @@
         <v>371</v>
       </c>
       <c r="B129" s="8">
-        <v>46168.51724622685</v>
+        <v>46168.68391289352</v>
       </c>
       <c r="C129" s="8">
-        <v>46204.72632216435</v>
+        <v>46204.89298883102</v>
       </c>
       <c r="D129" s="8">
-        <v>46204.72632418982</v>
+        <v>46204.89299085648</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>372</v>
@@ -9635,13 +9669,13 @@
         <v>373</v>
       </c>
       <c r="B130" s="5">
-        <v>46168.517251516205</v>
+        <v>46168.68391818287</v>
       </c>
       <c r="C130" s="5">
-        <v>46204.7259369213</v>
+        <v>46204.89260358796</v>
       </c>
       <c r="D130" s="5">
-        <v>46204.725938414354</v>
+        <v>46205.6085181713</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>212</v>
@@ -9690,13 +9724,13 @@
         <v>376</v>
       </c>
       <c r="B131" s="8">
-        <v>46168.517264016205</v>
+        <v>46168.68393068287</v>
       </c>
       <c r="C131" s="8">
-        <v>46204.725991168976</v>
+        <v>46204.89265783565</v>
       </c>
       <c r="D131" s="8">
-        <v>46204.72599314815</v>
+        <v>46205.60851520833</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>212</v>
@@ -9745,13 +9779,13 @@
         <v>379</v>
       </c>
       <c r="B132" s="5">
-        <v>46168.51727104167</v>
+        <v>46168.68393770834</v>
       </c>
       <c r="C132" s="5">
-        <v>46204.726057314816</v>
+        <v>46204.89272398148</v>
       </c>
       <c r="D132" s="5">
-        <v>46204.726058796296</v>
+        <v>46205.608516168984</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>216</v>
@@ -9800,13 +9834,13 @@
         <v>382</v>
       </c>
       <c r="B133" s="8">
-        <v>46168.51727677083</v>
+        <v>46168.6839434375</v>
       </c>
       <c r="C133" s="8">
-        <v>46204.72612608796</v>
+        <v>46204.89279275463</v>
       </c>
       <c r="D133" s="8">
-        <v>46204.72612752314</v>
+        <v>46205.608518877314</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>216</v>
@@ -9855,13 +9889,13 @@
         <v>383</v>
       </c>
       <c r="B134" s="5">
-        <v>46168.51731862269</v>
+        <v>46168.68398528935</v>
       </c>
       <c r="C134" s="5">
-        <v>46197.32948237269</v>
+        <v>46197.49614903935</v>
       </c>
       <c r="D134" s="5">
-        <v>46197.32948403935</v>
+        <v>46205.608517326385</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>220</v>
@@ -9910,13 +9944,13 @@
         <v>386</v>
       </c>
       <c r="B135" s="8">
-        <v>46168.51734421296</v>
+        <v>46168.68401087963</v>
       </c>
       <c r="C135" s="8">
-        <v>46204.72675548611</v>
+        <v>46204.893422152774</v>
       </c>
       <c r="D135" s="8">
-        <v>46204.726757094904</v>
+        <v>46204.893423761576</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>387</v>
@@ -9975,13 +10009,13 @@
         <v>388</v>
       </c>
       <c r="B136" s="5">
-        <v>46168.51734986111</v>
+        <v>46168.68401652778</v>
       </c>
       <c r="C136" s="5">
-        <v>46204.72651574074</v>
+        <v>46204.89318240741</v>
       </c>
       <c r="D136" s="5">
-        <v>46204.72651710648</v>
+        <v>46205.60828351852</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>212</v>
@@ -10030,13 +10064,13 @@
         <v>391</v>
       </c>
       <c r="B137" s="8">
-        <v>46168.517357372686</v>
+        <v>46168.68402403935</v>
       </c>
       <c r="C137" s="8">
-        <v>46204.72643394676</v>
+        <v>46204.89310061342</v>
       </c>
       <c r="D137" s="8">
-        <v>46204.72643519676</v>
+        <v>46205.60828236111</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>212</v>
@@ -10085,13 +10119,13 @@
         <v>392</v>
       </c>
       <c r="B138" s="5">
-        <v>46168.51736460648</v>
+        <v>46168.68403127315</v>
       </c>
       <c r="C138" s="5">
-        <v>46204.72637049769</v>
+        <v>46204.89303716435</v>
       </c>
       <c r="D138" s="5">
-        <v>46204.726371875004</v>
+        <v>46205.608284375005</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>216</v>
@@ -10140,13 +10174,13 @@
         <v>395</v>
       </c>
       <c r="B139" s="8">
-        <v>46168.517370891204</v>
+        <v>46168.68403755787</v>
       </c>
       <c r="C139" s="8">
-        <v>46204.7262408449</v>
+        <v>46204.892907511574</v>
       </c>
       <c r="D139" s="8">
-        <v>46204.72624239583</v>
+        <v>46205.60828523149</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>216</v>
@@ -10195,13 +10229,13 @@
         <v>397</v>
       </c>
       <c r="B140" s="5">
-        <v>46168.5173771875</v>
+        <v>46168.68404385417</v>
       </c>
       <c r="C140" s="5">
-        <v>46197.32960333333</v>
+        <v>46197.49627</v>
       </c>
       <c r="D140" s="5">
-        <v>46197.32969271991</v>
+        <v>46205.60828666667</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>220</v>
@@ -10250,11 +10284,11 @@
         <v>400</v>
       </c>
       <c r="B141" s="8">
-        <v>46168.51739630787</v>
+        <v>46168.68406297454</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46204.72667293981</v>
+        <v>46204.89333960648</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>401</v>
@@ -10313,11 +10347,11 @@
         <v>402</v>
       </c>
       <c r="B142" s="5">
-        <v>46168.51740085648</v>
+        <v>46168.68406752315</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46204.72652578704</v>
+        <v>46204.8931924537</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>212</v>
@@ -10366,11 +10400,11 @@
         <v>404</v>
       </c>
       <c r="B143" s="8">
-        <v>46168.517412719906</v>
+        <v>46168.68407938657</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46204.726440011575</v>
+        <v>46204.89310667824</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>212</v>
@@ -10419,11 +10453,11 @@
         <v>406</v>
       </c>
       <c r="B144" s="5">
-        <v>46168.517418564814</v>
+        <v>46168.68408523148</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46204.72637809028</v>
+        <v>46204.893044756944</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>216</v>
@@ -10472,11 +10506,11 @@
         <v>408</v>
       </c>
       <c r="B145" s="8">
-        <v>46168.51742321759</v>
+        <v>46168.684089884264</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46204.72624685185</v>
+        <v>46204.89291351852</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>216</v>
@@ -10525,13 +10559,13 @@
         <v>409</v>
       </c>
       <c r="B146" s="5">
-        <v>46168.51742790509</v>
+        <v>46168.684094571756</v>
       </c>
       <c r="C146" s="5">
-        <v>46204.726667442126</v>
+        <v>46204.8933341088</v>
       </c>
       <c r="D146" s="5">
-        <v>46204.72666900463</v>
+        <v>46204.893335671295</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>220</v>
@@ -10580,11 +10614,11 @@
         <v>411</v>
       </c>
       <c r="B147" s="8">
-        <v>46168.51747907407</v>
+        <v>46168.68414574074</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46168.70116519676</v>
+        <v>46168.86783186343</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>412</v>
@@ -10643,11 +10677,11 @@
         <v>414</v>
       </c>
       <c r="B148" s="5">
-        <v>46168.517484386575</v>
+        <v>46168.68415105324</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46168.70113376157</v>
+        <v>46168.86780042824</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>212</v>
@@ -10696,11 +10730,11 @@
         <v>416</v>
       </c>
       <c r="B149" s="8">
-        <v>46168.51748921296</v>
+        <v>46168.68415587963</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46168.70113033565</v>
+        <v>46168.86779700231</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>212</v>
@@ -10749,11 +10783,11 @@
         <v>418</v>
       </c>
       <c r="B150" s="5">
-        <v>46168.5174940162</v>
+        <v>46168.68416068287</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46168.70112755787</v>
+        <v>46168.86779422454</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>216</v>
@@ -10802,11 +10836,11 @@
         <v>420</v>
       </c>
       <c r="B151" s="8">
-        <v>46168.517497650464</v>
+        <v>46168.68416431713</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46168.70112471065</v>
+        <v>46168.86779137731</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>216</v>
@@ -10855,11 +10889,11 @@
         <v>421</v>
       </c>
       <c r="B152" s="5">
-        <v>46168.517501319446</v>
+        <v>46168.68416798611</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46168.70112032407</v>
+        <v>46168.86778699074</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>220</v>
@@ -10908,11 +10942,11 @@
         <v>423</v>
       </c>
       <c r="B153" s="8">
-        <v>46168.51751679398</v>
+        <v>46168.684183460646</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46168.69303797453</v>
+        <v>46168.8597046412</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>424</v>
@@ -10955,11 +10989,11 @@
         <v>426</v>
       </c>
       <c r="B154" s="5">
-        <v>46168.51752033565</v>
+        <v>46168.68418700232</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46196.727490000005</v>
+        <v>46196.89415666666</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>427</v>
@@ -11018,11 +11052,11 @@
         <v>431</v>
       </c>
       <c r="B155" s="8">
-        <v>46168.517526932876</v>
+        <v>46168.68419359953</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46168.70138209491</v>
+        <v>46168.86804876158</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>212</v>
@@ -11071,11 +11105,11 @@
         <v>433</v>
       </c>
       <c r="B156" s="5">
-        <v>46168.51753167824</v>
+        <v>46168.68419834491</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46168.70137912037</v>
+        <v>46168.868045787036</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>212</v>
@@ -11124,11 +11158,11 @@
         <v>434</v>
       </c>
       <c r="B157" s="8">
-        <v>46168.51753611111</v>
+        <v>46168.684202777775</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46168.70137597222</v>
+        <v>46168.86804263889</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>216</v>
@@ -11177,11 +11211,11 @@
         <v>436</v>
       </c>
       <c r="B158" s="5">
-        <v>46168.51754043982</v>
+        <v>46168.68420710648</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46168.70137328704</v>
+        <v>46168.868039953704</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>216</v>
@@ -11230,11 +11264,11 @@
         <v>437</v>
       </c>
       <c r="B159" s="8">
-        <v>46168.51754460648</v>
+        <v>46168.68421127315</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46168.70137042824</v>
+        <v>46168.86803709491</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>220</v>
@@ -11283,14 +11317,14 @@
         <v>439</v>
       </c>
       <c r="B160" s="5">
-        <v>46168.51756329861</v>
+        <v>46168.68422996528</v>
       </c>
       <c r="C160" s="6"/>
       <c r="D160" s="5">
-        <v>46196.72764913195</v>
+        <v>46196.89431579861</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11320,7 +11354,7 @@
         <v>427</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>440</v>
@@ -11336,14 +11370,14 @@
         <v>441</v>
       </c>
       <c r="B161" s="8">
-        <v>46168.51756674769</v>
+        <v>46168.68423341435</v>
       </c>
       <c r="C161" s="9"/>
       <c r="D161" s="8">
-        <v>46196.72769763889</v>
+        <v>46196.89436430555</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>26</v>
@@ -11373,7 +11407,7 @@
         <v>427</v>
       </c>
       <c r="O161" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P161" s="9" t="s">
         <v>440</v>
@@ -11389,14 +11423,14 @@
         <v>442</v>
       </c>
       <c r="B162" s="5">
-        <v>46168.51757037037</v>
+        <v>46168.684237037036</v>
       </c>
       <c r="C162" s="6"/>
       <c r="D162" s="5">
-        <v>46196.72774357639</v>
+        <v>46196.894410243054</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11426,7 +11460,7 @@
         <v>427</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>440</v>
@@ -11442,14 +11476,14 @@
         <v>443</v>
       </c>
       <c r="B163" s="8">
-        <v>46168.517573923615</v>
+        <v>46168.68424059028</v>
       </c>
       <c r="C163" s="9"/>
       <c r="D163" s="8">
-        <v>46196.72779189815</v>
+        <v>46196.89445856481</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
@@ -11479,7 +11513,7 @@
         <v>427</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P163" s="9" t="s">
         <v>444</v>
@@ -11495,14 +11529,14 @@
         <v>445</v>
       </c>
       <c r="B164" s="5">
-        <v>46168.51757753472</v>
+        <v>46168.68424420139</v>
       </c>
       <c r="C164" s="6"/>
       <c r="D164" s="5">
-        <v>46196.727842141205</v>
+        <v>46196.89450880787</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11532,7 +11566,7 @@
         <v>427</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>444</v>
@@ -11548,14 +11582,14 @@
         <v>446</v>
       </c>
       <c r="B165" s="8">
-        <v>46168.51758112268</v>
+        <v>46168.68424778935</v>
       </c>
       <c r="C165" s="9"/>
       <c r="D165" s="8">
-        <v>46196.727895601856</v>
+        <v>46196.89456226851</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
@@ -11585,7 +11619,7 @@
         <v>427</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P165" s="9" t="s">
         <v>447</v>
@@ -11601,11 +11635,11 @@
         <v>448</v>
       </c>
       <c r="B166" s="5">
-        <v>46168.51759153935</v>
+        <v>46168.68425820602</v>
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46195.38560393518</v>
+        <v>46195.55227060185</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>449</v>
@@ -11662,11 +11696,11 @@
         <v>451</v>
       </c>
       <c r="B167" s="8">
-        <v>46168.5175958912</v>
+        <v>46168.68426255787</v>
       </c>
       <c r="C167" s="9"/>
       <c r="D167" s="8">
-        <v>46168.70160164352</v>
+        <v>46168.86826831019</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>212</v>
@@ -11713,11 +11747,11 @@
         <v>453</v>
       </c>
       <c r="B168" s="5">
-        <v>46168.51760038194</v>
+        <v>46168.68426704861</v>
       </c>
       <c r="C168" s="6"/>
       <c r="D168" s="5">
-        <v>46168.70159834491</v>
+        <v>46168.86826501157</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>212</v>
@@ -11764,11 +11798,11 @@
         <v>454</v>
       </c>
       <c r="B169" s="8">
-        <v>46168.517604953704</v>
+        <v>46168.68427162037</v>
       </c>
       <c r="C169" s="9"/>
       <c r="D169" s="8">
-        <v>46168.70159511574</v>
+        <v>46168.86826178241</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>216</v>
@@ -11815,11 +11849,11 @@
         <v>456</v>
       </c>
       <c r="B170" s="5">
-        <v>46168.51760960648</v>
+        <v>46168.68427627315</v>
       </c>
       <c r="C170" s="6"/>
       <c r="D170" s="5">
-        <v>46168.70159207176</v>
+        <v>46168.868258738425</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>216</v>
@@ -11866,11 +11900,11 @@
         <v>457</v>
       </c>
       <c r="B171" s="8">
-        <v>46168.51761401621</v>
+        <v>46168.68428068287</v>
       </c>
       <c r="C171" s="9"/>
       <c r="D171" s="8">
-        <v>46168.70158836806</v>
+        <v>46168.86825503472</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>220</v>
@@ -11917,14 +11951,14 @@
         <v>459</v>
       </c>
       <c r="B172" s="5">
-        <v>46168.517669560184</v>
+        <v>46168.684336226856</v>
       </c>
       <c r="C172" s="6"/>
       <c r="D172" s="5">
-        <v>46168.701585092596</v>
+        <v>46168.86825175926</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -11952,7 +11986,7 @@
         <v>449</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>460</v>
@@ -11968,14 +12002,14 @@
         <v>461</v>
       </c>
       <c r="B173" s="8">
-        <v>46168.5176734375</v>
+        <v>46168.68434010417</v>
       </c>
       <c r="C173" s="9"/>
       <c r="D173" s="8">
-        <v>46168.701582002315</v>
+        <v>46168.86824866898</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
@@ -12003,7 +12037,7 @@
         <v>449</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P173" s="9" t="s">
         <v>462</v>
@@ -12019,14 +12053,14 @@
         <v>463</v>
       </c>
       <c r="B174" s="5">
-        <v>46168.51767756944</v>
+        <v>46168.68434423611</v>
       </c>
       <c r="C174" s="6"/>
       <c r="D174" s="5">
-        <v>46168.701578796296</v>
+        <v>46168.86824546296</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -12054,7 +12088,7 @@
         <v>449</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>460</v>
@@ -12070,14 +12104,14 @@
         <v>464</v>
       </c>
       <c r="B175" s="8">
-        <v>46168.51768159722</v>
+        <v>46168.684348263894</v>
       </c>
       <c r="C175" s="9"/>
       <c r="D175" s="8">
-        <v>46168.70157584491</v>
+        <v>46168.86824251157</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>26</v>
@@ -12105,7 +12139,7 @@
         <v>449</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P175" s="9" t="s">
         <v>465</v>
@@ -12121,14 +12155,14 @@
         <v>466</v>
       </c>
       <c r="B176" s="5">
-        <v>46168.51768535879</v>
+        <v>46168.68435202546</v>
       </c>
       <c r="C176" s="6"/>
       <c r="D176" s="5">
-        <v>46168.701568425924</v>
+        <v>46168.868235092596</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -12156,7 +12190,7 @@
         <v>449</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>465</v>
@@ -12172,14 +12206,14 @@
         <v>467</v>
       </c>
       <c r="B177" s="8">
-        <v>46168.51768986111</v>
+        <v>46168.68435652778</v>
       </c>
       <c r="C177" s="9"/>
       <c r="D177" s="8">
-        <v>46168.7015677662</v>
+        <v>46168.86823443287</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
@@ -12207,7 +12241,7 @@
         <v>449</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P177" s="9" t="s">
         <v>468</v>
@@ -12223,11 +12257,11 @@
         <v>469</v>
       </c>
       <c r="B178" s="5">
-        <v>46168.51770648148</v>
+        <v>46168.68437314815</v>
       </c>
       <c r="C178" s="6"/>
       <c r="D178" s="5">
-        <v>46168.70178509259</v>
+        <v>46168.86845175926</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>470</v>
@@ -12284,11 +12318,11 @@
         <v>472</v>
       </c>
       <c r="B179" s="8">
-        <v>46168.51771180556</v>
+        <v>46168.68437847222</v>
       </c>
       <c r="C179" s="9"/>
       <c r="D179" s="8">
-        <v>46168.701782476855</v>
+        <v>46168.86844914352</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>212</v>
@@ -12337,11 +12371,11 @@
         <v>474</v>
       </c>
       <c r="B180" s="5">
-        <v>46168.517721550925</v>
+        <v>46168.68438821759</v>
       </c>
       <c r="C180" s="6"/>
       <c r="D180" s="5">
-        <v>46168.701779201394</v>
+        <v>46168.86844586805</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>212</v>
@@ -12390,11 +12424,11 @@
         <v>476</v>
       </c>
       <c r="B181" s="8">
-        <v>46168.51772787037</v>
+        <v>46168.684394537035</v>
       </c>
       <c r="C181" s="9"/>
       <c r="D181" s="8">
-        <v>46168.70177555556</v>
+        <v>46168.86844222222</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>216</v>
@@ -12443,11 +12477,11 @@
         <v>478</v>
       </c>
       <c r="B182" s="5">
-        <v>46168.51773277778</v>
+        <v>46168.68439944445</v>
       </c>
       <c r="C182" s="6"/>
       <c r="D182" s="5">
-        <v>46168.70177208333</v>
+        <v>46168.868438749996</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>216</v>
@@ -12496,11 +12530,11 @@
         <v>480</v>
       </c>
       <c r="B183" s="8">
-        <v>46168.51773770833</v>
+        <v>46168.684404375</v>
       </c>
       <c r="C183" s="9"/>
       <c r="D183" s="8">
-        <v>46168.701768391205</v>
+        <v>46168.86843505787</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>220</v>
@@ -12549,14 +12583,14 @@
         <v>482</v>
       </c>
       <c r="B184" s="5">
-        <v>46168.517752395834</v>
+        <v>46168.6844190625</v>
       </c>
       <c r="C184" s="6"/>
       <c r="D184" s="5">
-        <v>46168.701765150465</v>
+        <v>46168.86843181713</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12586,7 +12620,7 @@
         <v>470</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P184" s="6" t="s">
         <v>483</v>
@@ -12602,11 +12636,11 @@
         <v>484</v>
       </c>
       <c r="B185" s="8">
-        <v>46168.51775611111</v>
+        <v>46168.68442277778</v>
       </c>
       <c r="C185" s="9"/>
       <c r="D185" s="8">
-        <v>46168.701757627314</v>
+        <v>46168.86842429398</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>485</v>
@@ -12639,7 +12673,7 @@
         <v>470</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P185" s="9" t="s">
         <v>486</v>
@@ -12655,14 +12689,14 @@
         <v>487</v>
       </c>
       <c r="B186" s="5">
-        <v>46168.51775987269</v>
+        <v>46168.68442653935</v>
       </c>
       <c r="C186" s="6"/>
       <c r="D186" s="5">
-        <v>46168.70175685185</v>
+        <v>46168.86842351852</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12692,7 +12726,7 @@
         <v>470</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>488</v>
@@ -12708,14 +12742,14 @@
         <v>489</v>
       </c>
       <c r="B187" s="8">
-        <v>46168.51776332176</v>
+        <v>46168.684429988425</v>
       </c>
       <c r="C187" s="9"/>
       <c r="D187" s="8">
-        <v>46168.70175613426</v>
+        <v>46168.86842280092</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
@@ -12745,7 +12779,7 @@
         <v>470</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P187" s="9" t="s">
         <v>490</v>
@@ -12761,14 +12795,14 @@
         <v>491</v>
       </c>
       <c r="B188" s="5">
-        <v>46168.51776693287</v>
+        <v>46168.68443359954</v>
       </c>
       <c r="C188" s="6"/>
       <c r="D188" s="5">
-        <v>46168.701755381946</v>
+        <v>46168.86842204861</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12798,7 +12832,7 @@
         <v>470</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>492</v>
@@ -12814,14 +12848,14 @@
         <v>493</v>
       </c>
       <c r="B189" s="8">
-        <v>46168.517770624996</v>
+        <v>46168.68443729167</v>
       </c>
       <c r="C189" s="9"/>
       <c r="D189" s="8">
-        <v>46168.70175445602</v>
+        <v>46168.86842112269</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>26</v>
@@ -12851,7 +12885,7 @@
         <v>470</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P189" s="9" t="s">
         <v>494</v>
@@ -12867,11 +12901,11 @@
         <v>495</v>
       </c>
       <c r="B190" s="5">
-        <v>46168.517817395834</v>
+        <v>46168.6844840625</v>
       </c>
       <c r="C190" s="6"/>
       <c r="D190" s="5">
-        <v>46168.70196324074</v>
+        <v>46168.8686299074</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>496</v>
@@ -12930,11 +12964,11 @@
         <v>499</v>
       </c>
       <c r="B191" s="8">
-        <v>46168.5178246412</v>
+        <v>46168.68449130787</v>
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46168.701955173616</v>
+        <v>46168.86862184027</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>500</v>
@@ -12981,11 +13015,11 @@
         <v>501</v>
       </c>
       <c r="B192" s="5">
-        <v>46168.51782923611</v>
+        <v>46168.68449590278</v>
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46168.70195228009</v>
+        <v>46168.868618946755</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>502</v>
@@ -13032,11 +13066,11 @@
         <v>503</v>
       </c>
       <c r="B193" s="8">
-        <v>46168.51783361111</v>
+        <v>46168.68450027778</v>
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46168.701949594906</v>
+        <v>46168.86861626158</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>504</v>
@@ -13083,11 +13117,11 @@
         <v>505</v>
       </c>
       <c r="B194" s="5">
-        <v>46168.51783813657</v>
+        <v>46168.68450480324</v>
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46168.701946574074</v>
+        <v>46168.868613240746</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>506</v>
@@ -13134,11 +13168,11 @@
         <v>507</v>
       </c>
       <c r="B195" s="8">
-        <v>46168.51784267361</v>
+        <v>46168.68450934028</v>
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46168.70194290509</v>
+        <v>46168.86860957176</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>508</v>
@@ -13185,11 +13219,11 @@
         <v>509</v>
       </c>
       <c r="B196" s="5">
-        <v>46168.51785674768</v>
+        <v>46168.684523414355</v>
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46168.70193974537</v>
+        <v>46168.86860641204</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>510</v>
@@ -13220,7 +13254,7 @@
         <v>496</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P196" s="6" t="s">
         <v>496</v>
@@ -13236,11 +13270,11 @@
         <v>511</v>
       </c>
       <c r="B197" s="8">
-        <v>46168.51786047454</v>
+        <v>46168.6845271412</v>
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46168.701936666665</v>
+        <v>46168.868603333336</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>512</v>
@@ -13287,11 +13321,11 @@
         <v>513</v>
       </c>
       <c r="B198" s="5">
-        <v>46168.517868449075</v>
+        <v>46168.68453511574</v>
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46168.70193398148</v>
+        <v>46168.868600648144</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>514</v>
@@ -13322,7 +13356,7 @@
         <v>496</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>496</v>
@@ -13338,11 +13372,11 @@
         <v>515</v>
       </c>
       <c r="B199" s="8">
-        <v>46168.51787196759</v>
+        <v>46168.68453863426</v>
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46168.7019261574</v>
+        <v>46168.868592824074</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>516</v>
@@ -13373,7 +13407,7 @@
         <v>496</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P199" s="9" t="s">
         <v>496</v>
@@ -13389,11 +13423,11 @@
         <v>517</v>
       </c>
       <c r="B200" s="5">
-        <v>46168.517875439815</v>
+        <v>46168.68454210648</v>
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46168.701925416666</v>
+        <v>46168.86859208334</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>518</v>
@@ -13424,7 +13458,7 @@
         <v>496</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>496</v>
@@ -13440,11 +13474,11 @@
         <v>519</v>
       </c>
       <c r="B201" s="8">
-        <v>46168.51787891204</v>
+        <v>46168.684545578704</v>
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46168.70192471065</v>
+        <v>46168.868591377315</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>520</v>
@@ -13475,7 +13509,7 @@
         <v>496</v>
       </c>
       <c r="O201" s="9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P201" s="9" t="s">
         <v>496</v>
@@ -13491,11 +13525,11 @@
         <v>521</v>
       </c>
       <c r="B202" s="5">
-        <v>46168.5178891088</v>
+        <v>46168.684555775464</v>
       </c>
       <c r="C202" s="6"/>
       <c r="D202" s="5">
-        <v>46168.69520931713</v>
+        <v>46168.8618759838</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>522</v>
@@ -13538,11 +13572,11 @@
         <v>524</v>
       </c>
       <c r="B203" s="8">
-        <v>46168.517892800926</v>
+        <v>46168.6845594676</v>
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46168.7020271875</v>
+        <v>46168.868693854165</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>525</v>
@@ -13601,11 +13635,11 @@
         <v>528</v>
       </c>
       <c r="B204" s="5">
-        <v>46168.517897592596</v>
+        <v>46168.68456425926</v>
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46196.711112627316</v>
+        <v>46196.87777929398</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>529</v>
@@ -13664,11 +13698,11 @@
         <v>530</v>
       </c>
       <c r="B205" s="8">
-        <v>46168.517903831016</v>
+        <v>46168.68457049769</v>
       </c>
       <c r="C205" s="9"/>
       <c r="D205" s="8">
-        <v>46168.69567876158</v>
+        <v>46168.86234542824</v>
       </c>
       <c r="E205" s="9" t="s">
         <v>531</v>
@@ -13717,11 +13751,11 @@
         <v>533</v>
       </c>
       <c r="B206" s="5">
-        <v>46168.51790748842</v>
+        <v>46168.68457415509</v>
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46168.70213266204</v>
+        <v>46168.8687993287</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>534</v>
@@ -13780,11 +13814,11 @@
         <v>536</v>
       </c>
       <c r="B207" s="8">
-        <v>46168.51791253472</v>
+        <v>46168.68457920139</v>
       </c>
       <c r="C207" s="9"/>
       <c r="D207" s="8">
-        <v>46168.70212927084</v>
+        <v>46168.868795937495</v>
       </c>
       <c r="E207" s="9" t="s">
         <v>537</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -5374,9 +5374,11 @@
       <c r="B55" s="8">
         <v>46168.68338271991</v>
       </c>
-      <c r="C55" s="9"/>
+      <c r="C55" s="8">
+        <v>46205.64435017361</v>
+      </c>
       <c r="D55" s="8">
-        <v>46204.60155028936</v>
+        <v>46205.644352627314</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>192</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="538">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -843,19 +843,19 @@
     <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
   </si>
   <si>
+    <t>1215141533986830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Bodega:,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141533986830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Bodega:,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215141533986852</t>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46168.86492854166</v>
+        <v>46206.48580733796</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>212</v>
@@ -6789,7 +6789,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46168.86492561342</v>
+        <v>46206.48579508102</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>212</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46168.86492288194</v>
+        <v>46206.48578787037</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>216</v>
@@ -6895,7 +6895,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46168.864920162036</v>
+        <v>46206.48578125</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>216</v>
@@ -7056,7 +7056,7 @@
         <v>46205.61802771991</v>
       </c>
       <c r="D85" s="8">
-        <v>46205.618041678244</v>
+        <v>46206.18878055556</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>260</v>
@@ -7100,8 +7100,8 @@
       <c r="R85" s="8">
         <v>46205</v>
       </c>
-      <c r="S85" s="11" t="s">
-        <v>264</v>
+      <c r="S85" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -7112,7 +7112,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B86" s="5">
         <v>46168.68352011574</v>
@@ -7124,7 +7124,7 @@
         <v>46205.618054756946</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -7154,10 +7154,10 @@
         <v>257</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="Q86" s="5">
         <v>46206</v>
@@ -7166,7 +7166,7 @@
         <v>46209</v>
       </c>
       <c r="S86" s="11" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -7186,7 +7186,7 @@
         <v>46205.61804003472</v>
       </c>
       <c r="D87" s="8">
-        <v>46205.618055127314</v>
+        <v>46206.18878028935</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>270</v>
@@ -7230,8 +7230,8 @@
       <c r="R87" s="8">
         <v>46205</v>
       </c>
-      <c r="S87" s="11" t="s">
-        <v>264</v>
+      <c r="S87" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -7296,7 +7296,7 @@
         <v>46209</v>
       </c>
       <c r="S88" s="11" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -7316,7 +7316,7 @@
         <v>46205.61804746528</v>
       </c>
       <c r="D89" s="8">
-        <v>46205.618063437505</v>
+        <v>46206.1887803125</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>276</v>
@@ -7360,8 +7360,8 @@
       <c r="R89" s="8">
         <v>46205</v>
       </c>
-      <c r="S89" s="11" t="s">
-        <v>264</v>
+      <c r="S89" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T89" s="9">
         <v>1</v>
@@ -7426,7 +7426,7 @@
         <v>46209</v>
       </c>
       <c r="S90" s="11" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
@@ -7540,7 +7540,7 @@
         <v>46212</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46204.893428194446</v>
+        <v>46206.48624146991</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>342</v>
@@ -8919,7 +8919,9 @@
       <c r="R116" s="6"/>
       <c r="S116" s="6"/>
       <c r="T116" s="6"/>
-      <c r="U116" s="6"/>
+      <c r="U116" s="11" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
@@ -10288,9 +10290,11 @@
       <c r="B141" s="8">
         <v>46168.68406297454</v>
       </c>
-      <c r="C141" s="9"/>
+      <c r="C141" s="8">
+        <v>46206.4858124537</v>
+      </c>
       <c r="D141" s="8">
-        <v>46204.89333960648</v>
+        <v>46206.48582321759</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>401</v>
@@ -10338,10 +10342,10 @@
         <v>32</v>
       </c>
       <c r="T141" s="9">
-        <v>0</v>
-      </c>
-      <c r="U141" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U141" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
@@ -10351,9 +10355,11 @@
       <c r="B142" s="5">
         <v>46168.68406752315</v>
       </c>
-      <c r="C142" s="6"/>
+      <c r="C142" s="5">
+        <v>46206.48579756945</v>
+      </c>
       <c r="D142" s="5">
-        <v>46204.8931924537</v>
+        <v>46206.48579965278</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>212</v>
@@ -10404,9 +10410,11 @@
       <c r="B143" s="8">
         <v>46168.68407938657</v>
       </c>
-      <c r="C143" s="9"/>
+      <c r="C143" s="8">
+        <v>46206.485788935184</v>
+      </c>
       <c r="D143" s="8">
-        <v>46204.89310667824</v>
+        <v>46206.48579032408</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>212</v>
@@ -10457,9 +10465,11 @@
       <c r="B144" s="5">
         <v>46168.68408523148</v>
       </c>
-      <c r="C144" s="6"/>
+      <c r="C144" s="5">
+        <v>46206.48578153935</v>
+      </c>
       <c r="D144" s="5">
-        <v>46204.893044756944</v>
+        <v>46206.48578297454</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>216</v>
@@ -10510,9 +10520,11 @@
       <c r="B145" s="8">
         <v>46168.684089884264</v>
       </c>
-      <c r="C145" s="9"/>
+      <c r="C145" s="8">
+        <v>46206.4857743287</v>
+      </c>
       <c r="D145" s="8">
-        <v>46204.89291351852</v>
+        <v>46206.48577649306</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>216</v>
@@ -10618,9 +10630,11 @@
       <c r="B147" s="8">
         <v>46168.68414574074</v>
       </c>
-      <c r="C147" s="9"/>
+      <c r="C147" s="8">
+        <v>46206.48621289352</v>
+      </c>
       <c r="D147" s="8">
-        <v>46168.86783186343</v>
+        <v>46206.486229999995</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>412</v>
@@ -10668,10 +10682,10 @@
         <v>32</v>
       </c>
       <c r="T147" s="9">
-        <v>0</v>
-      </c>
-      <c r="U147" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U147" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
@@ -10681,9 +10695,11 @@
       <c r="B148" s="5">
         <v>46168.68415105324</v>
       </c>
-      <c r="C148" s="6"/>
+      <c r="C148" s="5">
+        <v>46206.48597313657</v>
+      </c>
       <c r="D148" s="5">
-        <v>46168.86780042824</v>
+        <v>46206.48597475694</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>212</v>
@@ -10734,9 +10750,11 @@
       <c r="B149" s="8">
         <v>46168.68415587963</v>
       </c>
-      <c r="C149" s="9"/>
+      <c r="C149" s="8">
+        <v>46206.48603997685</v>
+      </c>
       <c r="D149" s="8">
-        <v>46168.86779700231</v>
+        <v>46206.48604142361</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>212</v>
@@ -10787,9 +10805,11 @@
       <c r="B150" s="5">
         <v>46168.68416068287</v>
       </c>
-      <c r="C150" s="6"/>
+      <c r="C150" s="5">
+        <v>46206.48609505787</v>
+      </c>
       <c r="D150" s="5">
-        <v>46168.86779422454</v>
+        <v>46206.48609666667</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>216</v>
@@ -10840,9 +10860,11 @@
       <c r="B151" s="8">
         <v>46168.68416431713</v>
       </c>
-      <c r="C151" s="9"/>
+      <c r="C151" s="8">
+        <v>46206.48614579861</v>
+      </c>
       <c r="D151" s="8">
-        <v>46168.86779137731</v>
+        <v>46206.48614756945</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>216</v>
@@ -10893,9 +10915,11 @@
       <c r="B152" s="5">
         <v>46168.68416798611</v>
       </c>
-      <c r="C152" s="6"/>
+      <c r="C152" s="5">
+        <v>46206.48619949074</v>
+      </c>
       <c r="D152" s="5">
-        <v>46168.86778699074</v>
+        <v>46206.4862009375</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>220</v>
@@ -10995,7 +11019,7 @@
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46196.89415666666</v>
+        <v>46206.48623072916</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>427</v>
@@ -11058,7 +11082,7 @@
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46168.86804876158</v>
+        <v>46206.48597956018</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>212</v>
@@ -11111,7 +11135,7 @@
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46168.868045787036</v>
+        <v>46206.48604722222</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>212</v>
@@ -11164,7 +11188,7 @@
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46168.86804263889</v>
+        <v>46206.48610329861</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>216</v>
@@ -11217,7 +11241,7 @@
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46168.868039953704</v>
+        <v>46206.486152997684</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>216</v>
@@ -11270,7 +11294,7 @@
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46168.86803709491</v>
+        <v>46206.48620774306</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>220</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -10972,7 +10972,7 @@
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46168.8597046412</v>
+        <v>46209.71535164352</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>424</v>
@@ -11665,7 +11665,7 @@
       </c>
       <c r="C166" s="6"/>
       <c r="D166" s="5">
-        <v>46195.55227060185</v>
+        <v>46209.716104039355</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>449</v>
@@ -11724,9 +11724,11 @@
       <c r="B167" s="8">
         <v>46168.68426255787</v>
       </c>
-      <c r="C167" s="9"/>
+      <c r="C167" s="8">
+        <v>46209.71549736111</v>
+      </c>
       <c r="D167" s="8">
-        <v>46168.86826831019</v>
+        <v>46209.715499224534</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>212</v>
@@ -11775,9 +11777,11 @@
       <c r="B168" s="5">
         <v>46168.68426704861</v>
       </c>
-      <c r="C168" s="6"/>
+      <c r="C168" s="5">
+        <v>46209.71563954861</v>
+      </c>
       <c r="D168" s="5">
-        <v>46168.86826501157</v>
+        <v>46209.71564094907</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>212</v>
@@ -11826,9 +11830,11 @@
       <c r="B169" s="8">
         <v>46168.68427162037</v>
       </c>
-      <c r="C169" s="9"/>
+      <c r="C169" s="8">
+        <v>46209.7157528588</v>
+      </c>
       <c r="D169" s="8">
-        <v>46168.86826178241</v>
+        <v>46209.715754687495</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>216</v>
@@ -11877,9 +11883,11 @@
       <c r="B170" s="5">
         <v>46168.68427627315</v>
       </c>
-      <c r="C170" s="6"/>
+      <c r="C170" s="5">
+        <v>46209.71582945602</v>
+      </c>
       <c r="D170" s="5">
-        <v>46168.868258738425</v>
+        <v>46209.71583108796</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>216</v>
@@ -11928,9 +11936,11 @@
       <c r="B171" s="8">
         <v>46168.68428068287</v>
       </c>
-      <c r="C171" s="9"/>
+      <c r="C171" s="8">
+        <v>46209.71609789351</v>
+      </c>
       <c r="D171" s="8">
-        <v>46168.86825503472</v>
+        <v>46209.71609957176</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>220</v>
@@ -12285,9 +12295,11 @@
       <c r="B178" s="5">
         <v>46168.68437314815</v>
       </c>
-      <c r="C178" s="6"/>
+      <c r="C178" s="5">
+        <v>46209.71534268519</v>
+      </c>
       <c r="D178" s="5">
-        <v>46168.86845175926</v>
+        <v>46209.715354976855</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>470</v>
@@ -12333,10 +12345,10 @@
         <v>32</v>
       </c>
       <c r="T178" s="6">
-        <v>0</v>
-      </c>
-      <c r="U178" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U178" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
@@ -12346,9 +12358,11 @@
       <c r="B179" s="8">
         <v>46168.68437847222</v>
       </c>
-      <c r="C179" s="9"/>
+      <c r="C179" s="8">
+        <v>46209.714091435184</v>
+      </c>
       <c r="D179" s="8">
-        <v>46168.86844914352</v>
+        <v>46209.71550439815</v>
       </c>
       <c r="E179" s="9" t="s">
         <v>212</v>
@@ -12399,9 +12413,11 @@
       <c r="B180" s="5">
         <v>46168.68438821759</v>
       </c>
-      <c r="C180" s="6"/>
+      <c r="C180" s="5">
+        <v>46209.71433162037</v>
+      </c>
       <c r="D180" s="5">
-        <v>46168.86844586805</v>
+        <v>46209.7156449537</v>
       </c>
       <c r="E180" s="6" t="s">
         <v>212</v>
@@ -12452,9 +12468,11 @@
       <c r="B181" s="8">
         <v>46168.684394537035</v>
       </c>
-      <c r="C181" s="9"/>
+      <c r="C181" s="8">
+        <v>46209.71452164352</v>
+      </c>
       <c r="D181" s="8">
-        <v>46168.86844222222</v>
+        <v>46209.715759733794</v>
       </c>
       <c r="E181" s="9" t="s">
         <v>216</v>
@@ -12505,9 +12523,11 @@
       <c r="B182" s="5">
         <v>46168.68439944445</v>
       </c>
-      <c r="C182" s="6"/>
+      <c r="C182" s="5">
+        <v>46209.71464302084</v>
+      </c>
       <c r="D182" s="5">
-        <v>46168.868438749996</v>
+        <v>46209.71583459491</v>
       </c>
       <c r="E182" s="6" t="s">
         <v>216</v>
@@ -12558,9 +12578,11 @@
       <c r="B183" s="8">
         <v>46168.684404375</v>
       </c>
-      <c r="C183" s="9"/>
+      <c r="C183" s="8">
+        <v>46209.714748530096</v>
+      </c>
       <c r="D183" s="8">
-        <v>46168.86843505787</v>
+        <v>46209.71610449074</v>
       </c>
       <c r="E183" s="9" t="s">
         <v>220</v>
@@ -12611,9 +12633,11 @@
       <c r="B184" s="5">
         <v>46168.6844190625</v>
       </c>
-      <c r="C184" s="6"/>
+      <c r="C184" s="5">
+        <v>46209.71483280092</v>
+      </c>
       <c r="D184" s="5">
-        <v>46168.86843181713</v>
+        <v>46209.714834328704</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>62</v>
@@ -12664,9 +12688,11 @@
       <c r="B185" s="8">
         <v>46168.68442277778</v>
       </c>
-      <c r="C185" s="9"/>
+      <c r="C185" s="8">
+        <v>46209.714913159725</v>
+      </c>
       <c r="D185" s="8">
-        <v>46168.86842429398</v>
+        <v>46209.71491484954</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>485</v>
@@ -12717,9 +12743,11 @@
       <c r="B186" s="5">
         <v>46168.68442653935</v>
       </c>
-      <c r="C186" s="6"/>
+      <c r="C186" s="5">
+        <v>46209.71499541667</v>
+      </c>
       <c r="D186" s="5">
-        <v>46168.86842351852</v>
+        <v>46209.71499678241</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>62</v>
@@ -12770,9 +12798,11 @@
       <c r="B187" s="8">
         <v>46168.684429988425</v>
       </c>
-      <c r="C187" s="9"/>
+      <c r="C187" s="8">
+        <v>46209.715088171295</v>
+      </c>
       <c r="D187" s="8">
-        <v>46168.86842280092</v>
+        <v>46209.71508988426</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>66</v>
@@ -12823,9 +12853,11 @@
       <c r="B188" s="5">
         <v>46168.68443359954</v>
       </c>
-      <c r="C188" s="6"/>
+      <c r="C188" s="5">
+        <v>46209.71518017361</v>
+      </c>
       <c r="D188" s="5">
-        <v>46168.86842204861</v>
+        <v>46209.715181817126</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>66</v>
@@ -12876,9 +12908,11 @@
       <c r="B189" s="8">
         <v>46168.68443729167</v>
       </c>
-      <c r="C189" s="9"/>
+      <c r="C189" s="8">
+        <v>46209.71532783565</v>
+      </c>
       <c r="D189" s="8">
-        <v>46168.86842112269</v>
+        <v>46209.71532934028</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>69</v>
@@ -12994,7 +13028,7 @@
       </c>
       <c r="C191" s="9"/>
       <c r="D191" s="8">
-        <v>46168.86862184027</v>
+        <v>46209.714100509256</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>500</v>
@@ -13045,7 +13079,7 @@
       </c>
       <c r="C192" s="6"/>
       <c r="D192" s="5">
-        <v>46168.868618946755</v>
+        <v>46209.714339432874</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>502</v>
@@ -13096,7 +13130,7 @@
       </c>
       <c r="C193" s="9"/>
       <c r="D193" s="8">
-        <v>46168.86861626158</v>
+        <v>46209.71452784722</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>504</v>
@@ -13147,7 +13181,7 @@
       </c>
       <c r="C194" s="6"/>
       <c r="D194" s="5">
-        <v>46168.868613240746</v>
+        <v>46209.71464846065</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>506</v>
@@ -13198,7 +13232,7 @@
       </c>
       <c r="C195" s="9"/>
       <c r="D195" s="8">
-        <v>46168.86860957176</v>
+        <v>46209.71475407407</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>508</v>
@@ -13249,7 +13283,7 @@
       </c>
       <c r="C196" s="6"/>
       <c r="D196" s="5">
-        <v>46168.86860641204</v>
+        <v>46209.71484002315</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>510</v>
@@ -13300,7 +13334,7 @@
       </c>
       <c r="C197" s="9"/>
       <c r="D197" s="8">
-        <v>46168.868603333336</v>
+        <v>46209.71492104167</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>512</v>
@@ -13351,7 +13385,7 @@
       </c>
       <c r="C198" s="6"/>
       <c r="D198" s="5">
-        <v>46168.868600648144</v>
+        <v>46209.71500105324</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>514</v>
@@ -13402,7 +13436,7 @@
       </c>
       <c r="C199" s="9"/>
       <c r="D199" s="8">
-        <v>46168.868592824074</v>
+        <v>46209.71509673611</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>516</v>
@@ -13453,7 +13487,7 @@
       </c>
       <c r="C200" s="6"/>
       <c r="D200" s="5">
-        <v>46168.86859208334</v>
+        <v>46209.71518885417</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>518</v>
@@ -13504,7 +13538,7 @@
       </c>
       <c r="C201" s="9"/>
       <c r="D201" s="8">
-        <v>46168.868591377315</v>
+        <v>46209.715337222224</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>520</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -855,61 +855,61 @@
     <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Bodega:,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
+    <t>1215141533986852</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215141533987066</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141533987083</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215141533988318</t>
+  </si>
+  <si>
+    <t>1215141318374043</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215141318374055</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141533986852</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215141533987066</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141533987083</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215141533988318</t>
-  </si>
-  <si>
-    <t>1215141318374043</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215141318374055</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46190.60524740741</v>
+        <v>46210.52421333334</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>204</v>
@@ -7121,7 +7121,7 @@
         <v>46197.85117512732</v>
       </c>
       <c r="D86" s="5">
-        <v>46205.618054756946</v>
+        <v>46210.20097684028</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>265</v>
@@ -7165,8 +7165,8 @@
       <c r="R86" s="5">
         <v>46209</v>
       </c>
-      <c r="S86" s="11" t="s">
-        <v>268</v>
+      <c r="S86" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -7177,7 +7177,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46168.68352736111</v>
@@ -7189,7 +7189,7 @@
         <v>46206.18878028935</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -7222,7 +7222,7 @@
         <v>179</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -7242,7 +7242,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46168.68353292824</v>
@@ -7251,10 +7251,10 @@
         <v>46197.851300173614</v>
       </c>
       <c r="D88" s="5">
-        <v>46205.618055</v>
+        <v>46210.20097686343</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7284,10 +7284,10 @@
         <v>257</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="5">
         <v>46206</v>
@@ -7295,8 +7295,8 @@
       <c r="R88" s="5">
         <v>46209</v>
       </c>
-      <c r="S88" s="11" t="s">
-        <v>268</v>
+      <c r="S88" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -7307,7 +7307,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B89" s="8">
         <v>46168.68353787037</v>
@@ -7319,7 +7319,7 @@
         <v>46206.1887803125</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
@@ -7352,7 +7352,7 @@
         <v>201</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="8">
         <v>46204</v>
@@ -7372,7 +7372,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46168.68354247685</v>
@@ -7381,10 +7381,10 @@
         <v>46197.85161460648</v>
       </c>
       <c r="D90" s="5">
-        <v>46205.61806439815</v>
+        <v>46210.20097706019</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7414,10 +7414,10 @@
         <v>257</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q90" s="5">
         <v>46206</v>
@@ -7425,8 +7425,8 @@
       <c r="R90" s="5">
         <v>46209</v>
       </c>
-      <c r="S90" s="11" t="s">
-        <v>268</v>
+      <c r="S90" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
@@ -7437,7 +7437,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46168.68354741899</v>
@@ -7447,7 +7447,7 @@
         <v>46204.89010925926</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>25</v>
@@ -7471,7 +7471,7 @@
         <v>26</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>26</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46168.68355052083</v>
@@ -7498,16 +7498,16 @@
         <v>46205.17836196759</v>
       </c>
       <c r="E92" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="F92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" s="6" t="s">
+      <c r="H92" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7525,13 +7525,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="5">
         <v>46210</v>
@@ -7540,7 +7540,7 @@
         <v>46212</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -7569,10 +7569,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I93" s="8">
         <v>46210</v>
@@ -7590,7 +7590,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>288</v>
@@ -7624,10 +7624,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7645,7 +7645,7 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>291</v>
@@ -7679,10 +7679,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I95" s="8">
         <v>46210</v>
@@ -7700,7 +7700,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>293</v>
@@ -7734,10 +7734,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7755,7 +7755,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>293</v>
@@ -7789,10 +7789,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I97" s="8">
         <v>46210</v>
@@ -7810,7 +7810,7 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>293</v>
@@ -7844,10 +7844,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I98" s="5">
         <v>46213</v>
@@ -7865,13 +7865,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>300</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q98" s="5">
         <v>46213</v>
@@ -7909,10 +7909,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I99" s="8">
         <v>46213</v>
@@ -7964,10 +7964,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I100" s="5">
         <v>46213</v>
@@ -8019,10 +8019,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I101" s="8">
         <v>46213</v>
@@ -8074,10 +8074,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I102" s="5">
         <v>46213</v>
@@ -8129,10 +8129,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H103" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I103" s="8">
         <v>46213</v>
@@ -8205,13 +8205,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>314</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q104" s="5">
         <v>46224</v>
@@ -12308,10 +12308,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H178" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -12371,10 +12371,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H179" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H179" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I179" s="8">
         <v>46244</v>
@@ -12426,10 +12426,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H180" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I180" s="5">
         <v>46244</v>
@@ -12481,10 +12481,10 @@
         <v>26</v>
       </c>
       <c r="G181" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H181" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H181" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I181" s="8">
         <v>46244</v>
@@ -12536,10 +12536,10 @@
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H182" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H182" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I182" s="5">
         <v>46244</v>
@@ -12591,10 +12591,10 @@
         <v>26</v>
       </c>
       <c r="G183" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H183" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H183" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I183" s="8">
         <v>46244</v>
@@ -12646,10 +12646,10 @@
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H184" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H184" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I184" s="5">
         <v>46244</v>
@@ -12701,10 +12701,10 @@
         <v>26</v>
       </c>
       <c r="G185" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H185" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H185" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I185" s="8">
         <v>46244</v>
@@ -12756,10 +12756,10 @@
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H186" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I186" s="5">
         <v>46244</v>
@@ -12811,10 +12811,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H187" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H187" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I187" s="8">
         <v>46244</v>
@@ -12866,10 +12866,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H188" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I188" s="5">
         <v>46244</v>
@@ -12921,10 +12921,10 @@
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H189" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H189" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I189" s="8">
         <v>46244</v>
@@ -12974,10 +12974,10 @@
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H190" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H190" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I190" s="5">
         <v>46245</v>
@@ -13037,10 +13037,10 @@
         <v>26</v>
       </c>
       <c r="G191" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H191" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H191" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="8">
@@ -13088,10 +13088,10 @@
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H192" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -13139,10 +13139,10 @@
         <v>26</v>
       </c>
       <c r="G193" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H193" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H193" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="8">
@@ -13190,10 +13190,10 @@
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H194" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="5">
@@ -13241,10 +13241,10 @@
         <v>26</v>
       </c>
       <c r="G195" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H195" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H195" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I195" s="9"/>
       <c r="J195" s="8">
@@ -13292,10 +13292,10 @@
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H196" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -13343,10 +13343,10 @@
         <v>26</v>
       </c>
       <c r="G197" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H197" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H197" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I197" s="9"/>
       <c r="J197" s="8">
@@ -13394,10 +13394,10 @@
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H198" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13445,10 +13445,10 @@
         <v>26</v>
       </c>
       <c r="G199" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H199" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H199" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I199" s="9"/>
       <c r="J199" s="8">
@@ -13496,10 +13496,10 @@
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H200" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13547,10 +13547,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H201" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H201" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="8">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="538">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -7442,9 +7442,11 @@
       <c r="B91" s="8">
         <v>46168.68354741899</v>
       </c>
-      <c r="C91" s="9"/>
+      <c r="C91" s="8">
+        <v>46211.83132788194</v>
+      </c>
       <c r="D91" s="8">
-        <v>46204.89010925926</v>
+        <v>46211.83134737269</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>279</v>
@@ -7479,9 +7481,11 @@
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
       <c r="S91" s="9"/>
-      <c r="T91" s="9"/>
-      <c r="U91" s="11" t="s">
-        <v>60</v>
+      <c r="T91" s="9">
+        <v>1</v>
+      </c>
+      <c r="U91" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
@@ -8511,9 +8515,11 @@
       <c r="B110" s="5">
         <v>46168.68373005787</v>
       </c>
-      <c r="C110" s="6"/>
+      <c r="C110" s="5">
+        <v>46211.83000219907</v>
+      </c>
       <c r="D110" s="5">
-        <v>46205.614553402775</v>
+        <v>46211.830014363426</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>257</v>
@@ -8548,9 +8554,11 @@
       <c r="Q110" s="6"/>
       <c r="R110" s="6"/>
       <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-      <c r="U110" s="11" t="s">
-        <v>60</v>
+      <c r="T110" s="6">
+        <v>1</v>
+      </c>
+      <c r="U110" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
@@ -8753,9 +8761,11 @@
       <c r="B114" s="5">
         <v>46168.68375502314</v>
       </c>
-      <c r="C114" s="6"/>
+      <c r="C114" s="5">
+        <v>46211.82998440972</v>
+      </c>
       <c r="D114" s="5">
-        <v>46204.60155983796</v>
+        <v>46211.83000291667</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>337</v>
@@ -8803,10 +8813,10 @@
         <v>32</v>
       </c>
       <c r="T114" s="6">
-        <v>0</v>
-      </c>
-      <c r="U114" s="11" t="s">
-        <v>60</v>
+        <v>1</v>
+      </c>
+      <c r="U114" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
@@ -8934,7 +8944,7 @@
         <v>46204.89075866898</v>
       </c>
       <c r="D117" s="8">
-        <v>46204.890769143516</v>
+        <v>46211.830007129625</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>345</v>
@@ -8984,8 +8994,8 @@
       <c r="T117" s="9">
         <v>1</v>
       </c>
-      <c r="U117" s="10" t="s">
-        <v>33</v>
+      <c r="U117" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -8999,7 +9009,7 @@
         <v>46204.89074575232</v>
       </c>
       <c r="D118" s="5">
-        <v>46204.89074728009</v>
+        <v>46211.82999423611</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>212</v>
@@ -9054,7 +9064,7 @@
         <v>46204.890660798614</v>
       </c>
       <c r="D119" s="8">
-        <v>46204.8906627199</v>
+        <v>46211.82999525463</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>212</v>
@@ -10970,9 +10980,11 @@
       <c r="B153" s="8">
         <v>46168.684183460646</v>
       </c>
-      <c r="C153" s="9"/>
+      <c r="C153" s="8">
+        <v>46211.8327128588</v>
+      </c>
       <c r="D153" s="8">
-        <v>46209.71535164352</v>
+        <v>46211.832724733795</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>424</v>
@@ -11007,8 +11019,12 @@
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
       <c r="S153" s="9"/>
-      <c r="T153" s="9"/>
-      <c r="U153" s="9"/>
+      <c r="T153" s="9">
+        <v>1</v>
+      </c>
+      <c r="U153" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
@@ -11017,9 +11033,11 @@
       <c r="B154" s="5">
         <v>46168.68418700232</v>
       </c>
-      <c r="C154" s="6"/>
+      <c r="C154" s="5">
+        <v>46211.83269833333</v>
+      </c>
       <c r="D154" s="5">
-        <v>46206.48623072916</v>
+        <v>46211.8327003125</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>427</v>
@@ -11067,10 +11085,10 @@
         <v>32</v>
       </c>
       <c r="T154" s="6">
-        <v>0</v>
-      </c>
-      <c r="U154" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U154" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
@@ -11080,9 +11098,11 @@
       <c r="B155" s="8">
         <v>46168.68419359953</v>
       </c>
-      <c r="C155" s="9"/>
+      <c r="C155" s="8">
+        <v>46211.831110914354</v>
+      </c>
       <c r="D155" s="8">
-        <v>46206.48597956018</v>
+        <v>46211.831112581014</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>212</v>
@@ -11133,9 +11153,11 @@
       <c r="B156" s="5">
         <v>46168.68419834491</v>
       </c>
-      <c r="C156" s="6"/>
+      <c r="C156" s="5">
+        <v>46211.83112224537</v>
+      </c>
       <c r="D156" s="5">
-        <v>46206.48604722222</v>
+        <v>46211.83112387732</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>212</v>
@@ -11186,9 +11208,11 @@
       <c r="B157" s="8">
         <v>46168.684202777775</v>
       </c>
-      <c r="C157" s="9"/>
+      <c r="C157" s="8">
+        <v>46211.83112747685</v>
+      </c>
       <c r="D157" s="8">
-        <v>46206.48610329861</v>
+        <v>46211.83112878472</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>216</v>
@@ -11239,9 +11263,11 @@
       <c r="B158" s="5">
         <v>46168.68420710648</v>
       </c>
-      <c r="C158" s="6"/>
+      <c r="C158" s="5">
+        <v>46211.83116035879</v>
+      </c>
       <c r="D158" s="5">
-        <v>46206.486152997684</v>
+        <v>46211.83116206019</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>216</v>
@@ -11292,9 +11318,11 @@
       <c r="B159" s="8">
         <v>46168.68421127315</v>
       </c>
-      <c r="C159" s="9"/>
+      <c r="C159" s="8">
+        <v>46211.831169108795</v>
+      </c>
       <c r="D159" s="8">
-        <v>46206.48620774306</v>
+        <v>46211.83117125</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>220</v>
@@ -11345,9 +11373,11 @@
       <c r="B160" s="5">
         <v>46168.68422996528</v>
       </c>
-      <c r="C160" s="6"/>
+      <c r="C160" s="5">
+        <v>46211.83117549769</v>
+      </c>
       <c r="D160" s="5">
-        <v>46196.89431579861</v>
+        <v>46211.83117747685</v>
       </c>
       <c r="E160" s="6" t="s">
         <v>62</v>
@@ -11398,9 +11428,11 @@
       <c r="B161" s="8">
         <v>46168.68423341435</v>
       </c>
-      <c r="C161" s="9"/>
+      <c r="C161" s="8">
+        <v>46211.83120342593</v>
+      </c>
       <c r="D161" s="8">
-        <v>46196.89436430555</v>
+        <v>46211.831204988426</v>
       </c>
       <c r="E161" s="9" t="s">
         <v>62</v>
@@ -11451,9 +11483,11 @@
       <c r="B162" s="5">
         <v>46168.684237037036</v>
       </c>
-      <c r="C162" s="6"/>
+      <c r="C162" s="5">
+        <v>46211.83120920139</v>
+      </c>
       <c r="D162" s="5">
-        <v>46196.894410243054</v>
+        <v>46211.83121074074</v>
       </c>
       <c r="E162" s="6" t="s">
         <v>62</v>
@@ -11504,9 +11538,11 @@
       <c r="B163" s="8">
         <v>46168.68424059028</v>
       </c>
-      <c r="C163" s="9"/>
+      <c r="C163" s="8">
+        <v>46211.83121532407</v>
+      </c>
       <c r="D163" s="8">
-        <v>46196.89445856481</v>
+        <v>46211.83121682871</v>
       </c>
       <c r="E163" s="9" t="s">
         <v>66</v>
@@ -11557,9 +11593,11 @@
       <c r="B164" s="5">
         <v>46168.68424420139</v>
       </c>
-      <c r="C164" s="6"/>
+      <c r="C164" s="5">
+        <v>46211.831241921296</v>
+      </c>
       <c r="D164" s="5">
-        <v>46196.89450880787</v>
+        <v>46211.83124355324</v>
       </c>
       <c r="E164" s="6" t="s">
         <v>66</v>
@@ -11610,9 +11648,11 @@
       <c r="B165" s="8">
         <v>46168.68424778935</v>
       </c>
-      <c r="C165" s="9"/>
+      <c r="C165" s="8">
+        <v>46211.831248981485</v>
+      </c>
       <c r="D165" s="8">
-        <v>46196.89456226851</v>
+        <v>46211.83125052083</v>
       </c>
       <c r="E165" s="9" t="s">
         <v>69</v>
@@ -11663,9 +11703,11 @@
       <c r="B166" s="5">
         <v>46168.68425820602</v>
       </c>
-      <c r="C166" s="6"/>
+      <c r="C166" s="5">
+        <v>46211.83055506945</v>
+      </c>
       <c r="D166" s="5">
-        <v>46209.716104039355</v>
+        <v>46211.83114409722</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>449</v>
@@ -11711,10 +11753,10 @@
         <v>32</v>
       </c>
       <c r="T166" s="6">
-        <v>0</v>
-      </c>
-      <c r="U166" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U166" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -11728,7 +11770,7 @@
         <v>46209.71549736111</v>
       </c>
       <c r="D167" s="8">
-        <v>46209.715499224534</v>
+        <v>46211.83112083333</v>
       </c>
       <c r="E167" s="9" t="s">
         <v>212</v>
@@ -11781,7 +11823,7 @@
         <v>46209.71563954861</v>
       </c>
       <c r="D168" s="5">
-        <v>46209.71564094907</v>
+        <v>46211.83112822917</v>
       </c>
       <c r="E168" s="6" t="s">
         <v>212</v>
@@ -11834,7 +11876,7 @@
         <v>46209.7157528588</v>
       </c>
       <c r="D169" s="8">
-        <v>46209.715754687495</v>
+        <v>46211.83113427083</v>
       </c>
       <c r="E169" s="9" t="s">
         <v>216</v>
@@ -11887,7 +11929,7 @@
         <v>46209.71582945602</v>
       </c>
       <c r="D170" s="5">
-        <v>46209.71583108796</v>
+        <v>46211.83116765047</v>
       </c>
       <c r="E170" s="6" t="s">
         <v>216</v>
@@ -11940,7 +11982,7 @@
         <v>46209.71609789351</v>
       </c>
       <c r="D171" s="8">
-        <v>46209.71609957176</v>
+        <v>46211.831175914354</v>
       </c>
       <c r="E171" s="9" t="s">
         <v>220</v>
@@ -11989,9 +12031,11 @@
       <c r="B172" s="5">
         <v>46168.684336226856</v>
       </c>
-      <c r="C172" s="6"/>
+      <c r="C172" s="5">
+        <v>46211.83065361111</v>
+      </c>
       <c r="D172" s="5">
-        <v>46168.86825175926</v>
+        <v>46211.83118184027</v>
       </c>
       <c r="E172" s="6" t="s">
         <v>62</v>
@@ -12040,9 +12084,11 @@
       <c r="B173" s="8">
         <v>46168.68434010417</v>
       </c>
-      <c r="C173" s="9"/>
+      <c r="C173" s="8">
+        <v>46211.830803923614</v>
+      </c>
       <c r="D173" s="8">
-        <v>46168.86824866898</v>
+        <v>46211.831210868055</v>
       </c>
       <c r="E173" s="9" t="s">
         <v>62</v>
@@ -12091,9 +12137,11 @@
       <c r="B174" s="5">
         <v>46168.68434423611</v>
       </c>
-      <c r="C174" s="6"/>
+      <c r="C174" s="5">
+        <v>46211.83087340278</v>
+      </c>
       <c r="D174" s="5">
-        <v>46168.86824546296</v>
+        <v>46211.83121509259</v>
       </c>
       <c r="E174" s="6" t="s">
         <v>62</v>
@@ -12142,9 +12190,11 @@
       <c r="B175" s="8">
         <v>46168.684348263894</v>
       </c>
-      <c r="C175" s="9"/>
+      <c r="C175" s="8">
+        <v>46211.83096753473</v>
+      </c>
       <c r="D175" s="8">
-        <v>46168.86824251157</v>
+        <v>46211.831221932865</v>
       </c>
       <c r="E175" s="9" t="s">
         <v>66</v>
@@ -12193,9 +12243,11 @@
       <c r="B176" s="5">
         <v>46168.68435202546</v>
       </c>
-      <c r="C176" s="6"/>
+      <c r="C176" s="5">
+        <v>46211.83104849537</v>
+      </c>
       <c r="D176" s="5">
-        <v>46168.868235092596</v>
+        <v>46211.831248912036</v>
       </c>
       <c r="E176" s="6" t="s">
         <v>66</v>
@@ -12244,9 +12296,11 @@
       <c r="B177" s="8">
         <v>46168.68435652778</v>
       </c>
-      <c r="C177" s="9"/>
+      <c r="C177" s="8">
+        <v>46211.83112699074</v>
+      </c>
       <c r="D177" s="8">
-        <v>46168.86823443287</v>
+        <v>46211.831259189814</v>
       </c>
       <c r="E177" s="9" t="s">
         <v>69</v>
@@ -12637,7 +12691,7 @@
         <v>46209.71483280092</v>
       </c>
       <c r="D184" s="5">
-        <v>46209.714834328704</v>
+        <v>46211.83066165509</v>
       </c>
       <c r="E184" s="6" t="s">
         <v>62</v>
@@ -12692,7 +12746,7 @@
         <v>46209.714913159725</v>
       </c>
       <c r="D185" s="8">
-        <v>46209.71491484954</v>
+        <v>46211.83081103009</v>
       </c>
       <c r="E185" s="9" t="s">
         <v>485</v>
@@ -12747,7 +12801,7 @@
         <v>46209.71499541667</v>
       </c>
       <c r="D186" s="5">
-        <v>46209.71499678241</v>
+        <v>46211.83088054398</v>
       </c>
       <c r="E186" s="6" t="s">
         <v>62</v>
@@ -12802,7 +12856,7 @@
         <v>46209.715088171295</v>
       </c>
       <c r="D187" s="8">
-        <v>46209.71508988426</v>
+        <v>46211.83097425926</v>
       </c>
       <c r="E187" s="9" t="s">
         <v>66</v>
@@ -12857,7 +12911,7 @@
         <v>46209.71518017361</v>
       </c>
       <c r="D188" s="5">
-        <v>46209.715181817126</v>
+        <v>46211.83105417824</v>
       </c>
       <c r="E188" s="6" t="s">
         <v>66</v>
@@ -12912,7 +12966,7 @@
         <v>46209.71532783565</v>
       </c>
       <c r="D189" s="8">
-        <v>46209.71532934028</v>
+        <v>46211.8311371412</v>
       </c>
       <c r="E189" s="9" t="s">
         <v>69</v>
@@ -12963,9 +13017,11 @@
       <c r="B190" s="5">
         <v>46168.6844840625</v>
       </c>
-      <c r="C190" s="6"/>
+      <c r="C190" s="5">
+        <v>46211.83022659722</v>
+      </c>
       <c r="D190" s="5">
-        <v>46168.8686299074</v>
+        <v>46211.830323738424</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>496</v>
@@ -13013,10 +13069,10 @@
         <v>32</v>
       </c>
       <c r="T190" s="6">
-        <v>0</v>
-      </c>
-      <c r="U190" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U190" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
@@ -13026,9 +13082,11 @@
       <c r="B191" s="8">
         <v>46168.68449130787</v>
       </c>
-      <c r="C191" s="9"/>
+      <c r="C191" s="8">
+        <v>46211.83028650463</v>
+      </c>
       <c r="D191" s="8">
-        <v>46209.714100509256</v>
+        <v>46211.830295844906</v>
       </c>
       <c r="E191" s="9" t="s">
         <v>500</v>
@@ -13077,9 +13135,11 @@
       <c r="B192" s="5">
         <v>46168.68449590278</v>
       </c>
-      <c r="C192" s="6"/>
+      <c r="C192" s="5">
+        <v>46211.83028740741</v>
+      </c>
       <c r="D192" s="5">
-        <v>46209.714339432874</v>
+        <v>46211.83029662037</v>
       </c>
       <c r="E192" s="6" t="s">
         <v>502</v>
@@ -13128,9 +13188,11 @@
       <c r="B193" s="8">
         <v>46168.68450027778</v>
       </c>
-      <c r="C193" s="9"/>
+      <c r="C193" s="8">
+        <v>46211.830288032404</v>
+      </c>
       <c r="D193" s="8">
-        <v>46209.71452784722</v>
+        <v>46211.83029733796</v>
       </c>
       <c r="E193" s="9" t="s">
         <v>504</v>
@@ -13179,9 +13241,11 @@
       <c r="B194" s="5">
         <v>46168.68450480324</v>
       </c>
-      <c r="C194" s="6"/>
+      <c r="C194" s="5">
+        <v>46211.83028862269</v>
+      </c>
       <c r="D194" s="5">
-        <v>46209.71464846065</v>
+        <v>46211.83029778935</v>
       </c>
       <c r="E194" s="6" t="s">
         <v>506</v>
@@ -13230,9 +13294,11 @@
       <c r="B195" s="8">
         <v>46168.68450934028</v>
       </c>
-      <c r="C195" s="9"/>
+      <c r="C195" s="8">
+        <v>46211.830289247686</v>
+      </c>
       <c r="D195" s="8">
-        <v>46209.71475407407</v>
+        <v>46211.83029865741</v>
       </c>
       <c r="E195" s="9" t="s">
         <v>508</v>
@@ -13281,9 +13347,11 @@
       <c r="B196" s="5">
         <v>46168.684523414355</v>
       </c>
-      <c r="C196" s="6"/>
+      <c r="C196" s="5">
+        <v>46211.83029025463</v>
+      </c>
       <c r="D196" s="5">
-        <v>46209.71484002315</v>
+        <v>46211.83029902777</v>
       </c>
       <c r="E196" s="6" t="s">
         <v>510</v>
@@ -13332,9 +13400,11 @@
       <c r="B197" s="8">
         <v>46168.6845271412</v>
       </c>
-      <c r="C197" s="9"/>
+      <c r="C197" s="8">
+        <v>46211.8302908912</v>
+      </c>
       <c r="D197" s="8">
-        <v>46209.71492104167</v>
+        <v>46211.83029945602</v>
       </c>
       <c r="E197" s="9" t="s">
         <v>512</v>
@@ -13383,9 +13453,11 @@
       <c r="B198" s="5">
         <v>46168.68453511574</v>
       </c>
-      <c r="C198" s="6"/>
+      <c r="C198" s="5">
+        <v>46211.830291562495</v>
+      </c>
       <c r="D198" s="5">
-        <v>46209.71500105324</v>
+        <v>46211.830299953705</v>
       </c>
       <c r="E198" s="6" t="s">
         <v>514</v>
@@ -13434,9 +13506,11 @@
       <c r="B199" s="8">
         <v>46168.68453863426</v>
       </c>
-      <c r="C199" s="9"/>
+      <c r="C199" s="8">
+        <v>46211.83029222222</v>
+      </c>
       <c r="D199" s="8">
-        <v>46209.71509673611</v>
+        <v>46211.83030041667</v>
       </c>
       <c r="E199" s="9" t="s">
         <v>516</v>
@@ -13485,9 +13559,11 @@
       <c r="B200" s="5">
         <v>46168.68454210648</v>
       </c>
-      <c r="C200" s="6"/>
+      <c r="C200" s="5">
+        <v>46211.83029298611</v>
+      </c>
       <c r="D200" s="5">
-        <v>46209.71518885417</v>
+        <v>46211.830300891204</v>
       </c>
       <c r="E200" s="6" t="s">
         <v>518</v>
@@ -13536,9 +13612,11 @@
       <c r="B201" s="8">
         <v>46168.684545578704</v>
       </c>
-      <c r="C201" s="9"/>
+      <c r="C201" s="8">
+        <v>46211.830293680556</v>
+      </c>
       <c r="D201" s="8">
-        <v>46209.715337222224</v>
+        <v>46211.83030140046</v>
       </c>
       <c r="E201" s="9" t="s">
         <v>520</v>
@@ -13636,7 +13714,7 @@
       </c>
       <c r="C203" s="9"/>
       <c r="D203" s="8">
-        <v>46168.868693854165</v>
+        <v>46211.83025064815</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>525</v>
@@ -13686,8 +13764,8 @@
       <c r="T203" s="9">
         <v>0</v>
       </c>
-      <c r="U203" s="12" t="s">
-        <v>129</v>
+      <c r="U203" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
@@ -13699,7 +13777,7 @@
       </c>
       <c r="C204" s="6"/>
       <c r="D204" s="5">
-        <v>46196.87777929398</v>
+        <v>46211.83025032407</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>529</v>
@@ -13749,8 +13827,8 @@
       <c r="T204" s="6">
         <v>0</v>
       </c>
-      <c r="U204" s="12" t="s">
-        <v>129</v>
+      <c r="U204" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
@@ -13815,7 +13893,7 @@
       </c>
       <c r="C206" s="6"/>
       <c r="D206" s="5">
-        <v>46168.8687993287</v>
+        <v>46211.830253541666</v>
       </c>
       <c r="E206" s="6" t="s">
         <v>534</v>
@@ -13865,8 +13943,8 @@
       <c r="T206" s="6">
         <v>0</v>
       </c>
-      <c r="U206" s="12" t="s">
-        <v>129</v>
+      <c r="U206" s="11" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -6673,9 +6673,11 @@
       <c r="B78" s="5">
         <v>46168.683480625</v>
       </c>
-      <c r="C78" s="6"/>
+      <c r="C78" s="5">
+        <v>46211.83846215278</v>
+      </c>
       <c r="D78" s="5">
-        <v>46168.86495055555</v>
+        <v>46211.83847391204</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>246</v>
@@ -6721,10 +6723,10 @@
         <v>32</v>
       </c>
       <c r="T78" s="6">
-        <v>0</v>
-      </c>
-      <c r="U78" s="12" t="s">
-        <v>129</v>
+        <v>1</v>
+      </c>
+      <c r="U78" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
@@ -6734,9 +6736,11 @@
       <c r="B79" s="8">
         <v>46168.683484629626</v>
       </c>
-      <c r="C79" s="9"/>
+      <c r="C79" s="8">
+        <v>46211.83842483796</v>
+      </c>
       <c r="D79" s="8">
-        <v>46206.48580733796</v>
+        <v>46211.83842664352</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>212</v>
@@ -6787,9 +6791,11 @@
       <c r="B80" s="5">
         <v>46168.683488877316</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46211.83843038195</v>
+      </c>
       <c r="D80" s="5">
-        <v>46206.48579508102</v>
+        <v>46211.83843200232</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>212</v>
@@ -6840,9 +6846,11 @@
       <c r="B81" s="8">
         <v>46168.68349300926</v>
       </c>
-      <c r="C81" s="9"/>
+      <c r="C81" s="8">
+        <v>46211.83843398148</v>
+      </c>
       <c r="D81" s="8">
-        <v>46206.48578787037</v>
+        <v>46211.83843496528</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>216</v>
@@ -6893,9 +6901,11 @@
       <c r="B82" s="5">
         <v>46168.6834959375</v>
       </c>
-      <c r="C82" s="6"/>
+      <c r="C82" s="5">
+        <v>46211.83843877315</v>
+      </c>
       <c r="D82" s="5">
-        <v>46206.48578125</v>
+        <v>46211.83844040509</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>216</v>
@@ -6946,9 +6956,11 @@
       <c r="B83" s="8">
         <v>46168.68349899305</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="8">
+        <v>46211.838444583336</v>
+      </c>
       <c r="D83" s="8">
-        <v>46204.89334085648</v>
+        <v>46211.83844619213</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>220</v>
@@ -10709,7 +10721,7 @@
         <v>46206.48597313657</v>
       </c>
       <c r="D148" s="5">
-        <v>46206.48597475694</v>
+        <v>46211.838432476856</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>212</v>
@@ -10764,7 +10776,7 @@
         <v>46206.48603997685</v>
       </c>
       <c r="D149" s="8">
-        <v>46206.48604142361</v>
+        <v>46211.83844157407</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>212</v>
@@ -10819,7 +10831,7 @@
         <v>46206.48609505787</v>
       </c>
       <c r="D150" s="5">
-        <v>46206.48609666667</v>
+        <v>46211.83843866899</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>216</v>
@@ -10874,7 +10886,7 @@
         <v>46206.48614579861</v>
       </c>
       <c r="D151" s="8">
-        <v>46206.48614756945</v>
+        <v>46211.83844565973</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>216</v>
@@ -10929,7 +10941,7 @@
         <v>46206.48619949074</v>
       </c>
       <c r="D152" s="5">
-        <v>46206.4862009375</v>
+        <v>46211.83845115741</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>220</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -522,6 +522,9 @@
     <t>Generación OC   ot 4336 - 4338 -4341,fabricación tableros   ot 4336 - 4338 -4341</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>1215141318244929</t>
   </si>
   <si>
@@ -907,9 +910,6 @@
   </si>
   <si>
     <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -4666,7 +4666,7 @@
         <v>46195.92858413194</v>
       </c>
       <c r="D43" s="8">
-        <v>46195.92859513889</v>
+        <v>46212.17842539352</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>155</v>
@@ -4710,8 +4710,8 @@
       <c r="R43" s="8">
         <v>46219</v>
       </c>
-      <c r="S43" s="10" t="s">
-        <v>32</v>
+      <c r="S43" s="11" t="s">
+        <v>157</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4722,7 +4722,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B44" s="5">
         <v>46168.68332880787</v>
@@ -4767,7 +4767,7 @@
         <v>116</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4777,7 +4777,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B45" s="8">
         <v>46168.683333113426</v>
@@ -4789,7 +4789,7 @@
         <v>46195.92857017361</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
@@ -4822,7 +4822,7 @@
         <v>117</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4832,7 +4832,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B46" s="5">
         <v>46168.683337291666</v>
@@ -4844,16 +4844,16 @@
         <v>46204.1978837037</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I46" s="5">
         <v>46191</v>
@@ -4874,7 +4874,7 @@
         <v>119</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>119</v>
@@ -4897,7 +4897,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B47" s="8">
         <v>46168.68334179398</v>
@@ -4909,16 +4909,16 @@
         <v>46199.564988564816</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I47" s="8">
         <v>46191</v>
@@ -4936,13 +4936,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>100</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4958,7 +4958,7 @@
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B48" s="5">
         <v>46168.68334684028</v>
@@ -4970,16 +4970,16 @@
         <v>46199.5650378125</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I48" s="5">
         <v>46195</v>
@@ -4997,13 +4997,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -5019,7 +5019,7 @@
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B49" s="8">
         <v>46168.68335195602</v>
@@ -5031,16 +5031,16 @@
         <v>46204.19788363426</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I49" s="8">
         <v>46191</v>
@@ -5061,7 +5061,7 @@
         <v>119</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -5084,7 +5084,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B50" s="5">
         <v>46168.68335582176</v>
@@ -5102,10 +5102,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I50" s="5">
         <v>46191</v>
@@ -5123,13 +5123,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -5139,7 +5139,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B51" s="8">
         <v>46168.683360428244</v>
@@ -5151,16 +5151,16 @@
         <v>46199.56520053241</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I51" s="8">
         <v>46195</v>
@@ -5178,13 +5178,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O51" s="9" t="s">
         <v>108</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5194,7 +5194,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B52" s="5">
         <v>46168.68336471065</v>
@@ -5206,16 +5206,16 @@
         <v>46205.61765122685</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -5236,7 +5236,7 @@
         <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -5259,7 +5259,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B53" s="8">
         <v>46168.68337377315</v>
@@ -5277,10 +5277,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I53" s="8">
         <v>46191</v>
@@ -5298,13 +5298,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O53" s="9" t="s">
         <v>113</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5314,7 +5314,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B54" s="5">
         <v>46168.683378194444</v>
@@ -5326,16 +5326,16 @@
         <v>46204.601540787036</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I54" s="5">
         <v>46202</v>
@@ -5353,13 +5353,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>114</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5369,7 +5369,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B55" s="8">
         <v>46168.68338271991</v>
@@ -5381,16 +5381,16 @@
         <v>46205.644352627314</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I55" s="8">
         <v>46231</v>
@@ -5408,10 +5408,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5424,7 +5424,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B56" s="5">
         <v>46168.683385868055</v>
@@ -5436,16 +5436,16 @@
         <v>46204.19788391204</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I56" s="5">
         <v>46191</v>
@@ -5466,7 +5466,7 @@
         <v>119</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B57" s="8">
         <v>46168.68343064815</v>
@@ -5507,10 +5507,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I57" s="8">
         <v>46191</v>
@@ -5528,13 +5528,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>110</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5544,7 +5544,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B58" s="5">
         <v>46168.683436956024</v>
@@ -5556,16 +5556,16 @@
         <v>46199.56544034722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I58" s="5">
         <v>46195</v>
@@ -5583,13 +5583,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>111</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5599,7 +5599,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B59" s="8">
         <v>46168.68344221065</v>
@@ -5609,7 +5609,7 @@
         <v>46210.52421333334</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5633,7 +5633,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5648,7 +5648,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B60" s="5">
         <v>46168.683445787035</v>
@@ -5660,16 +5660,16 @@
         <v>46184.518844583334</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I60" s="5">
         <v>46167</v>
@@ -5687,13 +5687,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q60" s="5">
         <v>46167</v>
@@ -5713,7 +5713,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46168.6865996875</v>
@@ -5725,16 +5725,16 @@
         <v>46184.51878665509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I61" s="8">
         <v>46167</v>
@@ -5752,13 +5752,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5768,7 +5768,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46168.68683460648</v>
@@ -5780,16 +5780,16 @@
         <v>46184.518791319446</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46167</v>
@@ -5807,13 +5807,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5823,7 +5823,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B63" s="8">
         <v>46168.686918437495</v>
@@ -5835,16 +5835,16 @@
         <v>46184.51879930556</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I63" s="8">
         <v>46167</v>
@@ -5862,13 +5862,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5878,7 +5878,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5">
         <v>46168.687254143515</v>
@@ -5890,16 +5890,16 @@
         <v>46184.5188068287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46167</v>
@@ -5917,13 +5917,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>84</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B65" s="8">
         <v>46168.68731635417</v>
@@ -5945,16 +5945,16 @@
         <v>46184.51881454861</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I65" s="8">
         <v>46167</v>
@@ -5972,13 +5972,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>84</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B66" s="5">
         <v>46168.68345142361</v>
@@ -6000,16 +6000,16 @@
         <v>46190.605242708334</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46181</v>
@@ -6027,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="Q66" s="5">
         <v>46181</v>
@@ -6053,7 +6053,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B67" s="8">
         <v>46168.68857346065</v>
@@ -6065,16 +6065,16 @@
         <v>46190.60518608797</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I67" s="8">
         <v>46181</v>
@@ -6092,13 +6092,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -6108,7 +6108,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B68" s="5">
         <v>46168.688608275465</v>
@@ -6120,16 +6120,16 @@
         <v>46190.60519502315</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46181</v>
@@ -6147,13 +6147,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6163,7 +6163,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B69" s="8">
         <v>46168.68864659722</v>
@@ -6175,16 +6175,16 @@
         <v>46190.605203761574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I69" s="8">
         <v>46181</v>
@@ -6202,13 +6202,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6218,7 +6218,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B70" s="5">
         <v>46168.68868637731</v>
@@ -6230,16 +6230,16 @@
         <v>46190.605208946756</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I70" s="5">
         <v>46181</v>
@@ -6257,13 +6257,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6273,7 +6273,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B71" s="8">
         <v>46168.68871934028</v>
@@ -6285,16 +6285,16 @@
         <v>46190.60521709491</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I71" s="8">
         <v>46181</v>
@@ -6312,13 +6312,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -6328,7 +6328,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B72" s="5">
         <v>46168.68345790509</v>
@@ -6346,10 +6346,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I72" s="5">
         <v>46188</v>
@@ -6367,13 +6367,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q72" s="5">
         <v>46188</v>
@@ -6393,7 +6393,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B73" s="8">
         <v>46168.68880178241</v>
@@ -6405,16 +6405,16 @@
         <v>46190.60536361111</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -6435,7 +6435,7 @@
         <v>103</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>103</v>
@@ -6448,7 +6448,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46168.68883857639</v>
@@ -6460,16 +6460,16 @@
         <v>46190.605368206016</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I74" s="5">
         <v>46188</v>
@@ -6490,7 +6490,7 @@
         <v>103</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>103</v>
@@ -6503,7 +6503,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B75" s="8">
         <v>46168.688875775464</v>
@@ -6515,16 +6515,16 @@
         <v>46190.605373530096</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I75" s="8">
         <v>46188</v>
@@ -6545,7 +6545,7 @@
         <v>103</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>103</v>
@@ -6558,7 +6558,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46168.6889172338</v>
@@ -6570,16 +6570,16 @@
         <v>46190.60539957176</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I76" s="5">
         <v>46188</v>
@@ -6600,7 +6600,7 @@
         <v>103</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>103</v>
@@ -6613,7 +6613,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B77" s="8">
         <v>46168.688956620375</v>
@@ -6625,16 +6625,16 @@
         <v>46190.60538814815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I77" s="8">
         <v>46188</v>
@@ -6655,7 +6655,7 @@
         <v>103</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6668,7 +6668,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B78" s="5">
         <v>46168.683480625</v>
@@ -6680,16 +6680,16 @@
         <v>46211.83847391204</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6705,10 +6705,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6731,7 +6731,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46168.683484629626</v>
@@ -6743,16 +6743,16 @@
         <v>46211.83842664352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I79" s="8">
         <v>46238</v>
@@ -6770,13 +6770,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46168.683488877316</v>
@@ -6798,16 +6798,16 @@
         <v>46211.83843200232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I80" s="5">
         <v>46238</v>
@@ -6825,13 +6825,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6841,7 +6841,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B81" s="8">
         <v>46168.68349300926</v>
@@ -6853,16 +6853,16 @@
         <v>46211.83843496528</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46238</v>
@@ -6880,13 +6880,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6896,7 +6896,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5">
         <v>46168.6834959375</v>
@@ -6908,16 +6908,16 @@
         <v>46211.83844040509</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46238</v>
@@ -6935,13 +6935,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6951,7 +6951,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B83" s="8">
         <v>46168.68349899305</v>
@@ -6963,16 +6963,16 @@
         <v>46211.83844619213</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46238</v>
@@ -6990,13 +6990,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -7006,7 +7006,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B84" s="5">
         <v>46168.68351101852</v>
@@ -7018,7 +7018,7 @@
         <v>46205.618076087965</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -7042,7 +7042,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -7059,7 +7059,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B85" s="8">
         <v>46168.68351447917</v>
@@ -7071,16 +7071,16 @@
         <v>46206.18878055556</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I85" s="8">
         <v>46204</v>
@@ -7098,13 +7098,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q85" s="8">
         <v>46204</v>
@@ -7124,7 +7124,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B86" s="5">
         <v>46168.68352011574</v>
@@ -7136,16 +7136,16 @@
         <v>46210.20097684028</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I86" s="5">
         <v>46206</v>
@@ -7163,13 +7163,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q86" s="5">
         <v>46206</v>
@@ -7189,7 +7189,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
         <v>46168.68352736111</v>
@@ -7201,16 +7201,16 @@
         <v>46206.18878028935</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -7228,13 +7228,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -7254,7 +7254,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B88" s="5">
         <v>46168.68353292824</v>
@@ -7266,16 +7266,16 @@
         <v>46210.20097686343</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I88" s="5">
         <v>46206</v>
@@ -7293,13 +7293,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q88" s="5">
         <v>46206</v>
@@ -7319,7 +7319,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" s="8">
         <v>46168.68353787037</v>
@@ -7331,16 +7331,16 @@
         <v>46206.1887803125</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7358,13 +7358,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="8">
         <v>46204</v>
@@ -7384,7 +7384,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46168.68354247685</v>
@@ -7396,16 +7396,16 @@
         <v>46210.20097706019</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I90" s="5">
         <v>46206</v>
@@ -7423,13 +7423,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q90" s="5">
         <v>46206</v>
@@ -7449,7 +7449,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46168.68354741899</v>
@@ -7461,7 +7461,7 @@
         <v>46211.83134737269</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>25</v>
@@ -7485,7 +7485,7 @@
         <v>26</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>26</v>
@@ -7502,7 +7502,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46168.68355052083</v>
@@ -7514,16 +7514,16 @@
         <v>46205.17836196759</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7541,13 +7541,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="5">
         <v>46210</v>
@@ -7556,7 +7556,7 @@
         <v>46212</v>
       </c>
       <c r="S92" s="11" t="s">
-        <v>286</v>
+        <v>157</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -7579,16 +7579,16 @@
         <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I93" s="8">
         <v>46210</v>
@@ -7606,7 +7606,7 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O93" s="9" t="s">
         <v>288</v>
@@ -7634,16 +7634,16 @@
         <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7661,13 +7661,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>291</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7689,16 +7689,16 @@
         <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I95" s="8">
         <v>46210</v>
@@ -7716,7 +7716,7 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O95" s="9" t="s">
         <v>293</v>
@@ -7744,16 +7744,16 @@
         <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7771,7 +7771,7 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>293</v>
@@ -7799,16 +7799,16 @@
         <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I97" s="8">
         <v>46210</v>
@@ -7826,7 +7826,7 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>293</v>
@@ -7860,10 +7860,10 @@
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I98" s="5">
         <v>46213</v>
@@ -7881,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>300</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q98" s="5">
         <v>46213</v>
@@ -7919,16 +7919,16 @@
         <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I99" s="8">
         <v>46213</v>
@@ -7974,16 +7974,16 @@
         <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I100" s="5">
         <v>46213</v>
@@ -8029,16 +8029,16 @@
         <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I101" s="8">
         <v>46213</v>
@@ -8059,7 +8059,7 @@
         <v>299</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P101" s="9" t="s">
         <v>307</v>
@@ -8084,16 +8084,16 @@
         <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I102" s="5">
         <v>46213</v>
@@ -8114,7 +8114,7 @@
         <v>299</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>309</v>
@@ -8139,16 +8139,16 @@
         <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I103" s="8">
         <v>46213</v>
@@ -8169,7 +8169,7 @@
         <v>299</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>311</v>
@@ -8200,10 +8200,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I104" s="5">
         <v>46224</v>
@@ -8221,13 +8221,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>314</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q104" s="5">
         <v>46224</v>
@@ -8259,16 +8259,16 @@
         <v>46204.890051967595</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I105" s="8">
         <v>46224</v>
@@ -8320,10 +8320,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I106" s="5">
         <v>46224</v>
@@ -8369,16 +8369,16 @@
         <v>46204.89006394676</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I107" s="8">
         <v>46224</v>
@@ -8399,7 +8399,7 @@
         <v>313</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>313</v>
@@ -8424,16 +8424,16 @@
         <v>46204.89006936342</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I108" s="5">
         <v>46224</v>
@@ -8454,7 +8454,7 @@
         <v>313</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>322</v>
@@ -8479,16 +8479,16 @@
         <v>46204.890080185185</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I109" s="8">
         <v>46224</v>
@@ -8509,7 +8509,7 @@
         <v>313</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>324</v>
@@ -8534,7 +8534,7 @@
         <v>46211.830014363426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8593,10 +8593,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I111" s="8">
         <v>46185</v>
@@ -8614,7 +8614,7 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>140</v>
@@ -8658,10 +8658,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8677,7 +8677,7 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>131</v>
@@ -8721,10 +8721,10 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I113" s="8">
         <v>46199</v>
@@ -8742,7 +8742,7 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>149</v>
@@ -8786,10 +8786,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8807,10 +8807,10 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>338</v>
@@ -8851,10 +8851,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I115" s="8">
         <v>46220</v>
@@ -8872,10 +8872,10 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>340</v>
@@ -9024,7 +9024,7 @@
         <v>46211.82999423611</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -9079,7 +9079,7 @@
         <v>46211.82999525463</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -9134,7 +9134,7 @@
         <v>46204.89052016204</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -9164,7 +9164,7 @@
         <v>345</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>352</v>
@@ -9189,7 +9189,7 @@
         <v>46204.89050689815</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -9219,7 +9219,7 @@
         <v>345</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>352</v>
@@ -9244,7 +9244,7 @@
         <v>46204.890087210646</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9274,7 +9274,7 @@
         <v>345</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>355</v>
@@ -9364,7 +9364,7 @@
         <v>46205.61454657407</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9419,7 +9419,7 @@
         <v>46205.61454702546</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9474,7 +9474,7 @@
         <v>46205.614544861106</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9529,7 +9529,7 @@
         <v>46205.61454555555</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9584,7 +9584,7 @@
         <v>46205.614546122684</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9704,7 +9704,7 @@
         <v>46205.6085181713</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9759,7 +9759,7 @@
         <v>46205.60851520833</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9814,7 +9814,7 @@
         <v>46205.608516168984</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9869,7 +9869,7 @@
         <v>46205.608518877314</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9924,7 +9924,7 @@
         <v>46205.608517326385</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -10044,7 +10044,7 @@
         <v>46205.60828351852</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -10099,7 +10099,7 @@
         <v>46205.60828236111</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -10154,7 +10154,7 @@
         <v>46205.608284375005</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -10209,7 +10209,7 @@
         <v>46205.60828523149</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -10264,7 +10264,7 @@
         <v>46205.60828666667</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10384,7 +10384,7 @@
         <v>46206.48579965278</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10414,7 +10414,7 @@
         <v>401</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>403</v>
@@ -10439,7 +10439,7 @@
         <v>46206.48579032408</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -10469,7 +10469,7 @@
         <v>401</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>405</v>
@@ -10494,7 +10494,7 @@
         <v>46206.48578297454</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10524,7 +10524,7 @@
         <v>401</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>407</v>
@@ -10549,7 +10549,7 @@
         <v>46206.48577649306</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10579,7 +10579,7 @@
         <v>401</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>407</v>
@@ -10604,7 +10604,7 @@
         <v>46204.893335671295</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10634,7 +10634,7 @@
         <v>401</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>410</v>
@@ -10724,7 +10724,7 @@
         <v>46211.838432476856</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10754,7 +10754,7 @@
         <v>412</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>415</v>
@@ -10779,7 +10779,7 @@
         <v>46211.83844157407</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10809,7 +10809,7 @@
         <v>412</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>417</v>
@@ -10834,7 +10834,7 @@
         <v>46211.83843866899</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10864,7 +10864,7 @@
         <v>412</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>419</v>
@@ -10889,7 +10889,7 @@
         <v>46211.83844565973</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10919,7 +10919,7 @@
         <v>412</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>419</v>
@@ -10944,7 +10944,7 @@
         <v>46211.83845115741</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -10974,7 +10974,7 @@
         <v>412</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>422</v>
@@ -11117,7 +11117,7 @@
         <v>46211.831112581014</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -11147,7 +11147,7 @@
         <v>427</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>432</v>
@@ -11172,7 +11172,7 @@
         <v>46211.83112387732</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -11202,7 +11202,7 @@
         <v>427</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>432</v>
@@ -11227,7 +11227,7 @@
         <v>46211.83112878472</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
@@ -11257,7 +11257,7 @@
         <v>427</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>435</v>
@@ -11282,7 +11282,7 @@
         <v>46211.83116206019</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11312,7 +11312,7 @@
         <v>427</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>435</v>
@@ -11337,7 +11337,7 @@
         <v>46211.83117125</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -11367,7 +11367,7 @@
         <v>427</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>438</v>
@@ -11785,7 +11785,7 @@
         <v>46211.83112083333</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
@@ -11813,7 +11813,7 @@
         <v>449</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>452</v>
@@ -11838,7 +11838,7 @@
         <v>46211.83112822917</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11866,7 +11866,7 @@
         <v>449</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>452</v>
@@ -11891,7 +11891,7 @@
         <v>46211.83113427083</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
@@ -11919,7 +11919,7 @@
         <v>449</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P169" s="9" t="s">
         <v>455</v>
@@ -11944,7 +11944,7 @@
         <v>46211.83116765047</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -11972,7 +11972,7 @@
         <v>449</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>455</v>
@@ -11997,7 +11997,7 @@
         <v>46211.831175914354</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
@@ -12025,7 +12025,7 @@
         <v>449</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P171" s="9" t="s">
         <v>458</v>
@@ -12374,10 +12374,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -12431,16 +12431,16 @@
         <v>46209.71550439815</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H179" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I179" s="8">
         <v>46244</v>
@@ -12461,7 +12461,7 @@
         <v>470</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P179" s="9" t="s">
         <v>473</v>
@@ -12486,16 +12486,16 @@
         <v>46209.7156449537</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I180" s="5">
         <v>46244</v>
@@ -12516,7 +12516,7 @@
         <v>470</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>475</v>
@@ -12541,16 +12541,16 @@
         <v>46209.715759733794</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H181" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I181" s="8">
         <v>46244</v>
@@ -12571,7 +12571,7 @@
         <v>470</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P181" s="9" t="s">
         <v>477</v>
@@ -12596,16 +12596,16 @@
         <v>46209.71583459491</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I182" s="5">
         <v>46244</v>
@@ -12626,7 +12626,7 @@
         <v>470</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>479</v>
@@ -12651,16 +12651,16 @@
         <v>46209.71610449074</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H183" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I183" s="8">
         <v>46244</v>
@@ -12681,7 +12681,7 @@
         <v>470</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P183" s="9" t="s">
         <v>481</v>
@@ -12712,10 +12712,10 @@
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I184" s="5">
         <v>46244</v>
@@ -12767,10 +12767,10 @@
         <v>26</v>
       </c>
       <c r="G185" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H185" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I185" s="8">
         <v>46244</v>
@@ -12822,10 +12822,10 @@
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I186" s="5">
         <v>46244</v>
@@ -12877,10 +12877,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H187" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I187" s="8">
         <v>46244</v>
@@ -12932,10 +12932,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I188" s="5">
         <v>46244</v>
@@ -12987,10 +12987,10 @@
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I189" s="8">
         <v>46244</v>
@@ -13042,10 +13042,10 @@
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I190" s="5">
         <v>46245</v>
@@ -13107,10 +13107,10 @@
         <v>26</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="8">
@@ -13129,7 +13129,7 @@
         <v>496</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P191" s="9" t="s">
         <v>496</v>
@@ -13160,10 +13160,10 @@
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -13182,7 +13182,7 @@
         <v>496</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P192" s="6" t="s">
         <v>496</v>
@@ -13213,10 +13213,10 @@
         <v>26</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="8">
@@ -13235,7 +13235,7 @@
         <v>496</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P193" s="9" t="s">
         <v>496</v>
@@ -13266,10 +13266,10 @@
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="5">
@@ -13288,7 +13288,7 @@
         <v>496</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P194" s="6" t="s">
         <v>496</v>
@@ -13319,10 +13319,10 @@
         <v>26</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I195" s="9"/>
       <c r="J195" s="8">
@@ -13341,7 +13341,7 @@
         <v>496</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P195" s="9" t="s">
         <v>496</v>
@@ -13372,10 +13372,10 @@
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -13425,10 +13425,10 @@
         <v>26</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I197" s="9"/>
       <c r="J197" s="8">
@@ -13478,10 +13478,10 @@
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13531,10 +13531,10 @@
         <v>26</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I199" s="9"/>
       <c r="J199" s="8">
@@ -13584,10 +13584,10 @@
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13637,10 +13637,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="8">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -7511,7 +7511,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46205.17836196759</v>
+        <v>46213.20753342593</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>
@@ -7555,8 +7555,8 @@
       <c r="R92" s="5">
         <v>46212</v>
       </c>
-      <c r="S92" s="11" t="s">
-        <v>157</v>
+      <c r="S92" s="12" t="s">
+        <v>105</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -8842,7 +8842,7 @@
         <v>46205.61658686343</v>
       </c>
       <c r="D115" s="8">
-        <v>46205.61660277778</v>
+        <v>46213.19932342593</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>58</v>
@@ -8886,8 +8886,8 @@
       <c r="R115" s="8">
         <v>46220</v>
       </c>
-      <c r="S115" s="10" t="s">
-        <v>32</v>
+      <c r="S115" s="11" t="s">
+        <v>157</v>
       </c>
       <c r="T115" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="539">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -119,6 +119,72 @@
   </si>
   <si>
     <t>Apertura pedido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buen día,
+Para el pedido 1557 se tienen 2 equipos ZVN 1-7-37/2, 2 equipos ZVN 1-7-30/2, 1 equipo ZVN 1-9-37/2 y 1 equipo JZR 6-18.5/2 para Atacama Kozan:
+    *    Planos para fabricación Ventilador ZVN 1-7-37/2 con motor OMEC
+        *    Incluye: Tobera + Rejilla
+        *    hgutierrez@zitron.com, tu apoyo con los planos.
+    *    Rodete:
+        *    Rodete monobloque GEL 7-37  
+        *    Código: 300065
+        *    Plano Mecanizado 3534.07.04.37.D55
+    *    Datos eléctricos para el motor:
+        *    Motor 37 KW, 2 Polos, Frame 200L.
+        *    380 VAC, 50 Hz, IEC, IP55, FS 1.0.-
+        *    Código: 350004
+--
+    *    Planos para fabricación Ventilador ZVN 1-7-30/2 con motor OMEC
+        *    Incluye: Tobera + Rejilla
+        *    hgutierrez@zitron.com, tu apoyo con los planos.
+    *    Rodete:
+        *    Rodete monobloque GEL 7-30
+        *    Código: 300062
+        *    Plano Mecanizado 3534.07.04.30.D55
+    *    Datos eléctricos para el motor:
+        *    Motor 30 KW, 2 Polos, Frame 200L.
+        *    380 VAC, 50 Hz, IEC, IP55, FS 1.0.-
+        *    Código: 350004
+        *    benjamin.bustos@zitron.com, se debe solicitar duplicado de placas.
+--
+    *    Planos para fabricación Ventilador ZVN 1-9-37/2 con motor OMEC
+        *    Incluye: Tobera + Rejilla
+        *    hgutierrez@zitron.com, tu apoyo con los planos.
+    *    Rodete:
+        *    Rodete de placas s/plano 4999.00
+        *    Alabe s/ plano 4999.01
+        *    Z8 N590
+        *    Código 300000
+        *    hgutierrez@zitron.com, tu apoyo con la definición de calaje
+    *    Datos eléctricos para el motor:
+        *    Motor 37 KW, 2 Polos, Frame 200L.
+        *    380 VAC, 50 Hz, IEC, IP55, FS 1.0.-
+        *    Código: 350004
+--
+    *    Fabricación Ventilador JZR 6-18.5/2 con motor WEG
+        *    Incluye: Tobera + Rejilla + 2FAR90/100 + Bastidor
+        *    Plano CH1463
+    *    Rodete:
+        *    Rodete monobloque GEL 6-15  
+        *    Código 300056
+        *    Plano Mecanizado 3534.06.04.15.D42
+    *    Datos eléctricos para el motor:
+        *    Motor 18.5 KW, 2 Polos, Frame 160L.
+        *    380 VAC, 50 Hz, IEC, IP55, FS 1.0.-
+--
+    *    Datos eléctricos para tableros:
+        *    Tablero YD  18.5kW, 380 VAC, 50 Hz, IP66.
+        *    Tablero YD  30kW, 380 VAC, 50 Hz, IP66.
+        *    Tablero YD  37kW, 380 VAC, 50 Hz, IP66.
+        *    Incluye luces piloto, botones y protección de entrada
+        *    Propuestas en sistema.
+    *    Tratamiento superficial estándar Zitron para todas las unidades:
+        *    Preparación de superficie: Arenado SSPC-SP10
+        *    1ª capa imprimación 60 micras Hempadur 15570 Color 12430
+        *    2ª capa intermedia 40 micras Hempathane HS 55610 Color 20450 RAL 9001
+    *    Fecha de entrega: 16-06-2026
+</t>
   </si>
   <si>
     <t>1215155493700871</t>
@@ -2407,7 +2473,7 @@
         <v>46175.87163862269</v>
       </c>
       <c r="D6" s="5">
-        <v>46175.87166359954</v>
+        <v>46213.713806886575</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>
@@ -2429,7 +2495,7 @@
         <v>26</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>26</v>
@@ -2461,7 +2527,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="8">
         <v>46168.683132754624</v>
@@ -2473,7 +2539,7 @@
         <v>46175.87166400463</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>26</v>
@@ -2492,7 +2558,7 @@
         <v>26</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M7" s="9" t="s">
         <v>26</v>
@@ -2524,7 +2590,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="5">
         <v>46168.683135416664</v>
@@ -2536,7 +2602,7 @@
         <v>46175.871664895836</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>26</v>
@@ -2555,7 +2621,7 @@
         <v>26</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>26</v>
@@ -2567,7 +2633,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q8" s="5">
         <v>46154</v>
@@ -2587,7 +2653,7 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" s="8">
         <v>46168.683139201385</v>
@@ -2599,7 +2665,7 @@
         <v>46175.871664074075</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>26</v>
@@ -2618,7 +2684,7 @@
         <v>26</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M9" s="9" t="s">
         <v>26</v>
@@ -2650,7 +2716,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="5">
         <v>46168.68298012731</v>
@@ -2662,7 +2728,7 @@
         <v>46196.89418670139</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="6" t="s">
         <v>25</v>
@@ -2686,7 +2752,7 @@
         <v>26</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>26</v>
@@ -2703,7 +2769,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" s="8">
         <v>46168.683142650465</v>
@@ -2715,16 +2781,16 @@
         <v>46193.553190729166</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I11" s="8">
         <v>46155</v>
@@ -2742,13 +2808,13 @@
         <v>26</v>
       </c>
       <c r="N11" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O11" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P11" s="9" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="Q11" s="8">
         <v>46155</v>
@@ -2768,7 +2834,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B12" s="5">
         <v>46168.683148310185</v>
@@ -2780,16 +2846,16 @@
         <v>46205.61958375</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I12" s="5">
         <v>46223</v>
@@ -2807,13 +2873,13 @@
         <v>26</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="Q12" s="5">
         <v>46223</v>
@@ -2828,12 +2894,12 @@
         <v>1</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B13" s="8">
         <v>46168.68315351852</v>
@@ -2845,16 +2911,16 @@
         <v>46205.61659230324</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I13" s="8">
         <v>46223</v>
@@ -2872,13 +2938,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2888,7 +2954,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
         <v>46168.68315625</v>
@@ -2900,16 +2966,16 @@
         <v>46205.616595300926</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I14" s="5">
         <v>46223</v>
@@ -2927,13 +2993,13 @@
         <v>26</v>
       </c>
       <c r="N14" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2943,7 +3009,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8">
         <v>46168.68315891204</v>
@@ -2955,16 +3021,16 @@
         <v>46205.61659625</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I15" s="8">
         <v>46223</v>
@@ -2982,13 +3048,13 @@
         <v>26</v>
       </c>
       <c r="N15" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -2998,7 +3064,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B16" s="5">
         <v>46168.683161493056</v>
@@ -3010,16 +3076,16 @@
         <v>46205.616596921296</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I16" s="5">
         <v>46223</v>
@@ -3037,13 +3103,13 @@
         <v>26</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -3053,7 +3119,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B17" s="8">
         <v>46168.68316400463</v>
@@ -3065,16 +3131,16 @@
         <v>46205.61659773148</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I17" s="8">
         <v>46223</v>
@@ -3092,13 +3158,13 @@
         <v>26</v>
       </c>
       <c r="N17" s="9" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -3108,7 +3174,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="5">
         <v>46168.68316714121</v>
@@ -3120,16 +3186,16 @@
         <v>46205.61659839121</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I18" s="5">
         <v>46223</v>
@@ -3147,13 +3213,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -3163,7 +3229,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="8">
         <v>46168.682984189814</v>
@@ -3175,7 +3241,7 @@
         <v>46205.60495420139</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>25</v>
@@ -3199,7 +3265,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="P19" s="9" t="s">
         <v>26</v>
@@ -3216,7 +3282,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B20" s="5">
         <v>46168.68317581018</v>
@@ -3228,16 +3294,16 @@
         <v>46196.87777847222</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I20" s="5">
         <v>46155</v>
@@ -3249,19 +3315,19 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="5">
         <v>46155</v>
@@ -3281,7 +3347,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B21" s="8">
         <v>46168.6831808912</v>
@@ -3293,16 +3359,16 @@
         <v>46196.877778333335</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I21" s="8">
         <v>46155</v>
@@ -3314,19 +3380,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q21" s="8">
         <v>46155</v>
@@ -3346,7 +3412,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B22" s="5">
         <v>46168.68318591436</v>
@@ -3358,16 +3424,16 @@
         <v>46196.87777902778</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I22" s="5">
         <v>46155</v>
@@ -3385,13 +3451,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q22" s="5">
         <v>46155</v>
@@ -3411,7 +3477,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" s="8">
         <v>46168.68298827547</v>
@@ -3423,7 +3489,7 @@
         <v>46205.605017905094</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>25</v>
@@ -3447,7 +3513,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>26</v>
@@ -3462,7 +3528,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B24" s="5">
         <v>46168.68319888889</v>
@@ -3474,16 +3540,16 @@
         <v>46193.5530831713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3501,13 +3567,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Q24" s="5">
         <v>46157</v>
@@ -3527,7 +3593,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" s="8">
         <v>46168.68320439815</v>
@@ -3539,16 +3605,16 @@
         <v>46193.55308946759</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I25" s="8">
         <v>46157</v>
@@ -3566,13 +3632,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="8">
         <v>46157</v>
@@ -3592,7 +3658,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46168.68320962963</v>
@@ -3604,16 +3670,16 @@
         <v>46183.90442146991</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3631,13 +3697,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3657,7 +3723,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8">
         <v>46168.68321476852</v>
@@ -3669,16 +3735,16 @@
         <v>46197.8530077662</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I27" s="8">
         <v>46189</v>
@@ -3696,13 +3762,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="8">
         <v>46189</v>
@@ -3711,7 +3777,7 @@
         <v>46190</v>
       </c>
       <c r="S27" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T27" s="9">
         <v>1</v>
@@ -3722,7 +3788,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" s="5">
         <v>46168.68321959491</v>
@@ -3734,16 +3800,16 @@
         <v>46196.64668813658</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I28" s="5">
         <v>46189</v>
@@ -3761,13 +3827,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q28" s="5">
         <v>46189</v>
@@ -3776,7 +3842,7 @@
         <v>46190</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
@@ -3787,7 +3853,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46168.68322341435</v>
@@ -3799,16 +3865,16 @@
         <v>46196.647418912034</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I29" s="8">
         <v>46189</v>
@@ -3826,13 +3892,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q29" s="8">
         <v>46189</v>
@@ -3841,7 +3907,7 @@
         <v>46190</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3852,7 +3918,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5">
         <v>46168.683227245376</v>
@@ -3864,16 +3930,16 @@
         <v>46196.64801533565</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I30" s="5">
         <v>46189</v>
@@ -3891,13 +3957,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="5">
         <v>46189</v>
@@ -3906,7 +3972,7 @@
         <v>46190</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3917,7 +3983,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46168.683231365736</v>
@@ -3929,16 +3995,16 @@
         <v>46193.553499305555</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I31" s="8">
         <v>46157</v>
@@ -3956,13 +4022,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="8">
         <v>46157</v>
@@ -3982,7 +4048,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B32" s="5">
         <v>46168.682992511574</v>
@@ -3994,7 +4060,7 @@
         <v>46205.61594793982</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -4018,7 +4084,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -4035,7 +4101,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B33" s="8">
         <v>46168.68327652778</v>
@@ -4047,16 +4113,16 @@
         <v>46195.928396574076</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I33" s="8">
         <v>46161</v>
@@ -4074,13 +4140,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q33" s="8">
         <v>46161</v>
@@ -4100,7 +4166,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B34" s="5">
         <v>46168.68328149305</v>
@@ -4112,16 +4178,16 @@
         <v>46195.9258303588</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -4139,13 +4205,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4156,12 +4222,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B35" s="8">
         <v>46168.68328653935</v>
@@ -4173,16 +4239,16 @@
         <v>46195.928370243055</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I35" s="8">
         <v>46164</v>
@@ -4200,13 +4266,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -4217,12 +4283,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B36" s="5">
         <v>46168.68329140046</v>
@@ -4234,16 +4300,16 @@
         <v>46185.182775243054</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I36" s="5">
         <v>46161</v>
@@ -4261,13 +4327,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q36" s="5">
         <v>46161</v>
@@ -4276,7 +4342,7 @@
         <v>46184</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4287,7 +4353,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B37" s="8">
         <v>46168.68329584491</v>
@@ -4299,16 +4365,16 @@
         <v>46184.70350368056</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I37" s="8">
         <v>46161</v>
@@ -4326,13 +4392,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -4343,12 +4409,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B38" s="5">
         <v>46168.68330070602</v>
@@ -4360,16 +4426,16 @@
         <v>46184.703557789355</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I38" s="5">
         <v>46164</v>
@@ -4387,13 +4453,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4404,12 +4470,12 @@
         <v>0</v>
       </c>
       <c r="U38" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B39" s="8">
         <v>46168.68330542824</v>
@@ -4421,16 +4487,16 @@
         <v>46205.60819122686</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I39" s="8">
         <v>46161</v>
@@ -4448,13 +4514,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q39" s="8">
         <v>46161</v>
@@ -4463,7 +4529,7 @@
         <v>46198</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4474,7 +4540,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B40" s="5">
         <v>46168.683310092594</v>
@@ -4486,16 +4552,16 @@
         <v>46195.92587128472</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I40" s="5">
         <v>46161</v>
@@ -4513,13 +4579,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4530,12 +4596,12 @@
         <v>0</v>
       </c>
       <c r="U40" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" s="8">
         <v>46168.68331519676</v>
@@ -4547,16 +4613,16 @@
         <v>46205.60793128472</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I41" s="8">
         <v>46170</v>
@@ -4574,13 +4640,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4591,12 +4657,12 @@
         <v>0</v>
       </c>
       <c r="U41" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B42" s="5">
         <v>46168.68332027778</v>
@@ -4608,16 +4674,16 @@
         <v>46195.92587850694</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I42" s="5">
         <v>46170</v>
@@ -4635,13 +4701,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4652,12 +4718,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B43" s="8">
         <v>46168.68332520833</v>
@@ -4669,16 +4735,16 @@
         <v>46212.17842539352</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I43" s="8">
         <v>46161</v>
@@ -4696,10 +4762,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4711,7 +4777,7 @@
         <v>46219</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4722,7 +4788,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B44" s="5">
         <v>46168.68332880787</v>
@@ -4734,16 +4800,16 @@
         <v>46195.92577891204</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I44" s="5">
         <v>46161</v>
@@ -4761,13 +4827,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4777,7 +4843,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B45" s="8">
         <v>46168.683333113426</v>
@@ -4789,16 +4855,16 @@
         <v>46195.92857017361</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I45" s="8">
         <v>46171</v>
@@ -4816,13 +4882,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4832,7 +4898,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B46" s="5">
         <v>46168.683337291666</v>
@@ -4844,16 +4910,16 @@
         <v>46204.1978837037</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I46" s="5">
         <v>46191</v>
@@ -4871,13 +4937,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Q46" s="5">
         <v>46191</v>
@@ -4886,7 +4952,7 @@
         <v>46203</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4897,7 +4963,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B47" s="8">
         <v>46168.68334179398</v>
@@ -4909,16 +4975,16 @@
         <v>46199.564988564816</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I47" s="8">
         <v>46191</v>
@@ -4936,13 +5002,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -4953,12 +5019,12 @@
         <v>0</v>
       </c>
       <c r="U47" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B48" s="5">
         <v>46168.68334684028</v>
@@ -4970,16 +5036,16 @@
         <v>46199.5650378125</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I48" s="5">
         <v>46195</v>
@@ -4997,13 +5063,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -5014,12 +5080,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B49" s="8">
         <v>46168.68335195602</v>
@@ -5031,16 +5097,16 @@
         <v>46204.19788363426</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I49" s="8">
         <v>46191</v>
@@ -5058,10 +5124,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -5073,7 +5139,7 @@
         <v>46203</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -5084,7 +5150,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B50" s="5">
         <v>46168.68335582176</v>
@@ -5096,16 +5162,16 @@
         <v>46199.56512275463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I50" s="5">
         <v>46191</v>
@@ -5123,13 +5189,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -5139,7 +5205,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B51" s="8">
         <v>46168.683360428244</v>
@@ -5151,16 +5217,16 @@
         <v>46199.56520053241</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I51" s="8">
         <v>46195</v>
@@ -5178,13 +5244,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5194,7 +5260,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B52" s="5">
         <v>46168.68336471065</v>
@@ -5206,16 +5272,16 @@
         <v>46205.61765122685</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -5233,10 +5299,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -5259,7 +5325,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B53" s="8">
         <v>46168.68337377315</v>
@@ -5271,16 +5337,16 @@
         <v>46204.601485555555</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I53" s="8">
         <v>46191</v>
@@ -5298,13 +5364,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5314,7 +5380,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B54" s="5">
         <v>46168.683378194444</v>
@@ -5326,16 +5392,16 @@
         <v>46204.601540787036</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="I54" s="5">
         <v>46202</v>
@@ -5353,13 +5419,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5369,7 +5435,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B55" s="8">
         <v>46168.68338271991</v>
@@ -5381,16 +5447,16 @@
         <v>46205.644352627314</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I55" s="8">
         <v>46231</v>
@@ -5408,10 +5474,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5424,7 +5490,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B56" s="5">
         <v>46168.683385868055</v>
@@ -5436,16 +5502,16 @@
         <v>46204.19788391204</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I56" s="5">
         <v>46191</v>
@@ -5463,10 +5529,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5478,7 +5544,7 @@
         <v>46203</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5489,7 +5555,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B57" s="8">
         <v>46168.68343064815</v>
@@ -5501,16 +5567,16 @@
         <v>46199.56535409723</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I57" s="8">
         <v>46191</v>
@@ -5528,13 +5594,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5544,7 +5610,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B58" s="5">
         <v>46168.683436956024</v>
@@ -5556,16 +5622,16 @@
         <v>46199.56544034722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I58" s="5">
         <v>46195</v>
@@ -5583,13 +5649,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5599,7 +5665,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B59" s="8">
         <v>46168.68344221065</v>
@@ -5609,7 +5675,7 @@
         <v>46210.52421333334</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5633,7 +5699,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5643,12 +5709,12 @@
       <c r="S59" s="9"/>
       <c r="T59" s="9"/>
       <c r="U59" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B60" s="5">
         <v>46168.683445787035</v>
@@ -5660,16 +5726,16 @@
         <v>46184.518844583334</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I60" s="5">
         <v>46167</v>
@@ -5687,13 +5753,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q60" s="5">
         <v>46167</v>
@@ -5702,7 +5768,7 @@
         <v>46171</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5713,7 +5779,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B61" s="8">
         <v>46168.6865996875</v>
@@ -5725,16 +5791,16 @@
         <v>46184.51878665509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I61" s="8">
         <v>46167</v>
@@ -5752,13 +5818,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5768,7 +5834,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B62" s="5">
         <v>46168.68683460648</v>
@@ -5780,16 +5846,16 @@
         <v>46184.518791319446</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I62" s="5">
         <v>46167</v>
@@ -5807,13 +5873,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5823,7 +5889,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46168.686918437495</v>
@@ -5835,16 +5901,16 @@
         <v>46184.51879930556</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I63" s="8">
         <v>46167</v>
@@ -5862,13 +5928,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5878,7 +5944,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46168.687254143515</v>
@@ -5890,16 +5956,16 @@
         <v>46184.5188068287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I64" s="5">
         <v>46167</v>
@@ -5917,13 +5983,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5933,7 +5999,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B65" s="8">
         <v>46168.68731635417</v>
@@ -5945,16 +6011,16 @@
         <v>46184.51881454861</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I65" s="8">
         <v>46167</v>
@@ -5972,13 +6038,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5988,7 +6054,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B66" s="5">
         <v>46168.68345142361</v>
@@ -6000,16 +6066,16 @@
         <v>46190.605242708334</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I66" s="5">
         <v>46181</v>
@@ -6027,13 +6093,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="Q66" s="5">
         <v>46181</v>
@@ -6042,7 +6108,7 @@
         <v>46185</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -6053,7 +6119,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B67" s="8">
         <v>46168.68857346065</v>
@@ -6065,16 +6131,16 @@
         <v>46190.60518608797</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I67" s="8">
         <v>46181</v>
@@ -6092,13 +6158,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -6108,7 +6174,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B68" s="5">
         <v>46168.688608275465</v>
@@ -6120,16 +6186,16 @@
         <v>46190.60519502315</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I68" s="5">
         <v>46181</v>
@@ -6147,13 +6213,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6163,7 +6229,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B69" s="8">
         <v>46168.68864659722</v>
@@ -6175,16 +6241,16 @@
         <v>46190.605203761574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I69" s="8">
         <v>46181</v>
@@ -6202,13 +6268,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6218,7 +6284,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B70" s="5">
         <v>46168.68868637731</v>
@@ -6230,16 +6296,16 @@
         <v>46190.605208946756</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I70" s="5">
         <v>46181</v>
@@ -6257,13 +6323,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6273,7 +6339,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B71" s="8">
         <v>46168.68871934028</v>
@@ -6285,16 +6351,16 @@
         <v>46190.60521709491</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I71" s="8">
         <v>46181</v>
@@ -6312,13 +6378,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -6328,7 +6394,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5">
         <v>46168.68345790509</v>
@@ -6340,16 +6406,16 @@
         <v>46190.6054244213</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I72" s="5">
         <v>46188</v>
@@ -6367,13 +6433,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q72" s="5">
         <v>46188</v>
@@ -6382,7 +6448,7 @@
         <v>46188</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6393,7 +6459,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B73" s="8">
         <v>46168.68880178241</v>
@@ -6405,16 +6471,16 @@
         <v>46190.60536361111</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -6432,13 +6498,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6448,7 +6514,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B74" s="5">
         <v>46168.68883857639</v>
@@ -6460,16 +6526,16 @@
         <v>46190.605368206016</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I74" s="5">
         <v>46188</v>
@@ -6487,13 +6553,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6503,7 +6569,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B75" s="8">
         <v>46168.688875775464</v>
@@ -6515,16 +6581,16 @@
         <v>46190.605373530096</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I75" s="8">
         <v>46188</v>
@@ -6542,13 +6608,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6558,7 +6624,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B76" s="5">
         <v>46168.6889172338</v>
@@ -6570,16 +6636,16 @@
         <v>46190.60539957176</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I76" s="5">
         <v>46188</v>
@@ -6597,13 +6663,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6613,7 +6679,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B77" s="8">
         <v>46168.688956620375</v>
@@ -6625,16 +6691,16 @@
         <v>46190.60538814815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="I77" s="8">
         <v>46188</v>
@@ -6652,10 +6718,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6668,7 +6734,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B78" s="5">
         <v>46168.683480625</v>
@@ -6680,16 +6746,16 @@
         <v>46211.83847391204</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6705,10 +6771,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6731,7 +6797,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B79" s="8">
         <v>46168.683484629626</v>
@@ -6743,16 +6809,16 @@
         <v>46211.83842664352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I79" s="8">
         <v>46238</v>
@@ -6770,13 +6836,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6786,7 +6852,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B80" s="5">
         <v>46168.683488877316</v>
@@ -6798,16 +6864,16 @@
         <v>46211.83843200232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I80" s="5">
         <v>46238</v>
@@ -6825,13 +6891,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6841,7 +6907,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B81" s="8">
         <v>46168.68349300926</v>
@@ -6853,16 +6919,16 @@
         <v>46211.83843496528</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I81" s="8">
         <v>46238</v>
@@ -6880,13 +6946,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6896,7 +6962,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B82" s="5">
         <v>46168.6834959375</v>
@@ -6908,16 +6974,16 @@
         <v>46211.83844040509</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I82" s="5">
         <v>46238</v>
@@ -6935,13 +7001,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6951,7 +7017,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B83" s="8">
         <v>46168.68349899305</v>
@@ -6963,16 +7029,16 @@
         <v>46211.83844619213</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="I83" s="8">
         <v>46238</v>
@@ -6990,13 +7056,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -7006,7 +7072,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B84" s="5">
         <v>46168.68351101852</v>
@@ -7018,7 +7084,7 @@
         <v>46205.618076087965</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -7042,7 +7108,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -7059,7 +7125,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B85" s="8">
         <v>46168.68351447917</v>
@@ -7071,16 +7137,16 @@
         <v>46206.18878055556</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I85" s="8">
         <v>46204</v>
@@ -7098,13 +7164,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q85" s="8">
         <v>46204</v>
@@ -7113,7 +7179,7 @@
         <v>46205</v>
       </c>
       <c r="S85" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -7124,7 +7190,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B86" s="5">
         <v>46168.68352011574</v>
@@ -7136,16 +7202,16 @@
         <v>46210.20097684028</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I86" s="5">
         <v>46206</v>
@@ -7163,13 +7229,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q86" s="5">
         <v>46206</v>
@@ -7178,18 +7244,18 @@
         <v>46209</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
       </c>
       <c r="U86" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B87" s="8">
         <v>46168.68352736111</v>
@@ -7201,16 +7267,16 @@
         <v>46206.18878028935</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -7228,13 +7294,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -7243,7 +7309,7 @@
         <v>46205</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -7254,7 +7320,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B88" s="5">
         <v>46168.68353292824</v>
@@ -7266,16 +7332,16 @@
         <v>46210.20097686343</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I88" s="5">
         <v>46206</v>
@@ -7293,13 +7359,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q88" s="5">
         <v>46206</v>
@@ -7308,18 +7374,18 @@
         <v>46209</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B89" s="8">
         <v>46168.68353787037</v>
@@ -7331,16 +7397,16 @@
         <v>46206.1887803125</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7358,13 +7424,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q89" s="8">
         <v>46204</v>
@@ -7373,7 +7439,7 @@
         <v>46205</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T89" s="9">
         <v>1</v>
@@ -7384,7 +7450,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B90" s="5">
         <v>46168.68354247685</v>
@@ -7396,16 +7462,16 @@
         <v>46210.20097706019</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I90" s="5">
         <v>46206</v>
@@ -7423,13 +7489,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q90" s="5">
         <v>46206</v>
@@ -7438,18 +7504,18 @@
         <v>46209</v>
       </c>
       <c r="S90" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
       </c>
       <c r="U90" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B91" s="8">
         <v>46168.68354741899</v>
@@ -7461,7 +7527,7 @@
         <v>46211.83134737269</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>25</v>
@@ -7485,7 +7551,7 @@
         <v>26</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>26</v>
@@ -7502,7 +7568,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B92" s="5">
         <v>46168.68355052083</v>
@@ -7514,16 +7580,16 @@
         <v>46213.20753342593</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7541,13 +7607,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92" s="5">
         <v>46210</v>
@@ -7556,7 +7622,7 @@
         <v>46212</v>
       </c>
       <c r="S92" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -7567,7 +7633,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B93" s="8">
         <v>46168.68356208333</v>
@@ -7579,16 +7645,16 @@
         <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I93" s="8">
         <v>46210</v>
@@ -7606,13 +7672,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7622,7 +7688,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B94" s="5">
         <v>46168.68356922454</v>
@@ -7634,16 +7700,16 @@
         <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7661,13 +7727,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7677,7 +7743,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B95" s="8">
         <v>46168.683574780094</v>
@@ -7689,16 +7755,16 @@
         <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I95" s="8">
         <v>46210</v>
@@ -7716,13 +7782,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7732,7 +7798,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B96" s="5">
         <v>46168.68358024306</v>
@@ -7744,16 +7810,16 @@
         <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7771,13 +7837,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7787,7 +7853,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B97" s="8">
         <v>46168.68358578703</v>
@@ -7799,16 +7865,16 @@
         <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I97" s="8">
         <v>46210</v>
@@ -7826,13 +7892,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7842,7 +7908,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B98" s="5">
         <v>46168.68365474537</v>
@@ -7854,16 +7920,16 @@
         <v>46197.85243150463</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I98" s="5">
         <v>46213</v>
@@ -7881,13 +7947,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q98" s="5">
         <v>46213</v>
@@ -7902,12 +7968,12 @@
         <v>1</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B99" s="8">
         <v>46168.683659965274</v>
@@ -7919,16 +7985,16 @@
         <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I99" s="8">
         <v>46213</v>
@@ -7946,13 +8012,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -7962,7 +8028,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B100" s="5">
         <v>46168.68366613426</v>
@@ -7974,16 +8040,16 @@
         <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I100" s="5">
         <v>46213</v>
@@ -8001,13 +8067,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -8017,7 +8083,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B101" s="8">
         <v>46168.683671921295</v>
@@ -8029,16 +8095,16 @@
         <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I101" s="8">
         <v>46213</v>
@@ -8056,13 +8122,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -8072,7 +8138,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B102" s="5">
         <v>46168.68367622685</v>
@@ -8084,16 +8150,16 @@
         <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I102" s="5">
         <v>46213</v>
@@ -8111,13 +8177,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8127,7 +8193,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B103" s="8">
         <v>46168.683680069444</v>
@@ -8139,16 +8205,16 @@
         <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I103" s="8">
         <v>46213</v>
@@ -8166,13 +8232,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8182,7 +8248,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B104" s="5">
         <v>46168.68369409722</v>
@@ -8194,16 +8260,16 @@
         <v>46204.8901028588</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I104" s="5">
         <v>46224</v>
@@ -8221,13 +8287,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q104" s="5">
         <v>46224</v>
@@ -8247,7 +8313,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B105" s="8">
         <v>46168.68369849537</v>
@@ -8259,16 +8325,16 @@
         <v>46204.890051967595</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I105" s="8">
         <v>46224</v>
@@ -8286,13 +8352,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8302,7 +8368,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B106" s="5">
         <v>46168.683704490744</v>
@@ -8314,16 +8380,16 @@
         <v>46204.890058125005</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I106" s="5">
         <v>46224</v>
@@ -8341,13 +8407,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8357,7 +8423,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B107" s="8">
         <v>46168.683710150464</v>
@@ -8369,16 +8435,16 @@
         <v>46204.89006394676</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I107" s="8">
         <v>46224</v>
@@ -8396,13 +8462,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8412,7 +8478,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B108" s="5">
         <v>46168.68371309028</v>
@@ -8424,16 +8490,16 @@
         <v>46204.89006936342</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I108" s="5">
         <v>46224</v>
@@ -8451,13 +8517,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8467,7 +8533,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B109" s="8">
         <v>46168.68371646991</v>
@@ -8479,16 +8545,16 @@
         <v>46204.890080185185</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I109" s="8">
         <v>46224</v>
@@ -8506,13 +8572,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8522,7 +8588,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B110" s="5">
         <v>46168.68373005787</v>
@@ -8534,7 +8600,7 @@
         <v>46211.830014363426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8558,7 +8624,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8575,7 +8641,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B111" s="8">
         <v>46168.68373365741</v>
@@ -8587,16 +8653,16 @@
         <v>46205.61049446759</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I111" s="8">
         <v>46185</v>
@@ -8614,13 +8680,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q111" s="8">
         <v>46185</v>
@@ -8629,7 +8695,7 @@
         <v>46185</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T111" s="9">
         <v>1</v>
@@ -8640,7 +8706,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B112" s="5">
         <v>46168.6837408912</v>
@@ -8652,16 +8718,16 @@
         <v>46205.61455358796</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8677,13 +8743,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q112" s="5">
         <v>46168</v>
@@ -8692,7 +8758,7 @@
         <v>46168</v>
       </c>
       <c r="S112" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T112" s="6">
         <v>1</v>
@@ -8703,7 +8769,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B113" s="8">
         <v>46168.68374771991</v>
@@ -8715,16 +8781,16 @@
         <v>46205.6084347338</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I113" s="8">
         <v>46199</v>
@@ -8742,13 +8808,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q113" s="8">
         <v>46199</v>
@@ -8757,7 +8823,7 @@
         <v>46199</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8768,7 +8834,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B114" s="5">
         <v>46168.68375502314</v>
@@ -8780,16 +8846,16 @@
         <v>46211.83000291667</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8807,13 +8873,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q114" s="5">
         <v>46232</v>
@@ -8833,7 +8899,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B115" s="8">
         <v>46168.6837971412</v>
@@ -8845,16 +8911,16 @@
         <v>46213.19932342593</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="I115" s="8">
         <v>46220</v>
@@ -8872,13 +8938,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q115" s="8">
         <v>46220</v>
@@ -8887,7 +8953,7 @@
         <v>46220</v>
       </c>
       <c r="S115" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="T115" s="9">
         <v>1</v>
@@ -8898,7 +8964,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B116" s="5">
         <v>46168.68381362269</v>
@@ -8908,7 +8974,7 @@
         <v>46206.48624146991</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8932,7 +8998,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -8942,12 +9008,12 @@
       <c r="S116" s="6"/>
       <c r="T116" s="6"/>
       <c r="U116" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B117" s="8">
         <v>46168.68381783565</v>
@@ -8959,16 +9025,16 @@
         <v>46211.830007129625</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I117" s="8">
         <v>46225</v>
@@ -8986,13 +9052,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q117" s="8">
         <v>46225</v>
@@ -9007,12 +9073,12 @@
         <v>1</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B118" s="5">
         <v>46168.683825810185</v>
@@ -9024,16 +9090,16 @@
         <v>46211.82999423611</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I118" s="5">
         <v>46231</v>
@@ -9051,13 +9117,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -9067,7 +9133,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B119" s="8">
         <v>46168.68383587963</v>
@@ -9079,16 +9145,16 @@
         <v>46211.82999525463</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I119" s="8">
         <v>46231</v>
@@ -9106,13 +9172,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -9122,7 +9188,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B120" s="5">
         <v>46168.68384034722</v>
@@ -9134,16 +9200,16 @@
         <v>46204.89052016204</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I120" s="5">
         <v>46231</v>
@@ -9161,13 +9227,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -9177,7 +9243,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B121" s="8">
         <v>46168.683844074076</v>
@@ -9189,16 +9255,16 @@
         <v>46204.89050689815</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I121" s="8">
         <v>46231</v>
@@ -9216,13 +9282,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9232,7 +9298,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B122" s="5">
         <v>46168.683847673616</v>
@@ -9244,16 +9310,16 @@
         <v>46204.890087210646</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I122" s="5">
         <v>46231</v>
@@ -9271,13 +9337,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9287,7 +9353,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B123" s="8">
         <v>46168.683862453705</v>
@@ -9299,16 +9365,16 @@
         <v>46204.891766898145</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I123" s="8">
         <v>46232</v>
@@ -9326,13 +9392,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q123" s="8">
         <v>46232</v>
@@ -9352,7 +9418,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B124" s="5">
         <v>46168.683867141204</v>
@@ -9364,16 +9430,16 @@
         <v>46205.61454657407</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I124" s="5">
         <v>46232</v>
@@ -9391,13 +9457,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9407,7 +9473,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B125" s="8">
         <v>46168.683873368056</v>
@@ -9419,16 +9485,16 @@
         <v>46205.61454702546</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I125" s="8">
         <v>46232</v>
@@ -9446,13 +9512,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9462,7 +9528,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B126" s="5">
         <v>46168.68387903935</v>
@@ -9474,16 +9540,16 @@
         <v>46205.614544861106</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I126" s="5">
         <v>46232</v>
@@ -9501,13 +9567,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9517,7 +9583,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B127" s="8">
         <v>46168.683884618054</v>
@@ -9529,16 +9595,16 @@
         <v>46205.61454555555</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I127" s="8">
         <v>46232</v>
@@ -9556,13 +9622,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9572,7 +9638,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B128" s="5">
         <v>46168.68389033565</v>
@@ -9584,16 +9650,16 @@
         <v>46205.614546122684</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I128" s="5">
         <v>46232</v>
@@ -9611,13 +9677,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9627,7 +9693,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B129" s="8">
         <v>46168.68391289352</v>
@@ -9639,16 +9705,16 @@
         <v>46204.89299085648</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I129" s="8">
         <v>46233</v>
@@ -9666,13 +9732,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q129" s="8">
         <v>46233</v>
@@ -9692,7 +9758,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B130" s="5">
         <v>46168.68391818287</v>
@@ -9704,16 +9770,16 @@
         <v>46205.6085181713</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I130" s="5">
         <v>46233</v>
@@ -9731,13 +9797,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9747,7 +9813,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B131" s="8">
         <v>46168.68393068287</v>
@@ -9759,16 +9825,16 @@
         <v>46205.60851520833</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I131" s="8">
         <v>46233</v>
@@ -9786,13 +9852,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9802,7 +9868,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B132" s="5">
         <v>46168.68393770834</v>
@@ -9814,16 +9880,16 @@
         <v>46205.608516168984</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I132" s="5">
         <v>46233</v>
@@ -9841,13 +9907,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9857,7 +9923,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B133" s="8">
         <v>46168.6839434375</v>
@@ -9869,16 +9935,16 @@
         <v>46205.608518877314</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I133" s="8">
         <v>46233</v>
@@ -9896,13 +9962,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9912,7 +9978,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B134" s="5">
         <v>46168.68398528935</v>
@@ -9924,16 +9990,16 @@
         <v>46205.608517326385</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I134" s="5">
         <v>46233</v>
@@ -9951,13 +10017,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9967,7 +10033,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B135" s="8">
         <v>46168.68401087963</v>
@@ -9979,16 +10045,16 @@
         <v>46204.893423761576</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I135" s="8">
         <v>46234</v>
@@ -10006,13 +10072,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q135" s="8">
         <v>46234</v>
@@ -10032,7 +10098,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B136" s="5">
         <v>46168.68401652778</v>
@@ -10044,16 +10110,16 @@
         <v>46205.60828351852</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I136" s="5">
         <v>46234</v>
@@ -10071,13 +10137,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -10087,7 +10153,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B137" s="8">
         <v>46168.68402403935</v>
@@ -10099,16 +10165,16 @@
         <v>46205.60828236111</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I137" s="8">
         <v>46234</v>
@@ -10126,13 +10192,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -10142,7 +10208,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B138" s="5">
         <v>46168.68403127315</v>
@@ -10154,16 +10220,16 @@
         <v>46205.608284375005</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I138" s="5">
         <v>46234</v>
@@ -10181,13 +10247,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -10197,7 +10263,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B139" s="8">
         <v>46168.68403755787</v>
@@ -10209,16 +10275,16 @@
         <v>46205.60828523149</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I139" s="8">
         <v>46234</v>
@@ -10236,13 +10302,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -10252,7 +10318,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B140" s="5">
         <v>46168.68404385417</v>
@@ -10264,16 +10330,16 @@
         <v>46205.60828666667</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I140" s="5">
         <v>46234</v>
@@ -10291,13 +10357,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10307,7 +10373,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B141" s="8">
         <v>46168.68406297454</v>
@@ -10319,16 +10385,16 @@
         <v>46206.48582321759</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I141" s="8">
         <v>46237</v>
@@ -10346,13 +10412,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q141" s="8">
         <v>46237</v>
@@ -10372,7 +10438,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B142" s="5">
         <v>46168.68406752315</v>
@@ -10384,16 +10450,16 @@
         <v>46206.48579965278</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I142" s="5">
         <v>46237</v>
@@ -10411,13 +10477,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10427,7 +10493,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B143" s="8">
         <v>46168.68407938657</v>
@@ -10439,16 +10505,16 @@
         <v>46206.48579032408</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I143" s="8">
         <v>46237</v>
@@ -10466,13 +10532,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10482,7 +10548,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B144" s="5">
         <v>46168.68408523148</v>
@@ -10494,16 +10560,16 @@
         <v>46206.48578297454</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I144" s="5">
         <v>46237</v>
@@ -10521,13 +10587,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10537,7 +10603,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B145" s="8">
         <v>46168.684089884264</v>
@@ -10549,16 +10615,16 @@
         <v>46206.48577649306</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I145" s="8">
         <v>46237</v>
@@ -10576,13 +10642,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10592,7 +10658,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B146" s="5">
         <v>46168.684094571756</v>
@@ -10604,16 +10670,16 @@
         <v>46204.893335671295</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I146" s="5">
         <v>46237</v>
@@ -10631,13 +10697,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10647,7 +10713,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B147" s="8">
         <v>46168.68414574074</v>
@@ -10659,16 +10725,16 @@
         <v>46206.486229999995</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I147" s="8">
         <v>46239</v>
@@ -10686,13 +10752,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q147" s="8">
         <v>46239</v>
@@ -10712,7 +10778,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B148" s="5">
         <v>46168.68415105324</v>
@@ -10724,16 +10790,16 @@
         <v>46211.838432476856</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I148" s="5">
         <v>46239</v>
@@ -10751,13 +10817,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10767,7 +10833,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B149" s="8">
         <v>46168.68415587963</v>
@@ -10779,16 +10845,16 @@
         <v>46211.83844157407</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I149" s="8">
         <v>46239</v>
@@ -10806,13 +10872,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10822,7 +10888,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B150" s="5">
         <v>46168.68416068287</v>
@@ -10834,16 +10900,16 @@
         <v>46211.83843866899</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I150" s="5">
         <v>46239</v>
@@ -10861,13 +10927,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10877,7 +10943,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B151" s="8">
         <v>46168.68416431713</v>
@@ -10889,16 +10955,16 @@
         <v>46211.83844565973</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I151" s="8">
         <v>46239</v>
@@ -10916,13 +10982,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10932,7 +10998,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B152" s="5">
         <v>46168.68416798611</v>
@@ -10944,16 +11010,16 @@
         <v>46211.83845115741</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I152" s="5">
         <v>46239</v>
@@ -10971,13 +11037,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10987,7 +11053,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B153" s="8">
         <v>46168.684183460646</v>
@@ -10999,7 +11065,7 @@
         <v>46211.832724733795</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -11023,7 +11089,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -11040,7 +11106,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B154" s="5">
         <v>46168.68418700232</v>
@@ -11052,16 +11118,16 @@
         <v>46211.8327003125</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I154" s="5">
         <v>46240</v>
@@ -11079,13 +11145,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q154" s="5">
         <v>46240</v>
@@ -11105,7 +11171,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B155" s="8">
         <v>46168.68419359953</v>
@@ -11117,16 +11183,16 @@
         <v>46211.831112581014</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I155" s="8">
         <v>46240</v>
@@ -11144,13 +11210,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -11160,7 +11226,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B156" s="5">
         <v>46168.68419834491</v>
@@ -11172,16 +11238,16 @@
         <v>46211.83112387732</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I156" s="5">
         <v>46240</v>
@@ -11199,13 +11265,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -11215,7 +11281,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B157" s="8">
         <v>46168.684202777775</v>
@@ -11227,16 +11293,16 @@
         <v>46211.83112878472</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I157" s="8">
         <v>46240</v>
@@ -11254,13 +11320,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -11270,7 +11336,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B158" s="5">
         <v>46168.68420710648</v>
@@ -11282,16 +11348,16 @@
         <v>46211.83116206019</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I158" s="5">
         <v>46240</v>
@@ -11309,13 +11375,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -11325,7 +11391,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B159" s="8">
         <v>46168.68421127315</v>
@@ -11337,16 +11403,16 @@
         <v>46211.83117125</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I159" s="8">
         <v>46240</v>
@@ -11364,13 +11430,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -11380,7 +11446,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B160" s="5">
         <v>46168.68422996528</v>
@@ -11392,16 +11458,16 @@
         <v>46211.83117747685</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I160" s="5">
         <v>46240</v>
@@ -11419,13 +11485,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11435,7 +11501,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B161" s="8">
         <v>46168.68423341435</v>
@@ -11447,16 +11513,16 @@
         <v>46211.831204988426</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I161" s="8">
         <v>46240</v>
@@ -11474,13 +11540,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O161" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11490,7 +11556,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B162" s="5">
         <v>46168.684237037036</v>
@@ -11502,16 +11568,16 @@
         <v>46211.83121074074</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I162" s="5">
         <v>46240</v>
@@ -11529,13 +11595,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11545,7 +11611,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B163" s="8">
         <v>46168.68424059028</v>
@@ -11557,16 +11623,16 @@
         <v>46211.83121682871</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I163" s="8">
         <v>46240</v>
@@ -11584,13 +11650,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11600,7 +11666,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B164" s="5">
         <v>46168.68424420139</v>
@@ -11612,16 +11678,16 @@
         <v>46211.83124355324</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I164" s="5">
         <v>46240</v>
@@ -11639,13 +11705,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11655,7 +11721,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B165" s="8">
         <v>46168.68424778935</v>
@@ -11667,16 +11733,16 @@
         <v>46211.83125052083</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="I165" s="8">
         <v>46240</v>
@@ -11694,13 +11760,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11710,7 +11776,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B166" s="5">
         <v>46168.68425820602</v>
@@ -11722,16 +11788,16 @@
         <v>46211.83114409722</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I166" s="6"/>
       <c r="J166" s="5">
@@ -11747,13 +11813,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q166" s="5">
         <v>46241</v>
@@ -11768,12 +11834,12 @@
         <v>1</v>
       </c>
       <c r="U166" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B167" s="8">
         <v>46168.68426255787</v>
@@ -11785,16 +11851,16 @@
         <v>46211.83112083333</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H167" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I167" s="9"/>
       <c r="J167" s="8">
@@ -11810,13 +11876,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11826,7 +11892,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B168" s="5">
         <v>46168.68426704861</v>
@@ -11838,16 +11904,16 @@
         <v>46211.83112822917</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I168" s="6"/>
       <c r="J168" s="5">
@@ -11863,13 +11929,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11879,7 +11945,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B169" s="8">
         <v>46168.68427162037</v>
@@ -11891,16 +11957,16 @@
         <v>46211.83113427083</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I169" s="9"/>
       <c r="J169" s="8">
@@ -11916,13 +11982,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11932,7 +11998,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B170" s="5">
         <v>46168.68427627315</v>
@@ -11944,16 +12010,16 @@
         <v>46211.83116765047</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
@@ -11969,13 +12035,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11985,7 +12051,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B171" s="8">
         <v>46168.68428068287</v>
@@ -11997,16 +12063,16 @@
         <v>46211.831175914354</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H171" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I171" s="9"/>
       <c r="J171" s="8">
@@ -12022,13 +12088,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -12038,7 +12104,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B172" s="5">
         <v>46168.684336226856</v>
@@ -12050,16 +12116,16 @@
         <v>46211.83118184027</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
@@ -12075,13 +12141,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -12091,7 +12157,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B173" s="8">
         <v>46168.68434010417</v>
@@ -12103,16 +12169,16 @@
         <v>46211.831210868055</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H173" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I173" s="9"/>
       <c r="J173" s="8">
@@ -12128,13 +12194,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -12144,7 +12210,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B174" s="5">
         <v>46168.68434423611</v>
@@ -12156,16 +12222,16 @@
         <v>46211.83121509259</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I174" s="6"/>
       <c r="J174" s="5">
@@ -12181,13 +12247,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -12197,7 +12263,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B175" s="8">
         <v>46168.684348263894</v>
@@ -12209,16 +12275,16 @@
         <v>46211.831221932865</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H175" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I175" s="9"/>
       <c r="J175" s="8">
@@ -12234,13 +12300,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -12250,7 +12316,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B176" s="5">
         <v>46168.68435202546</v>
@@ -12262,16 +12328,16 @@
         <v>46211.831248912036</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I176" s="6"/>
       <c r="J176" s="5">
@@ -12287,13 +12353,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -12303,7 +12369,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B177" s="8">
         <v>46168.68435652778</v>
@@ -12315,16 +12381,16 @@
         <v>46211.831259189814</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H177" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I177" s="9"/>
       <c r="J177" s="8">
@@ -12340,13 +12406,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -12356,7 +12422,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B178" s="5">
         <v>46168.68437314815</v>
@@ -12368,16 +12434,16 @@
         <v>46209.715354976855</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -12393,13 +12459,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Q178" s="5">
         <v>46244</v>
@@ -12419,7 +12485,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B179" s="8">
         <v>46168.68437847222</v>
@@ -12431,16 +12497,16 @@
         <v>46209.71550439815</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H179" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I179" s="8">
         <v>46244</v>
@@ -12458,13 +12524,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
@@ -12474,7 +12540,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B180" s="5">
         <v>46168.68438821759</v>
@@ -12486,16 +12552,16 @@
         <v>46209.7156449537</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I180" s="5">
         <v>46244</v>
@@ -12513,13 +12579,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12529,7 +12595,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B181" s="8">
         <v>46168.684394537035</v>
@@ -12541,16 +12607,16 @@
         <v>46209.715759733794</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H181" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I181" s="8">
         <v>46244</v>
@@ -12568,13 +12634,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12584,7 +12650,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B182" s="5">
         <v>46168.68439944445</v>
@@ -12596,16 +12662,16 @@
         <v>46209.71583459491</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I182" s="5">
         <v>46244</v>
@@ -12623,13 +12689,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12639,7 +12705,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B183" s="8">
         <v>46168.684404375</v>
@@ -12651,16 +12717,16 @@
         <v>46209.71610449074</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H183" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I183" s="8">
         <v>46244</v>
@@ -12678,13 +12744,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12694,7 +12760,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B184" s="5">
         <v>46168.6844190625</v>
@@ -12706,16 +12772,16 @@
         <v>46211.83066165509</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I184" s="5">
         <v>46244</v>
@@ -12733,13 +12799,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12749,7 +12815,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B185" s="8">
         <v>46168.68442277778</v>
@@ -12761,16 +12827,16 @@
         <v>46211.83081103009</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H185" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I185" s="8">
         <v>46244</v>
@@ -12788,13 +12854,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12804,7 +12870,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B186" s="5">
         <v>46168.68442653935</v>
@@ -12816,16 +12882,16 @@
         <v>46211.83088054398</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I186" s="5">
         <v>46244</v>
@@ -12843,13 +12909,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12859,7 +12925,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B187" s="8">
         <v>46168.684429988425</v>
@@ -12871,16 +12937,16 @@
         <v>46211.83097425926</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H187" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I187" s="8">
         <v>46244</v>
@@ -12898,13 +12964,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12914,7 +12980,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B188" s="5">
         <v>46168.68443359954</v>
@@ -12926,16 +12992,16 @@
         <v>46211.83105417824</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I188" s="5">
         <v>46244</v>
@@ -12953,13 +13019,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12969,7 +13035,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B189" s="8">
         <v>46168.68443729167</v>
@@ -12981,16 +13047,16 @@
         <v>46211.8311371412</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I189" s="8">
         <v>46244</v>
@@ -13008,13 +13074,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -13024,7 +13090,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B190" s="5">
         <v>46168.6844840625</v>
@@ -13036,16 +13102,16 @@
         <v>46211.830323738424</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I190" s="5">
         <v>46245</v>
@@ -13063,13 +13129,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="Q190" s="5">
         <v>46245</v>
@@ -13084,12 +13150,12 @@
         <v>1</v>
       </c>
       <c r="U190" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B191" s="8">
         <v>46168.68449130787</v>
@@ -13101,16 +13167,16 @@
         <v>46211.830295844906</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="8">
@@ -13126,13 +13192,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -13142,7 +13208,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B192" s="5">
         <v>46168.68449590278</v>
@@ -13154,16 +13220,16 @@
         <v>46211.83029662037</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -13179,13 +13245,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -13195,7 +13261,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B193" s="8">
         <v>46168.68450027778</v>
@@ -13207,16 +13273,16 @@
         <v>46211.83029733796</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="8">
@@ -13232,13 +13298,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -13248,7 +13314,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B194" s="5">
         <v>46168.68450480324</v>
@@ -13260,16 +13326,16 @@
         <v>46211.83029778935</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="5">
@@ -13285,13 +13351,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -13301,7 +13367,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B195" s="8">
         <v>46168.68450934028</v>
@@ -13313,16 +13379,16 @@
         <v>46211.83029865741</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I195" s="9"/>
       <c r="J195" s="8">
@@ -13338,13 +13404,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -13354,7 +13420,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B196" s="5">
         <v>46168.684523414355</v>
@@ -13366,16 +13432,16 @@
         <v>46211.83029902777</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -13391,13 +13457,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -13407,7 +13473,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B197" s="8">
         <v>46168.6845271412</v>
@@ -13419,16 +13485,16 @@
         <v>46211.83029945602</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I197" s="9"/>
       <c r="J197" s="8">
@@ -13444,13 +13510,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -13460,7 +13526,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B198" s="5">
         <v>46168.68453511574</v>
@@ -13472,16 +13538,16 @@
         <v>46211.830299953705</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13497,13 +13563,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13513,7 +13579,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B199" s="8">
         <v>46168.68453863426</v>
@@ -13525,16 +13591,16 @@
         <v>46211.83030041667</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I199" s="9"/>
       <c r="J199" s="8">
@@ -13550,13 +13616,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13566,7 +13632,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B200" s="5">
         <v>46168.68454210648</v>
@@ -13578,16 +13644,16 @@
         <v>46211.830300891204</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13603,13 +13669,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13619,7 +13685,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B201" s="8">
         <v>46168.684545578704</v>
@@ -13631,16 +13697,16 @@
         <v>46211.83030140046</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="8">
@@ -13656,13 +13722,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O201" s="9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13672,7 +13738,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B202" s="5">
         <v>46168.684555775464</v>
@@ -13682,7 +13748,7 @@
         <v>46168.8618759838</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>25</v>
@@ -13706,7 +13772,7 @@
         <v>26</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>26</v>
@@ -13719,7 +13785,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B203" s="8">
         <v>46168.6845594676</v>
@@ -13729,16 +13795,16 @@
         <v>46211.83025064815</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="I203" s="8">
         <v>46246</v>
@@ -13756,13 +13822,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Q203" s="8">
         <v>46246</v>
@@ -13777,12 +13843,12 @@
         <v>0</v>
       </c>
       <c r="U203" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B204" s="5">
         <v>46168.68456425926</v>
@@ -13792,16 +13858,16 @@
         <v>46211.83025032407</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I204" s="5">
         <v>46246</v>
@@ -13819,13 +13885,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="Q204" s="5">
         <v>46246</v>
@@ -13840,12 +13906,12 @@
         <v>0</v>
       </c>
       <c r="U204" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B205" s="8">
         <v>46168.68457049769</v>
@@ -13855,7 +13921,7 @@
         <v>46168.86234542824</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>25</v>
@@ -13879,7 +13945,7 @@
         <v>26</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P205" s="9" t="s">
         <v>26</v>
@@ -13893,12 +13959,12 @@
         <v>0</v>
       </c>
       <c r="U205" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B206" s="5">
         <v>46168.68457415509</v>
@@ -13908,16 +13974,16 @@
         <v>46211.830253541666</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G206" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H206" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I206" s="5">
         <v>46246</v>
@@ -13935,13 +14001,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="Q206" s="5">
         <v>46246</v>
@@ -13956,12 +14022,12 @@
         <v>0</v>
       </c>
       <c r="U206" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B207" s="8">
         <v>46168.68457920139</v>
@@ -13971,16 +14037,16 @@
         <v>46168.868795937495</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G207" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H207" s="9" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I207" s="8">
         <v>46255</v>
@@ -13998,13 +14064,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="Q207" s="8">
         <v>46255</v>
@@ -14019,7 +14085,7 @@
         <v>0</v>
       </c>
       <c r="U207" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -7917,7 +7917,7 @@
         <v>46197.85007665509</v>
       </c>
       <c r="D98" s="5">
-        <v>46197.85243150463</v>
+        <v>46216.17956907407</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>300</v>
@@ -7961,8 +7961,8 @@
       <c r="R98" s="5">
         <v>46223</v>
       </c>
-      <c r="S98" s="10" t="s">
-        <v>32</v>
+      <c r="S98" s="11" t="s">
+        <v>158</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -8257,7 +8257,7 @@
         <v>46204.89009226851</v>
       </c>
       <c r="D104" s="5">
-        <v>46204.8901028588</v>
+        <v>46217.19617538195</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>314</v>
@@ -8301,8 +8301,8 @@
       <c r="R104" s="5">
         <v>46224</v>
       </c>
-      <c r="S104" s="10" t="s">
-        <v>32</v>
+      <c r="S104" s="11" t="s">
+        <v>158</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="536">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -408,9 +408,6 @@
     <t>propuesta nucleo rodete ot 4335 - 4337 -4339</t>
   </si>
   <si>
-    <t>benjamin.bustos@zitron.com</t>
-  </si>
-  <si>
     <t>Propuesta compras:,Generación OC Rodete ot 4335 - 4337 -4339</t>
   </si>
   <si>
@@ -418,12 +415,6 @@
   </si>
   <si>
     <t>propuesta Corte Laser ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>hugo isla martinez</t>
-  </si>
-  <si>
-    <t>hugo.isla@zitron.com</t>
   </si>
   <si>
     <t>check planos</t>
@@ -3676,11 +3667,9 @@
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H26" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H26" s="6"/>
       <c r="I26" s="5">
         <v>46157</v>
       </c>
@@ -3703,7 +3692,7 @@
         <v>81</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3723,7 +3712,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B27" s="8">
         <v>46168.68321476852</v>
@@ -3735,17 +3724,15 @@
         <v>46197.8530077662</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H27" s="9" t="s">
-        <v>103</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H27" s="9"/>
       <c r="I27" s="8">
         <v>46189</v>
       </c>
@@ -3765,10 +3752,10 @@
         <v>88</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="Q27" s="8">
         <v>46189</v>
@@ -3777,7 +3764,7 @@
         <v>46190</v>
       </c>
       <c r="S27" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T27" s="9">
         <v>1</v>
@@ -3788,7 +3775,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B28" s="5">
         <v>46168.68321959491</v>
@@ -3800,17 +3787,15 @@
         <v>46196.64668813658</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>103</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H28" s="6"/>
       <c r="I28" s="5">
         <v>46189</v>
       </c>
@@ -3830,10 +3815,10 @@
         <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="Q28" s="5">
         <v>46189</v>
@@ -3842,7 +3827,7 @@
         <v>46190</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
@@ -3853,7 +3838,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B29" s="8">
         <v>46168.68322341435</v>
@@ -3865,17 +3850,15 @@
         <v>46196.647418912034</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>102</v>
-      </c>
-      <c r="H29" s="9" t="s">
-        <v>103</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H29" s="9"/>
       <c r="I29" s="8">
         <v>46189</v>
       </c>
@@ -3895,10 +3878,10 @@
         <v>88</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="Q29" s="8">
         <v>46189</v>
@@ -3907,7 +3890,7 @@
         <v>46190</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3918,7 +3901,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B30" s="5">
         <v>46168.683227245376</v>
@@ -3930,17 +3913,15 @@
         <v>46196.64801533565</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>103</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H30" s="6"/>
       <c r="I30" s="5">
         <v>46189</v>
       </c>
@@ -3960,10 +3941,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q30" s="5">
         <v>46189</v>
@@ -3972,7 +3953,7 @@
         <v>46190</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3983,7 +3964,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B31" s="8">
         <v>46168.683231365736</v>
@@ -3995,7 +3976,7 @@
         <v>46193.553499305555</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -4028,7 +4009,7 @@
         <v>51</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q31" s="8">
         <v>46157</v>
@@ -4048,7 +4029,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5">
         <v>46168.682992511574</v>
@@ -4060,7 +4041,7 @@
         <v>46205.61594793982</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -4084,7 +4065,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -4101,7 +4082,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="B33" s="8">
         <v>46168.68327652778</v>
@@ -4113,16 +4094,16 @@
         <v>46195.928396574076</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I33" s="8">
         <v>46161</v>
@@ -4140,13 +4121,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q33" s="8">
         <v>46161</v>
@@ -4166,7 +4147,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B34" s="5">
         <v>46168.68328149305</v>
@@ -4178,16 +4159,16 @@
         <v>46195.9258303588</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -4205,13 +4186,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4222,12 +4203,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B35" s="8">
         <v>46168.68328653935</v>
@@ -4239,16 +4220,16 @@
         <v>46195.928370243055</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I35" s="8">
         <v>46164</v>
@@ -4266,13 +4247,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -4283,12 +4264,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B36" s="5">
         <v>46168.68329140046</v>
@@ -4300,16 +4281,16 @@
         <v>46185.182775243054</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I36" s="5">
         <v>46161</v>
@@ -4327,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q36" s="5">
         <v>46161</v>
@@ -4342,7 +4323,7 @@
         <v>46184</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4353,7 +4334,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B37" s="8">
         <v>46168.68329584491</v>
@@ -4365,16 +4346,16 @@
         <v>46184.70350368056</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I37" s="8">
         <v>46161</v>
@@ -4392,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>97</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -4409,12 +4390,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B38" s="5">
         <v>46168.68330070602</v>
@@ -4426,16 +4407,16 @@
         <v>46184.703557789355</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I38" s="5">
         <v>46164</v>
@@ -4453,13 +4434,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="O38" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="O38" s="6" t="s">
-        <v>138</v>
-      </c>
       <c r="P38" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4470,12 +4451,12 @@
         <v>0</v>
       </c>
       <c r="U38" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B39" s="8">
         <v>46168.68330542824</v>
@@ -4487,16 +4468,16 @@
         <v>46205.60819122686</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I39" s="8">
         <v>46161</v>
@@ -4514,13 +4495,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q39" s="8">
         <v>46161</v>
@@ -4529,7 +4510,7 @@
         <v>46198</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4540,7 +4521,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B40" s="5">
         <v>46168.683310092594</v>
@@ -4552,16 +4533,16 @@
         <v>46195.92587128472</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I40" s="5">
         <v>46161</v>
@@ -4579,13 +4560,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4596,12 +4577,12 @@
         <v>0</v>
       </c>
       <c r="U40" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B41" s="8">
         <v>46168.68331519676</v>
@@ -4613,16 +4594,16 @@
         <v>46205.60793128472</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I41" s="8">
         <v>46170</v>
@@ -4640,13 +4621,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="O41" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="O41" s="9" t="s">
-        <v>147</v>
-      </c>
       <c r="P41" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4657,12 +4638,12 @@
         <v>0</v>
       </c>
       <c r="U41" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B42" s="5">
         <v>46168.68332027778</v>
@@ -4674,16 +4655,16 @@
         <v>46195.92587850694</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I42" s="5">
         <v>46170</v>
@@ -4701,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="O42" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="O42" s="6" t="s">
-        <v>147</v>
-      </c>
       <c r="P42" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4718,12 +4699,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B43" s="8">
         <v>46168.68332520833</v>
@@ -4735,16 +4716,16 @@
         <v>46212.17842539352</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I43" s="8">
         <v>46161</v>
@@ -4762,10 +4743,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4777,7 +4758,7 @@
         <v>46219</v>
       </c>
       <c r="S43" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4788,7 +4769,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46168.68332880787</v>
@@ -4800,16 +4781,16 @@
         <v>46195.92577891204</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I44" s="5">
         <v>46161</v>
@@ -4827,13 +4808,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4843,7 +4824,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8">
         <v>46168.683333113426</v>
@@ -4855,16 +4836,16 @@
         <v>46195.92857017361</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="I45" s="8">
         <v>46171</v>
@@ -4882,13 +4863,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4898,7 +4879,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46168.683337291666</v>
@@ -4910,16 +4891,16 @@
         <v>46204.1978837037</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I46" s="5">
         <v>46191</v>
@@ -4937,13 +4918,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="Q46" s="5">
         <v>46191</v>
@@ -4952,7 +4933,7 @@
         <v>46203</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4963,7 +4944,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46168.68334179398</v>
@@ -4975,16 +4956,16 @@
         <v>46199.564988564816</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I47" s="8">
         <v>46191</v>
@@ -5002,13 +4983,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -5019,12 +5000,12 @@
         <v>0</v>
       </c>
       <c r="U47" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46168.68334684028</v>
@@ -5036,16 +5017,16 @@
         <v>46199.5650378125</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I48" s="5">
         <v>46195</v>
@@ -5063,13 +5044,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -5080,12 +5061,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B49" s="8">
         <v>46168.68335195602</v>
@@ -5097,16 +5078,16 @@
         <v>46204.19788363426</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I49" s="8">
         <v>46191</v>
@@ -5124,10 +5105,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -5139,7 +5120,7 @@
         <v>46203</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -5150,7 +5131,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46168.68335582176</v>
@@ -5162,16 +5143,16 @@
         <v>46199.56512275463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I50" s="5">
         <v>46191</v>
@@ -5189,13 +5170,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="P50" s="6" t="s">
         <v>176</v>
-      </c>
-      <c r="O50" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="P50" s="6" t="s">
-        <v>179</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -5205,7 +5186,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46168.683360428244</v>
@@ -5217,16 +5198,16 @@
         <v>46199.56520053241</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I51" s="8">
         <v>46195</v>
@@ -5244,13 +5225,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5260,7 +5241,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46168.68336471065</v>
@@ -5272,16 +5253,16 @@
         <v>46205.61765122685</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -5299,10 +5280,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -5325,7 +5306,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46168.68337377315</v>
@@ -5337,16 +5318,16 @@
         <v>46204.601485555555</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I53" s="8">
         <v>46191</v>
@@ -5364,13 +5345,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5380,7 +5361,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46168.683378194444</v>
@@ -5392,16 +5373,16 @@
         <v>46204.601540787036</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="I54" s="5">
         <v>46202</v>
@@ -5419,13 +5400,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5435,7 +5416,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B55" s="8">
         <v>46168.68338271991</v>
@@ -5447,16 +5428,16 @@
         <v>46205.644352627314</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I55" s="8">
         <v>46231</v>
@@ -5474,10 +5455,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5490,7 +5471,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46168.683385868055</v>
@@ -5502,16 +5483,16 @@
         <v>46204.19788391204</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I56" s="5">
         <v>46191</v>
@@ -5529,10 +5510,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5544,7 +5525,7 @@
         <v>46203</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5555,7 +5536,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46168.68343064815</v>
@@ -5567,16 +5548,16 @@
         <v>46199.56535409723</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I57" s="8">
         <v>46191</v>
@@ -5594,13 +5575,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="O57" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="P57" s="9" t="s">
         <v>198</v>
-      </c>
-      <c r="O57" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="P57" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5610,7 +5591,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46168.683436956024</v>
@@ -5622,16 +5603,16 @@
         <v>46199.56544034722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="I58" s="5">
         <v>46195</v>
@@ -5649,13 +5630,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5665,7 +5646,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B59" s="8">
         <v>46168.68344221065</v>
@@ -5675,7 +5656,7 @@
         <v>46210.52421333334</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5699,7 +5680,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5714,7 +5695,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46168.683445787035</v>
@@ -5726,16 +5707,16 @@
         <v>46184.518844583334</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I60" s="5">
         <v>46167</v>
@@ -5753,13 +5734,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="5">
         <v>46167</v>
@@ -5768,7 +5749,7 @@
         <v>46171</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5779,7 +5760,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B61" s="8">
         <v>46168.6865996875</v>
@@ -5791,16 +5772,16 @@
         <v>46184.51878665509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I61" s="8">
         <v>46167</v>
@@ -5818,13 +5799,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5834,7 +5815,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
         <v>46168.68683460648</v>
@@ -5846,16 +5827,16 @@
         <v>46184.518791319446</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I62" s="5">
         <v>46167</v>
@@ -5873,13 +5854,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5889,7 +5870,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B63" s="8">
         <v>46168.686918437495</v>
@@ -5901,16 +5882,16 @@
         <v>46184.51879930556</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I63" s="8">
         <v>46167</v>
@@ -5928,13 +5909,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5944,7 +5925,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B64" s="5">
         <v>46168.687254143515</v>
@@ -5956,16 +5937,16 @@
         <v>46184.5188068287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I64" s="5">
         <v>46167</v>
@@ -5983,13 +5964,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5999,7 +5980,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B65" s="8">
         <v>46168.68731635417</v>
@@ -6011,16 +5992,16 @@
         <v>46184.51881454861</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I65" s="8">
         <v>46167</v>
@@ -6038,13 +6019,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -6054,7 +6035,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B66" s="5">
         <v>46168.68345142361</v>
@@ -6066,16 +6047,16 @@
         <v>46190.605242708334</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I66" s="5">
         <v>46181</v>
@@ -6093,13 +6074,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="Q66" s="5">
         <v>46181</v>
@@ -6108,7 +6089,7 @@
         <v>46185</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -6119,7 +6100,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B67" s="8">
         <v>46168.68857346065</v>
@@ -6131,16 +6112,16 @@
         <v>46190.60518608797</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I67" s="8">
         <v>46181</v>
@@ -6158,13 +6139,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="O67" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="P67" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="O67" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>228</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -6174,7 +6155,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B68" s="5">
         <v>46168.688608275465</v>
@@ -6186,16 +6167,16 @@
         <v>46190.60519502315</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I68" s="5">
         <v>46181</v>
@@ -6213,13 +6194,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="O68" s="6" t="s">
-        <v>227</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6229,7 +6210,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="B69" s="8">
         <v>46168.68864659722</v>
@@ -6241,16 +6222,16 @@
         <v>46190.605203761574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I69" s="8">
         <v>46181</v>
@@ -6268,13 +6249,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6284,7 +6265,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B70" s="5">
         <v>46168.68868637731</v>
@@ -6296,16 +6277,16 @@
         <v>46190.605208946756</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I70" s="5">
         <v>46181</v>
@@ -6323,13 +6304,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O70" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="P70" s="6" t="s">
         <v>231</v>
-      </c>
-      <c r="P70" s="6" t="s">
-        <v>234</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6339,7 +6320,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B71" s="8">
         <v>46168.68871934028</v>
@@ -6351,16 +6332,16 @@
         <v>46190.60521709491</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I71" s="8">
         <v>46181</v>
@@ -6378,13 +6359,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -6394,7 +6375,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46168.68345790509</v>
@@ -6406,16 +6387,16 @@
         <v>46190.6054244213</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I72" s="5">
         <v>46188</v>
@@ -6433,13 +6414,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="Q72" s="5">
         <v>46188</v>
@@ -6448,7 +6429,7 @@
         <v>46188</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6459,7 +6440,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B73" s="8">
         <v>46168.68880178241</v>
@@ -6471,16 +6452,16 @@
         <v>46190.60536361111</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -6498,13 +6479,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6514,7 +6495,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B74" s="5">
         <v>46168.68883857639</v>
@@ -6526,16 +6507,16 @@
         <v>46190.605368206016</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I74" s="5">
         <v>46188</v>
@@ -6553,13 +6534,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6569,7 +6550,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B75" s="8">
         <v>46168.688875775464</v>
@@ -6581,16 +6562,16 @@
         <v>46190.605373530096</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I75" s="8">
         <v>46188</v>
@@ -6608,13 +6589,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6624,7 +6605,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B76" s="5">
         <v>46168.6889172338</v>
@@ -6636,16 +6617,16 @@
         <v>46190.60539957176</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I76" s="5">
         <v>46188</v>
@@ -6663,13 +6644,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6679,7 +6660,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B77" s="8">
         <v>46168.688956620375</v>
@@ -6691,16 +6672,16 @@
         <v>46190.60538814815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="I77" s="8">
         <v>46188</v>
@@ -6718,10 +6699,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6734,7 +6715,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B78" s="5">
         <v>46168.683480625</v>
@@ -6746,16 +6727,16 @@
         <v>46211.83847391204</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6771,10 +6752,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6797,7 +6778,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B79" s="8">
         <v>46168.683484629626</v>
@@ -6809,16 +6790,16 @@
         <v>46211.83842664352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I79" s="8">
         <v>46238</v>
@@ -6836,13 +6817,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6852,7 +6833,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
         <v>46168.683488877316</v>
@@ -6864,16 +6845,16 @@
         <v>46211.83843200232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I80" s="5">
         <v>46238</v>
@@ -6891,13 +6872,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6907,7 +6888,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B81" s="8">
         <v>46168.68349300926</v>
@@ -6919,16 +6900,16 @@
         <v>46211.83843496528</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I81" s="8">
         <v>46238</v>
@@ -6946,13 +6927,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6962,7 +6943,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B82" s="5">
         <v>46168.6834959375</v>
@@ -6974,16 +6955,16 @@
         <v>46211.83844040509</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I82" s="5">
         <v>46238</v>
@@ -7001,13 +6982,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -7017,7 +6998,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B83" s="8">
         <v>46168.68349899305</v>
@@ -7029,16 +7010,16 @@
         <v>46211.83844619213</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="I83" s="8">
         <v>46238</v>
@@ -7056,13 +7037,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -7072,7 +7053,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B84" s="5">
         <v>46168.68351101852</v>
@@ -7084,7 +7065,7 @@
         <v>46205.618076087965</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -7108,7 +7089,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -7125,7 +7106,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B85" s="8">
         <v>46168.68351447917</v>
@@ -7137,16 +7118,16 @@
         <v>46206.18878055556</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I85" s="8">
         <v>46204</v>
@@ -7164,13 +7145,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="Q85" s="8">
         <v>46204</v>
@@ -7179,7 +7160,7 @@
         <v>46205</v>
       </c>
       <c r="S85" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -7190,7 +7171,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B86" s="5">
         <v>46168.68352011574</v>
@@ -7202,16 +7183,16 @@
         <v>46210.20097684028</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I86" s="5">
         <v>46206</v>
@@ -7229,13 +7210,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="Q86" s="5">
         <v>46206</v>
@@ -7244,7 +7225,7 @@
         <v>46209</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -7255,7 +7236,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B87" s="8">
         <v>46168.68352736111</v>
@@ -7267,16 +7248,16 @@
         <v>46206.18878028935</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -7294,13 +7275,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -7309,7 +7290,7 @@
         <v>46205</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -7320,7 +7301,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
         <v>46168.68353292824</v>
@@ -7332,16 +7313,16 @@
         <v>46210.20097686343</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I88" s="5">
         <v>46206</v>
@@ -7359,13 +7340,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q88" s="5">
         <v>46206</v>
@@ -7374,7 +7355,7 @@
         <v>46209</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -7385,7 +7366,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B89" s="8">
         <v>46168.68353787037</v>
@@ -7397,16 +7378,16 @@
         <v>46206.1887803125</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7424,13 +7405,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="8">
         <v>46204</v>
@@ -7439,7 +7420,7 @@
         <v>46205</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T89" s="9">
         <v>1</v>
@@ -7450,7 +7431,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46168.68354247685</v>
@@ -7462,16 +7443,16 @@
         <v>46210.20097706019</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I90" s="5">
         <v>46206</v>
@@ -7489,13 +7470,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="Q90" s="5">
         <v>46206</v>
@@ -7504,7 +7485,7 @@
         <v>46209</v>
       </c>
       <c r="S90" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
@@ -7515,7 +7496,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B91" s="8">
         <v>46168.68354741899</v>
@@ -7527,7 +7508,7 @@
         <v>46211.83134737269</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>25</v>
@@ -7551,7 +7532,7 @@
         <v>26</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>26</v>
@@ -7568,7 +7549,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46168.68355052083</v>
@@ -7580,16 +7561,16 @@
         <v>46213.20753342593</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7607,13 +7588,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="5">
         <v>46210</v>
@@ -7622,7 +7603,7 @@
         <v>46212</v>
       </c>
       <c r="S92" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -7633,7 +7614,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B93" s="8">
         <v>46168.68356208333</v>
@@ -7645,16 +7626,16 @@
         <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I93" s="8">
         <v>46210</v>
@@ -7672,13 +7653,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7688,7 +7669,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B94" s="5">
         <v>46168.68356922454</v>
@@ -7700,16 +7681,16 @@
         <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7727,13 +7708,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7743,7 +7724,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="B95" s="8">
         <v>46168.683574780094</v>
@@ -7755,16 +7736,16 @@
         <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I95" s="8">
         <v>46210</v>
@@ -7782,13 +7763,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7798,7 +7779,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="B96" s="5">
         <v>46168.68358024306</v>
@@ -7810,16 +7791,16 @@
         <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7837,13 +7818,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7853,7 +7834,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="B97" s="8">
         <v>46168.68358578703</v>
@@ -7865,16 +7846,16 @@
         <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I97" s="8">
         <v>46210</v>
@@ -7892,13 +7873,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7908,7 +7889,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="B98" s="5">
         <v>46168.68365474537</v>
@@ -7920,16 +7901,16 @@
         <v>46216.17956907407</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I98" s="5">
         <v>46213</v>
@@ -7947,13 +7928,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q98" s="5">
         <v>46213</v>
@@ -7962,7 +7943,7 @@
         <v>46223</v>
       </c>
       <c r="S98" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
@@ -7973,7 +7954,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B99" s="8">
         <v>46168.683659965274</v>
@@ -7985,16 +7966,16 @@
         <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I99" s="8">
         <v>46213</v>
@@ -8012,13 +7993,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="O99" s="9" t="s">
         <v>300</v>
       </c>
-      <c r="O99" s="9" t="s">
-        <v>303</v>
-      </c>
       <c r="P99" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -8028,7 +8009,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B100" s="5">
         <v>46168.68366613426</v>
@@ -8040,16 +8021,16 @@
         <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I100" s="5">
         <v>46213</v>
@@ -8067,13 +8048,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="O100" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="O100" s="6" t="s">
+      <c r="P100" s="6" t="s">
         <v>303</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>306</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -8083,7 +8064,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="B101" s="8">
         <v>46168.683671921295</v>
@@ -8095,16 +8076,16 @@
         <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I101" s="8">
         <v>46213</v>
@@ -8122,13 +8103,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -8138,7 +8119,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B102" s="5">
         <v>46168.68367622685</v>
@@ -8150,16 +8131,16 @@
         <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I102" s="5">
         <v>46213</v>
@@ -8177,13 +8158,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8193,7 +8174,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="B103" s="8">
         <v>46168.683680069444</v>
@@ -8205,16 +8186,16 @@
         <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I103" s="8">
         <v>46213</v>
@@ -8232,13 +8213,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8248,7 +8229,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B104" s="5">
         <v>46168.68369409722</v>
@@ -8260,16 +8241,16 @@
         <v>46217.19617538195</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I104" s="5">
         <v>46224</v>
@@ -8287,13 +8268,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="Q104" s="5">
         <v>46224</v>
@@ -8302,7 +8283,7 @@
         <v>46224</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
@@ -8313,7 +8294,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B105" s="8">
         <v>46168.68369849537</v>
@@ -8325,16 +8306,16 @@
         <v>46204.890051967595</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I105" s="8">
         <v>46224</v>
@@ -8352,13 +8333,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
+        <v>311</v>
+      </c>
+      <c r="O105" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="P105" s="9" t="s">
         <v>314</v>
-      </c>
-      <c r="O105" s="9" t="s">
-        <v>303</v>
-      </c>
-      <c r="P105" s="9" t="s">
-        <v>317</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8368,7 +8349,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B106" s="5">
         <v>46168.683704490744</v>
@@ -8380,16 +8361,16 @@
         <v>46204.890058125005</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I106" s="5">
         <v>46224</v>
@@ -8407,13 +8388,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8423,7 +8404,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B107" s="8">
         <v>46168.683710150464</v>
@@ -8435,16 +8416,16 @@
         <v>46204.89006394676</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I107" s="8">
         <v>46224</v>
@@ -8462,13 +8443,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8478,7 +8459,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B108" s="5">
         <v>46168.68371309028</v>
@@ -8490,16 +8471,16 @@
         <v>46204.89006936342</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I108" s="5">
         <v>46224</v>
@@ -8517,13 +8498,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8533,7 +8514,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B109" s="8">
         <v>46168.68371646991</v>
@@ -8545,16 +8526,16 @@
         <v>46204.890080185185</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="I109" s="8">
         <v>46224</v>
@@ -8572,13 +8553,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8588,7 +8569,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B110" s="5">
         <v>46168.68373005787</v>
@@ -8600,7 +8581,7 @@
         <v>46211.830014363426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8624,7 +8605,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8641,7 +8622,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B111" s="8">
         <v>46168.68373365741</v>
@@ -8653,16 +8634,16 @@
         <v>46205.61049446759</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I111" s="8">
         <v>46185</v>
@@ -8680,13 +8661,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="Q111" s="8">
         <v>46185</v>
@@ -8695,7 +8676,7 @@
         <v>46185</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T111" s="9">
         <v>1</v>
@@ -8706,7 +8687,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B112" s="5">
         <v>46168.6837408912</v>
@@ -8718,16 +8699,16 @@
         <v>46205.61455358796</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8743,13 +8724,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="Q112" s="5">
         <v>46168</v>
@@ -8758,7 +8739,7 @@
         <v>46168</v>
       </c>
       <c r="S112" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T112" s="6">
         <v>1</v>
@@ -8769,7 +8750,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="B113" s="8">
         <v>46168.68374771991</v>
@@ -8781,16 +8762,16 @@
         <v>46205.6084347338</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I113" s="8">
         <v>46199</v>
@@ -8808,13 +8789,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="Q113" s="8">
         <v>46199</v>
@@ -8823,7 +8804,7 @@
         <v>46199</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8834,7 +8815,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="B114" s="5">
         <v>46168.68375502314</v>
@@ -8846,16 +8827,16 @@
         <v>46211.83000291667</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8873,13 +8854,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="Q114" s="5">
         <v>46232</v>
@@ -8899,7 +8880,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B115" s="8">
         <v>46168.6837971412</v>
@@ -8917,10 +8898,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I115" s="8">
         <v>46220</v>
@@ -8938,13 +8919,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="Q115" s="8">
         <v>46220</v>
@@ -8953,7 +8934,7 @@
         <v>46220</v>
       </c>
       <c r="S115" s="11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="T115" s="9">
         <v>1</v>
@@ -8964,7 +8945,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="B116" s="5">
         <v>46168.68381362269</v>
@@ -8974,7 +8955,7 @@
         <v>46206.48624146991</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8998,7 +8979,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -9013,7 +8994,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B117" s="8">
         <v>46168.68381783565</v>
@@ -9025,17 +9006,15 @@
         <v>46211.830007129625</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H117" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H117" s="9"/>
       <c r="I117" s="8">
         <v>46225</v>
       </c>
@@ -9052,13 +9031,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="Q117" s="8">
         <v>46225</v>
@@ -9078,7 +9057,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="B118" s="5">
         <v>46168.683825810185</v>
@@ -9090,17 +9069,15 @@
         <v>46211.82999423611</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H118" s="6"/>
       <c r="I118" s="5">
         <v>46231</v>
       </c>
@@ -9117,13 +9094,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="O118" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="O118" s="6" t="s">
-        <v>349</v>
-      </c>
       <c r="P118" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -9133,7 +9110,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B119" s="8">
         <v>46168.68383587963</v>
@@ -9145,17 +9122,15 @@
         <v>46211.82999525463</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H119" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H119" s="9"/>
       <c r="I119" s="8">
         <v>46231</v>
       </c>
@@ -9172,13 +9147,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -9188,7 +9163,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="B120" s="5">
         <v>46168.68384034722</v>
@@ -9200,17 +9175,15 @@
         <v>46204.89052016204</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H120" s="6"/>
       <c r="I120" s="5">
         <v>46231</v>
       </c>
@@ -9227,13 +9200,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -9243,7 +9216,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="B121" s="8">
         <v>46168.683844074076</v>
@@ -9255,17 +9228,15 @@
         <v>46204.89050689815</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H121" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H121" s="9"/>
       <c r="I121" s="8">
         <v>46231</v>
       </c>
@@ -9282,13 +9253,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9298,7 +9269,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="B122" s="5">
         <v>46168.683847673616</v>
@@ -9310,17 +9281,15 @@
         <v>46204.890087210646</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H122" s="6"/>
       <c r="I122" s="5">
         <v>46231</v>
       </c>
@@ -9337,13 +9306,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9353,7 +9322,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B123" s="8">
         <v>46168.683862453705</v>
@@ -9365,17 +9334,15 @@
         <v>46204.891766898145</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H123" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H123" s="9"/>
       <c r="I123" s="8">
         <v>46232</v>
       </c>
@@ -9392,13 +9359,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="Q123" s="8">
         <v>46232</v>
@@ -9418,7 +9385,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B124" s="5">
         <v>46168.683867141204</v>
@@ -9430,17 +9397,15 @@
         <v>46205.61454657407</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H124" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H124" s="6"/>
       <c r="I124" s="5">
         <v>46232</v>
       </c>
@@ -9457,13 +9422,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="P124" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="O124" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>361</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9473,7 +9438,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B125" s="8">
         <v>46168.683873368056</v>
@@ -9485,17 +9450,15 @@
         <v>46205.61454702546</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H125" s="9"/>
       <c r="I125" s="8">
         <v>46232</v>
       </c>
@@ -9512,13 +9475,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O125" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="P125" s="9" t="s">
         <v>360</v>
-      </c>
-      <c r="P125" s="9" t="s">
-        <v>363</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9528,7 +9491,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B126" s="5">
         <v>46168.68387903935</v>
@@ -9540,17 +9503,15 @@
         <v>46205.614544861106</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H126" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H126" s="6"/>
       <c r="I126" s="5">
         <v>46232</v>
       </c>
@@ -9567,13 +9528,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9583,7 +9544,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B127" s="8">
         <v>46168.683884618054</v>
@@ -9595,17 +9556,15 @@
         <v>46205.61454555555</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H127" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H127" s="9"/>
       <c r="I127" s="8">
         <v>46232</v>
       </c>
@@ -9622,13 +9581,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9638,7 +9597,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B128" s="5">
         <v>46168.68389033565</v>
@@ -9650,17 +9609,15 @@
         <v>46205.614546122684</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H128" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H128" s="6"/>
       <c r="I128" s="5">
         <v>46232</v>
       </c>
@@ -9677,13 +9634,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9693,7 +9650,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="B129" s="8">
         <v>46168.68391289352</v>
@@ -9705,17 +9662,15 @@
         <v>46204.89299085648</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H129" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H129" s="9"/>
       <c r="I129" s="8">
         <v>46233</v>
       </c>
@@ -9732,13 +9687,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="Q129" s="8">
         <v>46233</v>
@@ -9758,7 +9713,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B130" s="5">
         <v>46168.68391818287</v>
@@ -9770,17 +9725,15 @@
         <v>46205.6085181713</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H130" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H130" s="6"/>
       <c r="I130" s="5">
         <v>46233</v>
       </c>
@@ -9797,13 +9750,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="O130" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="P130" s="6" t="s">
         <v>373</v>
-      </c>
-      <c r="O130" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="P130" s="6" t="s">
-        <v>376</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9813,7 +9766,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B131" s="8">
         <v>46168.68393068287</v>
@@ -9825,17 +9778,15 @@
         <v>46205.60851520833</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H131" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H131" s="9"/>
       <c r="I131" s="8">
         <v>46233</v>
       </c>
@@ -9852,13 +9803,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9868,7 +9819,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B132" s="5">
         <v>46168.68393770834</v>
@@ -9880,17 +9831,15 @@
         <v>46205.608516168984</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H132" s="6"/>
       <c r="I132" s="5">
         <v>46233</v>
       </c>
@@ -9907,13 +9856,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9923,7 +9872,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B133" s="8">
         <v>46168.6839434375</v>
@@ -9935,17 +9884,15 @@
         <v>46205.608518877314</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H133" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H133" s="9"/>
       <c r="I133" s="8">
         <v>46233</v>
       </c>
@@ -9962,13 +9909,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9978,7 +9925,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B134" s="5">
         <v>46168.68398528935</v>
@@ -9990,17 +9937,15 @@
         <v>46205.608517326385</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H134" s="6"/>
       <c r="I134" s="5">
         <v>46233</v>
       </c>
@@ -10017,13 +9962,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -10033,7 +9978,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B135" s="8">
         <v>46168.68401087963</v>
@@ -10045,17 +9990,15 @@
         <v>46204.893423761576</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H135" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H135" s="9"/>
       <c r="I135" s="8">
         <v>46234</v>
       </c>
@@ -10072,13 +10015,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="Q135" s="8">
         <v>46234</v>
@@ -10098,7 +10041,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B136" s="5">
         <v>46168.68401652778</v>
@@ -10110,17 +10053,15 @@
         <v>46205.60828351852</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H136" s="6"/>
       <c r="I136" s="5">
         <v>46234</v>
       </c>
@@ -10137,13 +10078,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="O136" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="P136" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="O136" s="6" t="s">
-        <v>390</v>
-      </c>
-      <c r="P136" s="6" t="s">
-        <v>391</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -10153,7 +10094,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B137" s="8">
         <v>46168.68402403935</v>
@@ -10165,17 +10106,15 @@
         <v>46205.60828236111</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H137" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H137" s="9"/>
       <c r="I137" s="8">
         <v>46234</v>
       </c>
@@ -10192,13 +10131,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="O137" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="P137" s="9" t="s">
         <v>388</v>
-      </c>
-      <c r="O137" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="P137" s="9" t="s">
-        <v>391</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -10208,7 +10147,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B138" s="5">
         <v>46168.68403127315</v>
@@ -10220,17 +10159,15 @@
         <v>46205.608284375005</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H138" s="6"/>
       <c r="I138" s="5">
         <v>46234</v>
       </c>
@@ -10247,13 +10184,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -10263,7 +10200,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B139" s="8">
         <v>46168.68403755787</v>
@@ -10275,17 +10212,15 @@
         <v>46205.60828523149</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H139" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H139" s="9"/>
       <c r="I139" s="8">
         <v>46234</v>
       </c>
@@ -10302,13 +10237,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -10318,7 +10253,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B140" s="5">
         <v>46168.68404385417</v>
@@ -10330,17 +10265,15 @@
         <v>46205.60828666667</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H140" s="6"/>
       <c r="I140" s="5">
         <v>46234</v>
       </c>
@@ -10357,13 +10290,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10373,7 +10306,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B141" s="8">
         <v>46168.68406297454</v>
@@ -10385,17 +10318,15 @@
         <v>46206.48582321759</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H141" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H141" s="9"/>
       <c r="I141" s="8">
         <v>46237</v>
       </c>
@@ -10412,13 +10343,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="Q141" s="8">
         <v>46237</v>
@@ -10438,7 +10369,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="B142" s="5">
         <v>46168.68406752315</v>
@@ -10450,17 +10381,15 @@
         <v>46206.48579965278</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H142" s="6"/>
       <c r="I142" s="5">
         <v>46237</v>
       </c>
@@ -10477,13 +10406,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10493,7 +10422,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B143" s="8">
         <v>46168.68407938657</v>
@@ -10505,17 +10434,15 @@
         <v>46206.48579032408</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H143" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H143" s="9"/>
       <c r="I143" s="8">
         <v>46237</v>
       </c>
@@ -10532,13 +10459,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10548,7 +10475,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="B144" s="5">
         <v>46168.68408523148</v>
@@ -10560,17 +10487,15 @@
         <v>46206.48578297454</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H144" s="6"/>
       <c r="I144" s="5">
         <v>46237</v>
       </c>
@@ -10587,13 +10512,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10603,7 +10528,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="B145" s="8">
         <v>46168.684089884264</v>
@@ -10615,17 +10540,15 @@
         <v>46206.48577649306</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H145" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H145" s="9"/>
       <c r="I145" s="8">
         <v>46237</v>
       </c>
@@ -10642,13 +10565,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10658,7 +10581,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="B146" s="5">
         <v>46168.684094571756</v>
@@ -10670,17 +10593,15 @@
         <v>46204.893335671295</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H146" s="6"/>
       <c r="I146" s="5">
         <v>46237</v>
       </c>
@@ -10697,13 +10618,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10713,7 +10634,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B147" s="8">
         <v>46168.68414574074</v>
@@ -10725,17 +10646,15 @@
         <v>46206.486229999995</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H147" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H147" s="9"/>
       <c r="I147" s="8">
         <v>46239</v>
       </c>
@@ -10752,13 +10671,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="Q147" s="8">
         <v>46239</v>
@@ -10778,7 +10697,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B148" s="5">
         <v>46168.68415105324</v>
@@ -10790,17 +10709,15 @@
         <v>46211.838432476856</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H148" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H148" s="6"/>
       <c r="I148" s="5">
         <v>46239</v>
       </c>
@@ -10817,13 +10734,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="O148" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="P148" s="6" t="s">
         <v>413</v>
-      </c>
-      <c r="O148" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="P148" s="6" t="s">
-        <v>416</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10833,7 +10750,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B149" s="8">
         <v>46168.68415587963</v>
@@ -10845,17 +10762,15 @@
         <v>46211.83844157407</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H149" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H149" s="9"/>
       <c r="I149" s="8">
         <v>46239</v>
       </c>
@@ -10872,13 +10787,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10888,7 +10803,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B150" s="5">
         <v>46168.68416068287</v>
@@ -10900,17 +10815,15 @@
         <v>46211.83843866899</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H150" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H150" s="6"/>
       <c r="I150" s="5">
         <v>46239</v>
       </c>
@@ -10927,13 +10840,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10943,7 +10856,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="B151" s="8">
         <v>46168.68416431713</v>
@@ -10955,17 +10868,15 @@
         <v>46211.83844565973</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H151" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H151" s="9"/>
       <c r="I151" s="8">
         <v>46239</v>
       </c>
@@ -10982,13 +10893,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10998,7 +10909,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="B152" s="5">
         <v>46168.68416798611</v>
@@ -11010,17 +10921,15 @@
         <v>46211.83845115741</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H152" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H152" s="6"/>
       <c r="I152" s="5">
         <v>46239</v>
       </c>
@@ -11037,13 +10946,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -11053,7 +10962,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="B153" s="8">
         <v>46168.684183460646</v>
@@ -11065,7 +10974,7 @@
         <v>46211.832724733795</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -11089,7 +10998,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -11106,7 +11015,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B154" s="5">
         <v>46168.68418700232</v>
@@ -11118,16 +11027,16 @@
         <v>46211.8327003125</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I154" s="5">
         <v>46240</v>
@@ -11145,13 +11054,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="Q154" s="5">
         <v>46240</v>
@@ -11171,7 +11080,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B155" s="8">
         <v>46168.68419359953</v>
@@ -11183,16 +11092,16 @@
         <v>46211.831112581014</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I155" s="8">
         <v>46240</v>
@@ -11210,13 +11119,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -11226,7 +11135,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="B156" s="5">
         <v>46168.68419834491</v>
@@ -11238,16 +11147,16 @@
         <v>46211.83112387732</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I156" s="5">
         <v>46240</v>
@@ -11265,13 +11174,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -11281,7 +11190,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="B157" s="8">
         <v>46168.684202777775</v>
@@ -11293,16 +11202,16 @@
         <v>46211.83112878472</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I157" s="8">
         <v>46240</v>
@@ -11320,13 +11229,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -11336,7 +11245,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B158" s="5">
         <v>46168.68420710648</v>
@@ -11348,16 +11257,16 @@
         <v>46211.83116206019</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I158" s="5">
         <v>46240</v>
@@ -11375,13 +11284,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -11391,7 +11300,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B159" s="8">
         <v>46168.68421127315</v>
@@ -11403,16 +11312,16 @@
         <v>46211.83117125</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I159" s="8">
         <v>46240</v>
@@ -11430,13 +11339,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -11446,7 +11355,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B160" s="5">
         <v>46168.68422996528</v>
@@ -11464,10 +11373,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I160" s="5">
         <v>46240</v>
@@ -11485,13 +11394,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11501,7 +11410,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="B161" s="8">
         <v>46168.68423341435</v>
@@ -11519,10 +11428,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I161" s="8">
         <v>46240</v>
@@ -11540,13 +11449,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11556,7 +11465,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B162" s="5">
         <v>46168.684237037036</v>
@@ -11574,10 +11483,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I162" s="5">
         <v>46240</v>
@@ -11595,13 +11504,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11611,7 +11520,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B163" s="8">
         <v>46168.68424059028</v>
@@ -11629,10 +11538,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I163" s="8">
         <v>46240</v>
@@ -11650,13 +11559,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11666,7 +11575,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="B164" s="5">
         <v>46168.68424420139</v>
@@ -11684,10 +11593,10 @@
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I164" s="5">
         <v>46240</v>
@@ -11705,13 +11614,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11721,7 +11630,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B165" s="8">
         <v>46168.68424778935</v>
@@ -11739,10 +11648,10 @@
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="I165" s="8">
         <v>46240</v>
@@ -11760,13 +11669,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="O165" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11776,7 +11685,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="B166" s="5">
         <v>46168.68425820602</v>
@@ -11788,17 +11697,15 @@
         <v>46211.83114409722</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H166" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H166" s="6"/>
       <c r="I166" s="6"/>
       <c r="J166" s="5">
         <v>46241</v>
@@ -11813,13 +11720,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="Q166" s="5">
         <v>46241</v>
@@ -11839,7 +11746,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B167" s="8">
         <v>46168.68426255787</v>
@@ -11851,17 +11758,15 @@
         <v>46211.83112083333</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H167" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H167" s="9"/>
       <c r="I167" s="9"/>
       <c r="J167" s="8">
         <v>46241</v>
@@ -11876,13 +11781,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
+        <v>447</v>
+      </c>
+      <c r="O167" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="P167" s="9" t="s">
         <v>450</v>
-      </c>
-      <c r="O167" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="P167" s="9" t="s">
-        <v>453</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11892,7 +11797,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B168" s="5">
         <v>46168.68426704861</v>
@@ -11904,17 +11809,15 @@
         <v>46211.83112822917</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H168" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H168" s="6"/>
       <c r="I168" s="6"/>
       <c r="J168" s="5">
         <v>46241</v>
@@ -11929,13 +11832,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="O168" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="P168" s="6" t="s">
         <v>450</v>
-      </c>
-      <c r="O168" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="P168" s="6" t="s">
-        <v>453</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11945,7 +11848,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="B169" s="8">
         <v>46168.68427162037</v>
@@ -11957,17 +11860,15 @@
         <v>46211.83113427083</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H169" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H169" s="9"/>
       <c r="I169" s="9"/>
       <c r="J169" s="8">
         <v>46241</v>
@@ -11982,13 +11883,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11998,7 +11899,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B170" s="5">
         <v>46168.68427627315</v>
@@ -12010,17 +11911,15 @@
         <v>46211.83116765047</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H170" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H170" s="6"/>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
         <v>46241</v>
@@ -12035,13 +11934,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -12051,7 +11950,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B171" s="8">
         <v>46168.68428068287</v>
@@ -12063,17 +11962,15 @@
         <v>46211.831175914354</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H171" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H171" s="9"/>
       <c r="I171" s="9"/>
       <c r="J171" s="8">
         <v>46241</v>
@@ -12088,13 +11985,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -12104,7 +12001,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B172" s="5">
         <v>46168.684336226856</v>
@@ -12122,11 +12019,9 @@
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H172" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H172" s="6"/>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
         <v>46241</v>
@@ -12141,13 +12036,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O172" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -12157,7 +12052,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="B173" s="8">
         <v>46168.68434010417</v>
@@ -12175,11 +12070,9 @@
         <v>26</v>
       </c>
       <c r="G173" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H173" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H173" s="9"/>
       <c r="I173" s="9"/>
       <c r="J173" s="8">
         <v>46241</v>
@@ -12194,13 +12087,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O173" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -12210,7 +12103,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="B174" s="5">
         <v>46168.68434423611</v>
@@ -12228,11 +12121,9 @@
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H174" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H174" s="6"/>
       <c r="I174" s="6"/>
       <c r="J174" s="5">
         <v>46241</v>
@@ -12247,13 +12138,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -12263,7 +12154,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="B175" s="8">
         <v>46168.684348263894</v>
@@ -12281,11 +12172,9 @@
         <v>26</v>
       </c>
       <c r="G175" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H175" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H175" s="9"/>
       <c r="I175" s="9"/>
       <c r="J175" s="8">
         <v>46241</v>
@@ -12300,13 +12189,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O175" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -12316,7 +12205,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="B176" s="5">
         <v>46168.68435202546</v>
@@ -12334,11 +12223,9 @@
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="H176" s="6" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H176" s="6"/>
       <c r="I176" s="6"/>
       <c r="J176" s="5">
         <v>46241</v>
@@ -12353,13 +12240,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -12369,7 +12256,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="B177" s="8">
         <v>46168.68435652778</v>
@@ -12387,11 +12274,9 @@
         <v>26</v>
       </c>
       <c r="G177" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="H177" s="9" t="s">
-        <v>98</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H177" s="9"/>
       <c r="I177" s="9"/>
       <c r="J177" s="8">
         <v>46241</v>
@@ -12406,13 +12291,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="O177" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -12422,7 +12307,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B178" s="5">
         <v>46168.68437314815</v>
@@ -12434,16 +12319,16 @@
         <v>46209.715354976855</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -12459,13 +12344,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="Q178" s="5">
         <v>46244</v>
@@ -12485,7 +12370,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B179" s="8">
         <v>46168.68437847222</v>
@@ -12497,16 +12382,16 @@
         <v>46209.71550439815</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H179" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I179" s="8">
         <v>46244</v>
@@ -12524,13 +12409,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="O179" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="P179" s="9" t="s">
         <v>471</v>
-      </c>
-      <c r="O179" s="9" t="s">
-        <v>214</v>
-      </c>
-      <c r="P179" s="9" t="s">
-        <v>474</v>
       </c>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
@@ -12540,7 +12425,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="B180" s="5">
         <v>46168.68438821759</v>
@@ -12552,16 +12437,16 @@
         <v>46209.7156449537</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I180" s="5">
         <v>46244</v>
@@ -12579,13 +12464,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12595,7 +12480,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="B181" s="8">
         <v>46168.684394537035</v>
@@ -12607,16 +12492,16 @@
         <v>46209.715759733794</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H181" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I181" s="8">
         <v>46244</v>
@@ -12634,13 +12519,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12650,7 +12535,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B182" s="5">
         <v>46168.68439944445</v>
@@ -12662,16 +12547,16 @@
         <v>46209.71583459491</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I182" s="5">
         <v>46244</v>
@@ -12689,13 +12574,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12705,7 +12590,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B183" s="8">
         <v>46168.684404375</v>
@@ -12717,16 +12602,16 @@
         <v>46209.71610449074</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H183" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I183" s="8">
         <v>46244</v>
@@ -12744,13 +12629,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12760,7 +12645,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B184" s="5">
         <v>46168.6844190625</v>
@@ -12778,10 +12663,10 @@
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I184" s="5">
         <v>46244</v>
@@ -12799,13 +12684,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O184" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12815,7 +12700,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="B185" s="8">
         <v>46168.68442277778</v>
@@ -12827,16 +12712,16 @@
         <v>46211.83081103009</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H185" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I185" s="8">
         <v>46244</v>
@@ -12854,13 +12739,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O185" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12870,7 +12755,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B186" s="5">
         <v>46168.68442653935</v>
@@ -12888,10 +12773,10 @@
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I186" s="5">
         <v>46244</v>
@@ -12909,13 +12794,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O186" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12925,7 +12810,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B187" s="8">
         <v>46168.684429988425</v>
@@ -12943,10 +12828,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H187" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I187" s="8">
         <v>46244</v>
@@ -12964,13 +12849,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O187" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12980,7 +12865,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B188" s="5">
         <v>46168.68443359954</v>
@@ -12998,10 +12883,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I188" s="5">
         <v>46244</v>
@@ -13019,13 +12904,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -13035,7 +12920,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B189" s="8">
         <v>46168.68443729167</v>
@@ -13053,10 +12938,10 @@
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I189" s="8">
         <v>46244</v>
@@ -13074,13 +12959,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="O189" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -13090,7 +12975,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B190" s="5">
         <v>46168.6844840625</v>
@@ -13102,16 +12987,16 @@
         <v>46211.830323738424</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I190" s="5">
         <v>46245</v>
@@ -13129,13 +13014,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="Q190" s="5">
         <v>46245</v>
@@ -13155,7 +13040,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B191" s="8">
         <v>46168.68449130787</v>
@@ -13167,16 +13052,16 @@
         <v>46211.830295844906</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="8">
@@ -13192,13 +13077,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -13208,7 +13093,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B192" s="5">
         <v>46168.68449590278</v>
@@ -13220,16 +13105,16 @@
         <v>46211.83029662037</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -13245,13 +13130,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -13261,7 +13146,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="B193" s="8">
         <v>46168.68450027778</v>
@@ -13273,16 +13158,16 @@
         <v>46211.83029733796</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="8">
@@ -13298,13 +13183,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -13314,7 +13199,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B194" s="5">
         <v>46168.68450480324</v>
@@ -13326,16 +13211,16 @@
         <v>46211.83029778935</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="5">
@@ -13351,13 +13236,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -13367,7 +13252,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B195" s="8">
         <v>46168.68450934028</v>
@@ -13379,16 +13264,16 @@
         <v>46211.83029865741</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I195" s="9"/>
       <c r="J195" s="8">
@@ -13404,13 +13289,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -13420,7 +13305,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B196" s="5">
         <v>46168.684523414355</v>
@@ -13432,16 +13317,16 @@
         <v>46211.83029902777</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -13457,13 +13342,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -13473,7 +13358,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B197" s="8">
         <v>46168.6845271412</v>
@@ -13485,16 +13370,16 @@
         <v>46211.83029945602</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I197" s="9"/>
       <c r="J197" s="8">
@@ -13510,13 +13395,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -13526,7 +13411,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B198" s="5">
         <v>46168.68453511574</v>
@@ -13538,16 +13423,16 @@
         <v>46211.830299953705</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13563,13 +13448,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13579,7 +13464,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B199" s="8">
         <v>46168.68453863426</v>
@@ -13591,16 +13476,16 @@
         <v>46211.83030041667</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I199" s="9"/>
       <c r="J199" s="8">
@@ -13616,13 +13501,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O199" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13632,7 +13517,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B200" s="5">
         <v>46168.68454210648</v>
@@ -13644,16 +13529,16 @@
         <v>46211.830300891204</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13669,13 +13554,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13685,7 +13570,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B201" s="8">
         <v>46168.684545578704</v>
@@ -13697,16 +13582,16 @@
         <v>46211.83030140046</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="8">
@@ -13722,13 +13607,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="O201" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13738,7 +13623,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B202" s="5">
         <v>46168.684555775464</v>
@@ -13748,7 +13633,7 @@
         <v>46168.8618759838</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>25</v>
@@ -13772,7 +13657,7 @@
         <v>26</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>26</v>
@@ -13785,7 +13670,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B203" s="8">
         <v>46168.6845594676</v>
@@ -13795,16 +13680,16 @@
         <v>46211.83025064815</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="I203" s="8">
         <v>46246</v>
@@ -13822,13 +13707,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="Q203" s="8">
         <v>46246</v>
@@ -13848,7 +13733,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B204" s="5">
         <v>46168.68456425926</v>
@@ -13858,7 +13743,7 @@
         <v>46211.83025032407</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13885,13 +13770,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="Q204" s="5">
         <v>46246</v>
@@ -13911,7 +13796,7 @@
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B205" s="8">
         <v>46168.68457049769</v>
@@ -13921,7 +13806,7 @@
         <v>46168.86234542824</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>25</v>
@@ -13945,7 +13830,7 @@
         <v>26</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="P205" s="9" t="s">
         <v>26</v>
@@ -13959,12 +13844,12 @@
         <v>0</v>
       </c>
       <c r="U205" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B206" s="5">
         <v>46168.68457415509</v>
@@ -13974,7 +13859,7 @@
         <v>46211.830253541666</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -14001,13 +13886,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="Q206" s="5">
         <v>46246</v>
@@ -14027,7 +13912,7 @@
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B207" s="8">
         <v>46168.68457920139</v>
@@ -14037,7 +13922,7 @@
         <v>46168.868795937495</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>26</v>
@@ -14064,13 +13949,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
+        <v>529</v>
+      </c>
+      <c r="O207" s="9" t="s">
         <v>532</v>
       </c>
-      <c r="O207" s="9" t="s">
-        <v>535</v>
-      </c>
       <c r="P207" s="9" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="Q207" s="8">
         <v>46255</v>
@@ -14085,7 +13970,7 @@
         <v>0</v>
       </c>
       <c r="U207" s="12" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -291,6 +291,9 @@
     <t>Ingenieria Servicios ,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>Media</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
   </si>
   <si>
@@ -577,9 +580,6 @@
   </si>
   <si>
     <t>Generación OC   ot 4336 - 4338 -4341,fabricación tableros   ot 4336 - 4338 -4341</t>
-  </si>
-  <si>
-    <t>Media</t>
   </si>
   <si>
     <t>1215141318244929</t>
@@ -2834,7 +2834,7 @@
         <v>46196.89414587963</v>
       </c>
       <c r="D12" s="5">
-        <v>46205.61958375</v>
+        <v>46220.171589571764</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2878,19 +2878,19 @@
       <c r="R12" s="5">
         <v>46227</v>
       </c>
-      <c r="S12" s="10" t="s">
-        <v>32</v>
+      <c r="S12" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T12" s="6">
         <v>1</v>
       </c>
       <c r="U12" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B13" s="8">
         <v>46168.68315351852</v>
@@ -2902,7 +2902,7 @@
         <v>46205.61659230324</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -2935,7 +2935,7 @@
         <v>59</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B14" s="5">
         <v>46168.68315625</v>
@@ -2957,7 +2957,7 @@
         <v>46205.616595300926</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2990,7 +2990,7 @@
         <v>59</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -3000,7 +3000,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B15" s="8">
         <v>46168.68315891204</v>
@@ -3012,7 +3012,7 @@
         <v>46205.61659625</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -3045,7 +3045,7 @@
         <v>59</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -3055,7 +3055,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" s="5">
         <v>46168.683161493056</v>
@@ -3067,7 +3067,7 @@
         <v>46205.616596921296</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -3100,7 +3100,7 @@
         <v>59</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -3110,7 +3110,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="8">
         <v>46168.68316400463</v>
@@ -3122,7 +3122,7 @@
         <v>46205.61659773148</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -3155,7 +3155,7 @@
         <v>59</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -3165,7 +3165,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="5">
         <v>46168.68316714121</v>
@@ -3177,7 +3177,7 @@
         <v>46205.61659839121</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -3210,7 +3210,7 @@
         <v>59</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B19" s="8">
         <v>46168.682984189814</v>
@@ -3232,7 +3232,7 @@
         <v>46205.60495420139</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>25</v>
@@ -3256,7 +3256,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P19" s="9" t="s">
         <v>26</v>
@@ -3273,7 +3273,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B20" s="5">
         <v>46168.68317581018</v>
@@ -3285,16 +3285,16 @@
         <v>46196.87777847222</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46155</v>
@@ -3306,19 +3306,19 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="5">
         <v>46155</v>
@@ -3338,7 +3338,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" s="8">
         <v>46168.6831808912</v>
@@ -3350,16 +3350,16 @@
         <v>46196.877778333335</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" s="8">
         <v>46155</v>
@@ -3371,19 +3371,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>41</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q21" s="8">
         <v>46155</v>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" s="5">
         <v>46168.68318591436</v>
@@ -3415,16 +3415,16 @@
         <v>46196.87777902778</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I22" s="5">
         <v>46155</v>
@@ -3442,13 +3442,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Q22" s="5">
         <v>46155</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="8">
         <v>46168.68298827547</v>
@@ -3480,7 +3480,7 @@
         <v>46205.605017905094</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>25</v>
@@ -3504,7 +3504,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>26</v>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" s="5">
         <v>46168.68319888889</v>
@@ -3531,16 +3531,16 @@
         <v>46193.5530831713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3558,13 +3558,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q24" s="5">
         <v>46157</v>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8">
         <v>46168.68320439815</v>
@@ -3596,16 +3596,16 @@
         <v>46193.55308946759</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I25" s="8">
         <v>46157</v>
@@ -3623,13 +3623,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q25" s="8">
         <v>46157</v>
@@ -3649,7 +3649,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" s="5">
         <v>46168.68320962963</v>
@@ -3661,7 +3661,7 @@
         <v>46183.90442146991</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
@@ -3686,13 +3686,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3712,7 +3712,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" s="8">
         <v>46168.68321476852</v>
@@ -3724,7 +3724,7 @@
         <v>46197.8530077662</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3749,13 +3749,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q27" s="8">
         <v>46189</v>
@@ -3764,7 +3764,7 @@
         <v>46190</v>
       </c>
       <c r="S27" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T27" s="9">
         <v>1</v>
@@ -3775,7 +3775,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B28" s="5">
         <v>46168.68321959491</v>
@@ -3787,7 +3787,7 @@
         <v>46196.64668813658</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3812,13 +3812,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Q28" s="5">
         <v>46189</v>
@@ -3827,7 +3827,7 @@
         <v>46190</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
@@ -3838,7 +3838,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B29" s="8">
         <v>46168.68322341435</v>
@@ -3850,7 +3850,7 @@
         <v>46196.647418912034</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3875,13 +3875,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Q29" s="8">
         <v>46189</v>
@@ -3890,7 +3890,7 @@
         <v>46190</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3901,7 +3901,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5">
         <v>46168.683227245376</v>
@@ -3913,7 +3913,7 @@
         <v>46196.64801533565</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3938,13 +3938,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="5">
         <v>46189</v>
@@ -3953,7 +3953,7 @@
         <v>46190</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3964,7 +3964,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" s="8">
         <v>46168.683231365736</v>
@@ -3976,16 +3976,16 @@
         <v>46193.553499305555</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I31" s="8">
         <v>46157</v>
@@ -4003,13 +4003,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>51</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="8">
         <v>46157</v>
@@ -4029,7 +4029,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46168.682992511574</v>
@@ -4041,7 +4041,7 @@
         <v>46205.61594793982</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -4065,7 +4065,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -4082,7 +4082,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B33" s="8">
         <v>46168.68327652778</v>
@@ -4094,16 +4094,16 @@
         <v>46195.928396574076</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I33" s="8">
         <v>46161</v>
@@ -4121,13 +4121,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q33" s="8">
         <v>46161</v>
@@ -4147,7 +4147,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46168.68328149305</v>
@@ -4159,16 +4159,16 @@
         <v>46195.9258303588</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -4186,13 +4186,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4203,12 +4203,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46168.68328653935</v>
@@ -4220,16 +4220,16 @@
         <v>46195.928370243055</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I35" s="8">
         <v>46164</v>
@@ -4247,13 +4247,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -4264,12 +4264,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46168.68329140046</v>
@@ -4281,16 +4281,16 @@
         <v>46185.182775243054</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I36" s="5">
         <v>46161</v>
@@ -4308,13 +4308,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q36" s="5">
         <v>46161</v>
@@ -4323,7 +4323,7 @@
         <v>46184</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4334,7 +4334,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46168.68329584491</v>
@@ -4346,16 +4346,16 @@
         <v>46184.70350368056</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I37" s="8">
         <v>46161</v>
@@ -4373,13 +4373,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -4390,12 +4390,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46168.68330070602</v>
@@ -4407,16 +4407,16 @@
         <v>46184.703557789355</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I38" s="5">
         <v>46164</v>
@@ -4434,13 +4434,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4451,12 +4451,12 @@
         <v>0</v>
       </c>
       <c r="U38" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46168.68330542824</v>
@@ -4468,16 +4468,16 @@
         <v>46205.60819122686</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I39" s="8">
         <v>46161</v>
@@ -4495,13 +4495,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q39" s="8">
         <v>46161</v>
@@ -4510,7 +4510,7 @@
         <v>46198</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4521,7 +4521,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46168.683310092594</v>
@@ -4533,16 +4533,16 @@
         <v>46195.92587128472</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I40" s="5">
         <v>46161</v>
@@ -4560,13 +4560,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4577,12 +4577,12 @@
         <v>0</v>
       </c>
       <c r="U40" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46168.68331519676</v>
@@ -4594,16 +4594,16 @@
         <v>46205.60793128472</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I41" s="8">
         <v>46170</v>
@@ -4621,13 +4621,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4638,12 +4638,12 @@
         <v>0</v>
       </c>
       <c r="U41" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46168.68332027778</v>
@@ -4655,16 +4655,16 @@
         <v>46195.92587850694</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I42" s="5">
         <v>46170</v>
@@ -4682,13 +4682,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4699,12 +4699,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46168.68332520833</v>
@@ -4713,19 +4713,19 @@
         <v>46195.92858413194</v>
       </c>
       <c r="D43" s="8">
-        <v>46212.17842539352</v>
+        <v>46220.18799388889</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I43" s="8">
         <v>46161</v>
@@ -4743,10 +4743,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4757,8 +4757,8 @@
       <c r="R43" s="8">
         <v>46219</v>
       </c>
-      <c r="S43" s="11" t="s">
-        <v>155</v>
+      <c r="S43" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4781,16 +4781,16 @@
         <v>46195.92577891204</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I44" s="5">
         <v>46161</v>
@@ -4808,10 +4808,10 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>157</v>
@@ -4842,10 +4842,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I45" s="8">
         <v>46171</v>
@@ -4863,10 +4863,10 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P45" s="9" t="s">
         <v>160</v>
@@ -4918,13 +4918,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="Q46" s="5">
         <v>46191</v>
@@ -4933,7 +4933,7 @@
         <v>46203</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4986,7 +4986,7 @@
         <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P47" s="9" t="s">
         <v>168</v>
@@ -5000,7 +5000,7 @@
         <v>0</v>
       </c>
       <c r="U47" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="U48" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
@@ -5105,7 +5105,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>174</v>
@@ -5120,7 +5120,7 @@
         <v>46203</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -5143,7 +5143,7 @@
         <v>46199.56512275463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
@@ -5173,7 +5173,7 @@
         <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>176</v>
@@ -5228,7 +5228,7 @@
         <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P51" s="9" t="s">
         <v>179</v>
@@ -5280,7 +5280,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>184</v>
@@ -5318,7 +5318,7 @@
         <v>46204.601485555555</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
@@ -5348,7 +5348,7 @@
         <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>186</v>
@@ -5403,7 +5403,7 @@
         <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>189</v>
@@ -5510,7 +5510,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>196</v>
@@ -5525,7 +5525,7 @@
         <v>46203</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5548,7 +5548,7 @@
         <v>46199.56535409723</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
@@ -5578,7 +5578,7 @@
         <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>198</v>
@@ -5633,7 +5633,7 @@
         <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>201</v>
@@ -5690,7 +5690,7 @@
       <c r="S59" s="9"/>
       <c r="T59" s="9"/>
       <c r="U59" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
@@ -5749,7 +5749,7 @@
         <v>46171</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5802,7 +5802,7 @@
         <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>212</v>
@@ -5857,7 +5857,7 @@
         <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>212</v>
@@ -5912,7 +5912,7 @@
         <v>206</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>216</v>
@@ -5967,7 +5967,7 @@
         <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>216</v>
@@ -6022,7 +6022,7 @@
         <v>206</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P65" s="9" t="s">
         <v>220</v>
@@ -6089,7 +6089,7 @@
         <v>46185</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -6387,7 +6387,7 @@
         <v>46190.6054244213</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
@@ -6429,7 +6429,7 @@
         <v>46188</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6479,13 +6479,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O73" s="9" t="s">
         <v>211</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6534,13 +6534,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>211</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6589,13 +6589,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O75" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6644,13 +6644,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>215</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6699,7 +6699,7 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O77" s="9" t="s">
         <v>219</v>
@@ -7160,7 +7160,7 @@
         <v>46205</v>
       </c>
       <c r="S85" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -7225,13 +7225,13 @@
         <v>46209</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
       </c>
       <c r="U86" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
@@ -7290,7 +7290,7 @@
         <v>46205</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -7355,13 +7355,13 @@
         <v>46209</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
       </c>
       <c r="U88" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
@@ -7420,7 +7420,7 @@
         <v>46205</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T89" s="9">
         <v>1</v>
@@ -7485,13 +7485,13 @@
         <v>46209</v>
       </c>
       <c r="S90" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
       </c>
       <c r="U90" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
@@ -7603,7 +7603,7 @@
         <v>46212</v>
       </c>
       <c r="S92" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -7943,13 +7943,13 @@
         <v>46223</v>
       </c>
       <c r="S98" s="11" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
       </c>
       <c r="U98" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
@@ -8283,7 +8283,7 @@
         <v>46224</v>
       </c>
       <c r="S104" s="11" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
@@ -8664,7 +8664,7 @@
         <v>256</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>327</v>
@@ -8676,7 +8676,7 @@
         <v>46185</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T111" s="9">
         <v>1</v>
@@ -8727,7 +8727,7 @@
         <v>256</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>330</v>
@@ -8739,7 +8739,7 @@
         <v>46168</v>
       </c>
       <c r="S112" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T112" s="6">
         <v>1</v>
@@ -8792,7 +8792,7 @@
         <v>256</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>333</v>
@@ -8804,7 +8804,7 @@
         <v>46199</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8934,7 +8934,7 @@
         <v>46220</v>
       </c>
       <c r="S115" s="11" t="s">
-        <v>155</v>
+        <v>61</v>
       </c>
       <c r="T115" s="9">
         <v>1</v>
@@ -8989,7 +8989,7 @@
       <c r="S116" s="6"/>
       <c r="T116" s="6"/>
       <c r="U116" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -9052,7 +9052,7 @@
         <v>1</v>
       </c>
       <c r="U117" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
@@ -11367,7 +11367,7 @@
         <v>46211.83117747685</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
@@ -11397,7 +11397,7 @@
         <v>425</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P160" s="6" t="s">
         <v>438</v>
@@ -11422,7 +11422,7 @@
         <v>46211.831204988426</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>26</v>
@@ -11452,7 +11452,7 @@
         <v>425</v>
       </c>
       <c r="O161" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P161" s="9" t="s">
         <v>438</v>
@@ -11477,7 +11477,7 @@
         <v>46211.83121074074</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
@@ -11507,7 +11507,7 @@
         <v>425</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P162" s="6" t="s">
         <v>438</v>
@@ -11532,7 +11532,7 @@
         <v>46211.83121682871</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
@@ -11562,7 +11562,7 @@
         <v>425</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P163" s="9" t="s">
         <v>442</v>
@@ -11587,7 +11587,7 @@
         <v>46211.83124355324</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
@@ -11617,7 +11617,7 @@
         <v>425</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P164" s="6" t="s">
         <v>442</v>
@@ -11642,7 +11642,7 @@
         <v>46211.83125052083</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
@@ -11672,7 +11672,7 @@
         <v>425</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P165" s="9" t="s">
         <v>445</v>
@@ -11741,7 +11741,7 @@
         <v>1</v>
       </c>
       <c r="U166" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
@@ -12013,7 +12013,7 @@
         <v>46211.83118184027</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
@@ -12039,7 +12039,7 @@
         <v>447</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P172" s="6" t="s">
         <v>458</v>
@@ -12064,7 +12064,7 @@
         <v>46211.831210868055</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
@@ -12090,7 +12090,7 @@
         <v>447</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P173" s="9" t="s">
         <v>460</v>
@@ -12115,7 +12115,7 @@
         <v>46211.83121509259</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
@@ -12141,7 +12141,7 @@
         <v>447</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P174" s="6" t="s">
         <v>458</v>
@@ -12166,7 +12166,7 @@
         <v>46211.831221932865</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>26</v>
@@ -12192,7 +12192,7 @@
         <v>447</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P175" s="9" t="s">
         <v>463</v>
@@ -12217,7 +12217,7 @@
         <v>46211.831248912036</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
@@ -12243,7 +12243,7 @@
         <v>447</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P176" s="6" t="s">
         <v>463</v>
@@ -12268,7 +12268,7 @@
         <v>46211.831259189814</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
@@ -12294,7 +12294,7 @@
         <v>447</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P177" s="9" t="s">
         <v>466</v>
@@ -12657,7 +12657,7 @@
         <v>46211.83066165509</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
@@ -12687,7 +12687,7 @@
         <v>468</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P184" s="6" t="s">
         <v>481</v>
@@ -12742,7 +12742,7 @@
         <v>468</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P185" s="9" t="s">
         <v>484</v>
@@ -12767,7 +12767,7 @@
         <v>46211.83088054398</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
@@ -12797,7 +12797,7 @@
         <v>468</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P186" s="6" t="s">
         <v>486</v>
@@ -12822,7 +12822,7 @@
         <v>46211.83097425926</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
@@ -12852,7 +12852,7 @@
         <v>468</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P187" s="9" t="s">
         <v>488</v>
@@ -12877,7 +12877,7 @@
         <v>46211.83105417824</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
@@ -12907,7 +12907,7 @@
         <v>468</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P188" s="6" t="s">
         <v>490</v>
@@ -12932,7 +12932,7 @@
         <v>46211.8311371412</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>26</v>
@@ -12962,7 +12962,7 @@
         <v>468</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P189" s="9" t="s">
         <v>492</v>
@@ -13035,7 +13035,7 @@
         <v>1</v>
       </c>
       <c r="U190" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
@@ -13345,7 +13345,7 @@
         <v>494</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P196" s="6" t="s">
         <v>494</v>
@@ -13451,7 +13451,7 @@
         <v>494</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="P198" s="6" t="s">
         <v>494</v>
@@ -13504,7 +13504,7 @@
         <v>494</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P199" s="9" t="s">
         <v>494</v>
@@ -13557,7 +13557,7 @@
         <v>494</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P200" s="6" t="s">
         <v>494</v>
@@ -13610,7 +13610,7 @@
         <v>494</v>
       </c>
       <c r="O201" s="9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="P201" s="9" t="s">
         <v>494</v>
@@ -13728,7 +13728,7 @@
         <v>0</v>
       </c>
       <c r="U203" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
@@ -13749,10 +13749,10 @@
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H204" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I204" s="5">
         <v>46246</v>
@@ -13791,7 +13791,7 @@
         <v>0</v>
       </c>
       <c r="U204" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
@@ -13844,7 +13844,7 @@
         <v>0</v>
       </c>
       <c r="U205" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
@@ -13907,7 +13907,7 @@
         <v>0</v>
       </c>
       <c r="U206" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
@@ -13970,7 +13970,7 @@
         <v>0</v>
       </c>
       <c r="U207" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -8889,7 +8889,7 @@
         <v>46205.61658686343</v>
       </c>
       <c r="D115" s="8">
-        <v>46213.19932342593</v>
+        <v>46221.20399085648</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>59</v>
@@ -8933,8 +8933,8 @@
       <c r="R115" s="8">
         <v>46220</v>
       </c>
-      <c r="S115" s="11" t="s">
-        <v>61</v>
+      <c r="S115" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="T115" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2347" uniqueCount="536">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="537">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -294,9 +294,6 @@
     <t>Media</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1215141566425255</t>
   </si>
   <si>
@@ -411,6 +408,9 @@
     <t>propuesta nucleo rodete ot 4335 - 4337 -4339</t>
   </si>
   <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
     <t>Propuesta compras:,Generación OC Rodete ot 4335 - 4337 -4339</t>
   </si>
   <si>
@@ -727,6 +727,9 @@
   </si>
   <si>
     <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
   </si>
   <si>
     <t>1215141533944745</t>
@@ -2834,7 +2837,7 @@
         <v>46196.89414587963</v>
       </c>
       <c r="D12" s="5">
-        <v>46220.171589571764</v>
+        <v>46223.57316143518</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -2884,13 +2887,13 @@
       <c r="T12" s="6">
         <v>1</v>
       </c>
-      <c r="U12" s="11" t="s">
-        <v>62</v>
+      <c r="U12" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B13" s="8">
         <v>46168.68315351852</v>
@@ -2902,7 +2905,7 @@
         <v>46205.61659230324</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
@@ -2935,7 +2938,7 @@
         <v>59</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2945,7 +2948,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B14" s="5">
         <v>46168.68315625</v>
@@ -2957,7 +2960,7 @@
         <v>46205.616595300926</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
@@ -2990,7 +2993,7 @@
         <v>59</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -3000,7 +3003,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8">
         <v>46168.68315891204</v>
@@ -3012,7 +3015,7 @@
         <v>46205.61659625</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
@@ -3045,7 +3048,7 @@
         <v>59</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -3055,7 +3058,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B16" s="5">
         <v>46168.683161493056</v>
@@ -3067,7 +3070,7 @@
         <v>46205.616596921296</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
@@ -3100,7 +3103,7 @@
         <v>59</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -3110,7 +3113,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B17" s="8">
         <v>46168.68316400463</v>
@@ -3122,7 +3125,7 @@
         <v>46205.61659773148</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>26</v>
@@ -3155,7 +3158,7 @@
         <v>59</v>
       </c>
       <c r="P17" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q17" s="9"/>
       <c r="R17" s="9"/>
@@ -3165,7 +3168,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="5">
         <v>46168.68316714121</v>
@@ -3177,7 +3180,7 @@
         <v>46205.61659839121</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -3210,7 +3213,7 @@
         <v>59</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q18" s="6"/>
       <c r="R18" s="6"/>
@@ -3220,7 +3223,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B19" s="8">
         <v>46168.682984189814</v>
@@ -3232,7 +3235,7 @@
         <v>46205.60495420139</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>25</v>
@@ -3256,7 +3259,7 @@
         <v>26</v>
       </c>
       <c r="O19" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P19" s="9" t="s">
         <v>26</v>
@@ -3273,7 +3276,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" s="5">
         <v>46168.68317581018</v>
@@ -3285,16 +3288,16 @@
         <v>46196.87777847222</v>
       </c>
       <c r="E20" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G20" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H20" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I20" s="5">
         <v>46155</v>
@@ -3306,19 +3309,19 @@
         <v>26</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q20" s="5">
         <v>46155</v>
@@ -3338,7 +3341,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B21" s="8">
         <v>46168.6831808912</v>
@@ -3350,16 +3353,16 @@
         <v>46196.877778333335</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="H21" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="I21" s="8">
         <v>46155</v>
@@ -3371,19 +3374,19 @@
         <v>26</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M21" s="9" t="s">
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O21" s="9" t="s">
         <v>41</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q21" s="8">
         <v>46155</v>
@@ -3403,7 +3406,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B22" s="5">
         <v>46168.68318591436</v>
@@ -3415,16 +3418,16 @@
         <v>46196.87777902778</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G22" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I22" s="5">
         <v>46155</v>
@@ -3442,13 +3445,13 @@
         <v>26</v>
       </c>
       <c r="N22" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>41</v>
       </c>
       <c r="P22" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="Q22" s="5">
         <v>46155</v>
@@ -3468,7 +3471,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B23" s="8">
         <v>46168.68298827547</v>
@@ -3480,7 +3483,7 @@
         <v>46205.605017905094</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>25</v>
@@ -3504,7 +3507,7 @@
         <v>26</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P23" s="9" t="s">
         <v>26</v>
@@ -3519,7 +3522,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B24" s="5">
         <v>46168.68319888889</v>
@@ -3531,16 +3534,16 @@
         <v>46193.5530831713</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I24" s="5">
         <v>46157</v>
@@ -3558,13 +3561,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q24" s="5">
         <v>46157</v>
@@ -3584,7 +3587,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B25" s="8">
         <v>46168.68320439815</v>
@@ -3596,16 +3599,16 @@
         <v>46193.55308946759</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="H25" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="I25" s="8">
         <v>46157</v>
@@ -3623,13 +3626,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O25" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q25" s="8">
         <v>46157</v>
@@ -3649,7 +3652,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B26" s="5">
         <v>46168.68320962963</v>
@@ -3658,18 +3661,20 @@
         <v>46183.904405775465</v>
       </c>
       <c r="D26" s="5">
-        <v>46183.90442146991</v>
+        <v>46223.5717293287</v>
       </c>
       <c r="E26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G26" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H26" s="6"/>
+      <c r="H26" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I26" s="5">
         <v>46157</v>
       </c>
@@ -3686,10 +3691,10 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>99</v>
@@ -3721,7 +3726,7 @@
         <v>46197.852991875</v>
       </c>
       <c r="D27" s="8">
-        <v>46197.8530077662</v>
+        <v>46223.5717261574</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>101</v>
@@ -3730,9 +3735,11 @@
         <v>26</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H27" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I27" s="8">
         <v>46189</v>
       </c>
@@ -3749,7 +3756,7 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O27" s="9" t="s">
         <v>102</v>
@@ -3784,7 +3791,7 @@
         <v>46196.646673379626</v>
       </c>
       <c r="D28" s="5">
-        <v>46196.64668813658</v>
+        <v>46223.57172274306</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>106</v>
@@ -3793,9 +3800,11 @@
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H28" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I28" s="5">
         <v>46189</v>
       </c>
@@ -3812,7 +3821,7 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>102</v>
@@ -3847,7 +3856,7 @@
         <v>46196.6474043287</v>
       </c>
       <c r="D29" s="8">
-        <v>46196.647418912034</v>
+        <v>46223.571718969906</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>109</v>
@@ -3856,9 +3865,11 @@
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H29" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I29" s="8">
         <v>46189</v>
       </c>
@@ -3875,7 +3886,7 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O29" s="9" t="s">
         <v>102</v>
@@ -3910,7 +3921,7 @@
         <v>46196.64760480324</v>
       </c>
       <c r="D30" s="5">
-        <v>46196.64801533565</v>
+        <v>46223.57171402778</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>112</v>
@@ -3919,9 +3930,11 @@
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H30" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I30" s="5">
         <v>46189</v>
       </c>
@@ -3938,7 +3951,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>102</v>
@@ -3982,10 +3995,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="9" t="s">
         <v>77</v>
-      </c>
-      <c r="H31" s="9" t="s">
-        <v>78</v>
       </c>
       <c r="I31" s="8">
         <v>46157</v>
@@ -4003,7 +4016,7 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="O31" s="9" t="s">
         <v>51</v>
@@ -4189,7 +4202,7 @@
         <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>127</v>
@@ -4376,7 +4389,7 @@
         <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P37" s="9" t="s">
         <v>137</v>
@@ -4563,7 +4576,7 @@
         <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>146</v>
@@ -5690,12 +5703,12 @@
       <c r="S59" s="9"/>
       <c r="T59" s="9"/>
       <c r="U59" s="11" t="s">
-        <v>62</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B60" s="5">
         <v>46168.683445787035</v>
@@ -5707,16 +5720,16 @@
         <v>46184.518844583334</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46167</v>
@@ -5737,7 +5750,7 @@
         <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>203</v>
@@ -5760,7 +5773,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B61" s="8">
         <v>46168.6865996875</v>
@@ -5772,16 +5785,16 @@
         <v>46184.51878665509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I61" s="8">
         <v>46167</v>
@@ -5799,13 +5812,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5815,7 +5828,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46168.68683460648</v>
@@ -5827,16 +5840,16 @@
         <v>46184.518791319446</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46167</v>
@@ -5854,13 +5867,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5870,7 +5883,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B63" s="8">
         <v>46168.686918437495</v>
@@ -5882,16 +5895,16 @@
         <v>46184.51879930556</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I63" s="8">
         <v>46167</v>
@@ -5909,13 +5922,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5925,7 +5938,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B64" s="5">
         <v>46168.687254143515</v>
@@ -5937,16 +5950,16 @@
         <v>46184.5188068287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46167</v>
@@ -5964,13 +5977,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5980,7 +5993,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B65" s="8">
         <v>46168.68731635417</v>
@@ -5992,16 +6005,16 @@
         <v>46184.51881454861</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I65" s="8">
         <v>46167</v>
@@ -6019,13 +6032,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -6035,7 +6048,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B66" s="5">
         <v>46168.68345142361</v>
@@ -6047,16 +6060,16 @@
         <v>46190.605242708334</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46181</v>
@@ -6077,7 +6090,7 @@
         <v>203</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>203</v>
@@ -6100,7 +6113,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B67" s="8">
         <v>46168.68857346065</v>
@@ -6112,16 +6125,16 @@
         <v>46190.60518608797</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I67" s="8">
         <v>46181</v>
@@ -6139,13 +6152,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -6155,7 +6168,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B68" s="5">
         <v>46168.688608275465</v>
@@ -6167,16 +6180,16 @@
         <v>46190.60519502315</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I68" s="5">
         <v>46181</v>
@@ -6194,13 +6207,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6210,7 +6223,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B69" s="8">
         <v>46168.68864659722</v>
@@ -6222,16 +6235,16 @@
         <v>46190.605203761574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I69" s="8">
         <v>46181</v>
@@ -6249,13 +6262,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6265,7 +6278,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B70" s="5">
         <v>46168.68868637731</v>
@@ -6277,16 +6290,16 @@
         <v>46190.605208946756</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I70" s="5">
         <v>46181</v>
@@ -6304,13 +6317,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6320,7 +6333,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B71" s="8">
         <v>46168.68871934028</v>
@@ -6332,16 +6345,16 @@
         <v>46190.60521709491</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I71" s="8">
         <v>46181</v>
@@ -6359,13 +6372,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -6375,7 +6388,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B72" s="5">
         <v>46168.68345790509</v>
@@ -6393,10 +6406,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I72" s="5">
         <v>46188</v>
@@ -6417,10 +6430,10 @@
         <v>203</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q72" s="5">
         <v>46188</v>
@@ -6440,7 +6453,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B73" s="8">
         <v>46168.68880178241</v>
@@ -6452,16 +6465,16 @@
         <v>46190.60536361111</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -6482,7 +6495,7 @@
         <v>102</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>102</v>
@@ -6495,7 +6508,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B74" s="5">
         <v>46168.68883857639</v>
@@ -6507,16 +6520,16 @@
         <v>46190.605368206016</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I74" s="5">
         <v>46188</v>
@@ -6537,7 +6550,7 @@
         <v>102</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>102</v>
@@ -6550,7 +6563,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B75" s="8">
         <v>46168.688875775464</v>
@@ -6562,16 +6575,16 @@
         <v>46190.605373530096</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I75" s="8">
         <v>46188</v>
@@ -6592,7 +6605,7 @@
         <v>102</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>102</v>
@@ -6605,7 +6618,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B76" s="5">
         <v>46168.6889172338</v>
@@ -6617,16 +6630,16 @@
         <v>46190.60539957176</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I76" s="5">
         <v>46188</v>
@@ -6647,7 +6660,7 @@
         <v>102</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>102</v>
@@ -6660,7 +6673,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B77" s="8">
         <v>46168.688956620375</v>
@@ -6672,16 +6685,16 @@
         <v>46190.60538814815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="I77" s="8">
         <v>46188</v>
@@ -6702,7 +6715,7 @@
         <v>102</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6715,7 +6728,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B78" s="5">
         <v>46168.683480625</v>
@@ -6727,16 +6740,16 @@
         <v>46211.83847391204</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6755,7 +6768,7 @@
         <v>203</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6778,7 +6791,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B79" s="8">
         <v>46168.683484629626</v>
@@ -6790,16 +6803,16 @@
         <v>46211.83842664352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I79" s="8">
         <v>46238</v>
@@ -6817,13 +6830,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6833,7 +6846,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B80" s="5">
         <v>46168.683488877316</v>
@@ -6845,16 +6858,16 @@
         <v>46211.83843200232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I80" s="5">
         <v>46238</v>
@@ -6872,13 +6885,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6888,7 +6901,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B81" s="8">
         <v>46168.68349300926</v>
@@ -6900,16 +6913,16 @@
         <v>46211.83843496528</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I81" s="8">
         <v>46238</v>
@@ -6927,13 +6940,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6943,7 +6956,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46168.6834959375</v>
@@ -6955,16 +6968,16 @@
         <v>46211.83844040509</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I82" s="5">
         <v>46238</v>
@@ -6982,13 +6995,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -6998,7 +7011,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B83" s="8">
         <v>46168.68349899305</v>
@@ -7010,16 +7023,16 @@
         <v>46211.83844619213</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="I83" s="8">
         <v>46238</v>
@@ -7037,13 +7050,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -7053,7 +7066,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B84" s="5">
         <v>46168.68351101852</v>
@@ -7065,7 +7078,7 @@
         <v>46205.618076087965</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -7089,7 +7102,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -7106,7 +7119,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B85" s="8">
         <v>46168.68351447917</v>
@@ -7118,16 +7131,16 @@
         <v>46206.18878055556</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I85" s="8">
         <v>46204</v>
@@ -7145,13 +7158,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>170</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q85" s="8">
         <v>46204</v>
@@ -7171,7 +7184,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B86" s="5">
         <v>46168.68352011574</v>
@@ -7180,10 +7193,10 @@
         <v>46197.85117512732</v>
       </c>
       <c r="D86" s="5">
-        <v>46210.20097684028</v>
+        <v>46223.57312579861</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -7210,13 +7223,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q86" s="5">
         <v>46206</v>
@@ -7230,13 +7243,13 @@
       <c r="T86" s="6">
         <v>1</v>
       </c>
-      <c r="U86" s="11" t="s">
-        <v>62</v>
+      <c r="U86" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46168.68352736111</v>
@@ -7248,16 +7261,16 @@
         <v>46206.18878028935</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -7275,13 +7288,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>178</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -7301,7 +7314,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46168.68353292824</v>
@@ -7310,10 +7323,10 @@
         <v>46197.851300173614</v>
       </c>
       <c r="D88" s="5">
-        <v>46210.20097686343</v>
+        <v>46223.573107916665</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7340,13 +7353,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="5">
         <v>46206</v>
@@ -7360,13 +7373,13 @@
       <c r="T88" s="6">
         <v>1</v>
       </c>
-      <c r="U88" s="11" t="s">
-        <v>62</v>
+      <c r="U88" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B89" s="8">
         <v>46168.68353787037</v>
@@ -7378,16 +7391,16 @@
         <v>46206.1887803125</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7405,13 +7418,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>200</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="8">
         <v>46204</v>
@@ -7431,7 +7444,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46168.68354247685</v>
@@ -7440,10 +7453,10 @@
         <v>46197.85161460648</v>
       </c>
       <c r="D90" s="5">
-        <v>46210.20097706019</v>
+        <v>46223.573090949074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7470,13 +7483,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q90" s="5">
         <v>46206</v>
@@ -7490,13 +7503,13 @@
       <c r="T90" s="6">
         <v>1</v>
       </c>
-      <c r="U90" s="11" t="s">
-        <v>62</v>
+      <c r="U90" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46168.68354741899</v>
@@ -7508,7 +7521,7 @@
         <v>46211.83134737269</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>25</v>
@@ -7532,7 +7545,7 @@
         <v>26</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>26</v>
@@ -7549,7 +7562,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46168.68355052083</v>
@@ -7561,16 +7574,16 @@
         <v>46213.20753342593</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7588,13 +7601,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="5">
         <v>46210</v>
@@ -7614,7 +7627,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B93" s="8">
         <v>46168.68356208333</v>
@@ -7626,16 +7639,16 @@
         <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I93" s="8">
         <v>46210</v>
@@ -7653,13 +7666,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7669,7 +7682,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B94" s="5">
         <v>46168.68356922454</v>
@@ -7681,16 +7694,16 @@
         <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7708,13 +7721,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7724,7 +7737,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B95" s="8">
         <v>46168.683574780094</v>
@@ -7736,16 +7749,16 @@
         <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I95" s="8">
         <v>46210</v>
@@ -7763,13 +7776,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7779,7 +7792,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B96" s="5">
         <v>46168.68358024306</v>
@@ -7791,16 +7804,16 @@
         <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7818,13 +7831,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7834,7 +7847,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B97" s="8">
         <v>46168.68358578703</v>
@@ -7846,16 +7859,16 @@
         <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I97" s="8">
         <v>46210</v>
@@ -7873,13 +7886,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7889,7 +7902,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B98" s="5">
         <v>46168.68365474537</v>
@@ -7898,19 +7911,19 @@
         <v>46197.85007665509</v>
       </c>
       <c r="D98" s="5">
-        <v>46216.17956907407</v>
+        <v>46223.573061076386</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I98" s="5">
         <v>46213</v>
@@ -7928,13 +7941,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q98" s="5">
         <v>46213</v>
@@ -7948,13 +7961,13 @@
       <c r="T98" s="6">
         <v>1</v>
       </c>
-      <c r="U98" s="11" t="s">
-        <v>62</v>
+      <c r="U98" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B99" s="8">
         <v>46168.683659965274</v>
@@ -7966,16 +7979,16 @@
         <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I99" s="8">
         <v>46213</v>
@@ -7993,13 +8006,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -8009,7 +8022,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B100" s="5">
         <v>46168.68366613426</v>
@@ -8021,16 +8034,16 @@
         <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I100" s="5">
         <v>46213</v>
@@ -8048,13 +8061,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -8064,7 +8077,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B101" s="8">
         <v>46168.683671921295</v>
@@ -8076,16 +8089,16 @@
         <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I101" s="8">
         <v>46213</v>
@@ -8103,13 +8116,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -8119,7 +8132,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B102" s="5">
         <v>46168.68367622685</v>
@@ -8131,16 +8144,16 @@
         <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I102" s="5">
         <v>46213</v>
@@ -8158,13 +8171,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8174,7 +8187,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B103" s="8">
         <v>46168.683680069444</v>
@@ -8186,16 +8199,16 @@
         <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I103" s="8">
         <v>46213</v>
@@ -8213,13 +8226,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8229,7 +8242,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B104" s="5">
         <v>46168.68369409722</v>
@@ -8241,7 +8254,7 @@
         <v>46217.19617538195</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8268,13 +8281,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q104" s="5">
         <v>46224</v>
@@ -8294,7 +8307,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B105" s="8">
         <v>46168.68369849537</v>
@@ -8306,7 +8319,7 @@
         <v>46204.890051967595</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8333,13 +8346,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8349,7 +8362,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B106" s="5">
         <v>46168.683704490744</v>
@@ -8361,7 +8374,7 @@
         <v>46204.890058125005</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8388,13 +8401,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8404,7 +8417,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B107" s="8">
         <v>46168.683710150464</v>
@@ -8416,7 +8429,7 @@
         <v>46204.89006394676</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8443,13 +8456,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8459,7 +8472,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B108" s="5">
         <v>46168.68371309028</v>
@@ -8471,7 +8484,7 @@
         <v>46204.89006936342</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8498,13 +8511,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8514,7 +8527,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B109" s="8">
         <v>46168.68371646991</v>
@@ -8526,7 +8539,7 @@
         <v>46204.890080185185</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8553,13 +8566,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8569,7 +8582,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B110" s="5">
         <v>46168.68373005787</v>
@@ -8581,7 +8594,7 @@
         <v>46211.830014363426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8605,7 +8618,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8622,7 +8635,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B111" s="8">
         <v>46168.68373365741</v>
@@ -8634,16 +8647,16 @@
         <v>46205.61049446759</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I111" s="8">
         <v>46185</v>
@@ -8661,13 +8674,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>139</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q111" s="8">
         <v>46185</v>
@@ -8687,7 +8700,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B112" s="5">
         <v>46168.6837408912</v>
@@ -8699,16 +8712,16 @@
         <v>46205.61455358796</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8724,13 +8737,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>130</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q112" s="5">
         <v>46168</v>
@@ -8750,7 +8763,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B113" s="8">
         <v>46168.68374771991</v>
@@ -8762,16 +8775,16 @@
         <v>46205.6084347338</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I113" s="8">
         <v>46199</v>
@@ -8789,13 +8802,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>148</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q113" s="8">
         <v>46199</v>
@@ -8815,7 +8828,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B114" s="5">
         <v>46168.68375502314</v>
@@ -8827,16 +8840,16 @@
         <v>46211.83000291667</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8854,13 +8867,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q114" s="5">
         <v>46232</v>
@@ -8880,7 +8893,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B115" s="8">
         <v>46168.6837971412</v>
@@ -8898,10 +8911,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I115" s="8">
         <v>46220</v>
@@ -8919,13 +8932,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>159</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q115" s="8">
         <v>46220</v>
@@ -8945,7 +8958,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B116" s="5">
         <v>46168.68381362269</v>
@@ -8955,7 +8968,7 @@
         <v>46206.48624146991</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8979,7 +8992,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -8989,12 +9002,12 @@
       <c r="S116" s="6"/>
       <c r="T116" s="6"/>
       <c r="U116" s="11" t="s">
-        <v>62</v>
+        <v>205</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B117" s="8">
         <v>46168.68381783565</v>
@@ -9003,18 +9016,20 @@
         <v>46204.89075866898</v>
       </c>
       <c r="D117" s="8">
-        <v>46211.830007129625</v>
+        <v>46223.57264675926</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I117" s="8">
         <v>46225</v>
       </c>
@@ -9031,13 +9046,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q117" s="8">
         <v>46225</v>
@@ -9051,13 +9066,13 @@
       <c r="T117" s="9">
         <v>1</v>
       </c>
-      <c r="U117" s="11" t="s">
-        <v>62</v>
+      <c r="U117" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B118" s="5">
         <v>46168.683825810185</v>
@@ -9066,18 +9081,20 @@
         <v>46204.89074575232</v>
       </c>
       <c r="D118" s="5">
-        <v>46211.82999423611</v>
+        <v>46223.57192800926</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I118" s="5">
         <v>46231</v>
       </c>
@@ -9094,13 +9111,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -9110,7 +9127,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B119" s="8">
         <v>46168.68383587963</v>
@@ -9119,18 +9136,20 @@
         <v>46204.890660798614</v>
       </c>
       <c r="D119" s="8">
-        <v>46211.82999525463</v>
+        <v>46223.57192443287</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I119" s="8">
         <v>46231</v>
       </c>
@@ -9147,13 +9166,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -9163,7 +9182,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B120" s="5">
         <v>46168.68384034722</v>
@@ -9172,18 +9191,20 @@
         <v>46204.890518506945</v>
       </c>
       <c r="D120" s="5">
-        <v>46204.89052016204</v>
+        <v>46223.571920902774</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I120" s="5">
         <v>46231</v>
       </c>
@@ -9200,13 +9221,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -9216,7 +9237,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B121" s="8">
         <v>46168.683844074076</v>
@@ -9225,18 +9246,20 @@
         <v>46204.890504930554</v>
       </c>
       <c r="D121" s="8">
-        <v>46204.89050689815</v>
+        <v>46223.571917685185</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I121" s="8">
         <v>46231</v>
       </c>
@@ -9253,13 +9276,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9269,27 +9292,29 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B122" s="5">
         <v>46168.683847673616</v>
       </c>
       <c r="C122" s="5">
-        <v>46197.49592710648</v>
+        <v>46223.57183185185</v>
       </c>
       <c r="D122" s="5">
-        <v>46204.890087210646</v>
+        <v>46223.57191195602</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H122" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I122" s="5">
         <v>46231</v>
       </c>
@@ -9306,13 +9331,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9322,7 +9347,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B123" s="8">
         <v>46168.683862453705</v>
@@ -9331,18 +9356,20 @@
         <v>46204.89175555555</v>
       </c>
       <c r="D123" s="8">
-        <v>46204.891766898145</v>
+        <v>46223.57264225694</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H123" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H123" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I123" s="8">
         <v>46232</v>
       </c>
@@ -9359,13 +9386,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q123" s="8">
         <v>46232</v>
@@ -9385,7 +9412,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B124" s="5">
         <v>46168.683867141204</v>
@@ -9394,18 +9421,20 @@
         <v>46204.89097627315</v>
       </c>
       <c r="D124" s="5">
-        <v>46205.61454657407</v>
+        <v>46223.57203607639</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I124" s="5">
         <v>46232</v>
       </c>
@@ -9422,13 +9451,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9438,7 +9467,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B125" s="8">
         <v>46168.683873368056</v>
@@ -9447,18 +9476,20 @@
         <v>46204.891655810185</v>
       </c>
       <c r="D125" s="8">
-        <v>46205.61454702546</v>
+        <v>46223.57203178241</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I125" s="8">
         <v>46232</v>
       </c>
@@ -9475,13 +9506,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9491,7 +9522,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B126" s="5">
         <v>46168.68387903935</v>
@@ -9500,18 +9531,20 @@
         <v>46204.891740266205</v>
       </c>
       <c r="D126" s="5">
-        <v>46205.614544861106</v>
+        <v>46223.5720284375</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H126" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I126" s="5">
         <v>46232</v>
       </c>
@@ -9528,13 +9561,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9544,7 +9577,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B127" s="8">
         <v>46168.683884618054</v>
@@ -9553,18 +9586,20 @@
         <v>46204.891592291664</v>
       </c>
       <c r="D127" s="8">
-        <v>46205.61454555555</v>
+        <v>46223.5720246875</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H127" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H127" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I127" s="8">
         <v>46232</v>
       </c>
@@ -9581,13 +9616,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9597,7 +9632,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B128" s="5">
         <v>46168.68389033565</v>
@@ -9606,18 +9641,20 @@
         <v>46197.49605328703</v>
       </c>
       <c r="D128" s="5">
-        <v>46205.614546122684</v>
+        <v>46223.57201939815</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H128" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I128" s="5">
         <v>46232</v>
       </c>
@@ -9634,13 +9671,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9650,7 +9687,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B129" s="8">
         <v>46168.68391289352</v>
@@ -9659,18 +9696,20 @@
         <v>46204.89298883102</v>
       </c>
       <c r="D129" s="8">
-        <v>46204.89299085648</v>
+        <v>46223.57263847222</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H129" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H129" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I129" s="8">
         <v>46233</v>
       </c>
@@ -9687,13 +9726,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q129" s="8">
         <v>46233</v>
@@ -9713,7 +9752,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B130" s="5">
         <v>46168.68391818287</v>
@@ -9722,18 +9761,20 @@
         <v>46204.89260358796</v>
       </c>
       <c r="D130" s="5">
-        <v>46205.6085181713</v>
+        <v>46223.57212789352</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H130" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I130" s="5">
         <v>46233</v>
       </c>
@@ -9750,13 +9791,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9766,7 +9807,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B131" s="8">
         <v>46168.68393068287</v>
@@ -9775,18 +9816,20 @@
         <v>46204.89265783565</v>
       </c>
       <c r="D131" s="8">
-        <v>46205.60851520833</v>
+        <v>46223.57212385417</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H131" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H131" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I131" s="8">
         <v>46233</v>
       </c>
@@ -9803,13 +9846,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9819,7 +9862,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B132" s="5">
         <v>46168.68393770834</v>
@@ -9828,18 +9871,20 @@
         <v>46204.89272398148</v>
       </c>
       <c r="D132" s="5">
-        <v>46205.608516168984</v>
+        <v>46223.57212008102</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H132" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I132" s="5">
         <v>46233</v>
       </c>
@@ -9856,13 +9901,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9872,7 +9917,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B133" s="8">
         <v>46168.6839434375</v>
@@ -9881,18 +9926,20 @@
         <v>46204.89279275463</v>
       </c>
       <c r="D133" s="8">
-        <v>46205.608518877314</v>
+        <v>46223.57211625</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H133" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H133" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I133" s="8">
         <v>46233</v>
       </c>
@@ -9909,13 +9956,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9925,7 +9972,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B134" s="5">
         <v>46168.68398528935</v>
@@ -9934,18 +9981,20 @@
         <v>46197.49614903935</v>
       </c>
       <c r="D134" s="5">
-        <v>46205.608517326385</v>
+        <v>46223.572111180554</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H134" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I134" s="5">
         <v>46233</v>
       </c>
@@ -9962,13 +10011,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9978,7 +10027,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B135" s="8">
         <v>46168.68401087963</v>
@@ -9987,18 +10036,20 @@
         <v>46204.893422152774</v>
       </c>
       <c r="D135" s="8">
-        <v>46204.893423761576</v>
+        <v>46223.57263368055</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H135" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H135" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I135" s="8">
         <v>46234</v>
       </c>
@@ -10015,13 +10066,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q135" s="8">
         <v>46234</v>
@@ -10041,7 +10092,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B136" s="5">
         <v>46168.68401652778</v>
@@ -10050,18 +10101,20 @@
         <v>46204.89318240741</v>
       </c>
       <c r="D136" s="5">
-        <v>46205.60828351852</v>
+        <v>46223.5722359375</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H136" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I136" s="5">
         <v>46234</v>
       </c>
@@ -10078,13 +10131,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -10094,7 +10147,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B137" s="8">
         <v>46168.68402403935</v>
@@ -10103,18 +10156,20 @@
         <v>46204.89310061342</v>
       </c>
       <c r="D137" s="8">
-        <v>46205.60828236111</v>
+        <v>46223.572232199076</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H137" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H137" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I137" s="8">
         <v>46234</v>
       </c>
@@ -10131,13 +10186,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -10147,7 +10202,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B138" s="5">
         <v>46168.68403127315</v>
@@ -10156,18 +10211,20 @@
         <v>46204.89303716435</v>
       </c>
       <c r="D138" s="5">
-        <v>46205.608284375005</v>
+        <v>46223.5722271875</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H138" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I138" s="5">
         <v>46234</v>
       </c>
@@ -10184,13 +10241,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -10200,7 +10257,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B139" s="8">
         <v>46168.68403755787</v>
@@ -10209,18 +10266,20 @@
         <v>46204.892907511574</v>
       </c>
       <c r="D139" s="8">
-        <v>46205.60828523149</v>
+        <v>46223.57222349537</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H139" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H139" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I139" s="8">
         <v>46234</v>
       </c>
@@ -10237,13 +10296,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -10253,7 +10312,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B140" s="5">
         <v>46168.68404385417</v>
@@ -10262,18 +10321,20 @@
         <v>46197.49627</v>
       </c>
       <c r="D140" s="5">
-        <v>46205.60828666667</v>
+        <v>46223.57221770834</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H140" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I140" s="5">
         <v>46234</v>
       </c>
@@ -10290,13 +10351,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10306,7 +10367,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B141" s="8">
         <v>46168.68406297454</v>
@@ -10315,18 +10376,20 @@
         <v>46206.4858124537</v>
       </c>
       <c r="D141" s="8">
-        <v>46206.48582321759</v>
+        <v>46223.57262464121</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H141" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H141" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I141" s="8">
         <v>46237</v>
       </c>
@@ -10343,13 +10406,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q141" s="8">
         <v>46237</v>
@@ -10369,7 +10432,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B142" s="5">
         <v>46168.68406752315</v>
@@ -10378,18 +10441,20 @@
         <v>46206.48579756945</v>
       </c>
       <c r="D142" s="5">
-        <v>46206.48579965278</v>
+        <v>46223.57235236111</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H142" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I142" s="5">
         <v>46237</v>
       </c>
@@ -10406,13 +10471,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10422,7 +10487,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B143" s="8">
         <v>46168.68407938657</v>
@@ -10431,18 +10496,20 @@
         <v>46206.485788935184</v>
       </c>
       <c r="D143" s="8">
-        <v>46206.48579032408</v>
+        <v>46223.57234864583</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H143" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H143" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I143" s="8">
         <v>46237</v>
       </c>
@@ -10459,13 +10526,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10475,7 +10542,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B144" s="5">
         <v>46168.68408523148</v>
@@ -10484,18 +10551,20 @@
         <v>46206.48578153935</v>
       </c>
       <c r="D144" s="5">
-        <v>46206.48578297454</v>
+        <v>46223.57234428241</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H144" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I144" s="5">
         <v>46237</v>
       </c>
@@ -10512,13 +10581,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10528,7 +10597,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B145" s="8">
         <v>46168.684089884264</v>
@@ -10537,18 +10606,20 @@
         <v>46206.4857743287</v>
       </c>
       <c r="D145" s="8">
-        <v>46206.48577649306</v>
+        <v>46223.572340370374</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H145" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I145" s="8">
         <v>46237</v>
       </c>
@@ -10565,13 +10636,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10581,7 +10652,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B146" s="5">
         <v>46168.684094571756</v>
@@ -10590,18 +10661,20 @@
         <v>46204.8933341088</v>
       </c>
       <c r="D146" s="5">
-        <v>46204.893335671295</v>
+        <v>46223.57233454861</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H146" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I146" s="5">
         <v>46237</v>
       </c>
@@ -10618,13 +10691,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10634,7 +10707,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B147" s="8">
         <v>46168.68414574074</v>
@@ -10643,18 +10716,20 @@
         <v>46206.48621289352</v>
       </c>
       <c r="D147" s="8">
-        <v>46206.486229999995</v>
+        <v>46223.57261809028</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H147" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I147" s="8">
         <v>46239</v>
       </c>
@@ -10671,13 +10746,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="Q147" s="8">
         <v>46239</v>
@@ -10697,7 +10772,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B148" s="5">
         <v>46168.68415105324</v>
@@ -10706,18 +10781,20 @@
         <v>46206.48597313657</v>
       </c>
       <c r="D148" s="5">
-        <v>46211.838432476856</v>
+        <v>46223.572544027775</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H148" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I148" s="5">
         <v>46239</v>
       </c>
@@ -10734,13 +10811,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10750,7 +10827,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B149" s="8">
         <v>46168.68415587963</v>
@@ -10759,18 +10836,20 @@
         <v>46206.48603997685</v>
       </c>
       <c r="D149" s="8">
-        <v>46211.83844157407</v>
+        <v>46223.5725400463</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H149" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I149" s="8">
         <v>46239</v>
       </c>
@@ -10787,13 +10866,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10803,7 +10882,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B150" s="5">
         <v>46168.68416068287</v>
@@ -10812,18 +10891,20 @@
         <v>46206.48609505787</v>
       </c>
       <c r="D150" s="5">
-        <v>46211.83843866899</v>
+        <v>46223.57253650463</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H150" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I150" s="5">
         <v>46239</v>
       </c>
@@ -10840,13 +10921,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10856,7 +10937,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B151" s="8">
         <v>46168.68416431713</v>
@@ -10865,18 +10946,20 @@
         <v>46206.48614579861</v>
       </c>
       <c r="D151" s="8">
-        <v>46211.83844565973</v>
+        <v>46223.5725334375</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H151" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I151" s="8">
         <v>46239</v>
       </c>
@@ -10893,13 +10976,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10909,7 +10992,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B152" s="5">
         <v>46168.68416798611</v>
@@ -10918,18 +11001,20 @@
         <v>46206.48619949074</v>
       </c>
       <c r="D152" s="5">
-        <v>46211.83845115741</v>
+        <v>46223.5725280787</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H152" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I152" s="5">
         <v>46239</v>
       </c>
@@ -10946,13 +11031,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10962,7 +11047,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B153" s="8">
         <v>46168.684183460646</v>
@@ -10974,7 +11059,7 @@
         <v>46211.832724733795</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -10998,7 +11083,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -11015,7 +11100,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B154" s="5">
         <v>46168.68418700232</v>
@@ -11027,16 +11112,16 @@
         <v>46211.8327003125</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I154" s="5">
         <v>46240</v>
@@ -11054,13 +11139,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q154" s="5">
         <v>46240</v>
@@ -11080,7 +11165,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B155" s="8">
         <v>46168.68419359953</v>
@@ -11092,16 +11177,16 @@
         <v>46211.831112581014</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I155" s="8">
         <v>46240</v>
@@ -11119,13 +11204,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -11135,7 +11220,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B156" s="5">
         <v>46168.68419834491</v>
@@ -11147,16 +11232,16 @@
         <v>46211.83112387732</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I156" s="5">
         <v>46240</v>
@@ -11174,13 +11259,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -11190,7 +11275,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B157" s="8">
         <v>46168.684202777775</v>
@@ -11202,16 +11287,16 @@
         <v>46211.83112878472</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I157" s="8">
         <v>46240</v>
@@ -11229,13 +11314,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -11245,7 +11330,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B158" s="5">
         <v>46168.68420710648</v>
@@ -11257,16 +11342,16 @@
         <v>46211.83116206019</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I158" s="5">
         <v>46240</v>
@@ -11284,13 +11369,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -11300,7 +11385,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B159" s="8">
         <v>46168.68421127315</v>
@@ -11312,16 +11397,16 @@
         <v>46211.83117125</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I159" s="8">
         <v>46240</v>
@@ -11339,13 +11424,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -11355,7 +11440,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B160" s="5">
         <v>46168.68422996528</v>
@@ -11367,16 +11452,16 @@
         <v>46211.83117747685</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F160" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I160" s="5">
         <v>46240</v>
@@ -11394,13 +11479,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O160" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11410,7 +11495,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B161" s="8">
         <v>46168.68423341435</v>
@@ -11422,16 +11507,16 @@
         <v>46211.831204988426</v>
       </c>
       <c r="E161" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F161" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I161" s="8">
         <v>46240</v>
@@ -11449,13 +11534,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O161" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11465,7 +11550,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B162" s="5">
         <v>46168.684237037036</v>
@@ -11477,16 +11562,16 @@
         <v>46211.83121074074</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F162" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I162" s="5">
         <v>46240</v>
@@ -11504,13 +11589,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O162" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11520,7 +11605,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B163" s="8">
         <v>46168.68424059028</v>
@@ -11532,16 +11617,16 @@
         <v>46211.83121682871</v>
       </c>
       <c r="E163" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F163" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I163" s="8">
         <v>46240</v>
@@ -11559,13 +11644,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O163" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11575,7 +11660,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B164" s="5">
         <v>46168.68424420139</v>
@@ -11587,16 +11672,16 @@
         <v>46211.83124355324</v>
       </c>
       <c r="E164" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F164" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I164" s="5">
         <v>46240</v>
@@ -11614,13 +11699,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O164" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11630,7 +11715,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B165" s="8">
         <v>46168.68424778935</v>
@@ -11642,16 +11727,16 @@
         <v>46211.83125052083</v>
       </c>
       <c r="E165" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F165" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="I165" s="8">
         <v>46240</v>
@@ -11669,13 +11754,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="O165" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11685,7 +11770,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B166" s="5">
         <v>46168.68425820602</v>
@@ -11694,18 +11779,20 @@
         <v>46211.83055506945</v>
       </c>
       <c r="D166" s="5">
-        <v>46211.83114409722</v>
+        <v>46223.57301792824</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G166" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H166" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H166" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I166" s="6"/>
       <c r="J166" s="5">
         <v>46241</v>
@@ -11720,13 +11807,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q166" s="5">
         <v>46241</v>
@@ -11740,13 +11827,13 @@
       <c r="T166" s="6">
         <v>1</v>
       </c>
-      <c r="U166" s="11" t="s">
-        <v>62</v>
+      <c r="U166" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B167" s="8">
         <v>46168.68426255787</v>
@@ -11755,18 +11842,20 @@
         <v>46209.71549736111</v>
       </c>
       <c r="D167" s="8">
-        <v>46211.83112083333</v>
+        <v>46223.5729158912</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G167" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H167" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H167" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I167" s="9"/>
       <c r="J167" s="8">
         <v>46241</v>
@@ -11781,13 +11870,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11797,7 +11886,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B168" s="5">
         <v>46168.68426704861</v>
@@ -11806,18 +11895,20 @@
         <v>46209.71563954861</v>
       </c>
       <c r="D168" s="5">
-        <v>46211.83112822917</v>
+        <v>46223.57291190972</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G168" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H168" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H168" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I168" s="6"/>
       <c r="J168" s="5">
         <v>46241</v>
@@ -11832,13 +11923,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11848,7 +11939,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B169" s="8">
         <v>46168.68427162037</v>
@@ -11857,18 +11948,20 @@
         <v>46209.7157528588</v>
       </c>
       <c r="D169" s="8">
-        <v>46211.83113427083</v>
+        <v>46223.57290799769</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G169" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H169" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H169" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I169" s="9"/>
       <c r="J169" s="8">
         <v>46241</v>
@@ -11883,13 +11976,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11899,7 +11992,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B170" s="5">
         <v>46168.68427627315</v>
@@ -11908,18 +12001,20 @@
         <v>46209.71582945602</v>
       </c>
       <c r="D170" s="5">
-        <v>46211.83116765047</v>
+        <v>46223.57290423611</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G170" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H170" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H170" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
         <v>46241</v>
@@ -11934,13 +12029,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11950,7 +12045,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B171" s="8">
         <v>46168.68428068287</v>
@@ -11959,18 +12054,20 @@
         <v>46209.71609789351</v>
       </c>
       <c r="D171" s="8">
-        <v>46211.831175914354</v>
+        <v>46223.57290035879</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G171" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H171" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H171" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I171" s="9"/>
       <c r="J171" s="8">
         <v>46241</v>
@@ -11985,13 +12082,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -12001,7 +12098,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B172" s="5">
         <v>46168.684336226856</v>
@@ -12010,18 +12107,20 @@
         <v>46211.83065361111</v>
       </c>
       <c r="D172" s="5">
-        <v>46211.83118184027</v>
+        <v>46223.57289640047</v>
       </c>
       <c r="E172" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F172" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G172" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H172" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H172" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
         <v>46241</v>
@@ -12036,13 +12135,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O172" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -12052,7 +12151,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B173" s="8">
         <v>46168.68434010417</v>
@@ -12061,18 +12160,20 @@
         <v>46211.830803923614</v>
       </c>
       <c r="D173" s="8">
-        <v>46211.831210868055</v>
+        <v>46223.57289268519</v>
       </c>
       <c r="E173" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F173" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G173" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H173" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H173" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I173" s="9"/>
       <c r="J173" s="8">
         <v>46241</v>
@@ -12087,13 +12188,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O173" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -12103,7 +12204,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B174" s="5">
         <v>46168.68434423611</v>
@@ -12112,18 +12213,20 @@
         <v>46211.83087340278</v>
       </c>
       <c r="D174" s="5">
-        <v>46211.83121509259</v>
+        <v>46223.572888229166</v>
       </c>
       <c r="E174" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F174" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G174" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H174" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H174" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I174" s="6"/>
       <c r="J174" s="5">
         <v>46241</v>
@@ -12138,13 +12241,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O174" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -12154,7 +12257,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B175" s="8">
         <v>46168.684348263894</v>
@@ -12163,18 +12266,20 @@
         <v>46211.83096753473</v>
       </c>
       <c r="D175" s="8">
-        <v>46211.831221932865</v>
+        <v>46223.57288417824</v>
       </c>
       <c r="E175" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F175" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G175" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H175" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H175" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I175" s="9"/>
       <c r="J175" s="8">
         <v>46241</v>
@@ -12189,13 +12294,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O175" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -12205,7 +12310,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B176" s="5">
         <v>46168.68435202546</v>
@@ -12214,18 +12319,20 @@
         <v>46211.83104849537</v>
       </c>
       <c r="D176" s="5">
-        <v>46211.831248912036</v>
+        <v>46223.57287741898</v>
       </c>
       <c r="E176" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F176" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G176" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H176" s="6"/>
+        <v>98</v>
+      </c>
+      <c r="H176" s="6" t="s">
+        <v>98</v>
+      </c>
       <c r="I176" s="6"/>
       <c r="J176" s="5">
         <v>46241</v>
@@ -12240,13 +12347,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O176" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -12256,7 +12363,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B177" s="8">
         <v>46168.68435652778</v>
@@ -12265,18 +12372,20 @@
         <v>46211.83112699074</v>
       </c>
       <c r="D177" s="8">
-        <v>46211.831259189814</v>
+        <v>46223.572876782404</v>
       </c>
       <c r="E177" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F177" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G177" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H177" s="9"/>
+        <v>98</v>
+      </c>
+      <c r="H177" s="9" t="s">
+        <v>98</v>
+      </c>
       <c r="I177" s="9"/>
       <c r="J177" s="8">
         <v>46241</v>
@@ -12291,13 +12400,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O177" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -12307,7 +12416,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B178" s="5">
         <v>46168.68437314815</v>
@@ -12319,16 +12428,16 @@
         <v>46209.715354976855</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -12344,13 +12453,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="Q178" s="5">
         <v>46244</v>
@@ -12370,7 +12479,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B179" s="8">
         <v>46168.68437847222</v>
@@ -12382,16 +12491,16 @@
         <v>46209.71550439815</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H179" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I179" s="8">
         <v>46244</v>
@@ -12409,13 +12518,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
@@ -12425,7 +12534,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B180" s="5">
         <v>46168.68438821759</v>
@@ -12437,16 +12546,16 @@
         <v>46209.7156449537</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I180" s="5">
         <v>46244</v>
@@ -12464,13 +12573,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12480,7 +12589,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B181" s="8">
         <v>46168.684394537035</v>
@@ -12492,16 +12601,16 @@
         <v>46209.715759733794</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H181" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I181" s="8">
         <v>46244</v>
@@ -12519,13 +12628,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12535,7 +12644,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B182" s="5">
         <v>46168.68439944445</v>
@@ -12547,16 +12656,16 @@
         <v>46209.71583459491</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I182" s="5">
         <v>46244</v>
@@ -12574,13 +12683,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12590,7 +12699,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B183" s="8">
         <v>46168.684404375</v>
@@ -12602,16 +12711,16 @@
         <v>46209.71610449074</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H183" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I183" s="8">
         <v>46244</v>
@@ -12629,13 +12738,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12645,7 +12754,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B184" s="5">
         <v>46168.6844190625</v>
@@ -12657,16 +12766,16 @@
         <v>46211.83066165509</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F184" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I184" s="5">
         <v>46244</v>
@@ -12684,13 +12793,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O184" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12700,7 +12809,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B185" s="8">
         <v>46168.68442277778</v>
@@ -12712,16 +12821,16 @@
         <v>46211.83081103009</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H185" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I185" s="8">
         <v>46244</v>
@@ -12739,13 +12848,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O185" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12755,7 +12864,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B186" s="5">
         <v>46168.68442653935</v>
@@ -12767,16 +12876,16 @@
         <v>46211.83088054398</v>
       </c>
       <c r="E186" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F186" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I186" s="5">
         <v>46244</v>
@@ -12794,13 +12903,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O186" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12810,7 +12919,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B187" s="8">
         <v>46168.684429988425</v>
@@ -12822,16 +12931,16 @@
         <v>46211.83097425926</v>
       </c>
       <c r="E187" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F187" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G187" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H187" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I187" s="8">
         <v>46244</v>
@@ -12849,13 +12958,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O187" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12865,7 +12974,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B188" s="5">
         <v>46168.68443359954</v>
@@ -12877,16 +12986,16 @@
         <v>46211.83105417824</v>
       </c>
       <c r="E188" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F188" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I188" s="5">
         <v>46244</v>
@@ -12904,13 +13013,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O188" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12920,7 +13029,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B189" s="8">
         <v>46168.68443729167</v>
@@ -12932,16 +13041,16 @@
         <v>46211.8311371412</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F189" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I189" s="8">
         <v>46244</v>
@@ -12959,13 +13068,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="O189" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -12975,7 +13084,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B190" s="5">
         <v>46168.6844840625</v>
@@ -12984,19 +13093,19 @@
         <v>46211.83022659722</v>
       </c>
       <c r="D190" s="5">
-        <v>46211.830323738424</v>
+        <v>46223.57240934028</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I190" s="5">
         <v>46245</v>
@@ -13014,13 +13123,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Q190" s="5">
         <v>46245</v>
@@ -13034,13 +13143,13 @@
       <c r="T190" s="6">
         <v>1</v>
       </c>
-      <c r="U190" s="11" t="s">
-        <v>62</v>
+      <c r="U190" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B191" s="8">
         <v>46168.68449130787</v>
@@ -13052,16 +13161,16 @@
         <v>46211.830295844906</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="8">
@@ -13077,13 +13186,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -13093,7 +13202,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B192" s="5">
         <v>46168.68449590278</v>
@@ -13105,16 +13214,16 @@
         <v>46211.83029662037</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -13130,13 +13239,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -13146,7 +13255,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B193" s="8">
         <v>46168.68450027778</v>
@@ -13158,16 +13267,16 @@
         <v>46211.83029733796</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="8">
@@ -13183,13 +13292,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -13199,7 +13308,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B194" s="5">
         <v>46168.68450480324</v>
@@ -13211,16 +13320,16 @@
         <v>46211.83029778935</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="5">
@@ -13236,13 +13345,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -13252,7 +13361,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="B195" s="8">
         <v>46168.68450934028</v>
@@ -13264,16 +13373,16 @@
         <v>46211.83029865741</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I195" s="9"/>
       <c r="J195" s="8">
@@ -13289,13 +13398,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -13305,7 +13414,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B196" s="5">
         <v>46168.684523414355</v>
@@ -13317,16 +13426,16 @@
         <v>46211.83029902777</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -13342,13 +13451,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O196" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -13358,7 +13467,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B197" s="8">
         <v>46168.6845271412</v>
@@ -13370,16 +13479,16 @@
         <v>46211.83029945602</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I197" s="9"/>
       <c r="J197" s="8">
@@ -13395,13 +13504,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -13411,7 +13520,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B198" s="5">
         <v>46168.68453511574</v>
@@ -13423,16 +13532,16 @@
         <v>46211.830299953705</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13448,13 +13557,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O198" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13464,7 +13573,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B199" s="8">
         <v>46168.68453863426</v>
@@ -13476,16 +13585,16 @@
         <v>46211.83030041667</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I199" s="9"/>
       <c r="J199" s="8">
@@ -13501,13 +13610,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O199" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13517,7 +13626,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B200" s="5">
         <v>46168.68454210648</v>
@@ -13529,16 +13638,16 @@
         <v>46211.830300891204</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13554,13 +13663,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O200" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13570,7 +13679,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B201" s="8">
         <v>46168.684545578704</v>
@@ -13582,16 +13691,16 @@
         <v>46211.83030140046</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="8">
@@ -13607,13 +13716,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O201" s="9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13623,7 +13732,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B202" s="5">
         <v>46168.684555775464</v>
@@ -13633,7 +13742,7 @@
         <v>46168.8618759838</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>25</v>
@@ -13657,7 +13766,7 @@
         <v>26</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>26</v>
@@ -13670,7 +13779,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B203" s="8">
         <v>46168.6845594676</v>
@@ -13680,16 +13789,16 @@
         <v>46211.83025064815</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="I203" s="8">
         <v>46246</v>
@@ -13707,13 +13816,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q203" s="8">
         <v>46246</v>
@@ -13728,12 +13837,12 @@
         <v>0</v>
       </c>
       <c r="U203" s="11" t="s">
-        <v>62</v>
+        <v>205</v>
       </c>
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B204" s="5">
         <v>46168.68456425926</v>
@@ -13743,16 +13852,16 @@
         <v>46211.83025032407</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G204" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H204" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="H204" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="I204" s="5">
         <v>46246</v>
@@ -13770,13 +13879,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Q204" s="5">
         <v>46246</v>
@@ -13791,12 +13900,12 @@
         <v>0</v>
       </c>
       <c r="U204" s="11" t="s">
-        <v>62</v>
+        <v>205</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B205" s="8">
         <v>46168.68457049769</v>
@@ -13806,7 +13915,7 @@
         <v>46168.86234542824</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>25</v>
@@ -13830,7 +13939,7 @@
         <v>26</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="P205" s="9" t="s">
         <v>26</v>
@@ -13849,7 +13958,7 @@
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B206" s="5">
         <v>46168.68457415509</v>
@@ -13859,7 +13968,7 @@
         <v>46211.830253541666</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13886,13 +13995,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Q206" s="5">
         <v>46246</v>
@@ -13907,12 +14016,12 @@
         <v>0</v>
       </c>
       <c r="U206" s="11" t="s">
-        <v>62</v>
+        <v>205</v>
       </c>
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B207" s="8">
         <v>46168.68457920139</v>
@@ -13922,7 +14031,7 @@
         <v>46168.868795937495</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>26</v>
@@ -13949,13 +14058,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="Q207" s="8">
         <v>46255</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -5263,7 +5263,7 @@
         <v>46204.86077883102</v>
       </c>
       <c r="D52" s="5">
-        <v>46205.61765122685</v>
+        <v>46224.18342847222</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>181</v>
@@ -5307,8 +5307,8 @@
       <c r="R52" s="5">
         <v>46231</v>
       </c>
-      <c r="S52" s="10" t="s">
-        <v>32</v>
+      <c r="S52" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -7911,7 +7911,7 @@
         <v>46197.85007665509</v>
       </c>
       <c r="D98" s="5">
-        <v>46223.573061076386</v>
+        <v>46224.175157731486</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>298</v>
@@ -7955,8 +7955,8 @@
       <c r="R98" s="5">
         <v>46223</v>
       </c>
-      <c r="S98" s="11" t="s">
-        <v>61</v>
+      <c r="S98" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
@@ -9016,7 +9016,7 @@
         <v>46204.89075866898</v>
       </c>
       <c r="D117" s="8">
-        <v>46223.57264675926</v>
+        <v>46224.18342798611</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>344</v>
@@ -9060,8 +9060,8 @@
       <c r="R117" s="8">
         <v>46231</v>
       </c>
-      <c r="S117" s="10" t="s">
-        <v>32</v>
+      <c r="S117" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T117" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -969,7 +969,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7571,7 +7571,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46213.20753342593</v>
+        <v>46224.878386331024</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -969,7 +969,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7571,7 +7571,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46224.878386331024</v>
+        <v>46225.00959119213</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>
@@ -8251,7 +8251,7 @@
         <v>46204.89009226851</v>
       </c>
       <c r="D104" s="5">
-        <v>46217.19617538195</v>
+        <v>46225.167433888884</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>312</v>
@@ -8295,8 +8295,8 @@
       <c r="R104" s="5">
         <v>46224</v>
       </c>
-      <c r="S104" s="11" t="s">
-        <v>61</v>
+      <c r="S104" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
@@ -8837,7 +8837,7 @@
         <v>46211.82998440972</v>
       </c>
       <c r="D114" s="5">
-        <v>46211.83000291667</v>
+        <v>46225.18216611111</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>336</v>
@@ -8881,8 +8881,8 @@
       <c r="R114" s="5">
         <v>46232</v>
       </c>
-      <c r="S114" s="10" t="s">
-        <v>32</v>
+      <c r="S114" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T114" s="6">
         <v>1</v>
@@ -9356,7 +9356,7 @@
         <v>46204.89175555555</v>
       </c>
       <c r="D123" s="8">
-        <v>46223.57264225694</v>
+        <v>46225.182165729166</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>356</v>
@@ -9400,8 +9400,8 @@
       <c r="R123" s="8">
         <v>46232</v>
       </c>
-      <c r="S123" s="10" t="s">
-        <v>32</v>
+      <c r="S123" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T123" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -969,7 +969,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA</t>
+    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7571,7 +7571,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46225.00959119213</v>
+        <v>46225.58945488426</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="537">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="538">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -408,6 +408,9 @@
     <t>propuesta nucleo rodete ot 4335 - 4337 -4339</t>
   </si>
   <si>
+    <t>NATALYA ESPINOZA</t>
+  </si>
+  <si>
     <t>nespinoza@zitron.com</t>
   </si>
   <si>
@@ -969,7 +972,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A </t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -3673,7 +3676,7 @@
         <v>98</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I26" s="5">
         <v>46157</v>
@@ -3697,7 +3700,7 @@
         <v>81</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q26" s="5">
         <v>46157</v>
@@ -3717,7 +3720,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B27" s="8">
         <v>46168.68321476852</v>
@@ -3729,7 +3732,7 @@
         <v>46223.5717261574</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3738,7 +3741,7 @@
         <v>98</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I27" s="8">
         <v>46189</v>
@@ -3759,10 +3762,10 @@
         <v>88</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="Q27" s="8">
         <v>46189</v>
@@ -3771,7 +3774,7 @@
         <v>46190</v>
       </c>
       <c r="S27" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T27" s="9">
         <v>1</v>
@@ -3782,7 +3785,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B28" s="5">
         <v>46168.68321959491</v>
@@ -3794,7 +3797,7 @@
         <v>46223.57172274306</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3803,7 +3806,7 @@
         <v>98</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I28" s="5">
         <v>46189</v>
@@ -3824,10 +3827,10 @@
         <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="Q28" s="5">
         <v>46189</v>
@@ -3836,7 +3839,7 @@
         <v>46190</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
@@ -3847,7 +3850,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B29" s="8">
         <v>46168.68322341435</v>
@@ -3859,7 +3862,7 @@
         <v>46223.571718969906</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3868,7 +3871,7 @@
         <v>98</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I29" s="8">
         <v>46189</v>
@@ -3889,10 +3892,10 @@
         <v>88</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Q29" s="8">
         <v>46189</v>
@@ -3901,7 +3904,7 @@
         <v>46190</v>
       </c>
       <c r="S29" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3912,7 +3915,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B30" s="5">
         <v>46168.683227245376</v>
@@ -3924,7 +3927,7 @@
         <v>46223.57171402778</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3933,7 +3936,7 @@
         <v>98</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I30" s="5">
         <v>46189</v>
@@ -3954,10 +3957,10 @@
         <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="Q30" s="5">
         <v>46189</v>
@@ -3966,7 +3969,7 @@
         <v>46190</v>
       </c>
       <c r="S30" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3977,7 +3980,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B31" s="8">
         <v>46168.683231365736</v>
@@ -3989,7 +3992,7 @@
         <v>46193.553499305555</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -4022,7 +4025,7 @@
         <v>51</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="8">
         <v>46157</v>
@@ -4042,7 +4045,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B32" s="5">
         <v>46168.682992511574</v>
@@ -4054,7 +4057,7 @@
         <v>46205.61594793982</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -4078,7 +4081,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -4095,7 +4098,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" s="8">
         <v>46168.68327652778</v>
@@ -4107,16 +4110,16 @@
         <v>46195.928396574076</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I33" s="8">
         <v>46161</v>
@@ -4134,13 +4137,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q33" s="8">
         <v>46161</v>
@@ -4160,7 +4163,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B34" s="5">
         <v>46168.68328149305</v>
@@ -4172,16 +4175,16 @@
         <v>46195.9258303588</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -4199,13 +4202,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4216,12 +4219,12 @@
         <v>0</v>
       </c>
       <c r="U34" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B35" s="8">
         <v>46168.68328653935</v>
@@ -4233,16 +4236,16 @@
         <v>46195.928370243055</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I35" s="8">
         <v>46164</v>
@@ -4260,13 +4263,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -4277,12 +4280,12 @@
         <v>0</v>
       </c>
       <c r="U35" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B36" s="5">
         <v>46168.68329140046</v>
@@ -4294,16 +4297,16 @@
         <v>46185.182775243054</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I36" s="5">
         <v>46161</v>
@@ -4321,13 +4324,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q36" s="5">
         <v>46161</v>
@@ -4336,7 +4339,7 @@
         <v>46184</v>
       </c>
       <c r="S36" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4347,7 +4350,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B37" s="8">
         <v>46168.68329584491</v>
@@ -4359,16 +4362,16 @@
         <v>46184.70350368056</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I37" s="8">
         <v>46161</v>
@@ -4386,13 +4389,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>97</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -4403,12 +4406,12 @@
         <v>0</v>
       </c>
       <c r="U37" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>46168.68330070602</v>
@@ -4420,16 +4423,16 @@
         <v>46184.703557789355</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I38" s="5">
         <v>46164</v>
@@ -4447,13 +4450,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4464,12 +4467,12 @@
         <v>0</v>
       </c>
       <c r="U38" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B39" s="8">
         <v>46168.68330542824</v>
@@ -4481,16 +4484,16 @@
         <v>46205.60819122686</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I39" s="8">
         <v>46161</v>
@@ -4508,13 +4511,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q39" s="8">
         <v>46161</v>
@@ -4523,7 +4526,7 @@
         <v>46198</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4534,7 +4537,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B40" s="5">
         <v>46168.683310092594</v>
@@ -4546,16 +4549,16 @@
         <v>46195.92587128472</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I40" s="5">
         <v>46161</v>
@@ -4573,13 +4576,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4590,12 +4593,12 @@
         <v>0</v>
       </c>
       <c r="U40" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B41" s="8">
         <v>46168.68331519676</v>
@@ -4607,16 +4610,16 @@
         <v>46205.60793128472</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I41" s="8">
         <v>46170</v>
@@ -4634,13 +4637,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4651,12 +4654,12 @@
         <v>0</v>
       </c>
       <c r="U41" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" s="5">
         <v>46168.68332027778</v>
@@ -4668,16 +4671,16 @@
         <v>46195.92587850694</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I42" s="5">
         <v>46170</v>
@@ -4695,13 +4698,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4712,12 +4715,12 @@
         <v>0</v>
       </c>
       <c r="U42" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B43" s="8">
         <v>46168.68332520833</v>
@@ -4729,16 +4732,16 @@
         <v>46220.18799388889</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I43" s="8">
         <v>46161</v>
@@ -4756,10 +4759,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4771,7 +4774,7 @@
         <v>46219</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4782,7 +4785,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" s="5">
         <v>46168.68332880787</v>
@@ -4794,16 +4797,16 @@
         <v>46195.92577891204</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I44" s="5">
         <v>46161</v>
@@ -4821,13 +4824,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4837,7 +4840,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B45" s="8">
         <v>46168.683333113426</v>
@@ -4849,16 +4852,16 @@
         <v>46195.92857017361</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I45" s="8">
         <v>46171</v>
@@ -4876,13 +4879,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4892,7 +4895,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" s="5">
         <v>46168.683337291666</v>
@@ -4904,16 +4907,16 @@
         <v>46204.1978837037</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46191</v>
@@ -4931,13 +4934,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Q46" s="5">
         <v>46191</v>
@@ -4946,7 +4949,7 @@
         <v>46203</v>
       </c>
       <c r="S46" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4957,7 +4960,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B47" s="8">
         <v>46168.68334179398</v>
@@ -4969,16 +4972,16 @@
         <v>46199.564988564816</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46191</v>
@@ -4996,13 +4999,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -5013,12 +5016,12 @@
         <v>0</v>
       </c>
       <c r="U47" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B48" s="5">
         <v>46168.68334684028</v>
@@ -5030,16 +5033,16 @@
         <v>46199.5650378125</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46195</v>
@@ -5057,13 +5060,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -5074,12 +5077,12 @@
         <v>0</v>
       </c>
       <c r="U48" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B49" s="8">
         <v>46168.68335195602</v>
@@ -5091,16 +5094,16 @@
         <v>46204.19788363426</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46191</v>
@@ -5118,10 +5121,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -5133,7 +5136,7 @@
         <v>46203</v>
       </c>
       <c r="S49" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -5144,7 +5147,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B50" s="5">
         <v>46168.68335582176</v>
@@ -5156,16 +5159,16 @@
         <v>46199.56512275463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46191</v>
@@ -5183,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -5199,7 +5202,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B51" s="8">
         <v>46168.683360428244</v>
@@ -5211,16 +5214,16 @@
         <v>46199.56520053241</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46195</v>
@@ -5238,13 +5241,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5254,7 +5257,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B52" s="5">
         <v>46168.68336471065</v>
@@ -5266,16 +5269,16 @@
         <v>46224.18342847222</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -5293,10 +5296,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -5319,7 +5322,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B53" s="8">
         <v>46168.68337377315</v>
@@ -5331,16 +5334,16 @@
         <v>46204.601485555555</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46191</v>
@@ -5358,13 +5361,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5374,7 +5377,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B54" s="5">
         <v>46168.683378194444</v>
@@ -5386,16 +5389,16 @@
         <v>46204.601540787036</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46202</v>
@@ -5413,13 +5416,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5429,7 +5432,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B55" s="8">
         <v>46168.68338271991</v>
@@ -5441,16 +5444,16 @@
         <v>46205.644352627314</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I55" s="8">
         <v>46231</v>
@@ -5468,10 +5471,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5484,7 +5487,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B56" s="5">
         <v>46168.683385868055</v>
@@ -5496,16 +5499,16 @@
         <v>46204.19788391204</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I56" s="5">
         <v>46191</v>
@@ -5523,10 +5526,10 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5538,7 +5541,7 @@
         <v>46203</v>
       </c>
       <c r="S56" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5549,7 +5552,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B57" s="8">
         <v>46168.68343064815</v>
@@ -5561,16 +5564,16 @@
         <v>46199.56535409723</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I57" s="8">
         <v>46191</v>
@@ -5588,13 +5591,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5604,7 +5607,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B58" s="5">
         <v>46168.683436956024</v>
@@ -5616,16 +5619,16 @@
         <v>46199.56544034722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I58" s="5">
         <v>46195</v>
@@ -5643,13 +5646,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5659,7 +5662,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B59" s="8">
         <v>46168.68344221065</v>
@@ -5669,7 +5672,7 @@
         <v>46210.52421333334</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5693,7 +5696,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5703,12 +5706,12 @@
       <c r="S59" s="9"/>
       <c r="T59" s="9"/>
       <c r="U59" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B60" s="5">
         <v>46168.683445787035</v>
@@ -5720,16 +5723,16 @@
         <v>46184.518844583334</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I60" s="5">
         <v>46167</v>
@@ -5747,13 +5750,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q60" s="5">
         <v>46167</v>
@@ -5762,7 +5765,7 @@
         <v>46171</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -5773,7 +5776,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46168.6865996875</v>
@@ -5785,16 +5788,16 @@
         <v>46184.51878665509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I61" s="8">
         <v>46167</v>
@@ -5812,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5828,7 +5831,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B62" s="5">
         <v>46168.68683460648</v>
@@ -5840,16 +5843,16 @@
         <v>46184.518791319446</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46167</v>
@@ -5867,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5883,7 +5886,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B63" s="8">
         <v>46168.686918437495</v>
@@ -5895,16 +5898,16 @@
         <v>46184.51879930556</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I63" s="8">
         <v>46167</v>
@@ -5922,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5938,7 +5941,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B64" s="5">
         <v>46168.687254143515</v>
@@ -5950,16 +5953,16 @@
         <v>46184.5188068287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46167</v>
@@ -5977,13 +5980,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5993,7 +5996,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B65" s="8">
         <v>46168.68731635417</v>
@@ -6005,16 +6008,16 @@
         <v>46184.51881454861</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I65" s="8">
         <v>46167</v>
@@ -6032,13 +6035,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -6048,7 +6051,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B66" s="5">
         <v>46168.68345142361</v>
@@ -6060,16 +6063,16 @@
         <v>46190.605242708334</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46181</v>
@@ -6087,13 +6090,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q66" s="5">
         <v>46181</v>
@@ -6102,7 +6105,7 @@
         <v>46185</v>
       </c>
       <c r="S66" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -6113,7 +6116,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B67" s="8">
         <v>46168.68857346065</v>
@@ -6125,16 +6128,16 @@
         <v>46190.60518608797</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H67" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I67" s="8">
         <v>46181</v>
@@ -6152,13 +6155,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -6168,7 +6171,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B68" s="5">
         <v>46168.688608275465</v>
@@ -6180,16 +6183,16 @@
         <v>46190.60519502315</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46181</v>
@@ -6207,13 +6210,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6223,7 +6226,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B69" s="8">
         <v>46168.68864659722</v>
@@ -6235,16 +6238,16 @@
         <v>46190.605203761574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I69" s="8">
         <v>46181</v>
@@ -6262,13 +6265,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6278,7 +6281,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B70" s="5">
         <v>46168.68868637731</v>
@@ -6290,16 +6293,16 @@
         <v>46190.605208946756</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I70" s="5">
         <v>46181</v>
@@ -6317,13 +6320,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6333,7 +6336,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B71" s="8">
         <v>46168.68871934028</v>
@@ -6345,16 +6348,16 @@
         <v>46190.60521709491</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I71" s="8">
         <v>46181</v>
@@ -6372,13 +6375,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -6388,7 +6391,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B72" s="5">
         <v>46168.68345790509</v>
@@ -6400,16 +6403,16 @@
         <v>46190.6054244213</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I72" s="5">
         <v>46188</v>
@@ -6427,13 +6430,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q72" s="5">
         <v>46188</v>
@@ -6442,7 +6445,7 @@
         <v>46188</v>
       </c>
       <c r="S72" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -6453,7 +6456,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B73" s="8">
         <v>46168.68880178241</v>
@@ -6465,16 +6468,16 @@
         <v>46190.60536361111</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -6492,13 +6495,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6508,7 +6511,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B74" s="5">
         <v>46168.68883857639</v>
@@ -6520,16 +6523,16 @@
         <v>46190.605368206016</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I74" s="5">
         <v>46188</v>
@@ -6547,13 +6550,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q74" s="6"/>
       <c r="R74" s="6"/>
@@ -6563,7 +6566,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B75" s="8">
         <v>46168.688875775464</v>
@@ -6575,16 +6578,16 @@
         <v>46190.605373530096</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I75" s="8">
         <v>46188</v>
@@ -6602,13 +6605,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6618,7 +6621,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B76" s="5">
         <v>46168.6889172338</v>
@@ -6630,16 +6633,16 @@
         <v>46190.60539957176</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I76" s="5">
         <v>46188</v>
@@ -6657,13 +6660,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6673,7 +6676,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B77" s="8">
         <v>46168.688956620375</v>
@@ -6685,16 +6688,16 @@
         <v>46190.60538814815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I77" s="8">
         <v>46188</v>
@@ -6712,10 +6715,10 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6728,7 +6731,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B78" s="5">
         <v>46168.683480625</v>
@@ -6740,16 +6743,16 @@
         <v>46211.83847391204</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6765,10 +6768,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6791,7 +6794,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B79" s="8">
         <v>46168.683484629626</v>
@@ -6803,16 +6806,16 @@
         <v>46211.83842664352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I79" s="8">
         <v>46238</v>
@@ -6830,13 +6833,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6846,7 +6849,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B80" s="5">
         <v>46168.683488877316</v>
@@ -6858,16 +6861,16 @@
         <v>46211.83843200232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I80" s="5">
         <v>46238</v>
@@ -6885,13 +6888,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6901,7 +6904,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B81" s="8">
         <v>46168.68349300926</v>
@@ -6913,16 +6916,16 @@
         <v>46211.83843496528</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46238</v>
@@ -6940,13 +6943,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6956,7 +6959,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B82" s="5">
         <v>46168.6834959375</v>
@@ -6968,16 +6971,16 @@
         <v>46211.83844040509</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46238</v>
@@ -6995,13 +6998,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -7011,7 +7014,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B83" s="8">
         <v>46168.68349899305</v>
@@ -7023,16 +7026,16 @@
         <v>46211.83844619213</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46238</v>
@@ -7050,13 +7053,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -7066,7 +7069,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B84" s="5">
         <v>46168.68351101852</v>
@@ -7078,7 +7081,7 @@
         <v>46205.618076087965</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -7102,7 +7105,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -7119,7 +7122,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B85" s="8">
         <v>46168.68351447917</v>
@@ -7131,16 +7134,16 @@
         <v>46206.18878055556</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I85" s="8">
         <v>46204</v>
@@ -7158,13 +7161,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q85" s="8">
         <v>46204</v>
@@ -7173,7 +7176,7 @@
         <v>46205</v>
       </c>
       <c r="S85" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -7184,7 +7187,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B86" s="5">
         <v>46168.68352011574</v>
@@ -7196,16 +7199,16 @@
         <v>46223.57312579861</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I86" s="5">
         <v>46206</v>
@@ -7223,13 +7226,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q86" s="5">
         <v>46206</v>
@@ -7238,7 +7241,7 @@
         <v>46209</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -7249,7 +7252,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B87" s="8">
         <v>46168.68352736111</v>
@@ -7261,16 +7264,16 @@
         <v>46206.18878028935</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -7288,13 +7291,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -7303,7 +7306,7 @@
         <v>46205</v>
       </c>
       <c r="S87" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -7314,7 +7317,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B88" s="5">
         <v>46168.68353292824</v>
@@ -7326,16 +7329,16 @@
         <v>46223.573107916665</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I88" s="5">
         <v>46206</v>
@@ -7353,13 +7356,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q88" s="5">
         <v>46206</v>
@@ -7368,7 +7371,7 @@
         <v>46209</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -7379,7 +7382,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B89" s="8">
         <v>46168.68353787037</v>
@@ -7391,16 +7394,16 @@
         <v>46206.1887803125</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7418,13 +7421,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q89" s="8">
         <v>46204</v>
@@ -7433,7 +7436,7 @@
         <v>46205</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T89" s="9">
         <v>1</v>
@@ -7444,7 +7447,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B90" s="5">
         <v>46168.68354247685</v>
@@ -7456,16 +7459,16 @@
         <v>46223.573090949074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I90" s="5">
         <v>46206</v>
@@ -7483,13 +7486,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q90" s="5">
         <v>46206</v>
@@ -7498,7 +7501,7 @@
         <v>46209</v>
       </c>
       <c r="S90" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
@@ -7509,7 +7512,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B91" s="8">
         <v>46168.68354741899</v>
@@ -7521,7 +7524,7 @@
         <v>46211.83134737269</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>25</v>
@@ -7545,7 +7548,7 @@
         <v>26</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>26</v>
@@ -7562,7 +7565,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B92" s="5">
         <v>46168.68355052083</v>
@@ -7571,19 +7574,19 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46225.58945488426</v>
+        <v>46225.86187162037</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7601,13 +7604,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q92" s="5">
         <v>46210</v>
@@ -7616,7 +7619,7 @@
         <v>46212</v>
       </c>
       <c r="S92" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -7627,7 +7630,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B93" s="8">
         <v>46168.68356208333</v>
@@ -7639,16 +7642,16 @@
         <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I93" s="8">
         <v>46210</v>
@@ -7666,13 +7669,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7682,7 +7685,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B94" s="5">
         <v>46168.68356922454</v>
@@ -7694,16 +7697,16 @@
         <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7721,13 +7724,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7737,7 +7740,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B95" s="8">
         <v>46168.683574780094</v>
@@ -7749,16 +7752,16 @@
         <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I95" s="8">
         <v>46210</v>
@@ -7776,13 +7779,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7792,7 +7795,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B96" s="5">
         <v>46168.68358024306</v>
@@ -7804,16 +7807,16 @@
         <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7831,13 +7834,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7847,7 +7850,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B97" s="8">
         <v>46168.68358578703</v>
@@ -7859,16 +7862,16 @@
         <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I97" s="8">
         <v>46210</v>
@@ -7886,13 +7889,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7902,7 +7905,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B98" s="5">
         <v>46168.68365474537</v>
@@ -7914,16 +7917,16 @@
         <v>46224.175157731486</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I98" s="5">
         <v>46213</v>
@@ -7941,13 +7944,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q98" s="5">
         <v>46213</v>
@@ -7956,7 +7959,7 @@
         <v>46223</v>
       </c>
       <c r="S98" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
@@ -7967,7 +7970,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B99" s="8">
         <v>46168.683659965274</v>
@@ -7979,16 +7982,16 @@
         <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I99" s="8">
         <v>46213</v>
@@ -8006,13 +8009,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -8022,7 +8025,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B100" s="5">
         <v>46168.68366613426</v>
@@ -8034,16 +8037,16 @@
         <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I100" s="5">
         <v>46213</v>
@@ -8061,13 +8064,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -8077,7 +8080,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B101" s="8">
         <v>46168.683671921295</v>
@@ -8089,16 +8092,16 @@
         <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I101" s="8">
         <v>46213</v>
@@ -8116,13 +8119,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -8132,7 +8135,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B102" s="5">
         <v>46168.68367622685</v>
@@ -8144,16 +8147,16 @@
         <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I102" s="5">
         <v>46213</v>
@@ -8171,13 +8174,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8187,7 +8190,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B103" s="8">
         <v>46168.683680069444</v>
@@ -8199,16 +8202,16 @@
         <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H103" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I103" s="8">
         <v>46213</v>
@@ -8226,13 +8229,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8242,7 +8245,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B104" s="5">
         <v>46168.68369409722</v>
@@ -8254,16 +8257,16 @@
         <v>46225.167433888884</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I104" s="5">
         <v>46224</v>
@@ -8281,13 +8284,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q104" s="5">
         <v>46224</v>
@@ -8296,7 +8299,7 @@
         <v>46224</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
@@ -8307,7 +8310,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B105" s="8">
         <v>46168.68369849537</v>
@@ -8319,16 +8322,16 @@
         <v>46204.890051967595</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I105" s="8">
         <v>46224</v>
@@ -8346,13 +8349,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8362,7 +8365,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B106" s="5">
         <v>46168.683704490744</v>
@@ -8374,16 +8377,16 @@
         <v>46204.890058125005</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I106" s="5">
         <v>46224</v>
@@ -8401,13 +8404,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8417,7 +8420,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B107" s="8">
         <v>46168.683710150464</v>
@@ -8429,16 +8432,16 @@
         <v>46204.89006394676</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I107" s="8">
         <v>46224</v>
@@ -8456,13 +8459,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8472,7 +8475,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B108" s="5">
         <v>46168.68371309028</v>
@@ -8484,16 +8487,16 @@
         <v>46204.89006936342</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I108" s="5">
         <v>46224</v>
@@ -8511,13 +8514,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8527,7 +8530,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B109" s="8">
         <v>46168.68371646991</v>
@@ -8539,16 +8542,16 @@
         <v>46204.890080185185</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="I109" s="8">
         <v>46224</v>
@@ -8566,13 +8569,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8582,7 +8585,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B110" s="5">
         <v>46168.68373005787</v>
@@ -8594,7 +8597,7 @@
         <v>46211.830014363426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8618,7 +8621,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8635,7 +8638,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B111" s="8">
         <v>46168.68373365741</v>
@@ -8647,16 +8650,16 @@
         <v>46205.61049446759</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I111" s="8">
         <v>46185</v>
@@ -8674,13 +8677,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q111" s="8">
         <v>46185</v>
@@ -8689,7 +8692,7 @@
         <v>46185</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T111" s="9">
         <v>1</v>
@@ -8700,7 +8703,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B112" s="5">
         <v>46168.6837408912</v>
@@ -8712,16 +8715,16 @@
         <v>46205.61455358796</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8737,13 +8740,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q112" s="5">
         <v>46168</v>
@@ -8752,7 +8755,7 @@
         <v>46168</v>
       </c>
       <c r="S112" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T112" s="6">
         <v>1</v>
@@ -8763,7 +8766,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B113" s="8">
         <v>46168.68374771991</v>
@@ -8775,16 +8778,16 @@
         <v>46205.6084347338</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I113" s="8">
         <v>46199</v>
@@ -8802,13 +8805,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q113" s="8">
         <v>46199</v>
@@ -8817,7 +8820,7 @@
         <v>46199</v>
       </c>
       <c r="S113" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8828,7 +8831,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B114" s="5">
         <v>46168.68375502314</v>
@@ -8840,16 +8843,16 @@
         <v>46225.18216611111</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8867,13 +8870,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q114" s="5">
         <v>46232</v>
@@ -8893,7 +8896,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B115" s="8">
         <v>46168.6837971412</v>
@@ -8911,10 +8914,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="I115" s="8">
         <v>46220</v>
@@ -8932,13 +8935,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q115" s="8">
         <v>46220</v>
@@ -8947,7 +8950,7 @@
         <v>46220</v>
       </c>
       <c r="S115" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="T115" s="9">
         <v>1</v>
@@ -8958,7 +8961,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B116" s="5">
         <v>46168.68381362269</v>
@@ -8968,7 +8971,7 @@
         <v>46206.48624146991</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8992,7 +8995,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -9002,12 +9005,12 @@
       <c r="S116" s="6"/>
       <c r="T116" s="6"/>
       <c r="U116" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B117" s="8">
         <v>46168.68381783565</v>
@@ -9019,7 +9022,7 @@
         <v>46224.18342798611</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -9028,7 +9031,7 @@
         <v>98</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I117" s="8">
         <v>46225</v>
@@ -9046,13 +9049,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q117" s="8">
         <v>46225</v>
@@ -9072,7 +9075,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B118" s="5">
         <v>46168.683825810185</v>
@@ -9084,7 +9087,7 @@
         <v>46223.57192800926</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -9093,7 +9096,7 @@
         <v>98</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I118" s="5">
         <v>46231</v>
@@ -9111,13 +9114,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -9127,7 +9130,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B119" s="8">
         <v>46168.68383587963</v>
@@ -9139,7 +9142,7 @@
         <v>46223.57192443287</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -9148,7 +9151,7 @@
         <v>98</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I119" s="8">
         <v>46231</v>
@@ -9166,13 +9169,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -9182,7 +9185,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B120" s="5">
         <v>46168.68384034722</v>
@@ -9194,7 +9197,7 @@
         <v>46223.571920902774</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -9203,7 +9206,7 @@
         <v>98</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I120" s="5">
         <v>46231</v>
@@ -9221,13 +9224,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -9237,7 +9240,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B121" s="8">
         <v>46168.683844074076</v>
@@ -9249,7 +9252,7 @@
         <v>46223.571917685185</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -9258,7 +9261,7 @@
         <v>98</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I121" s="8">
         <v>46231</v>
@@ -9276,13 +9279,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9292,7 +9295,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B122" s="5">
         <v>46168.683847673616</v>
@@ -9304,7 +9307,7 @@
         <v>46223.57191195602</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9313,7 +9316,7 @@
         <v>98</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I122" s="5">
         <v>46231</v>
@@ -9331,13 +9334,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9347,7 +9350,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B123" s="8">
         <v>46168.683862453705</v>
@@ -9359,7 +9362,7 @@
         <v>46225.182165729166</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9368,7 +9371,7 @@
         <v>98</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I123" s="8">
         <v>46232</v>
@@ -9386,13 +9389,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q123" s="8">
         <v>46232</v>
@@ -9412,7 +9415,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B124" s="5">
         <v>46168.683867141204</v>
@@ -9424,7 +9427,7 @@
         <v>46223.57203607639</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9433,7 +9436,7 @@
         <v>98</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I124" s="5">
         <v>46232</v>
@@ -9451,13 +9454,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9467,7 +9470,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B125" s="8">
         <v>46168.683873368056</v>
@@ -9479,7 +9482,7 @@
         <v>46223.57203178241</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9488,7 +9491,7 @@
         <v>98</v>
       </c>
       <c r="H125" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I125" s="8">
         <v>46232</v>
@@ -9506,13 +9509,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9522,7 +9525,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B126" s="5">
         <v>46168.68387903935</v>
@@ -9534,7 +9537,7 @@
         <v>46223.5720284375</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9543,7 +9546,7 @@
         <v>98</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I126" s="5">
         <v>46232</v>
@@ -9561,13 +9564,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9577,7 +9580,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B127" s="8">
         <v>46168.683884618054</v>
@@ -9589,7 +9592,7 @@
         <v>46223.5720246875</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9598,7 +9601,7 @@
         <v>98</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I127" s="8">
         <v>46232</v>
@@ -9616,13 +9619,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9632,7 +9635,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B128" s="5">
         <v>46168.68389033565</v>
@@ -9644,7 +9647,7 @@
         <v>46223.57201939815</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9653,7 +9656,7 @@
         <v>98</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I128" s="5">
         <v>46232</v>
@@ -9671,13 +9674,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9687,7 +9690,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B129" s="8">
         <v>46168.68391289352</v>
@@ -9699,7 +9702,7 @@
         <v>46223.57263847222</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9708,7 +9711,7 @@
         <v>98</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I129" s="8">
         <v>46233</v>
@@ -9726,13 +9729,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q129" s="8">
         <v>46233</v>
@@ -9752,7 +9755,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B130" s="5">
         <v>46168.68391818287</v>
@@ -9764,7 +9767,7 @@
         <v>46223.57212789352</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9773,7 +9776,7 @@
         <v>98</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I130" s="5">
         <v>46233</v>
@@ -9791,13 +9794,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9807,7 +9810,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B131" s="8">
         <v>46168.68393068287</v>
@@ -9819,7 +9822,7 @@
         <v>46223.57212385417</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9828,7 +9831,7 @@
         <v>98</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I131" s="8">
         <v>46233</v>
@@ -9846,13 +9849,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9862,7 +9865,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B132" s="5">
         <v>46168.68393770834</v>
@@ -9874,7 +9877,7 @@
         <v>46223.57212008102</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9883,7 +9886,7 @@
         <v>98</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I132" s="5">
         <v>46233</v>
@@ -9901,13 +9904,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9917,7 +9920,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B133" s="8">
         <v>46168.6839434375</v>
@@ -9929,7 +9932,7 @@
         <v>46223.57211625</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9938,7 +9941,7 @@
         <v>98</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I133" s="8">
         <v>46233</v>
@@ -9956,13 +9959,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9972,7 +9975,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B134" s="5">
         <v>46168.68398528935</v>
@@ -9984,7 +9987,7 @@
         <v>46223.572111180554</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9993,7 +9996,7 @@
         <v>98</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I134" s="5">
         <v>46233</v>
@@ -10011,13 +10014,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -10027,7 +10030,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B135" s="8">
         <v>46168.68401087963</v>
@@ -10039,7 +10042,7 @@
         <v>46223.57263368055</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -10048,7 +10051,7 @@
         <v>98</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I135" s="8">
         <v>46234</v>
@@ -10066,13 +10069,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q135" s="8">
         <v>46234</v>
@@ -10092,7 +10095,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B136" s="5">
         <v>46168.68401652778</v>
@@ -10104,7 +10107,7 @@
         <v>46223.5722359375</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -10113,7 +10116,7 @@
         <v>98</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I136" s="5">
         <v>46234</v>
@@ -10131,13 +10134,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -10147,7 +10150,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B137" s="8">
         <v>46168.68402403935</v>
@@ -10159,7 +10162,7 @@
         <v>46223.572232199076</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -10168,7 +10171,7 @@
         <v>98</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I137" s="8">
         <v>46234</v>
@@ -10186,13 +10189,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -10202,7 +10205,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B138" s="5">
         <v>46168.68403127315</v>
@@ -10214,7 +10217,7 @@
         <v>46223.5722271875</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -10223,7 +10226,7 @@
         <v>98</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I138" s="5">
         <v>46234</v>
@@ -10241,13 +10244,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -10257,7 +10260,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B139" s="8">
         <v>46168.68403755787</v>
@@ -10269,7 +10272,7 @@
         <v>46223.57222349537</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -10278,7 +10281,7 @@
         <v>98</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I139" s="8">
         <v>46234</v>
@@ -10296,13 +10299,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -10312,7 +10315,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B140" s="5">
         <v>46168.68404385417</v>
@@ -10324,7 +10327,7 @@
         <v>46223.57221770834</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10333,7 +10336,7 @@
         <v>98</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I140" s="5">
         <v>46234</v>
@@ -10351,13 +10354,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10367,7 +10370,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B141" s="8">
         <v>46168.68406297454</v>
@@ -10379,7 +10382,7 @@
         <v>46223.57262464121</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -10388,7 +10391,7 @@
         <v>98</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I141" s="8">
         <v>46237</v>
@@ -10406,13 +10409,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q141" s="8">
         <v>46237</v>
@@ -10432,7 +10435,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B142" s="5">
         <v>46168.68406752315</v>
@@ -10444,7 +10447,7 @@
         <v>46223.57235236111</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10453,7 +10456,7 @@
         <v>98</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I142" s="5">
         <v>46237</v>
@@ -10471,13 +10474,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10487,7 +10490,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B143" s="8">
         <v>46168.68407938657</v>
@@ -10499,7 +10502,7 @@
         <v>46223.57234864583</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -10508,7 +10511,7 @@
         <v>98</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I143" s="8">
         <v>46237</v>
@@ -10526,13 +10529,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10542,7 +10545,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B144" s="5">
         <v>46168.68408523148</v>
@@ -10554,7 +10557,7 @@
         <v>46223.57234428241</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10563,7 +10566,7 @@
         <v>98</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I144" s="5">
         <v>46237</v>
@@ -10581,13 +10584,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10597,7 +10600,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B145" s="8">
         <v>46168.684089884264</v>
@@ -10609,7 +10612,7 @@
         <v>46223.572340370374</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10618,7 +10621,7 @@
         <v>98</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I145" s="8">
         <v>46237</v>
@@ -10636,13 +10639,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10652,7 +10655,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B146" s="5">
         <v>46168.684094571756</v>
@@ -10664,7 +10667,7 @@
         <v>46223.57233454861</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10673,7 +10676,7 @@
         <v>98</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I146" s="5">
         <v>46237</v>
@@ -10691,13 +10694,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10707,7 +10710,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B147" s="8">
         <v>46168.68414574074</v>
@@ -10719,7 +10722,7 @@
         <v>46223.57261809028</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10728,7 +10731,7 @@
         <v>98</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I147" s="8">
         <v>46239</v>
@@ -10746,13 +10749,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="Q147" s="8">
         <v>46239</v>
@@ -10772,7 +10775,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B148" s="5">
         <v>46168.68415105324</v>
@@ -10784,7 +10787,7 @@
         <v>46223.572544027775</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10793,7 +10796,7 @@
         <v>98</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I148" s="5">
         <v>46239</v>
@@ -10811,13 +10814,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10827,7 +10830,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B149" s="8">
         <v>46168.68415587963</v>
@@ -10839,7 +10842,7 @@
         <v>46223.5725400463</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10848,7 +10851,7 @@
         <v>98</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I149" s="8">
         <v>46239</v>
@@ -10866,13 +10869,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10882,7 +10885,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B150" s="5">
         <v>46168.68416068287</v>
@@ -10894,7 +10897,7 @@
         <v>46223.57253650463</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10903,7 +10906,7 @@
         <v>98</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I150" s="5">
         <v>46239</v>
@@ -10921,13 +10924,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10937,7 +10940,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B151" s="8">
         <v>46168.68416431713</v>
@@ -10949,7 +10952,7 @@
         <v>46223.5725334375</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10958,7 +10961,7 @@
         <v>98</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I151" s="8">
         <v>46239</v>
@@ -10976,13 +10979,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10992,7 +10995,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B152" s="5">
         <v>46168.68416798611</v>
@@ -11004,7 +11007,7 @@
         <v>46223.5725280787</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -11013,7 +11016,7 @@
         <v>98</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I152" s="5">
         <v>46239</v>
@@ -11031,13 +11034,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -11047,7 +11050,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B153" s="8">
         <v>46168.684183460646</v>
@@ -11059,7 +11062,7 @@
         <v>46211.832724733795</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -11083,7 +11086,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -11100,7 +11103,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B154" s="5">
         <v>46168.68418700232</v>
@@ -11112,16 +11115,16 @@
         <v>46211.8327003125</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I154" s="5">
         <v>46240</v>
@@ -11139,13 +11142,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q154" s="5">
         <v>46240</v>
@@ -11165,7 +11168,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B155" s="8">
         <v>46168.68419359953</v>
@@ -11177,16 +11180,16 @@
         <v>46211.831112581014</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I155" s="8">
         <v>46240</v>
@@ -11204,13 +11207,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -11220,7 +11223,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B156" s="5">
         <v>46168.68419834491</v>
@@ -11232,16 +11235,16 @@
         <v>46211.83112387732</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H156" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I156" s="5">
         <v>46240</v>
@@ -11259,13 +11262,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -11275,7 +11278,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B157" s="8">
         <v>46168.684202777775</v>
@@ -11287,16 +11290,16 @@
         <v>46211.83112878472</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H157" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I157" s="8">
         <v>46240</v>
@@ -11314,13 +11317,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -11330,7 +11333,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B158" s="5">
         <v>46168.68420710648</v>
@@ -11342,16 +11345,16 @@
         <v>46211.83116206019</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I158" s="5">
         <v>46240</v>
@@ -11369,13 +11372,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -11385,7 +11388,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B159" s="8">
         <v>46168.68421127315</v>
@@ -11397,16 +11400,16 @@
         <v>46211.83117125</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H159" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I159" s="8">
         <v>46240</v>
@@ -11424,13 +11427,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -11440,7 +11443,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B160" s="5">
         <v>46168.68422996528</v>
@@ -11458,10 +11461,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H160" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I160" s="5">
         <v>46240</v>
@@ -11479,13 +11482,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11495,7 +11498,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B161" s="8">
         <v>46168.68423341435</v>
@@ -11513,10 +11516,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H161" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I161" s="8">
         <v>46240</v>
@@ -11534,13 +11537,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11550,7 +11553,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B162" s="5">
         <v>46168.684237037036</v>
@@ -11568,10 +11571,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H162" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I162" s="5">
         <v>46240</v>
@@ -11589,13 +11592,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11605,7 +11608,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B163" s="8">
         <v>46168.68424059028</v>
@@ -11623,10 +11626,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H163" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I163" s="8">
         <v>46240</v>
@@ -11644,13 +11647,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11660,7 +11663,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B164" s="5">
         <v>46168.68424420139</v>
@@ -11678,10 +11681,10 @@
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H164" s="6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I164" s="5">
         <v>46240</v>
@@ -11699,13 +11702,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11715,7 +11718,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B165" s="8">
         <v>46168.68424778935</v>
@@ -11733,10 +11736,10 @@
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H165" s="9" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="I165" s="8">
         <v>46240</v>
@@ -11754,13 +11757,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O165" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11770,7 +11773,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B166" s="5">
         <v>46168.68425820602</v>
@@ -11782,7 +11785,7 @@
         <v>46223.57301792824</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11791,7 +11794,7 @@
         <v>98</v>
       </c>
       <c r="H166" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I166" s="6"/>
       <c r="J166" s="5">
@@ -11807,13 +11810,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q166" s="5">
         <v>46241</v>
@@ -11833,7 +11836,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B167" s="8">
         <v>46168.68426255787</v>
@@ -11845,7 +11848,7 @@
         <v>46223.5729158912</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
@@ -11854,7 +11857,7 @@
         <v>98</v>
       </c>
       <c r="H167" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I167" s="9"/>
       <c r="J167" s="8">
@@ -11870,13 +11873,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11886,7 +11889,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B168" s="5">
         <v>46168.68426704861</v>
@@ -11898,7 +11901,7 @@
         <v>46223.57291190972</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11907,7 +11910,7 @@
         <v>98</v>
       </c>
       <c r="H168" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I168" s="6"/>
       <c r="J168" s="5">
@@ -11923,13 +11926,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11939,7 +11942,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B169" s="8">
         <v>46168.68427162037</v>
@@ -11951,7 +11954,7 @@
         <v>46223.57290799769</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
@@ -11960,7 +11963,7 @@
         <v>98</v>
       </c>
       <c r="H169" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I169" s="9"/>
       <c r="J169" s="8">
@@ -11976,13 +11979,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11992,7 +11995,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B170" s="5">
         <v>46168.68427627315</v>
@@ -12004,7 +12007,7 @@
         <v>46223.57290423611</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -12013,7 +12016,7 @@
         <v>98</v>
       </c>
       <c r="H170" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I170" s="6"/>
       <c r="J170" s="5">
@@ -12029,13 +12032,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -12045,7 +12048,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B171" s="8">
         <v>46168.68428068287</v>
@@ -12057,7 +12060,7 @@
         <v>46223.57290035879</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
@@ -12066,7 +12069,7 @@
         <v>98</v>
       </c>
       <c r="H171" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I171" s="9"/>
       <c r="J171" s="8">
@@ -12082,13 +12085,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -12098,7 +12101,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B172" s="5">
         <v>46168.684336226856</v>
@@ -12119,7 +12122,7 @@
         <v>98</v>
       </c>
       <c r="H172" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I172" s="6"/>
       <c r="J172" s="5">
@@ -12135,13 +12138,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O172" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -12151,7 +12154,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B173" s="8">
         <v>46168.68434010417</v>
@@ -12172,7 +12175,7 @@
         <v>98</v>
       </c>
       <c r="H173" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I173" s="9"/>
       <c r="J173" s="8">
@@ -12188,13 +12191,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O173" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -12204,7 +12207,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B174" s="5">
         <v>46168.68434423611</v>
@@ -12225,7 +12228,7 @@
         <v>98</v>
       </c>
       <c r="H174" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I174" s="6"/>
       <c r="J174" s="5">
@@ -12241,13 +12244,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -12257,7 +12260,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B175" s="8">
         <v>46168.684348263894</v>
@@ -12278,7 +12281,7 @@
         <v>98</v>
       </c>
       <c r="H175" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I175" s="9"/>
       <c r="J175" s="8">
@@ -12294,13 +12297,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O175" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -12310,7 +12313,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B176" s="5">
         <v>46168.68435202546</v>
@@ -12331,7 +12334,7 @@
         <v>98</v>
       </c>
       <c r="H176" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I176" s="6"/>
       <c r="J176" s="5">
@@ -12347,13 +12350,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -12363,7 +12366,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B177" s="8">
         <v>46168.68435652778</v>
@@ -12384,7 +12387,7 @@
         <v>98</v>
       </c>
       <c r="H177" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="I177" s="9"/>
       <c r="J177" s="8">
@@ -12400,13 +12403,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O177" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -12416,7 +12419,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B178" s="5">
         <v>46168.68437314815</v>
@@ -12428,16 +12431,16 @@
         <v>46209.715354976855</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H178" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -12453,13 +12456,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="Q178" s="5">
         <v>46244</v>
@@ -12479,7 +12482,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B179" s="8">
         <v>46168.68437847222</v>
@@ -12491,16 +12494,16 @@
         <v>46209.71550439815</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H179" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I179" s="8">
         <v>46244</v>
@@ -12518,13 +12521,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
@@ -12534,7 +12537,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B180" s="5">
         <v>46168.68438821759</v>
@@ -12546,16 +12549,16 @@
         <v>46209.7156449537</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H180" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I180" s="5">
         <v>46244</v>
@@ -12573,13 +12576,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12589,7 +12592,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B181" s="8">
         <v>46168.684394537035</v>
@@ -12601,16 +12604,16 @@
         <v>46209.715759733794</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H181" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I181" s="8">
         <v>46244</v>
@@ -12628,13 +12631,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12644,7 +12647,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B182" s="5">
         <v>46168.68439944445</v>
@@ -12656,16 +12659,16 @@
         <v>46209.71583459491</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H182" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I182" s="5">
         <v>46244</v>
@@ -12683,13 +12686,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12699,7 +12702,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B183" s="8">
         <v>46168.684404375</v>
@@ -12711,16 +12714,16 @@
         <v>46209.71610449074</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H183" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I183" s="8">
         <v>46244</v>
@@ -12738,13 +12741,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12754,7 +12757,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B184" s="5">
         <v>46168.6844190625</v>
@@ -12772,10 +12775,10 @@
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H184" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I184" s="5">
         <v>46244</v>
@@ -12793,13 +12796,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O184" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12809,7 +12812,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B185" s="8">
         <v>46168.68442277778</v>
@@ -12821,16 +12824,16 @@
         <v>46211.83081103009</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H185" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I185" s="8">
         <v>46244</v>
@@ -12848,13 +12851,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O185" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12864,7 +12867,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B186" s="5">
         <v>46168.68442653935</v>
@@ -12882,10 +12885,10 @@
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H186" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I186" s="5">
         <v>46244</v>
@@ -12903,13 +12906,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O186" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12919,7 +12922,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B187" s="8">
         <v>46168.684429988425</v>
@@ -12937,10 +12940,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H187" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I187" s="8">
         <v>46244</v>
@@ -12958,13 +12961,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O187" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12974,7 +12977,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B188" s="5">
         <v>46168.68443359954</v>
@@ -12992,10 +12995,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H188" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I188" s="5">
         <v>46244</v>
@@ -13013,13 +13016,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -13029,7 +13032,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B189" s="8">
         <v>46168.68443729167</v>
@@ -13047,10 +13050,10 @@
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H189" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I189" s="8">
         <v>46244</v>
@@ -13068,13 +13071,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O189" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -13084,7 +13087,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B190" s="5">
         <v>46168.6844840625</v>
@@ -13096,16 +13099,16 @@
         <v>46223.57240934028</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H190" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I190" s="5">
         <v>46245</v>
@@ -13123,13 +13126,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O190" s="6" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="P190" s="6" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="Q190" s="5">
         <v>46245</v>
@@ -13149,7 +13152,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B191" s="8">
         <v>46168.68449130787</v>
@@ -13161,16 +13164,16 @@
         <v>46211.830295844906</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H191" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="8">
@@ -13186,13 +13189,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -13202,7 +13205,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B192" s="5">
         <v>46168.68449590278</v>
@@ -13214,16 +13217,16 @@
         <v>46211.83029662037</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -13239,13 +13242,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -13255,7 +13258,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B193" s="8">
         <v>46168.68450027778</v>
@@ -13267,16 +13270,16 @@
         <v>46211.83029733796</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H193" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="8">
@@ -13292,13 +13295,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -13308,7 +13311,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B194" s="5">
         <v>46168.68450480324</v>
@@ -13320,16 +13323,16 @@
         <v>46211.83029778935</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="5">
@@ -13345,13 +13348,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -13361,7 +13364,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B195" s="8">
         <v>46168.68450934028</v>
@@ -13373,16 +13376,16 @@
         <v>46211.83029865741</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H195" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I195" s="9"/>
       <c r="J195" s="8">
@@ -13398,13 +13401,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -13414,7 +13417,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B196" s="5">
         <v>46168.684523414355</v>
@@ -13426,16 +13429,16 @@
         <v>46211.83029902777</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H196" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -13451,13 +13454,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -13467,7 +13470,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B197" s="8">
         <v>46168.6845271412</v>
@@ -13479,16 +13482,16 @@
         <v>46211.83029945602</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H197" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I197" s="9"/>
       <c r="J197" s="8">
@@ -13504,13 +13507,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -13520,7 +13523,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B198" s="5">
         <v>46168.68453511574</v>
@@ -13532,16 +13535,16 @@
         <v>46211.830299953705</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H198" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13557,13 +13560,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13573,7 +13576,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B199" s="8">
         <v>46168.68453863426</v>
@@ -13585,16 +13588,16 @@
         <v>46211.83030041667</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H199" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I199" s="9"/>
       <c r="J199" s="8">
@@ -13610,13 +13613,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O199" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13626,7 +13629,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B200" s="5">
         <v>46168.68454210648</v>
@@ -13638,16 +13641,16 @@
         <v>46211.830300891204</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13663,13 +13666,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13679,7 +13682,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B201" s="8">
         <v>46168.684545578704</v>
@@ -13691,16 +13694,16 @@
         <v>46211.83030140046</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H201" s="9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="8">
@@ -13716,13 +13719,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O201" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13732,7 +13735,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B202" s="5">
         <v>46168.684555775464</v>
@@ -13742,7 +13745,7 @@
         <v>46168.8618759838</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>25</v>
@@ -13766,7 +13769,7 @@
         <v>26</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>26</v>
@@ -13779,7 +13782,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B203" s="8">
         <v>46168.6845594676</v>
@@ -13789,16 +13792,16 @@
         <v>46211.83025064815</v>
       </c>
       <c r="E203" s="9" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="F203" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G203" s="9" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H203" s="9" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="I203" s="8">
         <v>46246</v>
@@ -13816,13 +13819,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q203" s="8">
         <v>46246</v>
@@ -13837,12 +13840,12 @@
         <v>0</v>
       </c>
       <c r="U203" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B204" s="5">
         <v>46168.68456425926</v>
@@ -13852,7 +13855,7 @@
         <v>46211.83025032407</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13879,13 +13882,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Q204" s="5">
         <v>46246</v>
@@ -13900,12 +13903,12 @@
         <v>0</v>
       </c>
       <c r="U204" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A205" s="7" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B205" s="8">
         <v>46168.68457049769</v>
@@ -13915,7 +13918,7 @@
         <v>46168.86234542824</v>
       </c>
       <c r="E205" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="F205" s="9" t="s">
         <v>25</v>
@@ -13939,7 +13942,7 @@
         <v>26</v>
       </c>
       <c r="O205" s="9" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P205" s="9" t="s">
         <v>26</v>
@@ -13953,12 +13956,12 @@
         <v>0</v>
       </c>
       <c r="U205" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B206" s="5">
         <v>46168.68457415509</v>
@@ -13968,7 +13971,7 @@
         <v>46211.830253541666</v>
       </c>
       <c r="E206" s="6" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="F206" s="6" t="s">
         <v>26</v>
@@ -13995,13 +13998,13 @@
         <v>26</v>
       </c>
       <c r="N206" s="6" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O206" s="6" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="P206" s="6" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Q206" s="5">
         <v>46246</v>
@@ -14016,12 +14019,12 @@
         <v>0</v>
       </c>
       <c r="U206" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A207" s="7" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B207" s="8">
         <v>46168.68457920139</v>
@@ -14031,7 +14034,7 @@
         <v>46168.868795937495</v>
       </c>
       <c r="E207" s="9" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F207" s="9" t="s">
         <v>26</v>
@@ -14058,13 +14061,13 @@
         <v>26</v>
       </c>
       <c r="N207" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O207" s="9" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P207" s="9" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q207" s="8">
         <v>46255</v>
@@ -14079,7 +14082,7 @@
         <v>0</v>
       </c>
       <c r="U207" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -9699,7 +9699,7 @@
         <v>46204.89298883102</v>
       </c>
       <c r="D129" s="8">
-        <v>46223.57263847222</v>
+        <v>46226.19708972222</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>372</v>
@@ -9743,8 +9743,8 @@
       <c r="R129" s="8">
         <v>46233</v>
       </c>
-      <c r="S129" s="10" t="s">
-        <v>32</v>
+      <c r="S129" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T129" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -291,7 +291,7 @@
     <t>Ingenieria Servicios ,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
-    <t>Media</t>
+    <t>Alta</t>
   </si>
   <si>
     <t>1215141566425255</t>
@@ -429,9 +429,6 @@
     <t>Propuesta compras:,Generación OC materiales corte Laser ot 4335 - 4337 -4339</t>
   </si>
   <si>
-    <t>Alta</t>
-  </si>
-  <si>
     <t>1215141533737633</t>
   </si>
   <si>
@@ -670,6 +667,9 @@
   </si>
   <si>
     <t>Fabricación estructura proveedor externo ot 4335 - 4337 -4339,Generacion OC Fabricación Externa ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Media</t>
   </si>
   <si>
     <t>1215141566544936</t>
@@ -1794,12 +1794,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
+        <fgColor rgb="FFe8384f"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFe8384f"/>
+        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -2840,7 +2840,7 @@
         <v>46196.89414587963</v>
       </c>
       <c r="D12" s="5">
-        <v>46223.57316143518</v>
+        <v>46228.17456038194</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -3773,8 +3773,8 @@
       <c r="R27" s="8">
         <v>46190</v>
       </c>
-      <c r="S27" s="12" t="s">
-        <v>105</v>
+      <c r="S27" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T27" s="9">
         <v>1</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B28" s="5">
         <v>46168.68321959491</v>
@@ -3797,7 +3797,7 @@
         <v>46223.57172274306</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
@@ -3830,7 +3830,7 @@
         <v>103</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q28" s="5">
         <v>46189</v>
@@ -3838,8 +3838,8 @@
       <c r="R28" s="5">
         <v>46190</v>
       </c>
-      <c r="S28" s="12" t="s">
-        <v>105</v>
+      <c r="S28" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
@@ -3850,7 +3850,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="8">
         <v>46168.68322341435</v>
@@ -3862,7 +3862,7 @@
         <v>46223.571718969906</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3895,7 +3895,7 @@
         <v>103</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q29" s="8">
         <v>46189</v>
@@ -3903,8 +3903,8 @@
       <c r="R29" s="8">
         <v>46190</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>105</v>
+      <c r="S29" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T29" s="9">
         <v>1</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B30" s="5">
         <v>46168.683227245376</v>
@@ -3927,7 +3927,7 @@
         <v>46223.57171402778</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3960,7 +3960,7 @@
         <v>103</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="5">
         <v>46189</v>
@@ -3968,8 +3968,8 @@
       <c r="R30" s="5">
         <v>46190</v>
       </c>
-      <c r="S30" s="12" t="s">
-        <v>105</v>
+      <c r="S30" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T30" s="6">
         <v>1</v>
@@ -3980,7 +3980,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B31" s="8">
         <v>46168.683231365736</v>
@@ -3992,7 +3992,7 @@
         <v>46193.553499305555</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -4025,7 +4025,7 @@
         <v>51</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q31" s="8">
         <v>46157</v>
@@ -4045,7 +4045,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B32" s="5">
         <v>46168.682992511574</v>
@@ -4057,7 +4057,7 @@
         <v>46205.61594793982</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -4081,7 +4081,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B33" s="8">
         <v>46168.68327652778</v>
@@ -4110,16 +4110,16 @@
         <v>46195.928396574076</v>
       </c>
       <c r="E33" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="I33" s="8">
         <v>46161</v>
@@ -4137,13 +4137,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q33" s="8">
         <v>46161</v>
@@ -4163,7 +4163,7 @@
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B34" s="5">
         <v>46168.68328149305</v>
@@ -4175,16 +4175,16 @@
         <v>46195.9258303588</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I34" s="5">
         <v>46161</v>
@@ -4202,13 +4202,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>94</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q34" s="6"/>
       <c r="R34" s="6"/>
@@ -4218,13 +4218,13 @@
       <c r="T34" s="6">
         <v>0</v>
       </c>
-      <c r="U34" s="12" t="s">
-        <v>129</v>
+      <c r="U34" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B35" s="8">
         <v>46168.68328653935</v>
@@ -4236,16 +4236,16 @@
         <v>46195.928370243055</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="I35" s="8">
         <v>46164</v>
@@ -4263,13 +4263,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q35" s="9"/>
       <c r="R35" s="9"/>
@@ -4279,13 +4279,13 @@
       <c r="T35" s="9">
         <v>0</v>
       </c>
-      <c r="U35" s="12" t="s">
-        <v>129</v>
+      <c r="U35" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B36" s="5">
         <v>46168.68329140046</v>
@@ -4297,16 +4297,16 @@
         <v>46185.182775243054</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I36" s="5">
         <v>46161</v>
@@ -4324,13 +4324,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q36" s="5">
         <v>46161</v>
@@ -4338,8 +4338,8 @@
       <c r="R36" s="5">
         <v>46184</v>
       </c>
-      <c r="S36" s="12" t="s">
-        <v>105</v>
+      <c r="S36" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T36" s="6">
         <v>1</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B37" s="8">
         <v>46168.68329584491</v>
@@ -4362,16 +4362,16 @@
         <v>46184.70350368056</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="I37" s="8">
         <v>46161</v>
@@ -4389,13 +4389,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>97</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="Q37" s="9"/>
       <c r="R37" s="9"/>
@@ -4405,13 +4405,13 @@
       <c r="T37" s="9">
         <v>0</v>
       </c>
-      <c r="U37" s="12" t="s">
-        <v>129</v>
+      <c r="U37" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B38" s="5">
         <v>46168.68330070602</v>
@@ -4423,16 +4423,16 @@
         <v>46184.703557789355</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I38" s="5">
         <v>46164</v>
@@ -4450,13 +4450,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
@@ -4466,13 +4466,13 @@
       <c r="T38" s="6">
         <v>0</v>
       </c>
-      <c r="U38" s="12" t="s">
-        <v>129</v>
+      <c r="U38" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="8">
         <v>46168.68330542824</v>
@@ -4484,16 +4484,16 @@
         <v>46205.60819122686</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="I39" s="8">
         <v>46161</v>
@@ -4511,13 +4511,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q39" s="8">
         <v>46161</v>
@@ -4525,8 +4525,8 @@
       <c r="R39" s="8">
         <v>46198</v>
       </c>
-      <c r="S39" s="12" t="s">
-        <v>105</v>
+      <c r="S39" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T39" s="9">
         <v>1</v>
@@ -4537,7 +4537,7 @@
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B40" s="5">
         <v>46168.683310092594</v>
@@ -4549,16 +4549,16 @@
         <v>46195.92587128472</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I40" s="5">
         <v>46161</v>
@@ -4576,13 +4576,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>91</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="Q40" s="6"/>
       <c r="R40" s="6"/>
@@ -4592,13 +4592,13 @@
       <c r="T40" s="6">
         <v>0</v>
       </c>
-      <c r="U40" s="12" t="s">
-        <v>129</v>
+      <c r="U40" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B41" s="8">
         <v>46168.68331519676</v>
@@ -4610,16 +4610,16 @@
         <v>46205.60793128472</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="I41" s="8">
         <v>46170</v>
@@ -4637,13 +4637,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="Q41" s="9"/>
       <c r="R41" s="9"/>
@@ -4653,13 +4653,13 @@
       <c r="T41" s="9">
         <v>0</v>
       </c>
-      <c r="U41" s="12" t="s">
-        <v>129</v>
+      <c r="U41" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B42" s="5">
         <v>46168.68332027778</v>
@@ -4671,16 +4671,16 @@
         <v>46195.92587850694</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I42" s="5">
         <v>46170</v>
@@ -4698,13 +4698,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="Q42" s="6"/>
       <c r="R42" s="6"/>
@@ -4714,13 +4714,13 @@
       <c r="T42" s="6">
         <v>0</v>
       </c>
-      <c r="U42" s="12" t="s">
-        <v>129</v>
+      <c r="U42" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B43" s="8">
         <v>46168.68332520833</v>
@@ -4732,16 +4732,16 @@
         <v>46220.18799388889</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="I43" s="8">
         <v>46161</v>
@@ -4759,10 +4759,10 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P43" s="9" t="s">
         <v>26</v>
@@ -4773,8 +4773,8 @@
       <c r="R43" s="8">
         <v>46219</v>
       </c>
-      <c r="S43" s="12" t="s">
-        <v>105</v>
+      <c r="S43" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T43" s="9">
         <v>1</v>
@@ -4785,7 +4785,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B44" s="5">
         <v>46168.68332880787</v>
@@ -4797,16 +4797,16 @@
         <v>46195.92577891204</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="I44" s="5">
         <v>46161</v>
@@ -4824,13 +4824,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Q44" s="6"/>
       <c r="R44" s="6"/>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B45" s="8">
         <v>46168.683333113426</v>
@@ -4852,16 +4852,16 @@
         <v>46195.92857017361</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>123</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>124</v>
       </c>
       <c r="I45" s="8">
         <v>46171</v>
@@ -4879,13 +4879,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q45" s="9"/>
       <c r="R45" s="9"/>
@@ -4895,7 +4895,7 @@
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B46" s="5">
         <v>46168.683337291666</v>
@@ -4907,16 +4907,16 @@
         <v>46204.1978837037</v>
       </c>
       <c r="E46" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="6" t="s">
+      <c r="H46" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I46" s="5">
         <v>46191</v>
@@ -4934,13 +4934,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q46" s="5">
         <v>46191</v>
@@ -4948,8 +4948,8 @@
       <c r="R46" s="5">
         <v>46203</v>
       </c>
-      <c r="S46" s="12" t="s">
-        <v>105</v>
+      <c r="S46" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T46" s="6">
         <v>1</v>
@@ -4960,7 +4960,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B47" s="8">
         <v>46168.68334179398</v>
@@ -4972,16 +4972,16 @@
         <v>46199.564988564816</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H47" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H47" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I47" s="8">
         <v>46191</v>
@@ -4999,13 +4999,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O47" s="9" t="s">
         <v>102</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Q47" s="9"/>
       <c r="R47" s="9"/>
@@ -5015,13 +5015,13 @@
       <c r="T47" s="9">
         <v>0</v>
       </c>
-      <c r="U47" s="12" t="s">
-        <v>129</v>
+      <c r="U47" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B48" s="5">
         <v>46168.68334684028</v>
@@ -5033,16 +5033,16 @@
         <v>46199.5650378125</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H48" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I48" s="5">
         <v>46195</v>
@@ -5060,13 +5060,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q48" s="6"/>
       <c r="R48" s="6"/>
@@ -5076,13 +5076,13 @@
       <c r="T48" s="6">
         <v>0</v>
       </c>
-      <c r="U48" s="12" t="s">
-        <v>129</v>
+      <c r="U48" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B49" s="8">
         <v>46168.68335195602</v>
@@ -5094,16 +5094,16 @@
         <v>46204.19788363426</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H49" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I49" s="8">
         <v>46191</v>
@@ -5121,10 +5121,10 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="P49" s="9" t="s">
         <v>26</v>
@@ -5135,8 +5135,8 @@
       <c r="R49" s="8">
         <v>46203</v>
       </c>
-      <c r="S49" s="12" t="s">
-        <v>105</v>
+      <c r="S49" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T49" s="9">
         <v>1</v>
@@ -5147,7 +5147,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" s="5">
         <v>46168.68335582176</v>
@@ -5159,16 +5159,16 @@
         <v>46199.56512275463</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H50" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H50" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I50" s="5">
         <v>46191</v>
@@ -5186,13 +5186,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q50" s="6"/>
       <c r="R50" s="6"/>
@@ -5202,7 +5202,7 @@
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B51" s="8">
         <v>46168.683360428244</v>
@@ -5214,16 +5214,16 @@
         <v>46199.56520053241</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H51" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I51" s="8">
         <v>46195</v>
@@ -5241,13 +5241,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q51" s="9"/>
       <c r="R51" s="9"/>
@@ -5257,7 +5257,7 @@
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B52" s="5">
         <v>46168.68336471065</v>
@@ -5269,16 +5269,16 @@
         <v>46224.18342847222</v>
       </c>
       <c r="E52" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="F52" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I52" s="5">
         <v>46191</v>
@@ -5296,10 +5296,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -5310,8 +5310,8 @@
       <c r="R52" s="5">
         <v>46231</v>
       </c>
-      <c r="S52" s="11" t="s">
-        <v>61</v>
+      <c r="S52" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -5334,16 +5334,16 @@
         <v>46204.601485555555</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>182</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>183</v>
-      </c>
-      <c r="H53" s="9" t="s">
-        <v>184</v>
       </c>
       <c r="I53" s="8">
         <v>46191</v>
@@ -5361,10 +5361,10 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>187</v>
@@ -5395,10 +5395,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="H54" s="6" t="s">
         <v>183</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>184</v>
       </c>
       <c r="I54" s="5">
         <v>46202</v>
@@ -5416,10 +5416,10 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>190</v>
@@ -5471,7 +5471,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>189</v>
@@ -5505,10 +5505,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H56" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I56" s="5">
         <v>46191</v>
@@ -5526,7 +5526,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>197</v>
@@ -5540,8 +5540,8 @@
       <c r="R56" s="5">
         <v>46203</v>
       </c>
-      <c r="S56" s="12" t="s">
-        <v>105</v>
+      <c r="S56" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T56" s="6">
         <v>1</v>
@@ -5564,16 +5564,16 @@
         <v>46199.56535409723</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="H57" s="9" t="s">
         <v>164</v>
-      </c>
-      <c r="H57" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="I57" s="8">
         <v>46191</v>
@@ -5594,7 +5594,7 @@
         <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P57" s="9" t="s">
         <v>199</v>
@@ -5625,10 +5625,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="H58" s="6" t="s">
         <v>164</v>
-      </c>
-      <c r="H58" s="6" t="s">
-        <v>165</v>
       </c>
       <c r="I58" s="5">
         <v>46195</v>
@@ -5649,7 +5649,7 @@
         <v>196</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>202</v>
@@ -5705,7 +5705,7 @@
       <c r="R59" s="9"/>
       <c r="S59" s="9"/>
       <c r="T59" s="9"/>
-      <c r="U59" s="11" t="s">
+      <c r="U59" s="12" t="s">
         <v>206</v>
       </c>
     </row>
@@ -5764,8 +5764,8 @@
       <c r="R60" s="5">
         <v>46171</v>
       </c>
-      <c r="S60" s="12" t="s">
-        <v>105</v>
+      <c r="S60" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T60" s="6">
         <v>1</v>
@@ -6104,8 +6104,8 @@
       <c r="R66" s="5">
         <v>46185</v>
       </c>
-      <c r="S66" s="12" t="s">
-        <v>105</v>
+      <c r="S66" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T66" s="6">
         <v>1</v>
@@ -6444,8 +6444,8 @@
       <c r="R72" s="5">
         <v>46188</v>
       </c>
-      <c r="S72" s="12" t="s">
-        <v>105</v>
+      <c r="S72" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T72" s="6">
         <v>1</v>
@@ -7164,7 +7164,7 @@
         <v>258</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P85" s="9" t="s">
         <v>264</v>
@@ -7175,8 +7175,8 @@
       <c r="R85" s="8">
         <v>46205</v>
       </c>
-      <c r="S85" s="12" t="s">
-        <v>105</v>
+      <c r="S85" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T85" s="9">
         <v>1</v>
@@ -7240,8 +7240,8 @@
       <c r="R86" s="5">
         <v>46209</v>
       </c>
-      <c r="S86" s="12" t="s">
-        <v>105</v>
+      <c r="S86" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T86" s="6">
         <v>1</v>
@@ -7294,7 +7294,7 @@
         <v>258</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="P87" s="9" t="s">
         <v>271</v>
@@ -7305,8 +7305,8 @@
       <c r="R87" s="8">
         <v>46205</v>
       </c>
-      <c r="S87" s="12" t="s">
-        <v>105</v>
+      <c r="S87" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T87" s="9">
         <v>1</v>
@@ -7370,8 +7370,8 @@
       <c r="R88" s="5">
         <v>46209</v>
       </c>
-      <c r="S88" s="12" t="s">
-        <v>105</v>
+      <c r="S88" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T88" s="6">
         <v>1</v>
@@ -7435,8 +7435,8 @@
       <c r="R89" s="8">
         <v>46205</v>
       </c>
-      <c r="S89" s="12" t="s">
-        <v>105</v>
+      <c r="S89" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T89" s="9">
         <v>1</v>
@@ -7500,8 +7500,8 @@
       <c r="R90" s="5">
         <v>46209</v>
       </c>
-      <c r="S90" s="12" t="s">
-        <v>105</v>
+      <c r="S90" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T90" s="6">
         <v>1</v>
@@ -7618,8 +7618,8 @@
       <c r="R92" s="5">
         <v>46212</v>
       </c>
-      <c r="S92" s="12" t="s">
-        <v>105</v>
+      <c r="S92" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T92" s="6">
         <v>1</v>
@@ -7958,8 +7958,8 @@
       <c r="R98" s="5">
         <v>46223</v>
       </c>
-      <c r="S98" s="12" t="s">
-        <v>105</v>
+      <c r="S98" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T98" s="6">
         <v>1</v>
@@ -8298,8 +8298,8 @@
       <c r="R104" s="5">
         <v>46224</v>
       </c>
-      <c r="S104" s="12" t="s">
-        <v>105</v>
+      <c r="S104" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
@@ -8680,7 +8680,7 @@
         <v>258</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="P111" s="9" t="s">
         <v>329</v>
@@ -8691,8 +8691,8 @@
       <c r="R111" s="8">
         <v>46185</v>
       </c>
-      <c r="S111" s="12" t="s">
-        <v>105</v>
+      <c r="S111" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T111" s="9">
         <v>1</v>
@@ -8743,7 +8743,7 @@
         <v>258</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="P112" s="6" t="s">
         <v>332</v>
@@ -8754,8 +8754,8 @@
       <c r="R112" s="5">
         <v>46168</v>
       </c>
-      <c r="S112" s="12" t="s">
-        <v>105</v>
+      <c r="S112" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T112" s="6">
         <v>1</v>
@@ -8808,7 +8808,7 @@
         <v>258</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P113" s="9" t="s">
         <v>335</v>
@@ -8819,8 +8819,8 @@
       <c r="R113" s="8">
         <v>46199</v>
       </c>
-      <c r="S113" s="12" t="s">
-        <v>105</v>
+      <c r="S113" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8884,8 +8884,8 @@
       <c r="R114" s="5">
         <v>46232</v>
       </c>
-      <c r="S114" s="11" t="s">
-        <v>61</v>
+      <c r="S114" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="T114" s="6">
         <v>1</v>
@@ -8938,7 +8938,7 @@
         <v>258</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P115" s="9" t="s">
         <v>340</v>
@@ -8949,8 +8949,8 @@
       <c r="R115" s="8">
         <v>46220</v>
       </c>
-      <c r="S115" s="12" t="s">
-        <v>105</v>
+      <c r="S115" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T115" s="9">
         <v>1</v>
@@ -9004,7 +9004,7 @@
       <c r="R116" s="6"/>
       <c r="S116" s="6"/>
       <c r="T116" s="6"/>
-      <c r="U116" s="11" t="s">
+      <c r="U116" s="12" t="s">
         <v>206</v>
       </c>
     </row>
@@ -9063,8 +9063,8 @@
       <c r="R117" s="8">
         <v>46231</v>
       </c>
-      <c r="S117" s="11" t="s">
-        <v>61</v>
+      <c r="S117" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="T117" s="9">
         <v>1</v>
@@ -9403,8 +9403,8 @@
       <c r="R123" s="8">
         <v>46232</v>
       </c>
-      <c r="S123" s="11" t="s">
-        <v>61</v>
+      <c r="S123" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="T123" s="9">
         <v>1</v>
@@ -9743,8 +9743,8 @@
       <c r="R129" s="8">
         <v>46233</v>
       </c>
-      <c r="S129" s="11" t="s">
-        <v>61</v>
+      <c r="S129" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="T129" s="9">
         <v>1</v>
@@ -10039,7 +10039,7 @@
         <v>46204.893422152774</v>
       </c>
       <c r="D135" s="8">
-        <v>46223.57263368055</v>
+        <v>46227.17239224537</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>387</v>
@@ -10083,8 +10083,8 @@
       <c r="R135" s="8">
         <v>46234</v>
       </c>
-      <c r="S135" s="10" t="s">
-        <v>32</v>
+      <c r="S135" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="T135" s="9">
         <v>1</v>
@@ -10379,7 +10379,7 @@
         <v>46206.4858124537</v>
       </c>
       <c r="D141" s="8">
-        <v>46223.57262464121</v>
+        <v>46230.168987060184</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>401</v>
@@ -10423,8 +10423,8 @@
       <c r="R141" s="8">
         <v>46237</v>
       </c>
-      <c r="S141" s="10" t="s">
-        <v>32</v>
+      <c r="S141" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="T141" s="9">
         <v>1</v>
@@ -13839,7 +13839,7 @@
       <c r="T203" s="9">
         <v>0</v>
       </c>
-      <c r="U203" s="11" t="s">
+      <c r="U203" s="12" t="s">
         <v>206</v>
       </c>
     </row>
@@ -13902,7 +13902,7 @@
       <c r="T204" s="6">
         <v>0</v>
       </c>
-      <c r="U204" s="11" t="s">
+      <c r="U204" s="12" t="s">
         <v>206</v>
       </c>
     </row>
@@ -13955,8 +13955,8 @@
       <c r="T205" s="9">
         <v>0</v>
       </c>
-      <c r="U205" s="12" t="s">
-        <v>129</v>
+      <c r="U205" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="206" spans="1:21" x14ac:dyDescent="0.25">
@@ -14018,7 +14018,7 @@
       <c r="T206" s="6">
         <v>0</v>
       </c>
-      <c r="U206" s="11" t="s">
+      <c r="U206" s="12" t="s">
         <v>206</v>
       </c>
     </row>
@@ -14081,8 +14081,8 @@
       <c r="T207" s="9">
         <v>0</v>
       </c>
-      <c r="U207" s="12" t="s">
-        <v>129</v>
+      <c r="U207" s="11" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -972,7 +972,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -6740,7 +6740,7 @@
         <v>46211.83846215278</v>
       </c>
       <c r="D78" s="5">
-        <v>46211.83847391204</v>
+        <v>46231.18753892361</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>247</v>
@@ -6782,8 +6782,8 @@
       <c r="R78" s="5">
         <v>46238</v>
       </c>
-      <c r="S78" s="10" t="s">
-        <v>32</v>
+      <c r="S78" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -7574,7 +7574,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46225.86187162037</v>
+        <v>46231.560379201386</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -7574,7 +7574,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46231.560379201386</v>
+        <v>46231.6530965162</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -669,202 +669,202 @@
     <t>Fabricación estructura proveedor externo ot 4335 - 4337 -4339,Generacion OC Fabricación Externa ot 4335 - 4337 -4339</t>
   </si>
   <si>
+    <t>1215141566544936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación estructura proveedor externo ot 4335 - 4337 -4339,Fabricación Externa ot 4335 - 4337 -4339 </t>
+  </si>
+  <si>
+    <t>1215141318257122</t>
+  </si>
+  <si>
+    <t>Fabricación estructura proveedor externo ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricación Externa ot 4335 - 4337 -4339 ,Control de calidad fabricación externa  ot 4335 - 4337 -4339,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215141318257139</t>
+  </si>
+  <si>
+    <t>Control de calidad fabricación externa  ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
+    <t>1215141451318143</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Generación OC Mecanizado ot 4335 - 4337 -4339,Fabricación Mecanizado ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402333046</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4335 - 4337 -4339,Fabricación Mecanizado ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>1215141402333063</t>
+  </si>
+  <si>
+    <t>Fabricación Mecanizado ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Mecanizado ot 4335 - 4337 -4339,Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>1215141533944733</t>
+  </si>
+  <si>
+    <t>Ingenieria y diseñoo:</t>
+  </si>
+  <si>
+    <t>Planos definitivos,Planos preliminar</t>
+  </si>
+  <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1215141533944745</t>
+  </si>
+  <si>
+    <t>Planos preliminar</t>
+  </si>
+  <si>
+    <t>Hernan Roberto Gutierrez Barrientos</t>
+  </si>
+  <si>
+    <t>hgutierrez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215139673478167</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215137857526183</t>
+  </si>
+  <si>
+    <t>1215137857526184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos preliminar,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526185</t>
+  </si>
+  <si>
+    <t>1215137857526186</t>
+  </si>
+  <si>
+    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>Planos preliminar,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141566627433</t>
+  </si>
+  <si>
+    <t>Planos definitivos</t>
+  </si>
+  <si>
+    <t>1215137857526187</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Planos motor proveedor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215137857526188</t>
+  </si>
+  <si>
+    <t>1215137857526189</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Planos motor proveedor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos definitivos,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526190</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planos definitivos,OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526191</t>
+  </si>
+  <si>
+    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Planos motor proveedor ot 4335 - 4337 -4339</t>
+  </si>
+  <si>
+    <t>Planos definitivos,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141318332820</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuesta Mecanizad ot 4335 - 4337 -4339o,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT  4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Propuesta Fabricación externa  ot 4335 - 4337 -4339,propuesta Corte Laser ot 4335 - 4337 -4339,Propuesta Corte plasma  ot 4335 - 4337 -4339,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526192</t>
+  </si>
+  <si>
+    <t>1215137857526193</t>
+  </si>
+  <si>
+    <t>1215137857526194</t>
+  </si>
+  <si>
+    <t>1215137857526195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215137857526196</t>
+  </si>
+  <si>
+    <t>1215141533950987</t>
+  </si>
+  <si>
+    <t>check pruebas FAT</t>
+  </si>
+  <si>
+    <t>Francisca González Cornejo</t>
+  </si>
+  <si>
+    <t>francisca.gonzalez@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141566544936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación estructura proveedor externo ot 4335 - 4337 -4339,Fabricación Externa ot 4335 - 4337 -4339 </t>
-  </si>
-  <si>
-    <t>1215141318257122</t>
-  </si>
-  <si>
-    <t>Fabricación estructura proveedor externo ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricación Externa ot 4335 - 4337 -4339 ,Control de calidad fabricación externa  ot 4335 - 4337 -4339,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215141318257139</t>
-  </si>
-  <si>
-    <t>Control de calidad fabricación externa  ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
-    <t>1215141451318143</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Generación OC Mecanizado ot 4335 - 4337 -4339,Fabricación Mecanizado ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402333046</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4335 - 4337 -4339,Fabricación Mecanizado ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>1215141402333063</t>
-  </si>
-  <si>
-    <t>Fabricación Mecanizado ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Mecanizado ot 4335 - 4337 -4339,Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>1215141533944733</t>
-  </si>
-  <si>
-    <t>Ingenieria y diseñoo:</t>
-  </si>
-  <si>
-    <t>Planos definitivos,Planos preliminar</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1215141533944745</t>
-  </si>
-  <si>
-    <t>Planos preliminar</t>
-  </si>
-  <si>
-    <t>Hernan Roberto Gutierrez Barrientos</t>
-  </si>
-  <si>
-    <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215139673478167</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215137857526183</t>
-  </si>
-  <si>
-    <t>1215137857526184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planos preliminar,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526185</t>
-  </si>
-  <si>
-    <t>1215137857526186</t>
-  </si>
-  <si>
-    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>Planos preliminar,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141566627433</t>
-  </si>
-  <si>
-    <t>Planos definitivos</t>
-  </si>
-  <si>
-    <t>1215137857526187</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Planos motor proveedor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215137857526188</t>
-  </si>
-  <si>
-    <t>1215137857526189</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Planos motor proveedor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planos definitivos,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526190</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planos definitivos,OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526191</t>
-  </si>
-  <si>
-    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Planos motor proveedor ot 4335 - 4337 -4339</t>
-  </si>
-  <si>
-    <t>Planos definitivos,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141318332820</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuesta Mecanizad ot 4335 - 4337 -4339o,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT  4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Propuesta Fabricación externa  ot 4335 - 4337 -4339,propuesta Corte Laser ot 4335 - 4337 -4339,Propuesta Corte plasma  ot 4335 - 4337 -4339,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526192</t>
-  </si>
-  <si>
-    <t>1215137857526193</t>
-  </si>
-  <si>
-    <t>1215137857526194</t>
-  </si>
-  <si>
-    <t>1215137857526195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215137857526196</t>
-  </si>
-  <si>
-    <t>1215141533950987</t>
-  </si>
-  <si>
-    <t>check pruebas FAT</t>
-  </si>
-  <si>
-    <t>Francisca González Cornejo</t>
-  </si>
-  <si>
-    <t>francisca.gonzalez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215141533950999</t>
@@ -5266,7 +5266,7 @@
         <v>46204.86077883102</v>
       </c>
       <c r="D52" s="5">
-        <v>46224.18342847222</v>
+        <v>46232.18354991898</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>181</v>
@@ -5310,8 +5310,8 @@
       <c r="R52" s="5">
         <v>46231</v>
       </c>
-      <c r="S52" s="12" t="s">
-        <v>185</v>
+      <c r="S52" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -5322,7 +5322,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B53" s="8">
         <v>46168.68337377315</v>
@@ -5367,7 +5367,7 @@
         <v>112</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B54" s="5">
         <v>46168.683378194444</v>
@@ -5389,7 +5389,7 @@
         <v>46204.601540787036</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
@@ -5422,7 +5422,7 @@
         <v>113</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5432,7 +5432,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B55" s="8">
         <v>46168.68338271991</v>
@@ -5444,16 +5444,16 @@
         <v>46205.644352627314</v>
       </c>
       <c r="E55" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="F55" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="F55" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G55" s="9" t="s">
+      <c r="H55" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I55" s="8">
         <v>46231</v>
@@ -5474,7 +5474,7 @@
         <v>181</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5487,7 +5487,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B56" s="5">
         <v>46168.683385868055</v>
@@ -5499,7 +5499,7 @@
         <v>46204.19788391204</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5529,7 +5529,7 @@
         <v>118</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>26</v>
@@ -5552,7 +5552,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B57" s="8">
         <v>46168.68343064815</v>
@@ -5591,13 +5591,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O57" s="9" t="s">
         <v>109</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5607,7 +5607,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B58" s="5">
         <v>46168.683436956024</v>
@@ -5619,7 +5619,7 @@
         <v>46199.56544034722</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
@@ -5646,13 +5646,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>110</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5662,7 +5662,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B59" s="8">
         <v>46168.68344221065</v>
@@ -5672,7 +5672,7 @@
         <v>46210.52421333334</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>25</v>
@@ -5696,7 +5696,7 @@
         <v>26</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>26</v>
@@ -5706,12 +5706,12 @@
       <c r="S59" s="9"/>
       <c r="T59" s="9"/>
       <c r="U59" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B60" s="5">
         <v>46168.683445787035</v>
@@ -5723,16 +5723,16 @@
         <v>46184.518844583334</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I60" s="5">
         <v>46167</v>
@@ -5750,13 +5750,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="5">
         <v>46167</v>
@@ -5776,7 +5776,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B61" s="8">
         <v>46168.6865996875</v>
@@ -5788,16 +5788,16 @@
         <v>46184.51878665509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I61" s="8">
         <v>46167</v>
@@ -5815,13 +5815,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5831,7 +5831,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46168.68683460648</v>
@@ -5843,16 +5843,16 @@
         <v>46184.518791319446</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I62" s="5">
         <v>46167</v>
@@ -5870,13 +5870,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5886,7 +5886,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B63" s="8">
         <v>46168.686918437495</v>
@@ -5898,16 +5898,16 @@
         <v>46184.51879930556</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I63" s="8">
         <v>46167</v>
@@ -5925,13 +5925,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5941,7 +5941,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B64" s="5">
         <v>46168.687254143515</v>
@@ -5953,16 +5953,16 @@
         <v>46184.5188068287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I64" s="5">
         <v>46167</v>
@@ -5980,13 +5980,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5996,7 +5996,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B65" s="8">
         <v>46168.68731635417</v>
@@ -6008,16 +6008,16 @@
         <v>46184.51881454861</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I65" s="8">
         <v>46167</v>
@@ -6035,13 +6035,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -6051,7 +6051,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B66" s="5">
         <v>46168.68345142361</v>
@@ -6063,16 +6063,16 @@
         <v>46190.605242708334</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I66" s="5">
         <v>46181</v>
@@ -6090,13 +6090,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="Q66" s="5">
         <v>46181</v>
@@ -6116,7 +6116,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B67" s="8">
         <v>46168.68857346065</v>
@@ -6128,16 +6128,16 @@
         <v>46190.60518608797</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I67" s="8">
         <v>46181</v>
@@ -6155,13 +6155,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O67" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="P67" s="9" t="s">
         <v>226</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>227</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -6171,7 +6171,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B68" s="5">
         <v>46168.688608275465</v>
@@ -6183,16 +6183,16 @@
         <v>46190.60519502315</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I68" s="5">
         <v>46181</v>
@@ -6210,13 +6210,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>227</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B69" s="8">
         <v>46168.68864659722</v>
@@ -6238,16 +6238,16 @@
         <v>46190.605203761574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I69" s="8">
         <v>46181</v>
@@ -6265,13 +6265,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>231</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6281,7 +6281,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B70" s="5">
         <v>46168.68868637731</v>
@@ -6293,16 +6293,16 @@
         <v>46190.605208946756</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I70" s="5">
         <v>46181</v>
@@ -6320,13 +6320,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6336,7 +6336,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B71" s="8">
         <v>46168.68871934028</v>
@@ -6348,16 +6348,16 @@
         <v>46190.60521709491</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I71" s="8">
         <v>46181</v>
@@ -6375,13 +6375,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>235</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -6391,7 +6391,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B72" s="5">
         <v>46168.68345790509</v>
@@ -6409,10 +6409,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I72" s="5">
         <v>46188</v>
@@ -6430,13 +6430,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>238</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>239</v>
       </c>
       <c r="Q72" s="5">
         <v>46188</v>
@@ -6456,7 +6456,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B73" s="8">
         <v>46168.68880178241</v>
@@ -6468,16 +6468,16 @@
         <v>46190.60536361111</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -6498,7 +6498,7 @@
         <v>103</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>103</v>
@@ -6511,7 +6511,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B74" s="5">
         <v>46168.68883857639</v>
@@ -6523,16 +6523,16 @@
         <v>46190.605368206016</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I74" s="5">
         <v>46188</v>
@@ -6553,7 +6553,7 @@
         <v>103</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>103</v>
@@ -6566,7 +6566,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B75" s="8">
         <v>46168.688875775464</v>
@@ -6578,16 +6578,16 @@
         <v>46190.605373530096</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I75" s="8">
         <v>46188</v>
@@ -6608,7 +6608,7 @@
         <v>103</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>103</v>
@@ -6621,7 +6621,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B76" s="5">
         <v>46168.6889172338</v>
@@ -6633,16 +6633,16 @@
         <v>46190.60539957176</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>209</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>210</v>
       </c>
       <c r="I76" s="5">
         <v>46188</v>
@@ -6663,7 +6663,7 @@
         <v>103</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>103</v>
@@ -6676,7 +6676,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B77" s="8">
         <v>46168.688956620375</v>
@@ -6688,16 +6688,16 @@
         <v>46190.60538814815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>209</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>210</v>
       </c>
       <c r="I77" s="8">
         <v>46188</v>
@@ -6718,7 +6718,7 @@
         <v>103</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6731,7 +6731,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B78" s="5">
         <v>46168.683480625</v>
@@ -6743,16 +6743,16 @@
         <v>46231.18753892361</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>247</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6768,10 +6768,10 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6783,7 +6783,7 @@
         <v>46238</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6806,16 +6806,16 @@
         <v>46211.83842664352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I79" s="8">
         <v>46238</v>
@@ -6833,10 +6833,10 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P79" s="9" t="s">
         <v>252</v>
@@ -6861,16 +6861,16 @@
         <v>46211.83843200232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I80" s="5">
         <v>46238</v>
@@ -6888,10 +6888,10 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>252</v>
@@ -6916,16 +6916,16 @@
         <v>46211.83843496528</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I81" s="8">
         <v>46238</v>
@@ -6943,13 +6943,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6971,16 +6971,16 @@
         <v>46211.83844040509</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>248</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>249</v>
       </c>
       <c r="I82" s="5">
         <v>46238</v>
@@ -6998,13 +6998,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -7026,16 +7026,16 @@
         <v>46211.83844619213</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="I83" s="8">
         <v>46238</v>
@@ -7053,13 +7053,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -7205,10 +7205,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H86" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I86" s="5">
         <v>46206</v>
@@ -7335,10 +7335,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H88" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I88" s="5">
         <v>46206</v>
@@ -7424,7 +7424,7 @@
         <v>258</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="P89" s="9" t="s">
         <v>277</v>
@@ -7465,10 +7465,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H90" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I90" s="5">
         <v>46206</v>
@@ -7642,7 +7642,7 @@
         <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7697,7 +7697,7 @@
         <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7730,7 +7730,7 @@
         <v>291</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7752,7 +7752,7 @@
         <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7807,7 +7807,7 @@
         <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
@@ -7862,7 +7862,7 @@
         <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
@@ -7982,7 +7982,7 @@
         <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
@@ -8037,7 +8037,7 @@
         <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
@@ -8092,7 +8092,7 @@
         <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
@@ -8122,7 +8122,7 @@
         <v>299</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P101" s="9" t="s">
         <v>307</v>
@@ -8147,7 +8147,7 @@
         <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
@@ -8177,7 +8177,7 @@
         <v>299</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P102" s="6" t="s">
         <v>309</v>
@@ -8202,7 +8202,7 @@
         <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
@@ -8232,7 +8232,7 @@
         <v>299</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>311</v>
@@ -8263,10 +8263,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H104" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H104" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I104" s="5">
         <v>46224</v>
@@ -8322,16 +8322,16 @@
         <v>46204.890051967595</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H105" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H105" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I105" s="8">
         <v>46224</v>
@@ -8383,10 +8383,10 @@
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H106" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H106" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I106" s="5">
         <v>46224</v>
@@ -8432,16 +8432,16 @@
         <v>46204.89006394676</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H107" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H107" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I107" s="8">
         <v>46224</v>
@@ -8462,7 +8462,7 @@
         <v>313</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P107" s="9" t="s">
         <v>313</v>
@@ -8487,16 +8487,16 @@
         <v>46204.89006936342</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H108" s="6" t="s">
         <v>193</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>194</v>
       </c>
       <c r="I108" s="5">
         <v>46224</v>
@@ -8517,7 +8517,7 @@
         <v>313</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P108" s="6" t="s">
         <v>322</v>
@@ -8542,16 +8542,16 @@
         <v>46204.890080185185</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H109" s="9" t="s">
         <v>193</v>
-      </c>
-      <c r="H109" s="9" t="s">
-        <v>194</v>
       </c>
       <c r="I109" s="8">
         <v>46224</v>
@@ -8572,7 +8572,7 @@
         <v>313</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P109" s="9" t="s">
         <v>324</v>
@@ -8873,7 +8873,7 @@
         <v>258</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
         <v>338</v>
@@ -8885,7 +8885,7 @@
         <v>46232</v>
       </c>
       <c r="S114" s="12" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="T114" s="6">
         <v>1</v>
@@ -9005,7 +9005,7 @@
       <c r="S116" s="6"/>
       <c r="T116" s="6"/>
       <c r="U116" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
@@ -9019,7 +9019,7 @@
         <v>46204.89075866898</v>
       </c>
       <c r="D117" s="8">
-        <v>46224.18342798611</v>
+        <v>46232.183549988426</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>345</v>
@@ -9063,8 +9063,8 @@
       <c r="R117" s="8">
         <v>46231</v>
       </c>
-      <c r="S117" s="12" t="s">
-        <v>185</v>
+      <c r="S117" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T117" s="9">
         <v>1</v>
@@ -9087,7 +9087,7 @@
         <v>46223.57192800926</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -9142,7 +9142,7 @@
         <v>46223.57192443287</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -9197,7 +9197,7 @@
         <v>46223.571920902774</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -9227,7 +9227,7 @@
         <v>345</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P120" s="6" t="s">
         <v>352</v>
@@ -9252,7 +9252,7 @@
         <v>46223.571917685185</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -9282,7 +9282,7 @@
         <v>345</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P121" s="9" t="s">
         <v>352</v>
@@ -9307,7 +9307,7 @@
         <v>46223.57191195602</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9337,7 +9337,7 @@
         <v>345</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P122" s="6" t="s">
         <v>355</v>
@@ -9404,7 +9404,7 @@
         <v>46232</v>
       </c>
       <c r="S123" s="12" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="T123" s="9">
         <v>1</v>
@@ -9427,7 +9427,7 @@
         <v>46223.57203607639</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9482,7 +9482,7 @@
         <v>46223.57203178241</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9537,7 +9537,7 @@
         <v>46223.5720284375</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9592,7 +9592,7 @@
         <v>46223.5720246875</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9647,7 +9647,7 @@
         <v>46223.57201939815</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9744,7 +9744,7 @@
         <v>46233</v>
       </c>
       <c r="S129" s="12" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="T129" s="9">
         <v>1</v>
@@ -9767,7 +9767,7 @@
         <v>46223.57212789352</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9822,7 +9822,7 @@
         <v>46223.57212385417</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9877,7 +9877,7 @@
         <v>46223.57212008102</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9932,7 +9932,7 @@
         <v>46223.57211625</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9987,7 +9987,7 @@
         <v>46223.572111180554</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -10084,7 +10084,7 @@
         <v>46234</v>
       </c>
       <c r="S135" s="12" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="T135" s="9">
         <v>1</v>
@@ -10107,7 +10107,7 @@
         <v>46223.5722359375</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -10162,7 +10162,7 @@
         <v>46223.572232199076</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -10217,7 +10217,7 @@
         <v>46223.5722271875</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -10272,7 +10272,7 @@
         <v>46223.57222349537</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -10327,7 +10327,7 @@
         <v>46223.57221770834</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10424,7 +10424,7 @@
         <v>46237</v>
       </c>
       <c r="S141" s="12" t="s">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="T141" s="9">
         <v>1</v>
@@ -10447,7 +10447,7 @@
         <v>46223.57235236111</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10477,7 +10477,7 @@
         <v>401</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P142" s="6" t="s">
         <v>403</v>
@@ -10502,7 +10502,7 @@
         <v>46223.57234864583</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -10532,7 +10532,7 @@
         <v>401</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P143" s="9" t="s">
         <v>405</v>
@@ -10557,7 +10557,7 @@
         <v>46223.57234428241</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10587,7 +10587,7 @@
         <v>401</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P144" s="6" t="s">
         <v>407</v>
@@ -10612,7 +10612,7 @@
         <v>46223.572340370374</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10642,7 +10642,7 @@
         <v>401</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P145" s="9" t="s">
         <v>407</v>
@@ -10667,7 +10667,7 @@
         <v>46223.57233454861</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10697,7 +10697,7 @@
         <v>401</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P146" s="6" t="s">
         <v>410</v>
@@ -10719,7 +10719,7 @@
         <v>46206.48621289352</v>
       </c>
       <c r="D147" s="8">
-        <v>46223.57261809028</v>
+        <v>46232.1816966551</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>412</v>
@@ -10763,8 +10763,8 @@
       <c r="R147" s="8">
         <v>46239</v>
       </c>
-      <c r="S147" s="10" t="s">
-        <v>32</v>
+      <c r="S147" s="12" t="s">
+        <v>250</v>
       </c>
       <c r="T147" s="9">
         <v>1</v>
@@ -10787,7 +10787,7 @@
         <v>46223.572544027775</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10817,7 +10817,7 @@
         <v>412</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P148" s="6" t="s">
         <v>415</v>
@@ -10842,7 +10842,7 @@
         <v>46223.5725400463</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10872,7 +10872,7 @@
         <v>412</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P149" s="9" t="s">
         <v>417</v>
@@ -10897,7 +10897,7 @@
         <v>46223.57253650463</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10927,7 +10927,7 @@
         <v>412</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P150" s="6" t="s">
         <v>419</v>
@@ -10952,7 +10952,7 @@
         <v>46223.5725334375</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10982,7 +10982,7 @@
         <v>412</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P151" s="9" t="s">
         <v>419</v>
@@ -11007,7 +11007,7 @@
         <v>46223.5725280787</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -11037,7 +11037,7 @@
         <v>412</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P152" s="6" t="s">
         <v>422</v>
@@ -11180,7 +11180,7 @@
         <v>46211.831112581014</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
@@ -11210,7 +11210,7 @@
         <v>427</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P155" s="9" t="s">
         <v>432</v>
@@ -11235,7 +11235,7 @@
         <v>46211.83112387732</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
@@ -11265,7 +11265,7 @@
         <v>427</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P156" s="6" t="s">
         <v>432</v>
@@ -11290,7 +11290,7 @@
         <v>46211.83112878472</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
@@ -11320,7 +11320,7 @@
         <v>427</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>435</v>
@@ -11345,7 +11345,7 @@
         <v>46211.83116206019</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11375,7 +11375,7 @@
         <v>427</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P158" s="6" t="s">
         <v>435</v>
@@ -11400,7 +11400,7 @@
         <v>46211.83117125</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -11430,7 +11430,7 @@
         <v>427</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P159" s="9" t="s">
         <v>438</v>
@@ -11848,7 +11848,7 @@
         <v>46223.5729158912</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
@@ -11876,7 +11876,7 @@
         <v>449</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P167" s="9" t="s">
         <v>452</v>
@@ -11901,7 +11901,7 @@
         <v>46223.57291190972</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11929,7 +11929,7 @@
         <v>449</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P168" s="6" t="s">
         <v>452</v>
@@ -11954,7 +11954,7 @@
         <v>46223.57290799769</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
@@ -11982,7 +11982,7 @@
         <v>449</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P169" s="9" t="s">
         <v>455</v>
@@ -12007,7 +12007,7 @@
         <v>46223.57290423611</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -12035,7 +12035,7 @@
         <v>449</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P170" s="6" t="s">
         <v>455</v>
@@ -12060,7 +12060,7 @@
         <v>46223.57290035879</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
@@ -12088,7 +12088,7 @@
         <v>449</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P171" s="9" t="s">
         <v>458</v>
@@ -12494,7 +12494,7 @@
         <v>46209.71550439815</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
@@ -12524,7 +12524,7 @@
         <v>470</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P179" s="9" t="s">
         <v>473</v>
@@ -12549,7 +12549,7 @@
         <v>46209.7156449537</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
@@ -12579,7 +12579,7 @@
         <v>470</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P180" s="6" t="s">
         <v>475</v>
@@ -12604,7 +12604,7 @@
         <v>46209.715759733794</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
@@ -12634,7 +12634,7 @@
         <v>470</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P181" s="9" t="s">
         <v>477</v>
@@ -12659,7 +12659,7 @@
         <v>46209.71583459491</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
@@ -12689,7 +12689,7 @@
         <v>470</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P182" s="6" t="s">
         <v>479</v>
@@ -12714,7 +12714,7 @@
         <v>46209.71610449074</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
@@ -12744,7 +12744,7 @@
         <v>470</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P183" s="9" t="s">
         <v>481</v>
@@ -13192,7 +13192,7 @@
         <v>496</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P191" s="9" t="s">
         <v>496</v>
@@ -13245,7 +13245,7 @@
         <v>496</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="P192" s="6" t="s">
         <v>496</v>
@@ -13298,7 +13298,7 @@
         <v>496</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P193" s="9" t="s">
         <v>496</v>
@@ -13351,7 +13351,7 @@
         <v>496</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P194" s="6" t="s">
         <v>496</v>
@@ -13404,7 +13404,7 @@
         <v>496</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="P195" s="9" t="s">
         <v>496</v>
@@ -13840,7 +13840,7 @@
         <v>0</v>
       </c>
       <c r="U203" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
@@ -13903,7 +13903,7 @@
         <v>0</v>
       </c>
       <c r="U204" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">
@@ -14019,7 +14019,7 @@
         <v>0</v>
       </c>
       <c r="U206" s="12" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="207" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2400" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="538">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -972,7 +972,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7574,7 +7574,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46231.6530965162</v>
+        <v>46232.83598015046</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>
@@ -13740,9 +13740,11 @@
       <c r="B202" s="5">
         <v>46168.684555775464</v>
       </c>
-      <c r="C202" s="6"/>
+      <c r="C202" s="5">
+        <v>46232.6631619213</v>
+      </c>
       <c r="D202" s="5">
-        <v>46168.8618759838</v>
+        <v>46232.66317605324</v>
       </c>
       <c r="E202" s="6" t="s">
         <v>522</v>
@@ -13777,8 +13779,12 @@
       <c r="Q202" s="6"/>
       <c r="R202" s="6"/>
       <c r="S202" s="6"/>
-      <c r="T202" s="6"/>
-      <c r="U202" s="6"/>
+      <c r="T202" s="6">
+        <v>1</v>
+      </c>
+      <c r="U202" s="10" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
@@ -13787,9 +13793,11 @@
       <c r="B203" s="8">
         <v>46168.6845594676</v>
       </c>
-      <c r="C203" s="9"/>
+      <c r="C203" s="8">
+        <v>46232.663133553244</v>
+      </c>
       <c r="D203" s="8">
-        <v>46211.83025064815</v>
+        <v>46232.663153229165</v>
       </c>
       <c r="E203" s="9" t="s">
         <v>525</v>
@@ -13837,10 +13845,10 @@
         <v>32</v>
       </c>
       <c r="T203" s="9">
-        <v>0</v>
-      </c>
-      <c r="U203" s="12" t="s">
-        <v>205</v>
+        <v>1</v>
+      </c>
+      <c r="U203" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
@@ -13850,9 +13858,11 @@
       <c r="B204" s="5">
         <v>46168.68456425926</v>
       </c>
-      <c r="C204" s="6"/>
+      <c r="C204" s="5">
+        <v>46232.663143171296</v>
+      </c>
       <c r="D204" s="5">
-        <v>46211.83025032407</v>
+        <v>46232.66316190972</v>
       </c>
       <c r="E204" s="6" t="s">
         <v>529</v>
@@ -13900,10 +13910,10 @@
         <v>32</v>
       </c>
       <c r="T204" s="6">
-        <v>0</v>
-      </c>
-      <c r="U204" s="12" t="s">
-        <v>205</v>
+        <v>1</v>
+      </c>
+      <c r="U204" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="205" spans="1:21" x14ac:dyDescent="0.25">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -972,7 +972,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -8840,7 +8840,7 @@
         <v>46211.82998440972</v>
       </c>
       <c r="D114" s="5">
-        <v>46225.18216611111</v>
+        <v>46233.16842706018</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>337</v>
@@ -8884,8 +8884,8 @@
       <c r="R114" s="5">
         <v>46232</v>
       </c>
-      <c r="S114" s="12" t="s">
-        <v>250</v>
+      <c r="S114" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T114" s="6">
         <v>1</v>
@@ -9359,7 +9359,7 @@
         <v>46204.89175555555</v>
       </c>
       <c r="D123" s="8">
-        <v>46225.182165729166</v>
+        <v>46233.16842686343</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>357</v>
@@ -9403,8 +9403,8 @@
       <c r="R123" s="8">
         <v>46232</v>
       </c>
-      <c r="S123" s="12" t="s">
-        <v>250</v>
+      <c r="S123" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T123" s="9">
         <v>1</v>
@@ -11112,7 +11112,7 @@
         <v>46211.83269833333</v>
       </c>
       <c r="D154" s="5">
-        <v>46211.8327003125</v>
+        <v>46233.19259844907</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>427</v>
@@ -11156,8 +11156,8 @@
       <c r="R154" s="5">
         <v>46240</v>
       </c>
-      <c r="S154" s="10" t="s">
-        <v>32</v>
+      <c r="S154" s="12" t="s">
+        <v>250</v>
       </c>
       <c r="T154" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -7574,7 +7574,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46232.83598015046</v>
+        <v>46233.64825932871</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -9699,7 +9699,7 @@
         <v>46204.89298883102</v>
       </c>
       <c r="D129" s="8">
-        <v>46226.19708972222</v>
+        <v>46234.18465609953</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>372</v>
@@ -9743,8 +9743,8 @@
       <c r="R129" s="8">
         <v>46233</v>
       </c>
-      <c r="S129" s="12" t="s">
-        <v>250</v>
+      <c r="S129" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T129" s="9">
         <v>1</v>
@@ -11782,7 +11782,7 @@
         <v>46211.83055506945</v>
       </c>
       <c r="D166" s="5">
-        <v>46223.57301792824</v>
+        <v>46234.17948802083</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>449</v>
@@ -11824,8 +11824,8 @@
       <c r="R166" s="5">
         <v>46241</v>
       </c>
-      <c r="S166" s="10" t="s">
-        <v>32</v>
+      <c r="S166" s="12" t="s">
+        <v>250</v>
       </c>
       <c r="T166" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -10039,7 +10039,7 @@
         <v>46204.893422152774</v>
       </c>
       <c r="D135" s="8">
-        <v>46227.17239224537</v>
+        <v>46235.16899013889</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>387</v>
@@ -10083,8 +10083,8 @@
       <c r="R135" s="8">
         <v>46234</v>
       </c>
-      <c r="S135" s="12" t="s">
-        <v>250</v>
+      <c r="S135" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T135" s="9">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -12428,7 +12428,7 @@
         <v>46209.71534268519</v>
       </c>
       <c r="D178" s="5">
-        <v>46209.715354976855</v>
+        <v>46237.20353347222</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>470</v>
@@ -12470,8 +12470,8 @@
       <c r="R178" s="5">
         <v>46244</v>
       </c>
-      <c r="S178" s="10" t="s">
-        <v>32</v>
+      <c r="S178" s="12" t="s">
+        <v>250</v>
       </c>
       <c r="T178" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -972,7 +972,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4</t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7574,7 +7574,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46233.64825932871</v>
+        <v>46237.57050487268</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -7574,7 +7574,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46237.57050487268</v>
+        <v>46237.810158101856</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>283</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -10379,7 +10379,7 @@
         <v>46206.4858124537</v>
       </c>
       <c r="D141" s="8">
-        <v>46230.168987060184</v>
+        <v>46238.20125695602</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>401</v>
@@ -10423,8 +10423,8 @@
       <c r="R141" s="8">
         <v>46237</v>
       </c>
-      <c r="S141" s="12" t="s">
-        <v>250</v>
+      <c r="S141" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T141" s="9">
         <v>1</v>
@@ -13096,7 +13096,7 @@
         <v>46211.83022659722</v>
       </c>
       <c r="D190" s="5">
-        <v>46223.57240934028</v>
+        <v>46238.19406451389</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>496</v>
@@ -13140,8 +13140,8 @@
       <c r="R190" s="5">
         <v>46245</v>
       </c>
-      <c r="S190" s="10" t="s">
-        <v>32</v>
+      <c r="S190" s="12" t="s">
+        <v>250</v>
       </c>
       <c r="T190" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -864,496 +864,496 @@
     <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
+    <t>1215141533950999</t>
+  </si>
+  <si>
+    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141533961665</t>
+  </si>
+  <si>
+    <t>1215141533961677</t>
+  </si>
+  <si>
+    <t>1215141533961684</t>
+  </si>
+  <si>
+    <t>1215141566669401</t>
+  </si>
+  <si>
+    <t>1215141402523613</t>
+  </si>
+  <si>
+    <t>Bodega:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215141402523625</t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser</t>
+  </si>
+  <si>
+    <t>Victor Muñoz</t>
+  </si>
+  <si>
+    <t>victor.munoz@zitron.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215141533986830</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Bodega:,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141533986852</t>
+  </si>
+  <si>
+    <t>Recepcion Materiales corte plasma</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>1215141533987066</t>
+  </si>
+  <si>
+    <t>Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141533987083</t>
+  </si>
+  <si>
+    <t>Recepcion mecanizado</t>
+  </si>
+  <si>
+    <t>Control de calidad Mecanizado</t>
+  </si>
+  <si>
+    <t>1215141533988318</t>
+  </si>
+  <si>
+    <t>1215141318374043</t>
+  </si>
+  <si>
+    <t>Caldereria:</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215141318374055</t>
+  </si>
+  <si>
+    <t>Preparación Materiales</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141566712673</t>
+  </si>
+  <si>
+    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Preparación Materiales</t>
+  </si>
+  <si>
+    <t>1215141566712700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t>1215141318385916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preparación Materiales,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141402549850</t>
+  </si>
+  <si>
+    <t>1215141451475643</t>
+  </si>
+  <si>
+    <t>Preparación Materiales,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141451524336</t>
+  </si>
+  <si>
+    <t>Armado</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141318462536</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,check planos</t>
+  </si>
+  <si>
+    <t>Armado,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141318470872</t>
+  </si>
+  <si>
+    <t>Armado,OT  4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141318470894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141738306513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141738306525</t>
+  </si>
+  <si>
+    <t>Armado,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141738325808</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT  4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141738325825</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Control de calidad Armado</t>
+  </si>
+  <si>
+    <t>1215141318505449</t>
+  </si>
+  <si>
+    <t>OT  4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141318505471</t>
+  </si>
+  <si>
+    <t>1215141738338450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Control de calidad Armado,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141738338462</t>
+  </si>
+  <si>
+    <t>Control de calidad Armado,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141566877123</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,Recepcion motor,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>1215141566877135</t>
+  </si>
+  <si>
+    <t>Recepcion Rodete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Bodega:,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141318552569</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Bodega:,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141318552591</t>
+  </si>
+  <si>
+    <t>Recepcion motor</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Bodega:,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141534133482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141318552544</t>
+  </si>
+  <si>
+    <t>OT 4336 -Tablero YD 37KW ,Revision Tableros,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW</t>
+  </si>
+  <si>
+    <t>1215141402790372</t>
+  </si>
+  <si>
+    <t>Montaje:</t>
+  </si>
+  <si>
+    <t>Revestimiento,Pruebas FAT,RE-PINTADO,Montaje Alabe,Montaje motor,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1215141402790384</t>
+  </si>
+  <si>
+    <t>Revestimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215141534177649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215141534177826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT  4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion fabricación externa </t>
+  </si>
+  <si>
+    <t>1215141534177843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141402796490</t>
+  </si>
+  <si>
+    <t>1215141402796502</t>
+  </si>
+  <si>
+    <t>Revestimiento,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141566973321</t>
+  </si>
+  <si>
+    <t>Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1215141566973338</t>
+  </si>
+  <si>
+    <t>Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141738442885</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Montaje Alabe</t>
+  </si>
+  <si>
+    <t>1215141738442907</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Recepcion Alabe,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje Alabe,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141402816902</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,check planos,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>1215141534245692</t>
+  </si>
+  <si>
+    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,check planos,Recepcion Alabe</t>
+  </si>
+  <si>
+    <t>Montaje Alabe,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141738469253</t>
+  </si>
+  <si>
+    <t>Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1215141738469270</t>
+  </si>
+  <si>
+    <t>check planos,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion Rodete</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141318649284</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Montaje Rodete</t>
+  </si>
+  <si>
+    <t>1215141402861161</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje Rodete,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141738502856</t>
+  </si>
+  <si>
+    <t>1215141318537021</t>
+  </si>
+  <si>
+    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Recepcion Rodete,check planos</t>
+  </si>
+  <si>
+    <t>Montaje Rodete,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141567096322</t>
+  </si>
+  <si>
+    <t>Montaje motor</t>
+  </si>
+  <si>
+    <t>1215141402916731</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141402916758</t>
+  </si>
+  <si>
+    <t>1215141318701544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">check planos,Recepcion motor,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje motor,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141402935589</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,check planos,Recepcion motor</t>
+  </si>
+  <si>
+    <t>1215141567126880</t>
+  </si>
+  <si>
+    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Recepcion motor,check planos</t>
+  </si>
+  <si>
+    <t>Montaje motor,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141534346024</t>
+  </si>
+  <si>
+    <t>Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1215141534346041</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141738618601</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Pruebas FAT</t>
+  </si>
+  <si>
+    <t>1215141590670997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pruebas FAT,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141590671014</t>
+  </si>
+  <si>
+    <t>1215141402981897</t>
+  </si>
+  <si>
+    <t>Pruebas FAT,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141534387126</t>
+  </si>
+  <si>
+    <t>RE-PINTADO</t>
+  </si>
+  <si>
+    <t>Montaje:,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141533950999</t>
-  </si>
-  <si>
-    <t>check pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141533961665</t>
-  </si>
-  <si>
-    <t>1215141533961677</t>
-  </si>
-  <si>
-    <t>1215141533961684</t>
-  </si>
-  <si>
-    <t>1215141566669401</t>
-  </si>
-  <si>
-    <t>1215141402523613</t>
-  </si>
-  <si>
-    <t>Bodega:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion materiales corte laser,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215141402523625</t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser</t>
-  </si>
-  <si>
-    <t>Victor Muñoz</t>
-  </si>
-  <si>
-    <t>victor.munoz@zitron.com</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bodega:,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215141533986830</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>Recepcion materiales corte laser,Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Bodega:,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141533986852</t>
-  </si>
-  <si>
-    <t>Recepcion Materiales corte plasma</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>1215141533987066</t>
-  </si>
-  <si>
-    <t>Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141533987083</t>
-  </si>
-  <si>
-    <t>Recepcion mecanizado</t>
-  </si>
-  <si>
-    <t>Control de calidad Mecanizado</t>
-  </si>
-  <si>
-    <t>1215141533988318</t>
-  </si>
-  <si>
-    <t>1215141318374043</t>
-  </si>
-  <si>
-    <t>Caldereria:</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,Armado,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215141318374055</t>
-  </si>
-  <si>
-    <t>Preparación Materiales</t>
-  </si>
-  <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141566712673</t>
-  </si>
-  <si>
-    <t>Control de calidad corte laser ,Control de calidad Mecanizado,Control de calidad Corte plasma</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Preparación Materiales</t>
-  </si>
-  <si>
-    <t>1215141566712700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Corte plasma,Control de calidad Mecanizado,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t>1215141318385916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Mecanizado,Control de calidad Corte plasma,Control de calidad corte laser </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preparación Materiales,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141402549850</t>
-  </si>
-  <si>
-    <t>1215141451475643</t>
-  </si>
-  <si>
-    <t>Preparación Materiales,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141451524336</t>
-  </si>
-  <si>
-    <t>Armado</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141318462536</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,check planos</t>
-  </si>
-  <si>
-    <t>Armado,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141318470872</t>
-  </si>
-  <si>
-    <t>Armado,OT  4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141318470894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141738306513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141738306525</t>
-  </si>
-  <si>
-    <t>Armado,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141738325808</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT  4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141738325825</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Control de calidad Armado</t>
-  </si>
-  <si>
-    <t>1215141318505449</t>
-  </si>
-  <si>
-    <t>OT  4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141318505471</t>
-  </si>
-  <si>
-    <t>1215141738338450</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control de calidad Armado,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141738338462</t>
-  </si>
-  <si>
-    <t>Control de calidad Armado,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141566877123</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,Recepcion motor,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>1215141566877135</t>
-  </si>
-  <si>
-    <t>Recepcion Rodete</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Bodega:,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141318552569</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Bodega:,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141318552591</t>
-  </si>
-  <si>
-    <t>Recepcion motor</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Bodega:,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141534133482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141318552544</t>
-  </si>
-  <si>
-    <t>OT 4336 -Tablero YD 37KW ,Revision Tableros,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW</t>
-  </si>
-  <si>
-    <t>1215141402790372</t>
-  </si>
-  <si>
-    <t>Montaje:</t>
-  </si>
-  <si>
-    <t>Revestimiento,Pruebas FAT,RE-PINTADO,Montaje Alabe,Montaje motor,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1215141402790384</t>
-  </si>
-  <si>
-    <t>Revestimiento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215141534177649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215141534177826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT  4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion fabricación externa </t>
-  </si>
-  <si>
-    <t>1215141534177843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141402796490</t>
-  </si>
-  <si>
-    <t>1215141402796502</t>
-  </si>
-  <si>
-    <t>Revestimiento,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141566973321</t>
-  </si>
-  <si>
-    <t>Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1215141566973338</t>
-  </si>
-  <si>
-    <t>Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141738442885</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Montaje Alabe</t>
-  </si>
-  <si>
-    <t>1215141738442907</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Recepcion Alabe,check planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje Alabe,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141402816902</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,check planos,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>1215141534245692</t>
-  </si>
-  <si>
-    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,check planos,Recepcion Alabe</t>
-  </si>
-  <si>
-    <t>Montaje Alabe,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141738469253</t>
-  </si>
-  <si>
-    <t>Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1215141738469270</t>
-  </si>
-  <si>
-    <t>check planos,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion Rodete</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141318649284</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Montaje Rodete</t>
-  </si>
-  <si>
-    <t>1215141402861161</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje Rodete,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141738502856</t>
-  </si>
-  <si>
-    <t>1215141318537021</t>
-  </si>
-  <si>
-    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Recepcion Rodete,check planos</t>
-  </si>
-  <si>
-    <t>Montaje Rodete,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141567096322</t>
-  </si>
-  <si>
-    <t>Montaje motor</t>
-  </si>
-  <si>
-    <t>1215141402916731</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141402916758</t>
-  </si>
-  <si>
-    <t>1215141318701544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">check planos,Recepcion motor,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje motor,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141402935589</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,check planos,Recepcion motor</t>
-  </si>
-  <si>
-    <t>1215141567126880</t>
-  </si>
-  <si>
-    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,Recepcion motor,check planos</t>
-  </si>
-  <si>
-    <t>Montaje motor,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141534346024</t>
-  </si>
-  <si>
-    <t>Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1215141534346041</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141738618601</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Pruebas FAT</t>
-  </si>
-  <si>
-    <t>1215141590670997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas FAT,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141590671014</t>
-  </si>
-  <si>
-    <t>1215141402981897</t>
-  </si>
-  <si>
-    <t>Pruebas FAT,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141534387126</t>
-  </si>
-  <si>
-    <t>RE-PINTADO</t>
-  </si>
-  <si>
-    <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
     <t>1215141590714176</t>
@@ -6740,7 +6740,7 @@
         <v>46211.83846215278</v>
       </c>
       <c r="D78" s="5">
-        <v>46231.18753892361</v>
+        <v>46239.194167118054</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>246</v>
@@ -6782,8 +6782,8 @@
       <c r="R78" s="5">
         <v>46238</v>
       </c>
-      <c r="S78" s="12" t="s">
-        <v>250</v>
+      <c r="S78" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T78" s="6">
         <v>1</v>
@@ -6794,7 +6794,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B79" s="8">
         <v>46168.683484629626</v>
@@ -6839,7 +6839,7 @@
         <v>212</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6849,7 +6849,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B80" s="5">
         <v>46168.683488877316</v>
@@ -6894,7 +6894,7 @@
         <v>212</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6904,7 +6904,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B81" s="8">
         <v>46168.68349300926</v>
@@ -6959,7 +6959,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B82" s="5">
         <v>46168.6834959375</v>
@@ -7014,7 +7014,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B83" s="8">
         <v>46168.68349899305</v>
@@ -7069,7 +7069,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B84" s="5">
         <v>46168.68351101852</v>
@@ -7081,7 +7081,7 @@
         <v>46205.618076087965</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -7105,7 +7105,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B85" s="8">
         <v>46168.68351447917</v>
@@ -7134,16 +7134,16 @@
         <v>46206.18878055556</v>
       </c>
       <c r="E85" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>261</v>
       </c>
-      <c r="F85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="9" t="s">
+      <c r="H85" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I85" s="8">
         <v>46204</v>
@@ -7161,13 +7161,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>170</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Q85" s="8">
         <v>46204</v>
@@ -7187,7 +7187,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B86" s="5">
         <v>46168.68352011574</v>
@@ -7199,7 +7199,7 @@
         <v>46223.57312579861</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -7226,13 +7226,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>268</v>
       </c>
       <c r="Q86" s="5">
         <v>46206</v>
@@ -7252,7 +7252,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B87" s="8">
         <v>46168.68352736111</v>
@@ -7264,16 +7264,16 @@
         <v>46206.18878028935</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -7291,13 +7291,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>178</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -7317,7 +7317,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B88" s="5">
         <v>46168.68353292824</v>
@@ -7329,7 +7329,7 @@
         <v>46223.573107916665</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7356,13 +7356,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q88" s="5">
         <v>46206</v>
@@ -7382,7 +7382,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B89" s="8">
         <v>46168.68353787037</v>
@@ -7394,16 +7394,16 @@
         <v>46206.1887803125</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7421,13 +7421,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>200</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Q89" s="8">
         <v>46204</v>
@@ -7447,7 +7447,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B90" s="5">
         <v>46168.68354247685</v>
@@ -7459,7 +7459,7 @@
         <v>46223.573090949074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7486,13 +7486,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="Q90" s="5">
         <v>46206</v>
@@ -7512,7 +7512,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B91" s="8">
         <v>46168.68354741899</v>
@@ -7524,7 +7524,7 @@
         <v>46211.83134737269</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>25</v>
@@ -7548,7 +7548,7 @@
         <v>26</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>26</v>
@@ -7565,7 +7565,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B92" s="5">
         <v>46168.68355052083</v>
@@ -7574,19 +7574,19 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46237.810158101856</v>
+        <v>46239.57423510417</v>
       </c>
       <c r="E92" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="F92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" s="6" t="s">
+      <c r="H92" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7604,13 +7604,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q92" s="5">
         <v>46210</v>
@@ -7630,7 +7630,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B93" s="8">
         <v>46168.68356208333</v>
@@ -7648,10 +7648,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I93" s="8">
         <v>46210</v>
@@ -7669,13 +7669,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O93" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="P93" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>289</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7685,7 +7685,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B94" s="5">
         <v>46168.68356922454</v>
@@ -7703,10 +7703,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7724,10 +7724,10 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="P94" s="6" t="s">
         <v>212</v>
@@ -7740,7 +7740,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B95" s="8">
         <v>46168.683574780094</v>
@@ -7758,10 +7758,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I95" s="8">
         <v>46210</v>
@@ -7779,13 +7779,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>293</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>294</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7795,7 +7795,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B96" s="5">
         <v>46168.68358024306</v>
@@ -7813,10 +7813,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7834,13 +7834,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>293</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>294</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B97" s="8">
         <v>46168.68358578703</v>
@@ -7868,10 +7868,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I97" s="8">
         <v>46210</v>
@@ -7889,13 +7889,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7905,7 +7905,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B98" s="5">
         <v>46168.68365474537</v>
@@ -7917,16 +7917,16 @@
         <v>46224.175157731486</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I98" s="5">
         <v>46213</v>
@@ -7944,13 +7944,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q98" s="5">
         <v>46213</v>
@@ -7970,7 +7970,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B99" s="8">
         <v>46168.683659965274</v>
@@ -7988,10 +7988,10 @@
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I99" s="8">
         <v>46213</v>
@@ -8009,13 +8009,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O99" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="P99" s="9" t="s">
         <v>302</v>
-      </c>
-      <c r="P99" s="9" t="s">
-        <v>303</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -8025,7 +8025,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B100" s="5">
         <v>46168.68366613426</v>
@@ -8043,10 +8043,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I100" s="5">
         <v>46213</v>
@@ -8064,13 +8064,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -8080,7 +8080,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B101" s="8">
         <v>46168.683671921295</v>
@@ -8098,10 +8098,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I101" s="8">
         <v>46213</v>
@@ -8119,13 +8119,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O101" s="9" t="s">
         <v>216</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -8135,7 +8135,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B102" s="5">
         <v>46168.68367622685</v>
@@ -8153,10 +8153,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I102" s="5">
         <v>46213</v>
@@ -8174,13 +8174,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>216</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8190,7 +8190,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B103" s="8">
         <v>46168.683680069444</v>
@@ -8208,10 +8208,10 @@
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H103" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I103" s="8">
         <v>46213</v>
@@ -8229,13 +8229,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="O103" s="9" t="s">
         <v>220</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8245,7 +8245,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B104" s="5">
         <v>46168.68369409722</v>
@@ -8257,7 +8257,7 @@
         <v>46225.167433888884</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8284,13 +8284,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="Q104" s="5">
         <v>46224</v>
@@ -8310,7 +8310,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B105" s="8">
         <v>46168.68369849537</v>
@@ -8349,13 +8349,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B106" s="5">
         <v>46168.683704490744</v>
@@ -8377,7 +8377,7 @@
         <v>46204.890058125005</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8404,13 +8404,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8420,7 +8420,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B107" s="8">
         <v>46168.683710150464</v>
@@ -8459,13 +8459,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O107" s="9" t="s">
         <v>216</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8475,7 +8475,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B108" s="5">
         <v>46168.68371309028</v>
@@ -8514,13 +8514,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>216</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8530,7 +8530,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B109" s="8">
         <v>46168.68371646991</v>
@@ -8569,13 +8569,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="O109" s="9" t="s">
         <v>220</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8585,7 +8585,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B110" s="5">
         <v>46168.68373005787</v>
@@ -8597,7 +8597,7 @@
         <v>46211.830014363426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8621,7 +8621,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8638,7 +8638,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B111" s="8">
         <v>46168.68373365741</v>
@@ -8650,16 +8650,16 @@
         <v>46205.61049446759</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H111" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I111" s="8">
         <v>46185</v>
@@ -8677,13 +8677,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>139</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="Q111" s="8">
         <v>46185</v>
@@ -8703,7 +8703,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B112" s="5">
         <v>46168.6837408912</v>
@@ -8715,16 +8715,16 @@
         <v>46205.61455358796</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8740,13 +8740,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>130</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="Q112" s="5">
         <v>46168</v>
@@ -8766,7 +8766,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B113" s="8">
         <v>46168.68374771991</v>
@@ -8778,16 +8778,16 @@
         <v>46205.6084347338</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H113" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I113" s="8">
         <v>46199</v>
@@ -8805,13 +8805,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>148</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="Q113" s="8">
         <v>46199</v>
@@ -8831,7 +8831,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B114" s="5">
         <v>46168.68375502314</v>
@@ -8843,16 +8843,16 @@
         <v>46233.16842706018</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>262</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>263</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8870,13 +8870,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="Q114" s="5">
         <v>46232</v>
@@ -8896,7 +8896,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B115" s="8">
         <v>46168.6837971412</v>
@@ -8914,10 +8914,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="H115" s="9" t="s">
         <v>262</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>263</v>
       </c>
       <c r="I115" s="8">
         <v>46220</v>
@@ -8935,13 +8935,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>159</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="Q115" s="8">
         <v>46220</v>
@@ -8961,7 +8961,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B116" s="5">
         <v>46168.68381362269</v>
@@ -8971,7 +8971,7 @@
         <v>46206.48624146991</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8995,7 +8995,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -9010,7 +9010,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B117" s="8">
         <v>46168.68381783565</v>
@@ -9022,7 +9022,7 @@
         <v>46232.183549988426</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -9049,13 +9049,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q117" s="8">
         <v>46225</v>
@@ -9075,7 +9075,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B118" s="5">
         <v>46168.683825810185</v>
@@ -9114,13 +9114,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -9130,7 +9130,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B119" s="8">
         <v>46168.68383587963</v>
@@ -9169,13 +9169,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -9185,7 +9185,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B120" s="5">
         <v>46168.68384034722</v>
@@ -9224,13 +9224,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>216</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -9240,7 +9240,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B121" s="8">
         <v>46168.683844074076</v>
@@ -9279,13 +9279,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O121" s="9" t="s">
         <v>216</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9295,7 +9295,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B122" s="5">
         <v>46168.683847673616</v>
@@ -9334,13 +9334,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>220</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9350,7 +9350,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B123" s="8">
         <v>46168.683862453705</v>
@@ -9362,7 +9362,7 @@
         <v>46233.16842686343</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9389,13 +9389,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q123" s="8">
         <v>46232</v>
@@ -9415,7 +9415,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B124" s="5">
         <v>46168.683867141204</v>
@@ -9454,13 +9454,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O124" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="P124" s="6" t="s">
         <v>359</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>360</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9470,7 +9470,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B125" s="8">
         <v>46168.683873368056</v>
@@ -9509,13 +9509,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9525,7 +9525,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B126" s="5">
         <v>46168.68387903935</v>
@@ -9564,13 +9564,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O126" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="P126" s="6" t="s">
         <v>364</v>
-      </c>
-      <c r="P126" s="6" t="s">
-        <v>365</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9580,7 +9580,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B127" s="8">
         <v>46168.683884618054</v>
@@ -9619,13 +9619,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9635,7 +9635,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B128" s="5">
         <v>46168.68389033565</v>
@@ -9674,13 +9674,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O128" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="P128" s="6" t="s">
         <v>369</v>
-      </c>
-      <c r="P128" s="6" t="s">
-        <v>370</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9690,7 +9690,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B129" s="8">
         <v>46168.68391289352</v>
@@ -9702,7 +9702,7 @@
         <v>46234.18465609953</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9729,13 +9729,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q129" s="8">
         <v>46233</v>
@@ -9755,7 +9755,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B130" s="5">
         <v>46168.68391818287</v>
@@ -9794,13 +9794,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O130" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="P130" s="6" t="s">
         <v>374</v>
-      </c>
-      <c r="P130" s="6" t="s">
-        <v>375</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B131" s="8">
         <v>46168.68393068287</v>
@@ -9849,13 +9849,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O131" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="P131" s="9" t="s">
         <v>377</v>
-      </c>
-      <c r="P131" s="9" t="s">
-        <v>378</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9865,7 +9865,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B132" s="5">
         <v>46168.68393770834</v>
@@ -9904,13 +9904,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O132" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>380</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>381</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9920,7 +9920,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B133" s="8">
         <v>46168.6839434375</v>
@@ -9959,13 +9959,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O133" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="P133" s="9" t="s">
         <v>380</v>
-      </c>
-      <c r="P133" s="9" t="s">
-        <v>381</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9975,7 +9975,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B134" s="5">
         <v>46168.68398528935</v>
@@ -10014,13 +10014,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="O134" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="P134" s="6" t="s">
         <v>384</v>
-      </c>
-      <c r="P134" s="6" t="s">
-        <v>385</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -10030,7 +10030,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B135" s="8">
         <v>46168.68401087963</v>
@@ -10042,7 +10042,7 @@
         <v>46235.16899013889</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -10069,13 +10069,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q135" s="8">
         <v>46234</v>
@@ -10095,7 +10095,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B136" s="5">
         <v>46168.68401652778</v>
@@ -10134,13 +10134,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O136" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="P136" s="6" t="s">
         <v>389</v>
-      </c>
-      <c r="P136" s="6" t="s">
-        <v>390</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -10150,7 +10150,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B137" s="8">
         <v>46168.68402403935</v>
@@ -10189,13 +10189,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O137" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="P137" s="9" t="s">
         <v>389</v>
-      </c>
-      <c r="P137" s="9" t="s">
-        <v>390</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -10205,7 +10205,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B138" s="5">
         <v>46168.68403127315</v>
@@ -10244,13 +10244,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O138" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="P138" s="6" t="s">
         <v>393</v>
-      </c>
-      <c r="P138" s="6" t="s">
-        <v>394</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -10260,7 +10260,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B139" s="8">
         <v>46168.68403755787</v>
@@ -10299,13 +10299,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -10315,7 +10315,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B140" s="5">
         <v>46168.68404385417</v>
@@ -10354,13 +10354,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="O140" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="P140" s="6" t="s">
         <v>398</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>399</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10370,7 +10370,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B141" s="8">
         <v>46168.68406297454</v>
@@ -10382,7 +10382,7 @@
         <v>46238.20125695602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -10409,13 +10409,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="Q141" s="8">
         <v>46237</v>
@@ -10435,7 +10435,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B142" s="5">
         <v>46168.68406752315</v>
@@ -10474,13 +10474,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>212</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10490,7 +10490,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B143" s="8">
         <v>46168.68407938657</v>
@@ -10529,13 +10529,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O143" s="9" t="s">
         <v>212</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10545,7 +10545,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B144" s="5">
         <v>46168.68408523148</v>
@@ -10584,13 +10584,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>216</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10600,7 +10600,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B145" s="8">
         <v>46168.684089884264</v>
@@ -10639,13 +10639,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O145" s="9" t="s">
         <v>216</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10655,7 +10655,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B146" s="5">
         <v>46168.684094571756</v>
@@ -10694,13 +10694,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>220</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10710,7 +10710,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B147" s="8">
         <v>46168.68414574074</v>
@@ -10722,7 +10722,7 @@
         <v>46232.1816966551</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10749,13 +10749,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="Q147" s="8">
         <v>46239</v>
@@ -10764,7 +10764,7 @@
         <v>46239</v>
       </c>
       <c r="S147" s="12" t="s">
-        <v>250</v>
+        <v>413</v>
       </c>
       <c r="T147" s="9">
         <v>1</v>
@@ -10814,7 +10814,7 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>212</v>
@@ -10869,7 +10869,7 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O149" s="9" t="s">
         <v>212</v>
@@ -10924,7 +10924,7 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>216</v>
@@ -10979,7 +10979,7 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>216</v>
@@ -11034,7 +11034,7 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>220</v>
@@ -11157,7 +11157,7 @@
         <v>46240</v>
       </c>
       <c r="S154" s="12" t="s">
-        <v>250</v>
+        <v>413</v>
       </c>
       <c r="T154" s="6">
         <v>1</v>
@@ -11825,7 +11825,7 @@
         <v>46241</v>
       </c>
       <c r="S166" s="12" t="s">
-        <v>250</v>
+        <v>413</v>
       </c>
       <c r="T166" s="6">
         <v>1</v>
@@ -12437,10 +12437,10 @@
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H178" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -12471,7 +12471,7 @@
         <v>46244</v>
       </c>
       <c r="S178" s="12" t="s">
-        <v>250</v>
+        <v>413</v>
       </c>
       <c r="T178" s="6">
         <v>1</v>
@@ -12500,10 +12500,10 @@
         <v>26</v>
       </c>
       <c r="G179" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H179" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H179" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I179" s="8">
         <v>46244</v>
@@ -12555,10 +12555,10 @@
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H180" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I180" s="5">
         <v>46244</v>
@@ -12610,10 +12610,10 @@
         <v>26</v>
       </c>
       <c r="G181" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H181" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H181" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I181" s="8">
         <v>46244</v>
@@ -12665,10 +12665,10 @@
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H182" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H182" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I182" s="5">
         <v>46244</v>
@@ -12720,10 +12720,10 @@
         <v>26</v>
       </c>
       <c r="G183" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H183" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H183" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I183" s="8">
         <v>46244</v>
@@ -12775,10 +12775,10 @@
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H184" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H184" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I184" s="5">
         <v>46244</v>
@@ -12830,10 +12830,10 @@
         <v>26</v>
       </c>
       <c r="G185" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H185" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H185" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I185" s="8">
         <v>46244</v>
@@ -12885,10 +12885,10 @@
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H186" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I186" s="5">
         <v>46244</v>
@@ -12940,10 +12940,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H187" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H187" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I187" s="8">
         <v>46244</v>
@@ -12995,10 +12995,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H188" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I188" s="5">
         <v>46244</v>
@@ -13050,10 +13050,10 @@
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H189" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H189" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I189" s="8">
         <v>46244</v>
@@ -13105,10 +13105,10 @@
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H190" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H190" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I190" s="5">
         <v>46245</v>
@@ -13141,7 +13141,7 @@
         <v>46245</v>
       </c>
       <c r="S190" s="12" t="s">
-        <v>250</v>
+        <v>413</v>
       </c>
       <c r="T190" s="6">
         <v>1</v>
@@ -13170,10 +13170,10 @@
         <v>26</v>
       </c>
       <c r="G191" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H191" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H191" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="8">
@@ -13223,10 +13223,10 @@
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H192" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -13276,10 +13276,10 @@
         <v>26</v>
       </c>
       <c r="G193" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H193" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H193" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="8">
@@ -13329,10 +13329,10 @@
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H194" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="5">
@@ -13382,10 +13382,10 @@
         <v>26</v>
       </c>
       <c r="G195" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H195" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H195" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I195" s="9"/>
       <c r="J195" s="8">
@@ -13435,10 +13435,10 @@
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H196" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -13488,10 +13488,10 @@
         <v>26</v>
       </c>
       <c r="G197" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H197" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H197" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I197" s="9"/>
       <c r="J197" s="8">
@@ -13541,10 +13541,10 @@
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H198" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13594,10 +13594,10 @@
         <v>26</v>
       </c>
       <c r="G199" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H199" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H199" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I199" s="9"/>
       <c r="J199" s="8">
@@ -13647,10 +13647,10 @@
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="H200" s="6" t="s">
         <v>284</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>285</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13700,10 +13700,10 @@
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="H201" s="9" t="s">
         <v>284</v>
-      </c>
-      <c r="H201" s="9" t="s">
-        <v>285</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="8">

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -969,7 +969,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ</t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1215141566712673</t>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -1353,58 +1353,58 @@
     <t>Montaje:,Coordinacion Entrega con Cliente</t>
   </si>
   <si>
+    <t>1215141590714176</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141590714193</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,RE-PINTADO</t>
+  </si>
+  <si>
+    <t>1215141738675425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RE-PINTADO,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141738675437</t>
+  </si>
+  <si>
+    <t>1215141738675449</t>
+  </si>
+  <si>
+    <t>RE-PINTADO,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141534472388</t>
+  </si>
+  <si>
+    <t>Logistica:</t>
+  </si>
+  <si>
+    <t>Embalaje,Despacho,PACKING LIST,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1215141534472400</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>Karin Pinto</t>
+  </si>
+  <si>
+    <t>kpinto@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Revision Tableros,RE-PINTADO,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141590714176</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141590714193</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,RE-PINTADO</t>
-  </si>
-  <si>
-    <t>1215141738675425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RE-PINTADO,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141738675437</t>
-  </si>
-  <si>
-    <t>1215141738675449</t>
-  </si>
-  <si>
-    <t>RE-PINTADO,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141534472388</t>
-  </si>
-  <si>
-    <t>Logistica:</t>
-  </si>
-  <si>
-    <t>Embalaje,Despacho,PACKING LIST,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1215141534472400</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>Karin Pinto</t>
-  </si>
-  <si>
-    <t>kpinto@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Revision Tableros,RE-PINTADO,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1215141738699711</t>
@@ -7574,7 +7574,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46239.57423510417</v>
+        <v>46240.58269997685</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>282</v>
@@ -10719,7 +10719,7 @@
         <v>46206.48621289352</v>
       </c>
       <c r="D147" s="8">
-        <v>46232.1816966551</v>
+        <v>46240.20595440972</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>411</v>
@@ -10763,8 +10763,8 @@
       <c r="R147" s="8">
         <v>46239</v>
       </c>
-      <c r="S147" s="12" t="s">
-        <v>413</v>
+      <c r="S147" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T147" s="9">
         <v>1</v>
@@ -10775,7 +10775,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B148" s="5">
         <v>46168.68415105324</v>
@@ -10820,7 +10820,7 @@
         <v>212</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10830,7 +10830,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B149" s="8">
         <v>46168.68415587963</v>
@@ -10875,7 +10875,7 @@
         <v>212</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10885,7 +10885,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B150" s="5">
         <v>46168.68416068287</v>
@@ -10930,7 +10930,7 @@
         <v>216</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10940,7 +10940,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B151" s="8">
         <v>46168.68416431713</v>
@@ -10985,7 +10985,7 @@
         <v>216</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10995,7 +10995,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B152" s="5">
         <v>46168.68416798611</v>
@@ -11040,7 +11040,7 @@
         <v>220</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -11050,7 +11050,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B153" s="8">
         <v>46168.684183460646</v>
@@ -11062,7 +11062,7 @@
         <v>46211.832724733795</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -11086,7 +11086,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -11103,7 +11103,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B154" s="5">
         <v>46168.68418700232</v>
@@ -11115,16 +11115,16 @@
         <v>46233.19259844907</v>
       </c>
       <c r="E154" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G154" s="6" t="s">
         <v>427</v>
       </c>
-      <c r="F154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G154" s="6" t="s">
+      <c r="H154" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="I154" s="5">
         <v>46240</v>
@@ -11142,13 +11142,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q154" s="5">
         <v>46240</v>
@@ -11157,7 +11157,7 @@
         <v>46240</v>
       </c>
       <c r="S154" s="12" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="T154" s="6">
         <v>1</v>
@@ -11186,10 +11186,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>428</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>429</v>
       </c>
       <c r="I155" s="8">
         <v>46240</v>
@@ -11207,7 +11207,7 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O155" s="9" t="s">
         <v>212</v>
@@ -11241,10 +11241,10 @@
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="I156" s="5">
         <v>46240</v>
@@ -11262,7 +11262,7 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>212</v>
@@ -11296,10 +11296,10 @@
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>428</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>429</v>
       </c>
       <c r="I157" s="8">
         <v>46240</v>
@@ -11317,7 +11317,7 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O157" s="9" t="s">
         <v>216</v>
@@ -11351,10 +11351,10 @@
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="I158" s="5">
         <v>46240</v>
@@ -11372,7 +11372,7 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O158" s="6" t="s">
         <v>216</v>
@@ -11406,10 +11406,10 @@
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H159" s="9" t="s">
         <v>428</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>429</v>
       </c>
       <c r="I159" s="8">
         <v>46240</v>
@@ -11427,7 +11427,7 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O159" s="9" t="s">
         <v>220</v>
@@ -11461,10 +11461,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="I160" s="5">
         <v>46240</v>
@@ -11482,7 +11482,7 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>63</v>
@@ -11516,10 +11516,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H161" s="9" t="s">
         <v>428</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>429</v>
       </c>
       <c r="I161" s="8">
         <v>46240</v>
@@ -11537,7 +11537,7 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>63</v>
@@ -11571,10 +11571,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="I162" s="5">
         <v>46240</v>
@@ -11592,7 +11592,7 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>63</v>
@@ -11626,10 +11626,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H163" s="9" t="s">
         <v>428</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>429</v>
       </c>
       <c r="I163" s="8">
         <v>46240</v>
@@ -11647,7 +11647,7 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>67</v>
@@ -11681,10 +11681,10 @@
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="H164" s="6" t="s">
         <v>428</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>429</v>
       </c>
       <c r="I164" s="5">
         <v>46240</v>
@@ -11702,7 +11702,7 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>67</v>
@@ -11736,10 +11736,10 @@
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
+        <v>427</v>
+      </c>
+      <c r="H165" s="9" t="s">
         <v>428</v>
-      </c>
-      <c r="H165" s="9" t="s">
-        <v>429</v>
       </c>
       <c r="I165" s="8">
         <v>46240</v>
@@ -11757,7 +11757,7 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="O165" s="9" t="s">
         <v>70</v>
@@ -11810,13 +11810,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O166" s="6" t="s">
         <v>450</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q166" s="5">
         <v>46241</v>
@@ -11825,7 +11825,7 @@
         <v>46241</v>
       </c>
       <c r="S166" s="12" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="T166" s="6">
         <v>1</v>
@@ -12456,13 +12456,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>471</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="Q178" s="5">
         <v>46244</v>
@@ -12471,7 +12471,7 @@
         <v>46244</v>
       </c>
       <c r="S178" s="12" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="T178" s="6">
         <v>1</v>
@@ -13126,7 +13126,7 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="O190" s="6" t="s">
         <v>497</v>
@@ -13141,7 +13141,7 @@
         <v>46245</v>
       </c>
       <c r="S190" s="12" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="T190" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2401" uniqueCount="538">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="529">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -729,9 +729,6 @@
     <t>Planos definitivos,Planos preliminar</t>
   </si>
   <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
     <t>1215141533944745</t>
   </si>
   <si>
@@ -1608,7 +1605,7 @@
     <t>OT5 4339 - ZVN 1-9-37/2 + TOB + REJ,OT6 4336 -Tablero YD 37KW ,OT7 4336 -Tablero YD 37KW ,OT8 4336 -Tablero YD 37KW ,OT9 4338 - Tablero YD 30KW,OT10  4338 - Tablero YD 30KW,OT11 4341 - Tablero YD 18.5KW,OT3 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT4 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT1 4335 - ZVN 1-7-37/2 + TOB + REJ,OT2  4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
-    <t>Logistica:,Instalación componentes,Gestion,Costos</t>
+    <t>Logistica:,Gestion,Costos</t>
   </si>
   <si>
     <t>1215141403129041</t>
@@ -1702,30 +1699,6 @@
   </si>
   <si>
     <t>Costos</t>
-  </si>
-  <si>
-    <t>1215141739029024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta En Marcha </t>
-  </si>
-  <si>
-    <t>Pruebas de Instalacion Componentes ,Instalación componentes</t>
-  </si>
-  <si>
-    <t>1215141739029039</t>
-  </si>
-  <si>
-    <t>Instalación componentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta En Marcha ,Pruebas de Instalacion Componentes </t>
-  </si>
-  <si>
-    <t>1215141534745475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de Instalacion Componentes </t>
   </si>
 </sst>
 </file>
@@ -2249,7 +2222,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U207"/>
+  <dimension ref="A1:U204"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -5667,9 +5640,11 @@
       <c r="B59" s="8">
         <v>46168.68344221065</v>
       </c>
-      <c r="C59" s="9"/>
+      <c r="C59" s="8">
+        <v>46240.71763709491</v>
+      </c>
       <c r="D59" s="8">
-        <v>46210.52421333334</v>
+        <v>46240.717654513894</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>203</v>
@@ -5704,14 +5679,16 @@
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
       <c r="S59" s="9"/>
-      <c r="T59" s="9"/>
-      <c r="U59" s="12" t="s">
-        <v>205</v>
+      <c r="T59" s="9">
+        <v>1</v>
+      </c>
+      <c r="U59" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B60" s="5">
         <v>46168.683445787035</v>
@@ -5723,16 +5700,16 @@
         <v>46184.518844583334</v>
       </c>
       <c r="E60" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G60" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="F60" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G60" s="6" t="s">
+      <c r="H60" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I60" s="5">
         <v>46167</v>
@@ -5753,7 +5730,7 @@
         <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>203</v>
@@ -5776,7 +5753,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B61" s="8">
         <v>46168.6865996875</v>
@@ -5788,16 +5765,16 @@
         <v>46184.51878665509</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H61" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H61" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I61" s="8">
         <v>46167</v>
@@ -5815,13 +5792,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O61" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5831,7 +5808,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B62" s="5">
         <v>46168.68683460648</v>
@@ -5843,16 +5820,16 @@
         <v>46184.518791319446</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H62" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I62" s="5">
         <v>46167</v>
@@ -5870,13 +5847,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5886,7 +5863,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B63" s="8">
         <v>46168.686918437495</v>
@@ -5898,16 +5875,16 @@
         <v>46184.51879930556</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H63" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H63" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I63" s="8">
         <v>46167</v>
@@ -5925,13 +5902,13 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O63" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q63" s="9"/>
       <c r="R63" s="9"/>
@@ -5941,7 +5918,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B64" s="5">
         <v>46168.687254143515</v>
@@ -5953,16 +5930,16 @@
         <v>46184.5188068287</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H64" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I64" s="5">
         <v>46167</v>
@@ -5980,13 +5957,13 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>85</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="Q64" s="6"/>
       <c r="R64" s="6"/>
@@ -5996,7 +5973,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B65" s="8">
         <v>46168.68731635417</v>
@@ -6008,16 +5985,16 @@
         <v>46184.51881454861</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H65" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H65" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I65" s="8">
         <v>46167</v>
@@ -6035,13 +6012,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="O65" s="9" t="s">
         <v>85</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -6051,7 +6028,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B66" s="5">
         <v>46168.68345142361</v>
@@ -6063,16 +6040,16 @@
         <v>46190.605242708334</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H66" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I66" s="5">
         <v>46181</v>
@@ -6093,7 +6070,7 @@
         <v>203</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>203</v>
@@ -6116,7 +6093,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B67" s="8">
         <v>46168.68857346065</v>
@@ -6128,16 +6105,16 @@
         <v>46190.60518608797</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H67" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H67" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I67" s="8">
         <v>46181</v>
@@ -6155,13 +6132,13 @@
         <v>26</v>
       </c>
       <c r="N67" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O67" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="P67" s="9" t="s">
         <v>225</v>
-      </c>
-      <c r="P67" s="9" t="s">
-        <v>226</v>
       </c>
       <c r="Q67" s="9"/>
       <c r="R67" s="9"/>
@@ -6171,7 +6148,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B68" s="5">
         <v>46168.688608275465</v>
@@ -6183,16 +6160,16 @@
         <v>46190.60519502315</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H68" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H68" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I68" s="5">
         <v>46181</v>
@@ -6210,13 +6187,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O68" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="P68" s="6" t="s">
         <v>225</v>
-      </c>
-      <c r="P68" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="Q68" s="6"/>
       <c r="R68" s="6"/>
@@ -6226,7 +6203,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B69" s="8">
         <v>46168.68864659722</v>
@@ -6238,16 +6215,16 @@
         <v>46190.605203761574</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I69" s="8">
         <v>46181</v>
@@ -6265,13 +6242,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O69" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="P69" s="9" t="s">
         <v>229</v>
-      </c>
-      <c r="P69" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6281,7 +6258,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B70" s="5">
         <v>46168.68868637731</v>
@@ -6293,16 +6270,16 @@
         <v>46190.605208946756</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I70" s="5">
         <v>46181</v>
@@ -6320,13 +6297,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6336,7 +6313,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B71" s="8">
         <v>46168.68871934028</v>
@@ -6348,16 +6325,16 @@
         <v>46190.60521709491</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H71" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H71" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I71" s="8">
         <v>46181</v>
@@ -6375,13 +6352,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="O71" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="P71" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>235</v>
       </c>
       <c r="Q71" s="9"/>
       <c r="R71" s="9"/>
@@ -6391,7 +6368,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B72" s="5">
         <v>46168.68345790509</v>
@@ -6409,10 +6386,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H72" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H72" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I72" s="5">
         <v>46188</v>
@@ -6433,10 +6410,10 @@
         <v>203</v>
       </c>
       <c r="O72" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="P72" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="P72" s="6" t="s">
-        <v>238</v>
       </c>
       <c r="Q72" s="5">
         <v>46188</v>
@@ -6456,7 +6433,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B73" s="8">
         <v>46168.68880178241</v>
@@ -6468,16 +6445,16 @@
         <v>46190.60536361111</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I73" s="8">
         <v>46188</v>
@@ -6498,7 +6475,7 @@
         <v>103</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>103</v>
@@ -6511,7 +6488,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B74" s="5">
         <v>46168.68883857639</v>
@@ -6523,16 +6500,16 @@
         <v>46190.605368206016</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H74" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I74" s="5">
         <v>46188</v>
@@ -6553,7 +6530,7 @@
         <v>103</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P74" s="6" t="s">
         <v>103</v>
@@ -6566,7 +6543,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B75" s="8">
         <v>46168.688875775464</v>
@@ -6578,16 +6555,16 @@
         <v>46190.605373530096</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H75" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H75" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I75" s="8">
         <v>46188</v>
@@ -6608,7 +6585,7 @@
         <v>103</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>103</v>
@@ -6621,7 +6598,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B76" s="5">
         <v>46168.6889172338</v>
@@ -6633,16 +6610,16 @@
         <v>46190.60539957176</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>208</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>209</v>
       </c>
       <c r="I76" s="5">
         <v>46188</v>
@@ -6663,7 +6640,7 @@
         <v>103</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>103</v>
@@ -6676,7 +6653,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B77" s="8">
         <v>46168.688956620375</v>
@@ -6688,16 +6665,16 @@
         <v>46190.60538814815</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="H77" s="9" t="s">
         <v>208</v>
-      </c>
-      <c r="H77" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="I77" s="8">
         <v>46188</v>
@@ -6718,7 +6695,7 @@
         <v>103</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>26</v>
@@ -6731,7 +6708,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B78" s="5">
         <v>46168.683480625</v>
@@ -6743,16 +6720,16 @@
         <v>46239.194167118054</v>
       </c>
       <c r="E78" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="F78" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G78" s="6" t="s">
+      <c r="H78" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6771,7 +6748,7 @@
         <v>203</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P78" s="6" t="s">
         <v>26</v>
@@ -6794,7 +6771,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B79" s="8">
         <v>46168.683484629626</v>
@@ -6806,16 +6783,16 @@
         <v>46211.83842664352</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H79" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H79" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I79" s="8">
         <v>46238</v>
@@ -6833,13 +6810,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6849,7 +6826,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B80" s="5">
         <v>46168.683488877316</v>
@@ -6861,16 +6838,16 @@
         <v>46211.83843200232</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G80" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H80" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I80" s="5">
         <v>46238</v>
@@ -6888,13 +6865,13 @@
         <v>26</v>
       </c>
       <c r="N80" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
@@ -6904,7 +6881,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B81" s="8">
         <v>46168.68349300926</v>
@@ -6916,16 +6893,16 @@
         <v>46211.83843496528</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H81" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H81" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I81" s="8">
         <v>46238</v>
@@ -6943,13 +6920,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q81" s="9"/>
       <c r="R81" s="9"/>
@@ -6959,7 +6936,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B82" s="5">
         <v>46168.6834959375</v>
@@ -6971,16 +6948,16 @@
         <v>46211.83844040509</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>247</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>248</v>
       </c>
       <c r="I82" s="5">
         <v>46238</v>
@@ -6998,13 +6975,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="Q82" s="6"/>
       <c r="R82" s="6"/>
@@ -7014,7 +6991,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B83" s="8">
         <v>46168.68349899305</v>
@@ -7026,16 +7003,16 @@
         <v>46211.83844619213</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>247</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>248</v>
       </c>
       <c r="I83" s="8">
         <v>46238</v>
@@ -7053,13 +7030,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="Q83" s="9"/>
       <c r="R83" s="9"/>
@@ -7069,7 +7046,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B84" s="5">
         <v>46168.68351101852</v>
@@ -7081,7 +7058,7 @@
         <v>46205.618076087965</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>25</v>
@@ -7105,7 +7082,7 @@
         <v>26</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="P84" s="6" t="s">
         <v>26</v>
@@ -7122,7 +7099,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B85" s="8">
         <v>46168.68351447917</v>
@@ -7134,16 +7111,16 @@
         <v>46206.18878055556</v>
       </c>
       <c r="E85" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="F85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="F85" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G85" s="9" t="s">
+      <c r="H85" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="H85" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="I85" s="8">
         <v>46204</v>
@@ -7161,13 +7138,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O85" s="9" t="s">
         <v>170</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Q85" s="8">
         <v>46204</v>
@@ -7187,7 +7164,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B86" s="5">
         <v>46168.68352011574</v>
@@ -7199,7 +7176,7 @@
         <v>46223.57312579861</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -7226,13 +7203,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O86" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="P86" s="6" t="s">
         <v>266</v>
-      </c>
-      <c r="P86" s="6" t="s">
-        <v>267</v>
       </c>
       <c r="Q86" s="5">
         <v>46206</v>
@@ -7252,7 +7229,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B87" s="8">
         <v>46168.68352736111</v>
@@ -7264,16 +7241,16 @@
         <v>46206.18878028935</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H87" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="H87" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="I87" s="8">
         <v>46204</v>
@@ -7291,13 +7268,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O87" s="9" t="s">
         <v>178</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Q87" s="8">
         <v>46204</v>
@@ -7317,7 +7294,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B88" s="5">
         <v>46168.68353292824</v>
@@ -7329,7 +7306,7 @@
         <v>46223.573107916665</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -7356,13 +7333,13 @@
         <v>26</v>
       </c>
       <c r="N88" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q88" s="5">
         <v>46206</v>
@@ -7382,7 +7359,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B89" s="8">
         <v>46168.68353787037</v>
@@ -7394,16 +7371,16 @@
         <v>46206.1887803125</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H89" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="I89" s="8">
         <v>46204</v>
@@ -7421,13 +7398,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O89" s="9" t="s">
         <v>200</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="Q89" s="8">
         <v>46204</v>
@@ -7447,7 +7424,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B90" s="5">
         <v>46168.68354247685</v>
@@ -7459,7 +7436,7 @@
         <v>46223.573090949074</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
@@ -7486,13 +7463,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="Q90" s="5">
         <v>46206</v>
@@ -7512,7 +7489,7 @@
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B91" s="8">
         <v>46168.68354741899</v>
@@ -7524,7 +7501,7 @@
         <v>46211.83134737269</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>25</v>
@@ -7548,7 +7525,7 @@
         <v>26</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="P91" s="9" t="s">
         <v>26</v>
@@ -7565,7 +7542,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B92" s="5">
         <v>46168.68355052083</v>
@@ -7577,16 +7554,16 @@
         <v>46240.58269997685</v>
       </c>
       <c r="E92" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="F92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" s="6" t="s">
+      <c r="H92" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I92" s="5">
         <v>46210</v>
@@ -7604,13 +7581,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q92" s="5">
         <v>46210</v>
@@ -7630,7 +7607,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B93" s="8">
         <v>46168.68356208333</v>
@@ -7642,16 +7619,16 @@
         <v>46197.85263298611</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H93" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H93" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I93" s="8">
         <v>46210</v>
@@ -7669,13 +7646,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O93" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="P93" s="9" t="s">
         <v>287</v>
-      </c>
-      <c r="P93" s="9" t="s">
-        <v>288</v>
       </c>
       <c r="Q93" s="9"/>
       <c r="R93" s="9"/>
@@ -7685,7 +7662,7 @@
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B94" s="5">
         <v>46168.68356922454</v>
@@ -7697,16 +7674,16 @@
         <v>46197.85263334491</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H94" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H94" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I94" s="5">
         <v>46210</v>
@@ -7724,13 +7701,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7740,7 +7717,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B95" s="8">
         <v>46168.683574780094</v>
@@ -7752,16 +7729,16 @@
         <v>46197.85263368055</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H95" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H95" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I95" s="8">
         <v>46210</v>
@@ -7779,13 +7756,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O95" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="P95" s="9" t="s">
         <v>292</v>
-      </c>
-      <c r="P95" s="9" t="s">
-        <v>293</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7795,7 +7772,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B96" s="5">
         <v>46168.68358024306</v>
@@ -7807,16 +7784,16 @@
         <v>46197.852634062496</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G96" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H96" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I96" s="5">
         <v>46210</v>
@@ -7834,13 +7811,13 @@
         <v>26</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O96" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="P96" s="6" t="s">
         <v>292</v>
-      </c>
-      <c r="P96" s="6" t="s">
-        <v>293</v>
       </c>
       <c r="Q96" s="6"/>
       <c r="R96" s="6"/>
@@ -7850,7 +7827,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B97" s="8">
         <v>46168.68358578703</v>
@@ -7862,16 +7839,16 @@
         <v>46197.852634490744</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H97" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H97" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I97" s="8">
         <v>46210</v>
@@ -7889,13 +7866,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="Q97" s="9"/>
       <c r="R97" s="9"/>
@@ -7905,7 +7882,7 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B98" s="5">
         <v>46168.68365474537</v>
@@ -7917,16 +7894,16 @@
         <v>46224.175157731486</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H98" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I98" s="5">
         <v>46213</v>
@@ -7944,13 +7921,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q98" s="5">
         <v>46213</v>
@@ -7970,7 +7947,7 @@
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B99" s="8">
         <v>46168.683659965274</v>
@@ -7982,16 +7959,16 @@
         <v>46197.852639861114</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H99" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H99" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I99" s="8">
         <v>46213</v>
@@ -8009,13 +7986,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O99" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="P99" s="9" t="s">
         <v>301</v>
-      </c>
-      <c r="P99" s="9" t="s">
-        <v>302</v>
       </c>
       <c r="Q99" s="9"/>
       <c r="R99" s="9"/>
@@ -8025,7 +8002,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B100" s="5">
         <v>46168.68366613426</v>
@@ -8037,16 +8014,16 @@
         <v>46197.85263996528</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H100" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H100" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I100" s="5">
         <v>46213</v>
@@ -8064,13 +8041,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q100" s="6"/>
       <c r="R100" s="6"/>
@@ -8080,7 +8057,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B101" s="8">
         <v>46168.683671921295</v>
@@ -8092,16 +8069,16 @@
         <v>46197.852640173616</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H101" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H101" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I101" s="8">
         <v>46213</v>
@@ -8119,13 +8096,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q101" s="9"/>
       <c r="R101" s="9"/>
@@ -8135,7 +8112,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B102" s="5">
         <v>46168.68367622685</v>
@@ -8147,16 +8124,16 @@
         <v>46197.85264196759</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H102" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H102" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I102" s="5">
         <v>46213</v>
@@ -8174,13 +8151,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q102" s="6"/>
       <c r="R102" s="6"/>
@@ -8190,7 +8167,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B103" s="8">
         <v>46168.683680069444</v>
@@ -8202,16 +8179,16 @@
         <v>46197.85264373843</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G103" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H103" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I103" s="8">
         <v>46213</v>
@@ -8229,13 +8206,13 @@
         <v>26</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q103" s="9"/>
       <c r="R103" s="9"/>
@@ -8245,7 +8222,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B104" s="5">
         <v>46168.68369409722</v>
@@ -8257,7 +8234,7 @@
         <v>46225.167433888884</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8284,13 +8261,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q104" s="5">
         <v>46224</v>
@@ -8310,7 +8287,7 @@
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B105" s="8">
         <v>46168.68369849537</v>
@@ -8322,7 +8299,7 @@
         <v>46204.890051967595</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8349,13 +8326,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8365,7 +8342,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B106" s="5">
         <v>46168.683704490744</v>
@@ -8377,7 +8354,7 @@
         <v>46204.890058125005</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8404,13 +8381,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8420,7 +8397,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B107" s="8">
         <v>46168.683710150464</v>
@@ -8432,7 +8409,7 @@
         <v>46204.89006394676</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8459,13 +8436,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q107" s="9"/>
       <c r="R107" s="9"/>
@@ -8475,7 +8452,7 @@
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B108" s="5">
         <v>46168.68371309028</v>
@@ -8487,7 +8464,7 @@
         <v>46204.89006936342</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8514,13 +8491,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8530,7 +8507,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B109" s="8">
         <v>46168.68371646991</v>
@@ -8542,7 +8519,7 @@
         <v>46204.890080185185</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8569,13 +8546,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8585,7 +8562,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B110" s="5">
         <v>46168.68373005787</v>
@@ -8597,7 +8574,7 @@
         <v>46211.830014363426</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>25</v>
@@ -8621,7 +8598,7 @@
         <v>26</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="P110" s="6" t="s">
         <v>26</v>
@@ -8638,7 +8615,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B111" s="8">
         <v>46168.68373365741</v>
@@ -8650,16 +8627,16 @@
         <v>46205.61049446759</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H111" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="H111" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="I111" s="8">
         <v>46185</v>
@@ -8677,13 +8654,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O111" s="9" t="s">
         <v>139</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="Q111" s="8">
         <v>46185</v>
@@ -8703,7 +8680,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B112" s="5">
         <v>46168.6837408912</v>
@@ -8715,16 +8692,16 @@
         <v>46205.61455358796</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="H112" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="I112" s="6"/>
       <c r="J112" s="5">
@@ -8740,13 +8717,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>130</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="Q112" s="5">
         <v>46168</v>
@@ -8766,7 +8743,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B113" s="8">
         <v>46168.68374771991</v>
@@ -8778,16 +8755,16 @@
         <v>46205.6084347338</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H113" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="H113" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="I113" s="8">
         <v>46199</v>
@@ -8805,13 +8782,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O113" s="9" t="s">
         <v>148</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="Q113" s="8">
         <v>46199</v>
@@ -8831,7 +8808,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B114" s="5">
         <v>46168.68375502314</v>
@@ -8843,16 +8820,16 @@
         <v>46233.16842706018</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="H114" s="6" t="s">
         <v>261</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>262</v>
       </c>
       <c r="I114" s="5">
         <v>46232</v>
@@ -8870,13 +8847,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>188</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="Q114" s="5">
         <v>46232</v>
@@ -8896,7 +8873,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B115" s="8">
         <v>46168.6837971412</v>
@@ -8914,10 +8891,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="H115" s="9" t="s">
         <v>261</v>
-      </c>
-      <c r="H115" s="9" t="s">
-        <v>262</v>
       </c>
       <c r="I115" s="8">
         <v>46220</v>
@@ -8935,13 +8912,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="O115" s="9" t="s">
         <v>159</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="Q115" s="8">
         <v>46220</v>
@@ -8961,17 +8938,19 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B116" s="5">
         <v>46168.68381362269</v>
       </c>
-      <c r="C116" s="6"/>
+      <c r="C116" s="5">
+        <v>46240.71750915509</v>
+      </c>
       <c r="D116" s="5">
-        <v>46206.48624146991</v>
+        <v>46240.7175233912</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>25</v>
@@ -8995,7 +8974,7 @@
         <v>26</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="P116" s="6" t="s">
         <v>26</v>
@@ -9003,14 +8982,16 @@
       <c r="Q116" s="6"/>
       <c r="R116" s="6"/>
       <c r="S116" s="6"/>
-      <c r="T116" s="6"/>
-      <c r="U116" s="12" t="s">
-        <v>205</v>
+      <c r="T116" s="6">
+        <v>1</v>
+      </c>
+      <c r="U116" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B117" s="8">
         <v>46168.68381783565</v>
@@ -9022,7 +9003,7 @@
         <v>46232.183549988426</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -9049,13 +9030,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q117" s="8">
         <v>46225</v>
@@ -9075,7 +9056,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B118" s="5">
         <v>46168.683825810185</v>
@@ -9087,7 +9068,7 @@
         <v>46223.57192800926</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -9114,13 +9095,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -9130,7 +9111,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B119" s="8">
         <v>46168.68383587963</v>
@@ -9142,7 +9123,7 @@
         <v>46223.57192443287</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -9169,13 +9150,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="Q119" s="9"/>
       <c r="R119" s="9"/>
@@ -9185,7 +9166,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B120" s="5">
         <v>46168.68384034722</v>
@@ -9197,7 +9178,7 @@
         <v>46223.571920902774</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -9224,13 +9205,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -9240,7 +9221,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B121" s="8">
         <v>46168.683844074076</v>
@@ -9252,7 +9233,7 @@
         <v>46223.571917685185</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -9279,13 +9260,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9295,7 +9276,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B122" s="5">
         <v>46168.683847673616</v>
@@ -9307,7 +9288,7 @@
         <v>46223.57191195602</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9334,13 +9315,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="Q122" s="6"/>
       <c r="R122" s="6"/>
@@ -9350,7 +9331,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B123" s="8">
         <v>46168.683862453705</v>
@@ -9362,7 +9343,7 @@
         <v>46233.16842686343</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9389,13 +9370,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q123" s="8">
         <v>46232</v>
@@ -9415,7 +9396,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B124" s="5">
         <v>46168.683867141204</v>
@@ -9427,7 +9408,7 @@
         <v>46223.57203607639</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9454,13 +9435,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O124" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="P124" s="6" t="s">
         <v>358</v>
-      </c>
-      <c r="P124" s="6" t="s">
-        <v>359</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9470,7 +9451,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B125" s="8">
         <v>46168.683873368056</v>
@@ -9482,7 +9463,7 @@
         <v>46223.57203178241</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>26</v>
@@ -9509,13 +9490,13 @@
         <v>26</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="Q125" s="9"/>
       <c r="R125" s="9"/>
@@ -9525,7 +9506,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B126" s="5">
         <v>46168.68387903935</v>
@@ -9537,7 +9518,7 @@
         <v>46223.5720284375</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
@@ -9564,13 +9545,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O126" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="P126" s="6" t="s">
         <v>363</v>
-      </c>
-      <c r="P126" s="6" t="s">
-        <v>364</v>
       </c>
       <c r="Q126" s="6"/>
       <c r="R126" s="6"/>
@@ -9580,7 +9561,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B127" s="8">
         <v>46168.683884618054</v>
@@ -9592,7 +9573,7 @@
         <v>46223.5720246875</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
@@ -9619,13 +9600,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9635,7 +9616,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B128" s="5">
         <v>46168.68389033565</v>
@@ -9647,7 +9628,7 @@
         <v>46223.57201939815</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
@@ -9674,13 +9655,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="O128" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="P128" s="6" t="s">
         <v>368</v>
-      </c>
-      <c r="P128" s="6" t="s">
-        <v>369</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9690,7 +9671,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B129" s="8">
         <v>46168.68391289352</v>
@@ -9702,7 +9683,7 @@
         <v>46234.18465609953</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
@@ -9729,13 +9710,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q129" s="8">
         <v>46233</v>
@@ -9755,7 +9736,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B130" s="5">
         <v>46168.68391818287</v>
@@ -9767,7 +9748,7 @@
         <v>46223.57212789352</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
@@ -9794,13 +9775,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O130" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="P130" s="6" t="s">
         <v>373</v>
-      </c>
-      <c r="P130" s="6" t="s">
-        <v>374</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9810,7 +9791,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B131" s="8">
         <v>46168.68393068287</v>
@@ -9822,7 +9803,7 @@
         <v>46223.57212385417</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
@@ -9849,13 +9830,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O131" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="P131" s="9" t="s">
         <v>376</v>
-      </c>
-      <c r="P131" s="9" t="s">
-        <v>377</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9865,7 +9846,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B132" s="5">
         <v>46168.68393770834</v>
@@ -9877,7 +9858,7 @@
         <v>46223.57212008102</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
@@ -9904,13 +9885,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O132" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="P132" s="6" t="s">
         <v>379</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>380</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9920,7 +9901,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B133" s="8">
         <v>46168.6839434375</v>
@@ -9932,7 +9913,7 @@
         <v>46223.57211625</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9959,13 +9940,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O133" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="P133" s="9" t="s">
         <v>379</v>
-      </c>
-      <c r="P133" s="9" t="s">
-        <v>380</v>
       </c>
       <c r="Q133" s="9"/>
       <c r="R133" s="9"/>
@@ -9975,7 +9956,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B134" s="5">
         <v>46168.68398528935</v>
@@ -9987,7 +9968,7 @@
         <v>46223.572111180554</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -10014,13 +9995,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O134" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="P134" s="6" t="s">
         <v>383</v>
-      </c>
-      <c r="P134" s="6" t="s">
-        <v>384</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -10030,7 +10011,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B135" s="8">
         <v>46168.68401087963</v>
@@ -10042,7 +10023,7 @@
         <v>46235.16899013889</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -10069,13 +10050,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q135" s="8">
         <v>46234</v>
@@ -10095,7 +10076,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B136" s="5">
         <v>46168.68401652778</v>
@@ -10107,7 +10088,7 @@
         <v>46223.5722359375</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -10134,13 +10115,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O136" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="P136" s="6" t="s">
         <v>388</v>
-      </c>
-      <c r="P136" s="6" t="s">
-        <v>389</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -10150,7 +10131,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B137" s="8">
         <v>46168.68402403935</v>
@@ -10162,7 +10143,7 @@
         <v>46223.572232199076</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -10189,13 +10170,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O137" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="P137" s="9" t="s">
         <v>388</v>
-      </c>
-      <c r="P137" s="9" t="s">
-        <v>389</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -10205,7 +10186,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B138" s="5">
         <v>46168.68403127315</v>
@@ -10217,7 +10198,7 @@
         <v>46223.5722271875</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -10244,13 +10225,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O138" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="P138" s="6" t="s">
         <v>392</v>
-      </c>
-      <c r="P138" s="6" t="s">
-        <v>393</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -10260,7 +10241,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B139" s="8">
         <v>46168.68403755787</v>
@@ -10272,7 +10253,7 @@
         <v>46223.57222349537</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -10299,13 +10280,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -10315,7 +10296,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B140" s="5">
         <v>46168.68404385417</v>
@@ -10327,7 +10308,7 @@
         <v>46223.57221770834</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
@@ -10354,13 +10335,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="O140" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="P140" s="6" t="s">
         <v>397</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>398</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10370,7 +10351,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B141" s="8">
         <v>46168.68406297454</v>
@@ -10382,7 +10363,7 @@
         <v>46238.20125695602</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
@@ -10409,13 +10390,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="Q141" s="8">
         <v>46237</v>
@@ -10435,7 +10416,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B142" s="5">
         <v>46168.68406752315</v>
@@ -10447,7 +10428,7 @@
         <v>46223.57235236111</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
@@ -10474,13 +10455,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10490,7 +10471,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B143" s="8">
         <v>46168.68407938657</v>
@@ -10502,7 +10483,7 @@
         <v>46223.57234864583</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
@@ -10529,13 +10510,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10545,7 +10526,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B144" s="5">
         <v>46168.68408523148</v>
@@ -10557,7 +10538,7 @@
         <v>46223.57234428241</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
@@ -10584,13 +10565,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10600,7 +10581,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B145" s="8">
         <v>46168.684089884264</v>
@@ -10612,7 +10593,7 @@
         <v>46223.572340370374</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
@@ -10639,13 +10620,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10655,7 +10636,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B146" s="5">
         <v>46168.684094571756</v>
@@ -10667,7 +10648,7 @@
         <v>46223.57233454861</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
@@ -10694,13 +10675,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10710,7 +10691,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B147" s="8">
         <v>46168.68414574074</v>
@@ -10722,7 +10703,7 @@
         <v>46240.20595440972</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
@@ -10749,13 +10730,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="Q147" s="8">
         <v>46239</v>
@@ -10775,7 +10756,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B148" s="5">
         <v>46168.68415105324</v>
@@ -10787,7 +10768,7 @@
         <v>46223.572544027775</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
@@ -10814,13 +10795,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10830,7 +10811,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B149" s="8">
         <v>46168.68415587963</v>
@@ -10842,7 +10823,7 @@
         <v>46223.5725400463</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
@@ -10869,13 +10850,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10885,7 +10866,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B150" s="5">
         <v>46168.68416068287</v>
@@ -10897,7 +10878,7 @@
         <v>46223.57253650463</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
@@ -10924,13 +10905,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10940,7 +10921,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B151" s="8">
         <v>46168.68416431713</v>
@@ -10952,7 +10933,7 @@
         <v>46223.5725334375</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
@@ -10979,13 +10960,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10995,7 +10976,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B152" s="5">
         <v>46168.68416798611</v>
@@ -11007,7 +10988,7 @@
         <v>46223.5725280787</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
@@ -11034,13 +11015,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -11050,7 +11031,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B153" s="8">
         <v>46168.684183460646</v>
@@ -11062,7 +11043,7 @@
         <v>46211.832724733795</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>25</v>
@@ -11086,7 +11067,7 @@
         <v>26</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="P153" s="9" t="s">
         <v>26</v>
@@ -11103,7 +11084,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B154" s="5">
         <v>46168.68418700232</v>
@@ -11115,16 +11096,16 @@
         <v>46233.19259844907</v>
       </c>
       <c r="E154" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G154" s="6" t="s">
         <v>426</v>
       </c>
-      <c r="F154" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G154" s="6" t="s">
+      <c r="H154" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>428</v>
       </c>
       <c r="I154" s="5">
         <v>46240</v>
@@ -11142,13 +11123,13 @@
         <v>26</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q154" s="5">
         <v>46240</v>
@@ -11157,7 +11138,7 @@
         <v>46240</v>
       </c>
       <c r="S154" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="T154" s="6">
         <v>1</v>
@@ -11168,7 +11149,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B155" s="8">
         <v>46168.68419359953</v>
@@ -11180,16 +11161,16 @@
         <v>46211.831112581014</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H155" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="H155" s="9" t="s">
-        <v>428</v>
       </c>
       <c r="I155" s="8">
         <v>46240</v>
@@ -11207,13 +11188,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -11223,7 +11204,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B156" s="5">
         <v>46168.68419834491</v>
@@ -11235,16 +11216,16 @@
         <v>46211.83112387732</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F156" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G156" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>428</v>
       </c>
       <c r="I156" s="5">
         <v>46240</v>
@@ -11262,13 +11243,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -11278,7 +11259,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B157" s="8">
         <v>46168.684202777775</v>
@@ -11290,16 +11271,16 @@
         <v>46211.83112878472</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G157" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H157" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>428</v>
       </c>
       <c r="I157" s="8">
         <v>46240</v>
@@ -11317,13 +11298,13 @@
         <v>26</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -11333,7 +11314,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B158" s="5">
         <v>46168.68420710648</v>
@@ -11345,16 +11326,16 @@
         <v>46211.83116206019</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G158" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="H158" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="H158" s="6" t="s">
-        <v>428</v>
       </c>
       <c r="I158" s="5">
         <v>46240</v>
@@ -11372,13 +11353,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -11388,7 +11369,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B159" s="8">
         <v>46168.68421127315</v>
@@ -11400,16 +11381,16 @@
         <v>46211.83117125</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G159" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H159" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="H159" s="9" t="s">
-        <v>428</v>
       </c>
       <c r="I159" s="8">
         <v>46240</v>
@@ -11427,13 +11408,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -11443,7 +11424,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B160" s="5">
         <v>46168.68422996528</v>
@@ -11461,10 +11442,10 @@
         <v>26</v>
       </c>
       <c r="G160" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="H160" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="H160" s="6" t="s">
-        <v>428</v>
       </c>
       <c r="I160" s="5">
         <v>46240</v>
@@ -11482,13 +11463,13 @@
         <v>26</v>
       </c>
       <c r="N160" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11498,7 +11479,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B161" s="8">
         <v>46168.68423341435</v>
@@ -11516,10 +11497,10 @@
         <v>26</v>
       </c>
       <c r="G161" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H161" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="H161" s="9" t="s">
-        <v>428</v>
       </c>
       <c r="I161" s="8">
         <v>46240</v>
@@ -11537,13 +11518,13 @@
         <v>26</v>
       </c>
       <c r="N161" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O161" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11553,7 +11534,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B162" s="5">
         <v>46168.684237037036</v>
@@ -11571,10 +11552,10 @@
         <v>26</v>
       </c>
       <c r="G162" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="H162" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>428</v>
       </c>
       <c r="I162" s="5">
         <v>46240</v>
@@ -11592,13 +11573,13 @@
         <v>26</v>
       </c>
       <c r="N162" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11608,7 +11589,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B163" s="8">
         <v>46168.68424059028</v>
@@ -11626,10 +11607,10 @@
         <v>26</v>
       </c>
       <c r="G163" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H163" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>428</v>
       </c>
       <c r="I163" s="8">
         <v>46240</v>
@@ -11647,13 +11628,13 @@
         <v>26</v>
       </c>
       <c r="N163" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O163" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11663,7 +11644,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B164" s="5">
         <v>46168.68424420139</v>
@@ -11681,10 +11662,10 @@
         <v>26</v>
       </c>
       <c r="G164" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="H164" s="6" t="s">
         <v>427</v>
-      </c>
-      <c r="H164" s="6" t="s">
-        <v>428</v>
       </c>
       <c r="I164" s="5">
         <v>46240</v>
@@ -11702,13 +11683,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11718,7 +11699,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B165" s="8">
         <v>46168.68424778935</v>
@@ -11736,10 +11717,10 @@
         <v>26</v>
       </c>
       <c r="G165" s="9" t="s">
+        <v>426</v>
+      </c>
+      <c r="H165" s="9" t="s">
         <v>427</v>
-      </c>
-      <c r="H165" s="9" t="s">
-        <v>428</v>
       </c>
       <c r="I165" s="8">
         <v>46240</v>
@@ -11757,13 +11738,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="9" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="O165" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11773,7 +11754,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B166" s="5">
         <v>46168.68425820602</v>
@@ -11785,7 +11766,7 @@
         <v>46234.17948802083</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11810,13 +11791,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q166" s="5">
         <v>46241</v>
@@ -11825,7 +11806,7 @@
         <v>46241</v>
       </c>
       <c r="S166" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="T166" s="6">
         <v>1</v>
@@ -11836,7 +11817,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B167" s="8">
         <v>46168.68426255787</v>
@@ -11848,7 +11829,7 @@
         <v>46223.5729158912</v>
       </c>
       <c r="E167" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F167" s="9" t="s">
         <v>26</v>
@@ -11873,13 +11854,13 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O167" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11889,7 +11870,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B168" s="5">
         <v>46168.68426704861</v>
@@ -11901,7 +11882,7 @@
         <v>46223.57291190972</v>
       </c>
       <c r="E168" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F168" s="6" t="s">
         <v>26</v>
@@ -11926,13 +11907,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O168" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11942,7 +11923,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B169" s="8">
         <v>46168.68427162037</v>
@@ -11954,7 +11935,7 @@
         <v>46223.57290799769</v>
       </c>
       <c r="E169" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F169" s="9" t="s">
         <v>26</v>
@@ -11979,13 +11960,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O169" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11995,7 +11976,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B170" s="5">
         <v>46168.68427627315</v>
@@ -12007,7 +11988,7 @@
         <v>46223.57290423611</v>
       </c>
       <c r="E170" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F170" s="6" t="s">
         <v>26</v>
@@ -12032,13 +12013,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O170" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -12048,7 +12029,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B171" s="8">
         <v>46168.68428068287</v>
@@ -12060,7 +12041,7 @@
         <v>46223.57290035879</v>
       </c>
       <c r="E171" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F171" s="9" t="s">
         <v>26</v>
@@ -12085,13 +12066,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O171" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -12101,7 +12082,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B172" s="5">
         <v>46168.684336226856</v>
@@ -12138,13 +12119,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O172" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -12154,7 +12135,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B173" s="8">
         <v>46168.68434010417</v>
@@ -12191,13 +12172,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O173" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -12207,7 +12188,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B174" s="5">
         <v>46168.68434423611</v>
@@ -12244,13 +12225,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -12260,7 +12241,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B175" s="8">
         <v>46168.684348263894</v>
@@ -12297,13 +12278,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O175" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -12313,7 +12294,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B176" s="5">
         <v>46168.68435202546</v>
@@ -12350,13 +12331,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -12366,7 +12347,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B177" s="8">
         <v>46168.68435652778</v>
@@ -12403,13 +12384,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O177" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -12419,7 +12400,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B178" s="5">
         <v>46168.68437314815</v>
@@ -12431,16 +12412,16 @@
         <v>46237.20353347222</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G178" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H178" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H178" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I178" s="6"/>
       <c r="J178" s="5">
@@ -12456,13 +12437,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="Q178" s="5">
         <v>46244</v>
@@ -12471,7 +12452,7 @@
         <v>46244</v>
       </c>
       <c r="S178" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="T178" s="6">
         <v>1</v>
@@ -12482,7 +12463,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B179" s="8">
         <v>46168.68437847222</v>
@@ -12494,16 +12475,16 @@
         <v>46209.71550439815</v>
       </c>
       <c r="E179" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F179" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G179" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H179" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H179" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I179" s="8">
         <v>46244</v>
@@ -12521,13 +12502,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O179" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
@@ -12537,7 +12518,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B180" s="5">
         <v>46168.68438821759</v>
@@ -12549,16 +12530,16 @@
         <v>46209.7156449537</v>
       </c>
       <c r="E180" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F180" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G180" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H180" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H180" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I180" s="5">
         <v>46244</v>
@@ -12576,13 +12557,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O180" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12592,7 +12573,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B181" s="8">
         <v>46168.684394537035</v>
@@ -12604,16 +12585,16 @@
         <v>46209.715759733794</v>
       </c>
       <c r="E181" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F181" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G181" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H181" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H181" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I181" s="8">
         <v>46244</v>
@@ -12631,13 +12612,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O181" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12647,7 +12628,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B182" s="5">
         <v>46168.68439944445</v>
@@ -12659,16 +12640,16 @@
         <v>46209.71583459491</v>
       </c>
       <c r="E182" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F182" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G182" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H182" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H182" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I182" s="5">
         <v>46244</v>
@@ -12686,13 +12667,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O182" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12702,7 +12683,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B183" s="8">
         <v>46168.684404375</v>
@@ -12714,16 +12695,16 @@
         <v>46209.71610449074</v>
       </c>
       <c r="E183" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F183" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G183" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H183" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H183" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I183" s="8">
         <v>46244</v>
@@ -12741,13 +12722,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O183" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12757,7 +12738,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B184" s="5">
         <v>46168.6844190625</v>
@@ -12775,10 +12756,10 @@
         <v>26</v>
       </c>
       <c r="G184" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H184" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H184" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I184" s="5">
         <v>46244</v>
@@ -12796,13 +12777,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O184" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12812,7 +12793,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B185" s="8">
         <v>46168.68442277778</v>
@@ -12824,16 +12805,16 @@
         <v>46211.83081103009</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G185" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H185" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H185" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I185" s="8">
         <v>46244</v>
@@ -12851,13 +12832,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O185" s="9" t="s">
         <v>63</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12867,7 +12848,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B186" s="5">
         <v>46168.68442653935</v>
@@ -12885,10 +12866,10 @@
         <v>26</v>
       </c>
       <c r="G186" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H186" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H186" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I186" s="5">
         <v>46244</v>
@@ -12906,13 +12887,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O186" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12922,7 +12903,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B187" s="8">
         <v>46168.684429988425</v>
@@ -12940,10 +12921,10 @@
         <v>26</v>
       </c>
       <c r="G187" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H187" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H187" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I187" s="8">
         <v>46244</v>
@@ -12961,13 +12942,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O187" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12977,7 +12958,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B188" s="5">
         <v>46168.68443359954</v>
@@ -12995,10 +12976,10 @@
         <v>26</v>
       </c>
       <c r="G188" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H188" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H188" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I188" s="5">
         <v>46244</v>
@@ -13016,13 +12997,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -13032,7 +13013,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B189" s="8">
         <v>46168.68443729167</v>
@@ -13050,10 +13031,10 @@
         <v>26</v>
       </c>
       <c r="G189" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H189" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H189" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I189" s="8">
         <v>46244</v>
@@ -13071,13 +13052,13 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="O189" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -13087,7 +13068,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B190" s="5">
         <v>46168.6844840625</v>
@@ -13096,19 +13077,19 @@
         <v>46211.83022659722</v>
       </c>
       <c r="D190" s="5">
-        <v>46238.19406451389</v>
+        <v>46240.71747699074</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G190" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H190" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H190" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I190" s="5">
         <v>46245</v>
@@ -13126,13 +13107,13 @@
         <v>26</v>
       </c>
       <c r="N190" s="6" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="O190" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="P190" s="6" t="s">
         <v>497</v>
-      </c>
-      <c r="P190" s="6" t="s">
-        <v>498</v>
       </c>
       <c r="Q190" s="5">
         <v>46245</v>
@@ -13141,7 +13122,7 @@
         <v>46245</v>
       </c>
       <c r="S190" s="12" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="T190" s="6">
         <v>1</v>
@@ -13152,7 +13133,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B191" s="8">
         <v>46168.68449130787</v>
@@ -13164,16 +13145,16 @@
         <v>46211.830295844906</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G191" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H191" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H191" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="8">
@@ -13189,13 +13170,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O191" s="9" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -13205,7 +13186,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B192" s="5">
         <v>46168.68449590278</v>
@@ -13217,16 +13198,16 @@
         <v>46211.83029662037</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G192" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H192" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I192" s="6"/>
       <c r="J192" s="5">
@@ -13242,13 +13223,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O192" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -13258,7 +13239,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B193" s="8">
         <v>46168.68450027778</v>
@@ -13270,16 +13251,16 @@
         <v>46211.83029733796</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G193" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H193" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H193" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="8">
@@ -13295,13 +13276,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O193" s="9" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -13311,7 +13292,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B194" s="5">
         <v>46168.68450480324</v>
@@ -13323,16 +13304,16 @@
         <v>46211.83029778935</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G194" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H194" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I194" s="6"/>
       <c r="J194" s="5">
@@ -13348,13 +13329,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O194" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -13364,7 +13345,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B195" s="8">
         <v>46168.68450934028</v>
@@ -13376,16 +13357,16 @@
         <v>46211.83029865741</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G195" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H195" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H195" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I195" s="9"/>
       <c r="J195" s="8">
@@ -13401,13 +13382,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O195" s="9" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -13417,7 +13398,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B196" s="5">
         <v>46168.684523414355</v>
@@ -13429,16 +13410,16 @@
         <v>46211.83029902777</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G196" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H196" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H196" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I196" s="6"/>
       <c r="J196" s="5">
@@ -13454,13 +13435,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -13470,7 +13451,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B197" s="8">
         <v>46168.6845271412</v>
@@ -13482,16 +13463,16 @@
         <v>46211.83029945602</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G197" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H197" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H197" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I197" s="9"/>
       <c r="J197" s="8">
@@ -13507,13 +13488,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -13523,7 +13504,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B198" s="5">
         <v>46168.68453511574</v>
@@ -13535,16 +13516,16 @@
         <v>46211.830299953705</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G198" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H198" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H198" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I198" s="6"/>
       <c r="J198" s="5">
@@ -13560,13 +13541,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13576,7 +13557,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B199" s="8">
         <v>46168.68453863426</v>
@@ -13588,16 +13569,16 @@
         <v>46211.83030041667</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G199" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H199" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H199" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I199" s="9"/>
       <c r="J199" s="8">
@@ -13613,13 +13594,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O199" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13629,7 +13610,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B200" s="5">
         <v>46168.68454210648</v>
@@ -13641,16 +13622,16 @@
         <v>46211.830300891204</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G200" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="H200" s="6" t="s">
         <v>283</v>
-      </c>
-      <c r="H200" s="6" t="s">
-        <v>284</v>
       </c>
       <c r="I200" s="6"/>
       <c r="J200" s="5">
@@ -13666,13 +13647,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13682,7 +13663,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B201" s="8">
         <v>46168.684545578704</v>
@@ -13694,16 +13675,16 @@
         <v>46211.83030140046</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G201" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="H201" s="9" t="s">
         <v>283</v>
-      </c>
-      <c r="H201" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="8">
@@ -13719,13 +13700,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="O201" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13735,7 +13716,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B202" s="5">
         <v>46168.684555775464</v>
@@ -13747,7 +13728,7 @@
         <v>46232.66317605324</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>25</v>
@@ -13771,7 +13752,7 @@
         <v>26</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>26</v>
@@ -13788,7 +13769,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B203" s="8">
         <v>46168.6845594676</v>
@@ -13800,16 +13781,16 @@
         <v>46232.663153229165</v>
       </c>
       <c r="E203" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G203" s="9" t="s">
         <v>525</v>
       </c>
-      <c r="F203" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G203" s="9" t="s">
+      <c r="H203" s="9" t="s">
         <v>526</v>
-      </c>
-      <c r="H203" s="9" t="s">
-        <v>527</v>
       </c>
       <c r="I203" s="8">
         <v>46246</v>
@@ -13827,13 +13808,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Q203" s="8">
         <v>46246</v>
@@ -13853,7 +13834,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B204" s="5">
         <v>46168.68456425926</v>
@@ -13865,7 +13846,7 @@
         <v>46232.66316190972</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13892,13 +13873,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="Q204" s="5">
         <v>46246</v>
@@ -13914,185 +13895,6 @@
       </c>
       <c r="U204" s="10" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="205" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A205" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="B205" s="8">
-        <v>46168.68457049769</v>
-      </c>
-      <c r="C205" s="9"/>
-      <c r="D205" s="8">
-        <v>46168.86234542824</v>
-      </c>
-      <c r="E205" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="F205" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G205" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H205" s="9"/>
-      <c r="I205" s="9"/>
-      <c r="J205" s="9"/>
-      <c r="K205" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L205" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M205" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N205" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O205" s="9" t="s">
-        <v>532</v>
-      </c>
-      <c r="P205" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q205" s="9"/>
-      <c r="R205" s="9"/>
-      <c r="S205" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T205" s="9">
-        <v>0</v>
-      </c>
-      <c r="U205" s="11" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="206" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A206" s="4" t="s">
-        <v>533</v>
-      </c>
-      <c r="B206" s="5">
-        <v>46168.68457415509</v>
-      </c>
-      <c r="C206" s="6"/>
-      <c r="D206" s="5">
-        <v>46211.830253541666</v>
-      </c>
-      <c r="E206" s="6" t="s">
-        <v>534</v>
-      </c>
-      <c r="F206" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G206" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="H206" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="I206" s="5">
-        <v>46246</v>
-      </c>
-      <c r="J206" s="5">
-        <v>46254</v>
-      </c>
-      <c r="K206" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L206" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M206" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N206" s="6" t="s">
-        <v>531</v>
-      </c>
-      <c r="O206" s="6" t="s">
-        <v>496</v>
-      </c>
-      <c r="P206" s="6" t="s">
-        <v>535</v>
-      </c>
-      <c r="Q206" s="5">
-        <v>46246</v>
-      </c>
-      <c r="R206" s="5">
-        <v>46254</v>
-      </c>
-      <c r="S206" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T206" s="6">
-        <v>0</v>
-      </c>
-      <c r="U206" s="12" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="207" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A207" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="B207" s="8">
-        <v>46168.68457920139</v>
-      </c>
-      <c r="C207" s="9"/>
-      <c r="D207" s="8">
-        <v>46168.868795937495</v>
-      </c>
-      <c r="E207" s="9" t="s">
-        <v>537</v>
-      </c>
-      <c r="F207" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G207" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="H207" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="I207" s="8">
-        <v>46255</v>
-      </c>
-      <c r="J207" s="8">
-        <v>46265</v>
-      </c>
-      <c r="K207" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L207" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M207" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N207" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="O207" s="9" t="s">
-        <v>534</v>
-      </c>
-      <c r="P207" s="9" t="s">
-        <v>531</v>
-      </c>
-      <c r="Q207" s="8">
-        <v>46255</v>
-      </c>
-      <c r="R207" s="8">
-        <v>46265</v>
-      </c>
-      <c r="S207" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="T207" s="9">
-        <v>0</v>
-      </c>
-      <c r="U207" s="11" t="s">
-        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -1401,67 +1401,67 @@
     <t>OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Revision Tableros,RE-PINTADO,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
   </si>
   <si>
+    <t>1215141738699711</t>
+  </si>
+  <si>
+    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Coordinacion Entrega con Cliente</t>
+  </si>
+  <si>
+    <t>1215141567211195</t>
+  </si>
+  <si>
+    <t>1215141567211212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinacion Entrega con Cliente,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
+    <t>1215141590736819</t>
+  </si>
+  <si>
+    <t>1215141590736836</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141534487801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordinacion Entrega con Cliente,OT 4336 -Tablero YD 37KW </t>
+  </si>
+  <si>
+    <t>1215141534487813</t>
+  </si>
+  <si>
+    <t>1215141403119446</t>
+  </si>
+  <si>
+    <t>1215141403119458</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4338 - Tablero YD 30KW</t>
+  </si>
+  <si>
+    <t>1215141403119470</t>
+  </si>
+  <si>
+    <t>1215141534498423</t>
+  </si>
+  <si>
+    <t>Coordinacion Entrega con Cliente,OT 4341 - Tablero YD 18.5KW</t>
+  </si>
+  <si>
+    <t>1215141403127903</t>
+  </si>
+  <si>
+    <t>Embalaje</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141738699711</t>
-  </si>
-  <si>
-    <t>OT 4335 - ZVN 1-7-37/2 + TOB + REJ,Coordinacion Entrega con Cliente</t>
-  </si>
-  <si>
-    <t>1215141567211195</t>
-  </si>
-  <si>
-    <t>1215141567211212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinacion Entrega con Cliente,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
-  </si>
-  <si>
-    <t>1215141590736819</t>
-  </si>
-  <si>
-    <t>1215141590736836</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141534487801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordinacion Entrega con Cliente,OT 4336 -Tablero YD 37KW </t>
-  </si>
-  <si>
-    <t>1215141534487813</t>
-  </si>
-  <si>
-    <t>1215141403119446</t>
-  </si>
-  <si>
-    <t>1215141403119458</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4338 - Tablero YD 30KW</t>
-  </si>
-  <si>
-    <t>1215141403119470</t>
-  </si>
-  <si>
-    <t>1215141534498423</t>
-  </si>
-  <si>
-    <t>Coordinacion Entrega con Cliente,OT 4341 - Tablero YD 18.5KW</t>
-  </si>
-  <si>
-    <t>1215141403127903</t>
-  </si>
-  <si>
-    <t>Embalaje</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
   </si>
   <si>
     <t>1215141403127920</t>
@@ -11093,7 +11093,7 @@
         <v>46211.83269833333</v>
       </c>
       <c r="D154" s="5">
-        <v>46233.19259844907</v>
+        <v>46241.168156099535</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>425</v>
@@ -11137,8 +11137,8 @@
       <c r="R154" s="5">
         <v>46240</v>
       </c>
-      <c r="S154" s="12" t="s">
-        <v>429</v>
+      <c r="S154" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T154" s="6">
         <v>1</v>
@@ -11149,7 +11149,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B155" s="8">
         <v>46168.68419359953</v>
@@ -11194,7 +11194,7 @@
         <v>211</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q155" s="9"/>
       <c r="R155" s="9"/>
@@ -11204,7 +11204,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B156" s="5">
         <v>46168.68419834491</v>
@@ -11249,7 +11249,7 @@
         <v>211</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="Q156" s="6"/>
       <c r="R156" s="6"/>
@@ -11259,7 +11259,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B157" s="8">
         <v>46168.684202777775</v>
@@ -11304,7 +11304,7 @@
         <v>215</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
@@ -11314,7 +11314,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B158" s="5">
         <v>46168.68420710648</v>
@@ -11359,7 +11359,7 @@
         <v>215</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q158" s="6"/>
       <c r="R158" s="6"/>
@@ -11369,7 +11369,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B159" s="8">
         <v>46168.68421127315</v>
@@ -11414,7 +11414,7 @@
         <v>219</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="Q159" s="9"/>
       <c r="R159" s="9"/>
@@ -11424,7 +11424,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B160" s="5">
         <v>46168.68422996528</v>
@@ -11469,7 +11469,7 @@
         <v>63</v>
       </c>
       <c r="P160" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q160" s="6"/>
       <c r="R160" s="6"/>
@@ -11479,7 +11479,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B161" s="8">
         <v>46168.68423341435</v>
@@ -11524,7 +11524,7 @@
         <v>63</v>
       </c>
       <c r="P161" s="9" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q161" s="9"/>
       <c r="R161" s="9"/>
@@ -11534,7 +11534,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B162" s="5">
         <v>46168.684237037036</v>
@@ -11579,7 +11579,7 @@
         <v>63</v>
       </c>
       <c r="P162" s="6" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q162" s="6"/>
       <c r="R162" s="6"/>
@@ -11589,7 +11589,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B163" s="8">
         <v>46168.68424059028</v>
@@ -11634,7 +11634,7 @@
         <v>67</v>
       </c>
       <c r="P163" s="9" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q163" s="9"/>
       <c r="R163" s="9"/>
@@ -11644,7 +11644,7 @@
     </row>
     <row r="164" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B164" s="5">
         <v>46168.68424420139</v>
@@ -11689,7 +11689,7 @@
         <v>67</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11699,7 +11699,7 @@
     </row>
     <row r="165" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A165" s="7" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B165" s="8">
         <v>46168.68424778935</v>
@@ -11744,7 +11744,7 @@
         <v>70</v>
       </c>
       <c r="P165" s="9" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="Q165" s="9"/>
       <c r="R165" s="9"/>
@@ -11754,7 +11754,7 @@
     </row>
     <row r="166" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B166" s="5">
         <v>46168.68425820602</v>
@@ -11766,7 +11766,7 @@
         <v>46234.17948802083</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="F166" s="6" t="s">
         <v>26</v>
@@ -11794,7 +11794,7 @@
         <v>422</v>
       </c>
       <c r="O166" s="6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P166" s="6" t="s">
         <v>422</v>
@@ -11806,7 +11806,7 @@
         <v>46241</v>
       </c>
       <c r="S166" s="12" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="T166" s="6">
         <v>1</v>
@@ -11854,7 +11854,7 @@
         <v>26</v>
       </c>
       <c r="N167" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O167" s="9" t="s">
         <v>211</v>
@@ -11907,7 +11907,7 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O168" s="6" t="s">
         <v>211</v>
@@ -11960,7 +11960,7 @@
         <v>26</v>
       </c>
       <c r="N169" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O169" s="9" t="s">
         <v>215</v>
@@ -12013,7 +12013,7 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O170" s="6" t="s">
         <v>215</v>
@@ -12066,7 +12066,7 @@
         <v>26</v>
       </c>
       <c r="N171" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O171" s="9" t="s">
         <v>219</v>
@@ -12119,7 +12119,7 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O172" s="6" t="s">
         <v>63</v>
@@ -12172,7 +12172,7 @@
         <v>26</v>
       </c>
       <c r="N173" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O173" s="9" t="s">
         <v>63</v>
@@ -12225,7 +12225,7 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>63</v>
@@ -12278,7 +12278,7 @@
         <v>26</v>
       </c>
       <c r="N175" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O175" s="9" t="s">
         <v>67</v>
@@ -12331,7 +12331,7 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>67</v>
@@ -12384,7 +12384,7 @@
         <v>26</v>
       </c>
       <c r="N177" s="9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="O177" s="9" t="s">
         <v>70</v>
@@ -12452,7 +12452,7 @@
         <v>46244</v>
       </c>
       <c r="S178" s="12" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="T178" s="6">
         <v>1</v>
@@ -13122,7 +13122,7 @@
         <v>46245</v>
       </c>
       <c r="S190" s="12" t="s">
-        <v>429</v>
+        <v>449</v>
       </c>
       <c r="T190" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -1461,70 +1461,70 @@
     <t xml:space="preserve">OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
   </si>
   <si>
+    <t>1215141403127920</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141403136289</t>
+  </si>
+  <si>
+    <t>1215141403136306</t>
+  </si>
+  <si>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Embalaje</t>
+  </si>
+  <si>
+    <t>1215141738798846</t>
+  </si>
+  <si>
+    <t>1215141738798863</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141738841286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Embalaje,OT 4336 -Tablero YD 37KW </t>
+  </si>
+  <si>
+    <t>1215141738841298</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4336 -Tablero YD 37KW - TABLERO SS 86 KW</t>
+  </si>
+  <si>
+    <t>1215141738841310</t>
+  </si>
+  <si>
+    <t>1215141738844551</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4338 - Tablero YD 30KW</t>
+  </si>
+  <si>
+    <t>1215141738844563</t>
+  </si>
+  <si>
+    <t>1215141738854096</t>
+  </si>
+  <si>
+    <t>Embalaje,OT 4341 - Tablero YD 18.5KW</t>
+  </si>
+  <si>
+    <t>1215141590902491</t>
+  </si>
+  <si>
+    <t>PACKING LIST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW - TABLERO SS 86 KW,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141403127920</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141403136289</t>
-  </si>
-  <si>
-    <t>1215141403136306</t>
-  </si>
-  <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,Embalaje</t>
-  </si>
-  <si>
-    <t>1215141738798846</t>
-  </si>
-  <si>
-    <t>1215141738798863</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141738841286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Embalaje,OT 4336 -Tablero YD 37KW </t>
-  </si>
-  <si>
-    <t>1215141738841298</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4336 -Tablero YD 37KW - TABLERO SS 86 KW</t>
-  </si>
-  <si>
-    <t>1215141738841310</t>
-  </si>
-  <si>
-    <t>1215141738844551</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4338 - Tablero YD 30KW</t>
-  </si>
-  <si>
-    <t>1215141738844563</t>
-  </si>
-  <si>
-    <t>1215141738854096</t>
-  </si>
-  <si>
-    <t>Embalaje,OT 4341 - Tablero YD 18.5KW</t>
-  </si>
-  <si>
-    <t>1215141590902491</t>
-  </si>
-  <si>
-    <t>PACKING LIST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW - TABLERO SS 86 KW,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
   </si>
   <si>
     <t>1215141590902508</t>
@@ -11763,7 +11763,7 @@
         <v>46211.83055506945</v>
       </c>
       <c r="D166" s="5">
-        <v>46234.17948802083</v>
+        <v>46242.18564827547</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>447</v>
@@ -11805,8 +11805,8 @@
       <c r="R166" s="5">
         <v>46241</v>
       </c>
-      <c r="S166" s="12" t="s">
-        <v>449</v>
+      <c r="S166" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T166" s="6">
         <v>1</v>
@@ -11817,7 +11817,7 @@
     </row>
     <row r="167" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A167" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B167" s="8">
         <v>46168.68426255787</v>
@@ -11860,7 +11860,7 @@
         <v>211</v>
       </c>
       <c r="P167" s="9" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q167" s="9"/>
       <c r="R167" s="9"/>
@@ -11870,7 +11870,7 @@
     </row>
     <row r="168" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B168" s="5">
         <v>46168.68426704861</v>
@@ -11913,7 +11913,7 @@
         <v>211</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11923,7 +11923,7 @@
     </row>
     <row r="169" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A169" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B169" s="8">
         <v>46168.68427162037</v>
@@ -11966,7 +11966,7 @@
         <v>215</v>
       </c>
       <c r="P169" s="9" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q169" s="9"/>
       <c r="R169" s="9"/>
@@ -11976,7 +11976,7 @@
     </row>
     <row r="170" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B170" s="5">
         <v>46168.68427627315</v>
@@ -12019,7 +12019,7 @@
         <v>215</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -12029,7 +12029,7 @@
     </row>
     <row r="171" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A171" s="7" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B171" s="8">
         <v>46168.68428068287</v>
@@ -12072,7 +12072,7 @@
         <v>219</v>
       </c>
       <c r="P171" s="9" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="Q171" s="9"/>
       <c r="R171" s="9"/>
@@ -12082,7 +12082,7 @@
     </row>
     <row r="172" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B172" s="5">
         <v>46168.684336226856</v>
@@ -12125,7 +12125,7 @@
         <v>63</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -12135,7 +12135,7 @@
     </row>
     <row r="173" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A173" s="7" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B173" s="8">
         <v>46168.68434010417</v>
@@ -12178,7 +12178,7 @@
         <v>63</v>
       </c>
       <c r="P173" s="9" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="Q173" s="9"/>
       <c r="R173" s="9"/>
@@ -12188,7 +12188,7 @@
     </row>
     <row r="174" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B174" s="5">
         <v>46168.68434423611</v>
@@ -12231,7 +12231,7 @@
         <v>63</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -12241,7 +12241,7 @@
     </row>
     <row r="175" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A175" s="7" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B175" s="8">
         <v>46168.684348263894</v>
@@ -12284,7 +12284,7 @@
         <v>67</v>
       </c>
       <c r="P175" s="9" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q175" s="9"/>
       <c r="R175" s="9"/>
@@ -12294,7 +12294,7 @@
     </row>
     <row r="176" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B176" s="5">
         <v>46168.68435202546</v>
@@ -12337,7 +12337,7 @@
         <v>67</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -12347,7 +12347,7 @@
     </row>
     <row r="177" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A177" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B177" s="8">
         <v>46168.68435652778</v>
@@ -12390,7 +12390,7 @@
         <v>70</v>
       </c>
       <c r="P177" s="9" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="Q177" s="9"/>
       <c r="R177" s="9"/>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="178" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B178" s="5">
         <v>46168.68437314815</v>
@@ -12412,7 +12412,7 @@
         <v>46237.20353347222</v>
       </c>
       <c r="E178" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F178" s="6" t="s">
         <v>26</v>
@@ -12440,7 +12440,7 @@
         <v>422</v>
       </c>
       <c r="O178" s="6" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="P178" s="6" t="s">
         <v>422</v>
@@ -12452,7 +12452,7 @@
         <v>46244</v>
       </c>
       <c r="S178" s="12" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="T178" s="6">
         <v>1</v>
@@ -12502,7 +12502,7 @@
         <v>26</v>
       </c>
       <c r="N179" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O179" s="9" t="s">
         <v>211</v>
@@ -12557,7 +12557,7 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>211</v>
@@ -12612,7 +12612,7 @@
         <v>26</v>
       </c>
       <c r="N181" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O181" s="9" t="s">
         <v>215</v>
@@ -12667,7 +12667,7 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>215</v>
@@ -12722,7 +12722,7 @@
         <v>26</v>
       </c>
       <c r="N183" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O183" s="9" t="s">
         <v>219</v>
@@ -12777,7 +12777,7 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O184" s="6" t="s">
         <v>63</v>
@@ -12832,7 +12832,7 @@
         <v>26</v>
       </c>
       <c r="N185" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O185" s="9" t="s">
         <v>63</v>
@@ -12887,7 +12887,7 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O186" s="6" t="s">
         <v>63</v>
@@ -12942,7 +12942,7 @@
         <v>26</v>
       </c>
       <c r="N187" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O187" s="9" t="s">
         <v>67</v>
@@ -12997,7 +12997,7 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>67</v>
@@ -13052,7 +13052,7 @@
         <v>26</v>
       </c>
       <c r="N189" s="9" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="O189" s="9" t="s">
         <v>70</v>
@@ -13122,7 +13122,7 @@
         <v>46245</v>
       </c>
       <c r="S190" s="12" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="T190" s="6">
         <v>1</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -966,7 +966,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7551,7 +7551,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46240.58269997685</v>
+        <v>46244.58203506944</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -966,7 +966,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200</t>
+    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7551,7 +7551,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46244.58203506944</v>
+        <v>46244.816465763884</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -966,7 +966,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -1524,88 +1524,88 @@
     <t xml:space="preserve">OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT 4336 -Tablero YD 37KW ,OT 4336 -Tablero YD 37KW - TABLERO SS 86 KW,OT 4336 -Tablero YD 37KW ,OT 4338 - Tablero YD 30KW,OT 4338 - Tablero YD 30KW,OT 4341 - Tablero YD 18.5KW,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ </t>
   </si>
   <si>
+    <t>1215141590902508</t>
+  </si>
+  <si>
+    <t>Planos Preliminar,PACKING LIST,OT1 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141403226270</t>
+  </si>
+  <si>
+    <t>Planos Preliminar,PACKING LIST,OT2  4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141590923666</t>
+  </si>
+  <si>
+    <t>OT3 4337 -ZVN 1-7-30/2 + TOB + REJ ,PACKING LIST</t>
+  </si>
+  <si>
+    <t>1215141590923683</t>
+  </si>
+  <si>
+    <t>OT4 4337 -ZVN 1-7-30/2 + TOB + REJ ,PACKING LIST</t>
+  </si>
+  <si>
+    <t>1215141403237128</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT5 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>1215141567356885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACKING LIST,OT6 4336 -Tablero YD 37KW </t>
+  </si>
+  <si>
+    <t>1215141567356897</t>
+  </si>
+  <si>
+    <t>OT 4336 -Tablero YD 37KW - TABLERO SS 86 KW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACKING LIST,OT7 4336 -Tablero YD 37KW </t>
+  </si>
+  <si>
+    <t>1215141567358294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACKING LIST,OT8 4336 -Tablero YD 37KW </t>
+  </si>
+  <si>
+    <t>1215141567358306</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT9 4338 - Tablero YD 30KW</t>
+  </si>
+  <si>
+    <t>1215141534635000</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT10  4338 - Tablero YD 30KW</t>
+  </si>
+  <si>
+    <t>1215141534635012</t>
+  </si>
+  <si>
+    <t>PACKING LIST,OT11 4341 - Tablero YD 18.5KW</t>
+  </si>
+  <si>
+    <t>1215141403129024</t>
+  </si>
+  <si>
+    <t>Despacho</t>
+  </si>
+  <si>
+    <t>OT5 4339 - ZVN 1-9-37/2 + TOB + REJ,OT6 4336 -Tablero YD 37KW ,OT7 4336 -Tablero YD 37KW ,OT8 4336 -Tablero YD 37KW ,OT9 4338 - Tablero YD 30KW,OT10  4338 - Tablero YD 30KW,OT11 4341 - Tablero YD 18.5KW,OT3 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT4 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT1 4335 - ZVN 1-7-37/2 + TOB + REJ,OT2  4335 - ZVN 1-7-37/2 + TOB + REJ</t>
+  </si>
+  <si>
+    <t>Logistica:,Gestion,Costos</t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1215141590902508</t>
-  </si>
-  <si>
-    <t>Planos Preliminar,PACKING LIST,OT1 4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141403226270</t>
-  </si>
-  <si>
-    <t>Planos Preliminar,PACKING LIST,OT2  4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141590923666</t>
-  </si>
-  <si>
-    <t>OT3 4337 -ZVN 1-7-30/2 + TOB + REJ ,PACKING LIST</t>
-  </si>
-  <si>
-    <t>1215141590923683</t>
-  </si>
-  <si>
-    <t>OT4 4337 -ZVN 1-7-30/2 + TOB + REJ ,PACKING LIST</t>
-  </si>
-  <si>
-    <t>1215141403237128</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT5 4339 - ZVN 1-9-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>1215141567356885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACKING LIST,OT6 4336 -Tablero YD 37KW </t>
-  </si>
-  <si>
-    <t>1215141567356897</t>
-  </si>
-  <si>
-    <t>OT 4336 -Tablero YD 37KW - TABLERO SS 86 KW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACKING LIST,OT7 4336 -Tablero YD 37KW </t>
-  </si>
-  <si>
-    <t>1215141567358294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACKING LIST,OT8 4336 -Tablero YD 37KW </t>
-  </si>
-  <si>
-    <t>1215141567358306</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT9 4338 - Tablero YD 30KW</t>
-  </si>
-  <si>
-    <t>1215141534635000</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT10  4338 - Tablero YD 30KW</t>
-  </si>
-  <si>
-    <t>1215141534635012</t>
-  </si>
-  <si>
-    <t>PACKING LIST,OT11 4341 - Tablero YD 18.5KW</t>
-  </si>
-  <si>
-    <t>1215141403129024</t>
-  </si>
-  <si>
-    <t>Despacho</t>
-  </si>
-  <si>
-    <t>OT5 4339 - ZVN 1-9-37/2 + TOB + REJ,OT6 4336 -Tablero YD 37KW ,OT7 4336 -Tablero YD 37KW ,OT8 4336 -Tablero YD 37KW ,OT9 4338 - Tablero YD 30KW,OT10  4338 - Tablero YD 30KW,OT11 4341 - Tablero YD 18.5KW,OT3 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT4 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT1 4335 - ZVN 1-7-37/2 + TOB + REJ,OT2  4335 - ZVN 1-7-37/2 + TOB + REJ</t>
-  </si>
-  <si>
-    <t>Logistica:,Gestion,Costos</t>
   </si>
   <si>
     <t>1215141403129041</t>
@@ -7551,7 +7551,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46244.816465763884</v>
+        <v>46244.91622329861</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>
@@ -12409,7 +12409,7 @@
         <v>46209.71534268519</v>
       </c>
       <c r="D178" s="5">
-        <v>46237.20353347222</v>
+        <v>46245.173739502316</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>468</v>
@@ -12451,8 +12451,8 @@
       <c r="R178" s="5">
         <v>46244</v>
       </c>
-      <c r="S178" s="12" t="s">
-        <v>470</v>
+      <c r="S178" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T178" s="6">
         <v>1</v>
@@ -12463,7 +12463,7 @@
     </row>
     <row r="179" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A179" s="7" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B179" s="8">
         <v>46168.68437847222</v>
@@ -12508,7 +12508,7 @@
         <v>211</v>
       </c>
       <c r="P179" s="9" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="Q179" s="9"/>
       <c r="R179" s="9"/>
@@ -12518,7 +12518,7 @@
     </row>
     <row r="180" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B180" s="5">
         <v>46168.68438821759</v>
@@ -12563,7 +12563,7 @@
         <v>211</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12573,7 +12573,7 @@
     </row>
     <row r="181" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A181" s="7" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B181" s="8">
         <v>46168.684394537035</v>
@@ -12618,7 +12618,7 @@
         <v>215</v>
       </c>
       <c r="P181" s="9" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="Q181" s="9"/>
       <c r="R181" s="9"/>
@@ -12628,7 +12628,7 @@
     </row>
     <row r="182" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B182" s="5">
         <v>46168.68439944445</v>
@@ -12673,7 +12673,7 @@
         <v>215</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12683,7 +12683,7 @@
     </row>
     <row r="183" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A183" s="7" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B183" s="8">
         <v>46168.684404375</v>
@@ -12728,7 +12728,7 @@
         <v>219</v>
       </c>
       <c r="P183" s="9" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Q183" s="9"/>
       <c r="R183" s="9"/>
@@ -12738,7 +12738,7 @@
     </row>
     <row r="184" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B184" s="5">
         <v>46168.6844190625</v>
@@ -12783,7 +12783,7 @@
         <v>63</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12793,7 +12793,7 @@
     </row>
     <row r="185" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A185" s="7" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B185" s="8">
         <v>46168.68442277778</v>
@@ -12805,7 +12805,7 @@
         <v>46211.83081103009</v>
       </c>
       <c r="E185" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F185" s="9" t="s">
         <v>26</v>
@@ -12838,7 +12838,7 @@
         <v>63</v>
       </c>
       <c r="P185" s="9" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="Q185" s="9"/>
       <c r="R185" s="9"/>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="186" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B186" s="5">
         <v>46168.68442653935</v>
@@ -12893,7 +12893,7 @@
         <v>63</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12903,7 +12903,7 @@
     </row>
     <row r="187" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A187" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B187" s="8">
         <v>46168.684429988425</v>
@@ -12948,7 +12948,7 @@
         <v>67</v>
       </c>
       <c r="P187" s="9" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q187" s="9"/>
       <c r="R187" s="9"/>
@@ -12958,7 +12958,7 @@
     </row>
     <row r="188" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B188" s="5">
         <v>46168.68443359954</v>
@@ -13003,7 +13003,7 @@
         <v>67</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -13013,7 +13013,7 @@
     </row>
     <row r="189" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A189" s="7" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B189" s="8">
         <v>46168.68443729167</v>
@@ -13058,7 +13058,7 @@
         <v>70</v>
       </c>
       <c r="P189" s="9" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="Q189" s="9"/>
       <c r="R189" s="9"/>
@@ -13068,7 +13068,7 @@
     </row>
     <row r="190" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B190" s="5">
         <v>46168.6844840625</v>
@@ -13080,7 +13080,7 @@
         <v>46240.71747699074</v>
       </c>
       <c r="E190" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F190" s="6" t="s">
         <v>26</v>
@@ -13110,10 +13110,10 @@
         <v>422</v>
       </c>
       <c r="O190" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="P190" s="6" t="s">
         <v>496</v>
-      </c>
-      <c r="P190" s="6" t="s">
-        <v>497</v>
       </c>
       <c r="Q190" s="5">
         <v>46245</v>
@@ -13122,7 +13122,7 @@
         <v>46245</v>
       </c>
       <c r="S190" s="12" t="s">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="T190" s="6">
         <v>1</v>
@@ -13170,13 +13170,13 @@
         <v>26</v>
       </c>
       <c r="N191" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O191" s="9" t="s">
         <v>211</v>
       </c>
       <c r="P191" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q191" s="9"/>
       <c r="R191" s="9"/>
@@ -13223,13 +13223,13 @@
         <v>26</v>
       </c>
       <c r="N192" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O192" s="6" t="s">
         <v>211</v>
       </c>
       <c r="P192" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q192" s="6"/>
       <c r="R192" s="6"/>
@@ -13276,13 +13276,13 @@
         <v>26</v>
       </c>
       <c r="N193" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O193" s="9" t="s">
         <v>215</v>
       </c>
       <c r="P193" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q193" s="9"/>
       <c r="R193" s="9"/>
@@ -13329,13 +13329,13 @@
         <v>26</v>
       </c>
       <c r="N194" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O194" s="6" t="s">
         <v>215</v>
       </c>
       <c r="P194" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q194" s="6"/>
       <c r="R194" s="6"/>
@@ -13382,13 +13382,13 @@
         <v>26</v>
       </c>
       <c r="N195" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O195" s="9" t="s">
         <v>219</v>
       </c>
       <c r="P195" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q195" s="9"/>
       <c r="R195" s="9"/>
@@ -13435,13 +13435,13 @@
         <v>26</v>
       </c>
       <c r="N196" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O196" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P196" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q196" s="6"/>
       <c r="R196" s="6"/>
@@ -13488,13 +13488,13 @@
         <v>26</v>
       </c>
       <c r="N197" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O197" s="9" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="P197" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q197" s="9"/>
       <c r="R197" s="9"/>
@@ -13541,13 +13541,13 @@
         <v>26</v>
       </c>
       <c r="N198" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O198" s="6" t="s">
         <v>63</v>
       </c>
       <c r="P198" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q198" s="6"/>
       <c r="R198" s="6"/>
@@ -13594,13 +13594,13 @@
         <v>26</v>
       </c>
       <c r="N199" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O199" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P199" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q199" s="9"/>
       <c r="R199" s="9"/>
@@ -13647,13 +13647,13 @@
         <v>26</v>
       </c>
       <c r="N200" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O200" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P200" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q200" s="6"/>
       <c r="R200" s="6"/>
@@ -13700,13 +13700,13 @@
         <v>26</v>
       </c>
       <c r="N201" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="O201" s="9" t="s">
         <v>70</v>
       </c>
       <c r="P201" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="Q201" s="9"/>
       <c r="R201" s="9"/>
@@ -13811,7 +13811,7 @@
         <v>521</v>
       </c>
       <c r="O203" s="9" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="P203" s="9" t="s">
         <v>521</v>
@@ -13876,7 +13876,7 @@
         <v>521</v>
       </c>
       <c r="O204" s="6" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="P204" s="6" t="s">
         <v>521</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2363" uniqueCount="528">
   <si>
     <t>50001557 - ATACAMA KOZAN</t>
   </si>
@@ -1605,9 +1605,6 @@
     <t>Logistica:,Gestion,Costos</t>
   </si>
   <si>
-    <t>Media</t>
-  </si>
-  <si>
     <t>1215141403129041</t>
   </si>
   <si>
@@ -1728,7 +1725,7 @@
       <color rgb="FF000000"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1768,11 +1765,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFe8384f"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFeec300"/>
       </patternFill>
     </fill>
   </fills>
@@ -1818,7 +1810,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1837,7 +1829,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -13077,7 +13068,7 @@
         <v>46211.83022659722</v>
       </c>
       <c r="D190" s="5">
-        <v>46240.71747699074</v>
+        <v>46246.198753125005</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>494</v>
@@ -13121,8 +13112,8 @@
       <c r="R190" s="5">
         <v>46245</v>
       </c>
-      <c r="S190" s="12" t="s">
-        <v>497</v>
+      <c r="S190" s="11" t="s">
+        <v>61</v>
       </c>
       <c r="T190" s="6">
         <v>1</v>
@@ -13133,7 +13124,7 @@
     </row>
     <row r="191" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A191" s="7" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B191" s="8">
         <v>46168.68449130787</v>
@@ -13145,7 +13136,7 @@
         <v>46211.830295844906</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F191" s="9" t="s">
         <v>26</v>
@@ -13186,7 +13177,7 @@
     </row>
     <row r="192" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B192" s="5">
         <v>46168.68449590278</v>
@@ -13198,7 +13189,7 @@
         <v>46211.83029662037</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F192" s="6" t="s">
         <v>26</v>
@@ -13239,7 +13230,7 @@
     </row>
     <row r="193" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A193" s="7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B193" s="8">
         <v>46168.68450027778</v>
@@ -13251,7 +13242,7 @@
         <v>46211.83029733796</v>
       </c>
       <c r="E193" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="F193" s="9" t="s">
         <v>26</v>
@@ -13292,7 +13283,7 @@
     </row>
     <row r="194" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B194" s="5">
         <v>46168.68450480324</v>
@@ -13304,7 +13295,7 @@
         <v>46211.83029778935</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F194" s="6" t="s">
         <v>26</v>
@@ -13345,7 +13336,7 @@
     </row>
     <row r="195" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A195" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B195" s="8">
         <v>46168.68450934028</v>
@@ -13357,7 +13348,7 @@
         <v>46211.83029865741</v>
       </c>
       <c r="E195" s="9" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="F195" s="9" t="s">
         <v>26</v>
@@ -13398,7 +13389,7 @@
     </row>
     <row r="196" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B196" s="5">
         <v>46168.684523414355</v>
@@ -13410,7 +13401,7 @@
         <v>46211.83029902777</v>
       </c>
       <c r="E196" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F196" s="6" t="s">
         <v>26</v>
@@ -13451,7 +13442,7 @@
     </row>
     <row r="197" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A197" s="7" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B197" s="8">
         <v>46168.6845271412</v>
@@ -13463,7 +13454,7 @@
         <v>46211.83029945602</v>
       </c>
       <c r="E197" s="9" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F197" s="9" t="s">
         <v>26</v>
@@ -13504,7 +13495,7 @@
     </row>
     <row r="198" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B198" s="5">
         <v>46168.68453511574</v>
@@ -13516,7 +13507,7 @@
         <v>46211.830299953705</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F198" s="6" t="s">
         <v>26</v>
@@ -13557,7 +13548,7 @@
     </row>
     <row r="199" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A199" s="7" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B199" s="8">
         <v>46168.68453863426</v>
@@ -13569,7 +13560,7 @@
         <v>46211.83030041667</v>
       </c>
       <c r="E199" s="9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F199" s="9" t="s">
         <v>26</v>
@@ -13610,7 +13601,7 @@
     </row>
     <row r="200" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B200" s="5">
         <v>46168.68454210648</v>
@@ -13622,7 +13613,7 @@
         <v>46211.830300891204</v>
       </c>
       <c r="E200" s="6" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="F200" s="6" t="s">
         <v>26</v>
@@ -13663,7 +13654,7 @@
     </row>
     <row r="201" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A201" s="7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B201" s="8">
         <v>46168.684545578704</v>
@@ -13675,7 +13666,7 @@
         <v>46211.83030140046</v>
       </c>
       <c r="E201" s="9" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="F201" s="9" t="s">
         <v>26</v>
@@ -13716,7 +13707,7 @@
     </row>
     <row r="202" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B202" s="5">
         <v>46168.684555775464</v>
@@ -13728,7 +13719,7 @@
         <v>46232.66317605324</v>
       </c>
       <c r="E202" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="F202" s="6" t="s">
         <v>25</v>
@@ -13752,7 +13743,7 @@
         <v>26</v>
       </c>
       <c r="O202" s="6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="P202" s="6" t="s">
         <v>26</v>
@@ -13769,7 +13760,7 @@
     </row>
     <row r="203" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A203" s="7" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B203" s="8">
         <v>46168.6845594676</v>
@@ -13781,16 +13772,16 @@
         <v>46232.663153229165</v>
       </c>
       <c r="E203" s="9" t="s">
+        <v>523</v>
+      </c>
+      <c r="F203" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G203" s="9" t="s">
         <v>524</v>
       </c>
-      <c r="F203" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G203" s="9" t="s">
+      <c r="H203" s="9" t="s">
         <v>525</v>
-      </c>
-      <c r="H203" s="9" t="s">
-        <v>526</v>
       </c>
       <c r="I203" s="8">
         <v>46246</v>
@@ -13808,13 +13799,13 @@
         <v>26</v>
       </c>
       <c r="N203" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="O203" s="9" t="s">
         <v>494</v>
       </c>
       <c r="P203" s="9" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q203" s="8">
         <v>46246</v>
@@ -13834,7 +13825,7 @@
     </row>
     <row r="204" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B204" s="5">
         <v>46168.68456425926</v>
@@ -13846,7 +13837,7 @@
         <v>46232.66316190972</v>
       </c>
       <c r="E204" s="6" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F204" s="6" t="s">
         <v>26</v>
@@ -13873,13 +13864,13 @@
         <v>26</v>
       </c>
       <c r="N204" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="O204" s="6" t="s">
         <v>494</v>
       </c>
       <c r="P204" s="6" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="Q204" s="5">
         <v>46246</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -2434,7 +2434,7 @@
         <v>46175.87163862269</v>
       </c>
       <c r="D6" s="5">
-        <v>46213.713806886575</v>
+        <v>46248.92943665509</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>35</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -2804,7 +2804,7 @@
         <v>46196.89414587963</v>
       </c>
       <c r="D12" s="5">
-        <v>46228.17456038194</v>
+        <v>46249.93870108796</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>56</v>
@@ -4018,7 +4018,7 @@
         <v>46205.61593267361</v>
       </c>
       <c r="D32" s="5">
-        <v>46205.61594793982</v>
+        <v>46249.98766475695</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>118</v>
@@ -6708,7 +6708,7 @@
         <v>46211.83846215278</v>
       </c>
       <c r="D78" s="5">
-        <v>46239.194167118054</v>
+        <v>46249.940088206014</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>245</v>
@@ -7489,7 +7489,7 @@
         <v>46211.83132788194</v>
       </c>
       <c r="D91" s="8">
-        <v>46211.83134737269</v>
+        <v>46249.99091736111</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>278</v>
@@ -7542,7 +7542,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46244.91622329861</v>
+        <v>46249.94030350694</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>
@@ -7882,7 +7882,7 @@
         <v>46197.85007665509</v>
       </c>
       <c r="D98" s="5">
-        <v>46224.175157731486</v>
+        <v>46249.940361388886</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>297</v>
@@ -8222,7 +8222,7 @@
         <v>46204.89009226851</v>
       </c>
       <c r="D104" s="5">
-        <v>46225.167433888884</v>
+        <v>46249.94047336806</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>311</v>
@@ -8991,7 +8991,7 @@
         <v>46204.89075866898</v>
       </c>
       <c r="D117" s="8">
-        <v>46232.183549988426</v>
+        <v>46249.94056688657</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>343</v>
@@ -9331,7 +9331,7 @@
         <v>46204.89175555555</v>
       </c>
       <c r="D123" s="8">
-        <v>46233.16842686343</v>
+        <v>46249.94067694445</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>355</v>
@@ -9671,7 +9671,7 @@
         <v>46204.89298883102</v>
       </c>
       <c r="D129" s="8">
-        <v>46234.18465609953</v>
+        <v>46249.940871412036</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>370</v>
@@ -10011,7 +10011,7 @@
         <v>46204.893422152774</v>
       </c>
       <c r="D135" s="8">
-        <v>46235.16899013889</v>
+        <v>46249.94102355324</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>385</v>
@@ -10351,7 +10351,7 @@
         <v>46206.4858124537</v>
       </c>
       <c r="D141" s="8">
-        <v>46238.20125695602</v>
+        <v>46249.941063645834</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>399</v>
@@ -10691,7 +10691,7 @@
         <v>46206.48621289352</v>
       </c>
       <c r="D147" s="8">
-        <v>46240.20595440972</v>
+        <v>46249.94115042824</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>410</v>
@@ -11031,7 +11031,7 @@
         <v>46211.8327128588</v>
       </c>
       <c r="D153" s="8">
-        <v>46211.832724733795</v>
+        <v>46249.98997956018</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>422</v>
@@ -11084,7 +11084,7 @@
         <v>46211.83269833333</v>
       </c>
       <c r="D154" s="5">
-        <v>46241.168156099535</v>
+        <v>46249.94153305556</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>425</v>
@@ -11754,7 +11754,7 @@
         <v>46211.83055506945</v>
       </c>
       <c r="D166" s="5">
-        <v>46242.18564827547</v>
+        <v>46249.941719131944</v>
       </c>
       <c r="E166" s="6" t="s">
         <v>447</v>
@@ -12400,7 +12400,7 @@
         <v>46209.71534268519</v>
       </c>
       <c r="D178" s="5">
-        <v>46245.173739502316</v>
+        <v>46249.94202814814</v>
       </c>
       <c r="E178" s="6" t="s">
         <v>468</v>
@@ -13068,7 +13068,7 @@
         <v>46211.83022659722</v>
       </c>
       <c r="D190" s="5">
-        <v>46246.198753125005</v>
+        <v>46249.94212266203</v>
       </c>
       <c r="E190" s="6" t="s">
         <v>494</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -966,7 +966,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ </t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7542,7 +7542,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46249.94030350694</v>
+        <v>46252.55708009259</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -966,7 +966,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7542,7 +7542,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46252.55708009259</v>
+        <v>46252.69802873842</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -966,7 +966,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7542,7 +7542,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46252.69802873842</v>
+        <v>46258.64931958333</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -966,7 +966,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4385 -VENTILADORES 45KCFMx4"CA - ZVN 1-12-37/4,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7542,7 +7542,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46258.64931958333</v>
+        <v>46260.679553333335</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -966,7 +966,7 @@
     <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
-    <t>OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6</t>
+    <t xml:space="preserve">OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4337 -ZVN 1-7-30/2 + TOB + REJ ,OT 4339 - ZVN 1-9-37/2 + TOB + REJ,OT2 4307 ZVN 1-9-86/2 ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4375 - ZVN 1-9-86/2 + TOB + REJ + TIPO A,OT 4376 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,OT 4377-ZVN 1-9-86/2 + TOB + REJ + TPA,OT4378-ZVN 1-9-63/2 + TOB + REJ + 2FAR + TIPO A ,OT 4381 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,OT 4394 -ZVN 1-9-86/2 + TOB + REJ,OT 4395 -ZVN 1-16-315/4 + TOB + REJ + 2FAR160/200,ot  4390 -ZVN 1-12-110/4 + TOB + REJ ,OT 4391 -ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4080 -VENTILADOR ZVNv 1-18-90/6,OT 4075  -ZVRv 1-16-37/6 ,OT 4413  -ZVRv 1-22-185/6  </t>
   </si>
   <si>
     <t>1215141566712673</t>
@@ -7542,7 +7542,7 @@
         <v>46192.63405665509</v>
       </c>
       <c r="D92" s="5">
-        <v>46260.679553333335</v>
+        <v>46261.600821342596</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>281</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -3199,7 +3199,7 @@
         <v>46205.604937083335</v>
       </c>
       <c r="D19" s="8">
-        <v>46205.60495420139</v>
+        <v>46264.11211134259</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>72</v>

--- a/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
+++ b/data/50001557 - ATACAMA KOZAN OT4335-4337-4339.xlsx
@@ -5635,7 +5635,7 @@
         <v>46240.71763709491</v>
       </c>
       <c r="D59" s="8">
-        <v>46240.717654513894</v>
+        <v>46271.88730806713</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>203</v>
